--- a/gstdatabase/GSTR-3B-2022-2023.xlsx
+++ b/gstdatabase/GSTR-3B-2022-2023.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Feb-26\GST Statistics Downloads 28th Feb 26\Downloads\GSTR 3B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\May-26\GST Statistics Downloads 31st May 26\Downloads\GSTR 3B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{704EDE98-DC1F-45E1-A6D1-D4E3CD2E6ADD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D6F5D85-E649-4638-B797-696BEA5E0392}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -185,10 +185,10 @@
     <t>-</t>
   </si>
   <si>
-    <t>Data Considered upto 28th Feb 2026</t>
+    <t>Data Considered upto 31st May 2026</t>
   </si>
   <si>
-    <t>Filing %age as on 28th Feb 2026</t>
+    <t>Filing %age as on 31st May 2026</t>
   </si>
 </sst>
 </file>
@@ -448,15 +448,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="17" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -474,6 +465,15 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="11">
@@ -775,12 +775,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:62" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="34" t="s">
         <v>47</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
@@ -855,10 +855,10 @@
       <c r="AK2" s="1"/>
     </row>
     <row r="3" spans="1:62" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="34" t="s">
+      <c r="A3" s="31" t="s">
         <v>46</v>
       </c>
-      <c r="B3" s="34"/>
+      <c r="B3" s="31"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -935,11 +935,11 @@
       <c r="AK4" s="1"/>
     </row>
     <row r="5" spans="1:62" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="34" t="s">
+      <c r="A5" s="31" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="34"/>
-      <c r="C5" s="34"/>
+      <c r="B5" s="31"/>
+      <c r="C5" s="31"/>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
@@ -1054,100 +1054,100 @@
       <c r="AK7" s="1"/>
     </row>
     <row r="8" spans="1:62" s="24" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="35" t="s">
+      <c r="A8" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="36" t="s">
+      <c r="B8" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="C8" s="31">
+      <c r="C8" s="28">
         <v>44652</v>
       </c>
-      <c r="D8" s="32"/>
-      <c r="E8" s="32"/>
-      <c r="F8" s="32"/>
-      <c r="G8" s="33"/>
-      <c r="H8" s="31">
+      <c r="D8" s="29"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="30"/>
+      <c r="H8" s="28">
         <v>44682</v>
       </c>
-      <c r="I8" s="32"/>
-      <c r="J8" s="32"/>
-      <c r="K8" s="32"/>
-      <c r="L8" s="33"/>
-      <c r="M8" s="31">
+      <c r="I8" s="29"/>
+      <c r="J8" s="29"/>
+      <c r="K8" s="29"/>
+      <c r="L8" s="30"/>
+      <c r="M8" s="28">
         <v>44713</v>
       </c>
-      <c r="N8" s="32"/>
-      <c r="O8" s="32"/>
-      <c r="P8" s="32"/>
-      <c r="Q8" s="33"/>
-      <c r="R8" s="31">
+      <c r="N8" s="29"/>
+      <c r="O8" s="29"/>
+      <c r="P8" s="29"/>
+      <c r="Q8" s="30"/>
+      <c r="R8" s="28">
         <v>44743</v>
       </c>
-      <c r="S8" s="32"/>
-      <c r="T8" s="32"/>
-      <c r="U8" s="32"/>
-      <c r="V8" s="33"/>
-      <c r="W8" s="31">
+      <c r="S8" s="29"/>
+      <c r="T8" s="29"/>
+      <c r="U8" s="29"/>
+      <c r="V8" s="30"/>
+      <c r="W8" s="28">
         <v>44774</v>
       </c>
-      <c r="X8" s="32"/>
-      <c r="Y8" s="32"/>
-      <c r="Z8" s="32"/>
-      <c r="AA8" s="33"/>
-      <c r="AB8" s="31">
+      <c r="X8" s="29"/>
+      <c r="Y8" s="29"/>
+      <c r="Z8" s="29"/>
+      <c r="AA8" s="30"/>
+      <c r="AB8" s="28">
         <v>44805</v>
       </c>
-      <c r="AC8" s="32"/>
-      <c r="AD8" s="32"/>
-      <c r="AE8" s="32"/>
-      <c r="AF8" s="33"/>
-      <c r="AG8" s="31">
+      <c r="AC8" s="29"/>
+      <c r="AD8" s="29"/>
+      <c r="AE8" s="29"/>
+      <c r="AF8" s="30"/>
+      <c r="AG8" s="28">
         <v>44835</v>
       </c>
-      <c r="AH8" s="32"/>
-      <c r="AI8" s="32"/>
-      <c r="AJ8" s="32"/>
-      <c r="AK8" s="33"/>
-      <c r="AL8" s="31">
+      <c r="AH8" s="29"/>
+      <c r="AI8" s="29"/>
+      <c r="AJ8" s="29"/>
+      <c r="AK8" s="30"/>
+      <c r="AL8" s="28">
         <v>44866</v>
       </c>
-      <c r="AM8" s="32"/>
-      <c r="AN8" s="32"/>
-      <c r="AO8" s="32"/>
-      <c r="AP8" s="33"/>
-      <c r="AQ8" s="31">
+      <c r="AM8" s="29"/>
+      <c r="AN8" s="29"/>
+      <c r="AO8" s="29"/>
+      <c r="AP8" s="30"/>
+      <c r="AQ8" s="28">
         <v>44896</v>
       </c>
-      <c r="AR8" s="32"/>
-      <c r="AS8" s="32"/>
-      <c r="AT8" s="32"/>
-      <c r="AU8" s="33"/>
-      <c r="AV8" s="31">
+      <c r="AR8" s="29"/>
+      <c r="AS8" s="29"/>
+      <c r="AT8" s="29"/>
+      <c r="AU8" s="30"/>
+      <c r="AV8" s="28">
         <v>44927</v>
       </c>
-      <c r="AW8" s="32"/>
-      <c r="AX8" s="32"/>
-      <c r="AY8" s="32"/>
-      <c r="AZ8" s="33"/>
-      <c r="BA8" s="31">
+      <c r="AW8" s="29"/>
+      <c r="AX8" s="29"/>
+      <c r="AY8" s="29"/>
+      <c r="AZ8" s="30"/>
+      <c r="BA8" s="28">
         <v>44958</v>
       </c>
-      <c r="BB8" s="32"/>
-      <c r="BC8" s="32"/>
-      <c r="BD8" s="32"/>
-      <c r="BE8" s="33"/>
-      <c r="BF8" s="31">
+      <c r="BB8" s="29"/>
+      <c r="BC8" s="29"/>
+      <c r="BD8" s="29"/>
+      <c r="BE8" s="30"/>
+      <c r="BF8" s="28">
         <v>44986</v>
       </c>
-      <c r="BG8" s="32"/>
-      <c r="BH8" s="32"/>
-      <c r="BI8" s="32"/>
-      <c r="BJ8" s="33"/>
+      <c r="BG8" s="29"/>
+      <c r="BH8" s="29"/>
+      <c r="BI8" s="29"/>
+      <c r="BJ8" s="30"/>
     </row>
     <row r="9" spans="1:62" s="24" customFormat="1" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="35"/>
-      <c r="B9" s="36"/>
+      <c r="A9" s="32"/>
+      <c r="B9" s="33"/>
       <c r="C9" s="25" t="s">
         <v>2</v>
       </c>
@@ -1344,14 +1344,14 @@
       </c>
       <c r="E10" s="4">
         <f>F10-D10</f>
-        <v>12630</v>
+        <v>12631</v>
       </c>
       <c r="F10" s="22">
-        <v>66935</v>
+        <v>66936</v>
       </c>
       <c r="G10" s="5">
         <f>F10/C10</f>
-        <v>1.0089993668787121</v>
+        <v>1.0090144411950919</v>
       </c>
       <c r="H10" s="9">
         <v>68361</v>
@@ -1361,14 +1361,14 @@
       </c>
       <c r="J10" s="4">
         <f>K10-I10</f>
-        <v>15192</v>
+        <v>15193</v>
       </c>
       <c r="K10" s="22">
-        <v>68799</v>
+        <v>68800</v>
       </c>
       <c r="L10" s="5">
         <f>K10/H10</f>
-        <v>1.006407161978321</v>
+        <v>1.0064217902020158</v>
       </c>
       <c r="M10" s="4">
         <v>109205</v>
@@ -1378,14 +1378,14 @@
       </c>
       <c r="O10" s="4">
         <f>P10-N10</f>
-        <v>21279</v>
+        <v>21280</v>
       </c>
       <c r="P10" s="8">
-        <v>108914</v>
+        <v>108915</v>
       </c>
       <c r="Q10" s="5">
         <f>P10/M10</f>
-        <v>0.99733528684584039</v>
+        <v>0.9973444439357172</v>
       </c>
       <c r="R10" s="9">
         <v>68216</v>
@@ -1395,14 +1395,14 @@
       </c>
       <c r="T10" s="4">
         <f>U10-S10</f>
-        <v>13778</v>
+        <v>13779</v>
       </c>
       <c r="U10" s="22">
-        <v>68412</v>
+        <v>68413</v>
       </c>
       <c r="V10" s="5">
         <f>U10/R10</f>
-        <v>1.002873226222587</v>
+        <v>1.0028878855400492</v>
       </c>
       <c r="W10" s="9">
         <v>69437</v>
@@ -1412,14 +1412,14 @@
       </c>
       <c r="Y10" s="4">
         <f>Z10-X10</f>
-        <v>14717</v>
+        <v>14719</v>
       </c>
       <c r="Z10" s="22">
-        <v>69766</v>
+        <v>69768</v>
       </c>
       <c r="AA10" s="5">
         <f>Z10/W10</f>
-        <v>1.0047381079251696</v>
+        <v>1.0047669110128605</v>
       </c>
       <c r="AB10" s="9">
         <v>112849</v>
@@ -1429,14 +1429,14 @@
       </c>
       <c r="AD10" s="4">
         <f>AE10-AC10</f>
-        <v>23742</v>
+        <v>23744</v>
       </c>
       <c r="AE10" s="8">
-        <v>112528</v>
+        <v>112530</v>
       </c>
       <c r="AF10" s="5">
         <f>AE10/AB10</f>
-        <v>0.99715549096580391</v>
+        <v>0.99717321376352475</v>
       </c>
       <c r="AG10" s="9">
         <v>69494</v>
@@ -1446,14 +1446,14 @@
       </c>
       <c r="AI10" s="4">
         <f>AJ10-AH10</f>
-        <v>14413</v>
+        <v>14414</v>
       </c>
       <c r="AJ10" s="22">
-        <v>69347</v>
+        <v>69348</v>
       </c>
       <c r="AK10" s="5">
         <f>AJ10/AG10</f>
-        <v>0.99788470947132124</v>
+        <v>0.99789909920280884</v>
       </c>
       <c r="AL10" s="9">
         <v>70757</v>
@@ -1463,14 +1463,14 @@
       </c>
       <c r="AN10" s="4">
         <f>AO10-AM10</f>
-        <v>12823</v>
+        <v>12824</v>
       </c>
       <c r="AO10" s="22">
-        <v>70329</v>
+        <v>70330</v>
       </c>
       <c r="AP10" s="5">
         <f>AO10/AL10</f>
-        <v>0.99395112851025336</v>
+        <v>0.99396526138756591</v>
       </c>
       <c r="AQ10" s="15">
         <v>115882</v>
@@ -1480,14 +1480,14 @@
       </c>
       <c r="AS10" s="4">
         <f>AT10-AR10</f>
-        <v>20527</v>
+        <v>20530</v>
       </c>
       <c r="AT10" s="8">
-        <v>114701</v>
+        <v>114704</v>
       </c>
       <c r="AU10" s="5">
         <f>AT10/AQ10</f>
-        <v>0.98980859840182256</v>
+        <v>0.98983448680554353</v>
       </c>
       <c r="AV10" s="9">
         <v>70382</v>
@@ -1497,14 +1497,14 @@
       </c>
       <c r="AX10" s="4">
         <f>AY10-AW10</f>
-        <v>13584</v>
+        <v>13585</v>
       </c>
       <c r="AY10" s="22">
-        <v>69440</v>
+        <v>69441</v>
       </c>
       <c r="AZ10" s="5">
         <f>AY10/AV10</f>
-        <v>0.98661589610980083</v>
+        <v>0.98663010428802822</v>
       </c>
       <c r="BA10" s="9">
         <v>70494</v>
@@ -1514,14 +1514,14 @@
       </c>
       <c r="BC10" s="4">
         <f>BD10-BB10</f>
-        <v>13844</v>
+        <v>13846</v>
       </c>
       <c r="BD10" s="8">
-        <v>70615</v>
+        <v>70617</v>
       </c>
       <c r="BE10" s="5">
         <f>BD10/BA10</f>
-        <v>1.0017164581382814</v>
+        <v>1.0017448293471785</v>
       </c>
       <c r="BF10" s="9">
         <v>117563</v>
@@ -1531,14 +1531,14 @@
       </c>
       <c r="BH10" s="4">
         <f>BI10-BG10</f>
-        <v>32201</v>
+        <v>32205</v>
       </c>
       <c r="BI10" s="8">
-        <v>117477</v>
+        <v>117481</v>
       </c>
       <c r="BJ10" s="5">
         <f>BI10/BF10</f>
-        <v>0.99926847732705015</v>
+        <v>0.99930250163741996</v>
       </c>
     </row>
     <row r="11" spans="1:62" x14ac:dyDescent="0.3">
@@ -1556,14 +1556,14 @@
       </c>
       <c r="E11" s="4">
         <f t="shared" ref="E11:E47" si="0">F11-D11</f>
-        <v>7530</v>
+        <v>7531</v>
       </c>
       <c r="F11" s="22">
-        <v>43242</v>
+        <v>43243</v>
       </c>
       <c r="G11" s="5">
         <f t="shared" ref="G11:G33" si="1">F11/C11</f>
-        <v>0.97558884577204219</v>
+        <v>0.97561140691273351</v>
       </c>
       <c r="H11" s="9">
         <v>45199</v>
@@ -1573,14 +1573,14 @@
       </c>
       <c r="J11" s="4">
         <f t="shared" ref="J11:J47" si="2">K11-I11</f>
-        <v>9555</v>
+        <v>9556</v>
       </c>
       <c r="K11" s="22">
-        <v>44035</v>
+        <v>44036</v>
       </c>
       <c r="L11" s="5">
         <f t="shared" ref="L11:L47" si="3">K11/H11</f>
-        <v>0.97424721785880219</v>
+        <v>0.97426934224208506</v>
       </c>
       <c r="M11" s="4">
         <v>98966</v>
@@ -1590,14 +1590,14 @@
       </c>
       <c r="O11" s="4">
         <f t="shared" ref="O11:O48" si="4">P11-N11</f>
-        <v>17697</v>
+        <v>17698</v>
       </c>
       <c r="P11" s="8">
-        <v>96225</v>
+        <v>96226</v>
       </c>
       <c r="Q11" s="5">
         <f t="shared" ref="Q11:Q48" si="5">P11/M11</f>
-        <v>0.97230361942485299</v>
+        <v>0.97231372390517956</v>
       </c>
       <c r="R11" s="9">
         <v>44504</v>
@@ -1607,14 +1607,14 @@
       </c>
       <c r="T11" s="4">
         <f t="shared" ref="T11:T48" si="6">U11-S11</f>
-        <v>8458</v>
+        <v>8459</v>
       </c>
       <c r="U11" s="22">
-        <v>43147</v>
+        <v>43148</v>
       </c>
       <c r="V11" s="5">
         <f t="shared" ref="V11:V48" si="7">U11/R11</f>
-        <v>0.96950835879920905</v>
+        <v>0.96953082868955598</v>
       </c>
       <c r="W11" s="9">
         <v>45023</v>
@@ -1624,14 +1624,14 @@
       </c>
       <c r="Y11" s="4">
         <f t="shared" ref="Y11:Y47" si="8">Z11-X11</f>
-        <v>9426</v>
+        <v>9427</v>
       </c>
       <c r="Z11" s="22">
-        <v>43806</v>
+        <v>43807</v>
       </c>
       <c r="AA11" s="5">
         <f t="shared" ref="AA11:AA47" si="9">Z11/W11</f>
-        <v>0.97296937121027027</v>
+        <v>0.97299158208027003</v>
       </c>
       <c r="AB11" s="9">
         <v>99888</v>
@@ -1641,14 +1641,14 @@
       </c>
       <c r="AD11" s="4">
         <f t="shared" ref="AD11:AD48" si="10">AE11-AC11</f>
-        <v>20290</v>
+        <v>20291</v>
       </c>
       <c r="AE11" s="8">
-        <v>97412</v>
+        <v>97413</v>
       </c>
       <c r="AF11" s="5">
         <f t="shared" ref="AF11:AF48" si="11">AE11/AB11</f>
-        <v>0.975212237706231</v>
+        <v>0.97522224891878906</v>
       </c>
       <c r="AG11" s="9">
         <v>44744</v>
@@ -1658,14 +1658,14 @@
       </c>
       <c r="AI11" s="4">
         <f t="shared" ref="AI11:AI48" si="12">AJ11-AH11</f>
-        <v>8864</v>
+        <v>8865</v>
       </c>
       <c r="AJ11" s="22">
-        <v>43368</v>
+        <v>43369</v>
       </c>
       <c r="AK11" s="5">
         <f t="shared" ref="AK11:AK48" si="13">AJ11/AG11</f>
-        <v>0.9692472733774361</v>
+        <v>0.96926962274271411</v>
       </c>
       <c r="AL11" s="9">
         <v>45303</v>
@@ -1675,14 +1675,14 @@
       </c>
       <c r="AN11" s="4">
         <f t="shared" ref="AN11:AN48" si="14">AO11-AM11</f>
-        <v>7702</v>
+        <v>7703</v>
       </c>
       <c r="AO11" s="22">
-        <v>43888</v>
+        <v>43889</v>
       </c>
       <c r="AP11" s="5">
         <f t="shared" ref="AP11:AP48" si="15">AO11/AL11</f>
-        <v>0.96876586539522769</v>
+        <v>0.96878793898858795</v>
       </c>
       <c r="AQ11" s="15">
         <v>100769</v>
@@ -1692,14 +1692,14 @@
       </c>
       <c r="AS11" s="4">
         <f t="shared" ref="AS11:AS48" si="16">AT11-AR11</f>
-        <v>14772</v>
+        <v>14773</v>
       </c>
       <c r="AT11" s="8">
-        <v>98354</v>
+        <v>98355</v>
       </c>
       <c r="AU11" s="5">
         <f t="shared" ref="AU11:AU48" si="17">AT11/AQ11</f>
-        <v>0.9760342962617472</v>
+        <v>0.97604421994859525</v>
       </c>
       <c r="AV11" s="9">
         <v>46153</v>
@@ -1709,14 +1709,14 @@
       </c>
       <c r="AX11" s="4">
         <f t="shared" ref="AX11:AX48" si="18">AY11-AW11</f>
-        <v>7690</v>
+        <v>7691</v>
       </c>
       <c r="AY11" s="22">
-        <v>43745</v>
+        <v>43746</v>
       </c>
       <c r="AZ11" s="5">
         <f t="shared" ref="AZ11:AZ48" si="19">AY11/AV11</f>
-        <v>0.9478257101380192</v>
+        <v>0.94784737720191536</v>
       </c>
       <c r="BA11" s="9">
         <v>44735</v>
@@ -1726,14 +1726,14 @@
       </c>
       <c r="BC11" s="4">
         <f t="shared" ref="BC11:BC48" si="20">BD11-BB11</f>
-        <v>7800</v>
+        <v>7801</v>
       </c>
       <c r="BD11" s="8">
-        <v>44765</v>
+        <v>44766</v>
       </c>
       <c r="BE11" s="5">
         <f t="shared" ref="BE11:BE48" si="21">BD11/BA11</f>
-        <v>1.0006706158488878</v>
+        <v>1.0006929697105176</v>
       </c>
       <c r="BF11" s="9">
         <v>99991</v>
@@ -1743,14 +1743,14 @@
       </c>
       <c r="BH11" s="4">
         <f t="shared" ref="BH11:BH48" si="22">BI11-BG11</f>
-        <v>21621</v>
+        <v>21624</v>
       </c>
       <c r="BI11" s="8">
-        <v>100714</v>
+        <v>100717</v>
       </c>
       <c r="BJ11" s="5">
         <f t="shared" ref="BJ11:BJ48" si="23">BI11/BF11</f>
-        <v>1.0072306507585682</v>
+        <v>1.0072606534588113</v>
       </c>
     </row>
     <row r="12" spans="1:62" x14ac:dyDescent="0.3">
@@ -1768,14 +1768,14 @@
       </c>
       <c r="E12" s="4">
         <f t="shared" si="0"/>
-        <v>19984</v>
+        <v>19985</v>
       </c>
       <c r="F12" s="22">
-        <v>155774</v>
+        <v>155775</v>
       </c>
       <c r="G12" s="5">
         <f t="shared" si="1"/>
-        <v>0.94490949677294123</v>
+        <v>0.94491556267287813</v>
       </c>
       <c r="H12" s="9">
         <v>167213</v>
@@ -1785,14 +1785,14 @@
       </c>
       <c r="J12" s="4">
         <f t="shared" si="2"/>
-        <v>24933</v>
+        <v>24934</v>
       </c>
       <c r="K12" s="22">
-        <v>158988</v>
+        <v>158989</v>
       </c>
       <c r="L12" s="5">
         <f t="shared" si="3"/>
-        <v>0.95081124075281231</v>
+        <v>0.9508172211490733</v>
       </c>
       <c r="M12" s="4">
         <v>342449</v>
@@ -1802,14 +1802,14 @@
       </c>
       <c r="O12" s="4">
         <f t="shared" si="4"/>
-        <v>51790</v>
+        <v>51792</v>
       </c>
       <c r="P12" s="8">
-        <v>327297</v>
+        <v>327299</v>
       </c>
       <c r="Q12" s="5">
         <f t="shared" si="5"/>
-        <v>0.95575399548545914</v>
+        <v>0.95575983577116597</v>
       </c>
       <c r="R12" s="9">
         <v>167538</v>
@@ -1819,14 +1819,14 @@
       </c>
       <c r="T12" s="4">
         <f t="shared" si="6"/>
-        <v>23860</v>
+        <v>23861</v>
       </c>
       <c r="U12" s="22">
-        <v>158028</v>
+        <v>158029</v>
       </c>
       <c r="V12" s="5">
         <f t="shared" si="7"/>
-        <v>0.94323675822798414</v>
+        <v>0.94324272702312306</v>
       </c>
       <c r="W12" s="9">
         <v>169859</v>
@@ -1836,14 +1836,14 @@
       </c>
       <c r="Y12" s="4">
         <f t="shared" si="8"/>
-        <v>27063</v>
+        <v>27064</v>
       </c>
       <c r="Z12" s="22">
-        <v>160586</v>
+        <v>160587</v>
       </c>
       <c r="AA12" s="5">
         <f t="shared" si="9"/>
-        <v>0.94540766164877932</v>
+        <v>0.94541354888466311</v>
       </c>
       <c r="AB12" s="9">
         <v>346997</v>
@@ -1853,14 +1853,14 @@
       </c>
       <c r="AD12" s="4">
         <f t="shared" si="10"/>
-        <v>64279</v>
+        <v>64281</v>
       </c>
       <c r="AE12" s="8">
-        <v>331746</v>
+        <v>331748</v>
       </c>
       <c r="AF12" s="5">
         <f t="shared" si="11"/>
-        <v>0.95604861137127983</v>
+        <v>0.95605437510987124</v>
       </c>
       <c r="AG12" s="9">
         <v>170493</v>
@@ -1870,14 +1870,14 @@
       </c>
       <c r="AI12" s="4">
         <f t="shared" si="12"/>
-        <v>26911</v>
+        <v>26913</v>
       </c>
       <c r="AJ12" s="22">
-        <v>160379</v>
+        <v>160381</v>
       </c>
       <c r="AK12" s="5">
         <f t="shared" si="13"/>
-        <v>0.94067791639539455</v>
+        <v>0.94068964708228486</v>
       </c>
       <c r="AL12" s="9">
         <v>172338</v>
@@ -1887,14 +1887,14 @@
       </c>
       <c r="AN12" s="4">
         <f t="shared" si="14"/>
-        <v>23341</v>
+        <v>23342</v>
       </c>
       <c r="AO12" s="22">
-        <v>162780</v>
+        <v>162781</v>
       </c>
       <c r="AP12" s="5">
         <f t="shared" si="15"/>
-        <v>0.94453921944086616</v>
+        <v>0.94454502199166757</v>
       </c>
       <c r="AQ12" s="15">
         <v>350104</v>
@@ -1904,14 +1904,14 @@
       </c>
       <c r="AS12" s="4">
         <f t="shared" si="16"/>
-        <v>43752</v>
+        <v>43755</v>
       </c>
       <c r="AT12" s="8">
-        <v>335246</v>
+        <v>335249</v>
       </c>
       <c r="AU12" s="5">
         <f t="shared" si="17"/>
-        <v>0.95756118182025918</v>
+        <v>0.95756975070264838</v>
       </c>
       <c r="AV12" s="9">
         <v>177002</v>
@@ -1921,14 +1921,14 @@
       </c>
       <c r="AX12" s="4">
         <f t="shared" si="18"/>
-        <v>22977</v>
+        <v>22978</v>
       </c>
       <c r="AY12" s="22">
-        <v>162387</v>
+        <v>162388</v>
       </c>
       <c r="AZ12" s="5">
         <f t="shared" si="19"/>
-        <v>0.91743031152190369</v>
+        <v>0.91743596117557991</v>
       </c>
       <c r="BA12" s="9">
         <v>166689</v>
@@ -1938,14 +1938,14 @@
       </c>
       <c r="BC12" s="4">
         <f t="shared" si="20"/>
-        <v>28215</v>
+        <v>28216</v>
       </c>
       <c r="BD12" s="8">
-        <v>164572</v>
+        <v>164573</v>
       </c>
       <c r="BE12" s="5">
         <f t="shared" si="21"/>
-        <v>0.98729970183995341</v>
+        <v>0.98730570103606119</v>
       </c>
       <c r="BF12" s="9">
         <v>341156</v>
@@ -1955,14 +1955,14 @@
       </c>
       <c r="BH12" s="4">
         <f t="shared" si="22"/>
-        <v>69380</v>
+        <v>69384</v>
       </c>
       <c r="BI12" s="8">
-        <v>339914</v>
+        <v>339918</v>
       </c>
       <c r="BJ12" s="5">
         <f t="shared" si="23"/>
-        <v>0.99635943673861815</v>
+        <v>0.99637116158003958</v>
       </c>
     </row>
     <row r="13" spans="1:62" x14ac:dyDescent="0.3">
@@ -2065,14 +2065,14 @@
       </c>
       <c r="AD13" s="4">
         <f t="shared" si="10"/>
-        <v>5403</v>
+        <v>5404</v>
       </c>
       <c r="AE13" s="8">
-        <v>27330</v>
+        <v>27331</v>
       </c>
       <c r="AF13" s="5">
         <f t="shared" si="11"/>
-        <v>0.9779224961534333</v>
+        <v>0.97795827816939207</v>
       </c>
       <c r="AG13" s="9">
         <v>16563</v>
@@ -2192,14 +2192,14 @@
       </c>
       <c r="E14" s="4">
         <f t="shared" si="0"/>
-        <v>15671</v>
+        <v>15674</v>
       </c>
       <c r="F14" s="22">
-        <v>78887</v>
+        <v>78890</v>
       </c>
       <c r="G14" s="5">
         <f t="shared" si="1"/>
-        <v>0.95274154589371984</v>
+        <v>0.95277777777777772</v>
       </c>
       <c r="H14" s="9">
         <v>84757</v>
@@ -2209,14 +2209,14 @@
       </c>
       <c r="J14" s="4">
         <f t="shared" si="2"/>
-        <v>18863</v>
+        <v>18866</v>
       </c>
       <c r="K14" s="22">
-        <v>80620</v>
+        <v>80623</v>
       </c>
       <c r="L14" s="5">
         <f t="shared" si="3"/>
-        <v>0.95118987222294327</v>
+        <v>0.95122526752952563</v>
       </c>
       <c r="M14" s="4">
         <v>154914</v>
@@ -2226,14 +2226,14 @@
       </c>
       <c r="O14" s="4">
         <f t="shared" si="4"/>
-        <v>31302</v>
+        <v>31307</v>
       </c>
       <c r="P14" s="8">
-        <v>147536</v>
+        <v>147541</v>
       </c>
       <c r="Q14" s="5">
         <f t="shared" si="5"/>
-        <v>0.95237357501581521</v>
+        <v>0.95240585098829023</v>
       </c>
       <c r="R14" s="9">
         <v>85475</v>
@@ -2243,14 +2243,14 @@
       </c>
       <c r="T14" s="4">
         <f t="shared" si="6"/>
-        <v>18030</v>
+        <v>18031</v>
       </c>
       <c r="U14" s="22">
-        <v>80369</v>
+        <v>80370</v>
       </c>
       <c r="V14" s="5">
         <f t="shared" si="7"/>
-        <v>0.94026323486399532</v>
+        <v>0.94027493419128405</v>
       </c>
       <c r="W14" s="9">
         <v>86445</v>
@@ -2260,14 +2260,14 @@
       </c>
       <c r="Y14" s="4">
         <f t="shared" si="8"/>
-        <v>19186</v>
+        <v>19187</v>
       </c>
       <c r="Z14" s="22">
-        <v>81629</v>
+        <v>81630</v>
       </c>
       <c r="AA14" s="5">
         <f t="shared" si="9"/>
-        <v>0.94428827578228935</v>
+        <v>0.9442998438313378</v>
       </c>
       <c r="AB14" s="9">
         <v>156524</v>
@@ -2277,14 +2277,14 @@
       </c>
       <c r="AD14" s="4">
         <f t="shared" si="10"/>
-        <v>37385</v>
+        <v>37393</v>
       </c>
       <c r="AE14" s="8">
-        <v>149068</v>
+        <v>149076</v>
       </c>
       <c r="AF14" s="5">
         <f t="shared" si="11"/>
-        <v>0.95236513250364163</v>
+        <v>0.95241624287649174</v>
       </c>
       <c r="AG14" s="9">
         <v>86459</v>
@@ -2294,14 +2294,14 @@
       </c>
       <c r="AI14" s="4">
         <f t="shared" si="12"/>
-        <v>19481</v>
+        <v>19484</v>
       </c>
       <c r="AJ14" s="22">
-        <v>81558</v>
+        <v>81561</v>
       </c>
       <c r="AK14" s="5">
         <f t="shared" si="13"/>
-        <v>0.94331417203529999</v>
+        <v>0.94334887056292582</v>
       </c>
       <c r="AL14" s="9">
         <v>87786</v>
@@ -2311,14 +2311,14 @@
       </c>
       <c r="AN14" s="4">
         <f t="shared" si="14"/>
-        <v>16937</v>
+        <v>16941</v>
       </c>
       <c r="AO14" s="22">
-        <v>83038</v>
+        <v>83042</v>
       </c>
       <c r="AP14" s="5">
         <f t="shared" si="15"/>
-        <v>0.94591392704987132</v>
+        <v>0.94595949240197752</v>
       </c>
       <c r="AQ14" s="15">
         <v>158597</v>
@@ -2328,14 +2328,14 @@
       </c>
       <c r="AS14" s="4">
         <f t="shared" si="16"/>
-        <v>28213</v>
+        <v>28223</v>
       </c>
       <c r="AT14" s="8">
-        <v>151367</v>
+        <v>151377</v>
       </c>
       <c r="AU14" s="5">
         <f t="shared" si="17"/>
-        <v>0.95441275686173133</v>
+        <v>0.95447580975680502</v>
       </c>
       <c r="AV14" s="9">
         <v>90863</v>
@@ -2345,14 +2345,14 @@
       </c>
       <c r="AX14" s="4">
         <f t="shared" si="18"/>
-        <v>17152</v>
+        <v>17156</v>
       </c>
       <c r="AY14" s="22">
-        <v>83726</v>
+        <v>83730</v>
       </c>
       <c r="AZ14" s="5">
         <f t="shared" si="19"/>
-        <v>0.92145317676061766</v>
+        <v>0.92149719907993355</v>
       </c>
       <c r="BA14" s="9">
         <v>86219</v>
@@ -2362,14 +2362,14 @@
       </c>
       <c r="BC14" s="4">
         <f t="shared" si="20"/>
-        <v>17691</v>
+        <v>17696</v>
       </c>
       <c r="BD14" s="8">
-        <v>85360</v>
+        <v>85365</v>
       </c>
       <c r="BE14" s="5">
         <f t="shared" si="21"/>
-        <v>0.99003699880536777</v>
+        <v>0.99009499066331086</v>
       </c>
       <c r="BF14" s="9">
         <v>155639</v>
@@ -2379,14 +2379,14 @@
       </c>
       <c r="BH14" s="4">
         <f t="shared" si="22"/>
-        <v>40033</v>
+        <v>40052</v>
       </c>
       <c r="BI14" s="8">
-        <v>154720</v>
+        <v>154739</v>
       </c>
       <c r="BJ14" s="5">
         <f t="shared" si="23"/>
-        <v>0.99409531030140263</v>
+        <v>0.99421738767275558</v>
       </c>
     </row>
     <row r="15" spans="1:62" x14ac:dyDescent="0.3">
@@ -2489,14 +2489,14 @@
       </c>
       <c r="AD15" s="4">
         <f t="shared" si="10"/>
-        <v>99580</v>
+        <v>99581</v>
       </c>
       <c r="AE15" s="8">
-        <v>465184</v>
+        <v>465185</v>
       </c>
       <c r="AF15" s="5">
         <f t="shared" si="11"/>
-        <v>0.9598448348791383</v>
+        <v>0.95984689824510727</v>
       </c>
       <c r="AG15" s="9">
         <v>282622</v>
@@ -2506,14 +2506,14 @@
       </c>
       <c r="AI15" s="4">
         <f t="shared" si="12"/>
-        <v>52762</v>
+        <v>52763</v>
       </c>
       <c r="AJ15" s="22">
-        <v>269149</v>
+        <v>269150</v>
       </c>
       <c r="AK15" s="5">
         <f t="shared" si="13"/>
-        <v>0.95232855191740207</v>
+        <v>0.95233209021236842</v>
       </c>
       <c r="AL15" s="9">
         <v>285773</v>
@@ -2523,14 +2523,14 @@
       </c>
       <c r="AN15" s="4">
         <f t="shared" si="14"/>
-        <v>46183</v>
+        <v>46185</v>
       </c>
       <c r="AO15" s="22">
-        <v>273138</v>
+        <v>273140</v>
       </c>
       <c r="AP15" s="5">
         <f t="shared" si="15"/>
-        <v>0.95578658585660647</v>
+        <v>0.95579358441840201</v>
       </c>
       <c r="AQ15" s="15">
         <v>491220</v>
@@ -2540,14 +2540,14 @@
       </c>
       <c r="AS15" s="4">
         <f t="shared" si="16"/>
-        <v>69964</v>
+        <v>69965</v>
       </c>
       <c r="AT15" s="8">
-        <v>472061</v>
+        <v>472062</v>
       </c>
       <c r="AU15" s="5">
         <f t="shared" si="17"/>
-        <v>0.96099710923822323</v>
+        <v>0.96099914498595329</v>
       </c>
       <c r="AV15" s="9">
         <v>292625</v>
@@ -2557,14 +2557,14 @@
       </c>
       <c r="AX15" s="4">
         <f t="shared" si="18"/>
-        <v>44925</v>
+        <v>44926</v>
       </c>
       <c r="AY15" s="22">
-        <v>275617</v>
+        <v>275618</v>
       </c>
       <c r="AZ15" s="5">
         <f t="shared" si="19"/>
-        <v>0.94187782998718494</v>
+        <v>0.94188124733020073</v>
       </c>
       <c r="BA15" s="9">
         <v>283148</v>
@@ -2574,14 +2574,14 @@
       </c>
       <c r="BC15" s="4">
         <f t="shared" si="20"/>
-        <v>46794</v>
+        <v>46795</v>
       </c>
       <c r="BD15" s="8">
-        <v>280224</v>
+        <v>280225</v>
       </c>
       <c r="BE15" s="5">
         <f t="shared" si="21"/>
-        <v>0.98967324508737475</v>
+        <v>0.98967677680930111</v>
       </c>
       <c r="BF15" s="9">
         <v>485122</v>
@@ -2591,14 +2591,14 @@
       </c>
       <c r="BH15" s="4">
         <f t="shared" si="22"/>
-        <v>100954</v>
+        <v>100955</v>
       </c>
       <c r="BI15" s="8">
-        <v>481817</v>
+        <v>481818</v>
       </c>
       <c r="BJ15" s="5">
         <f t="shared" si="23"/>
-        <v>0.99318728072526086</v>
+        <v>0.99318934206240905</v>
       </c>
     </row>
     <row r="16" spans="1:62" x14ac:dyDescent="0.3">
@@ -2616,14 +2616,14 @@
       </c>
       <c r="E16" s="4">
         <f t="shared" si="0"/>
-        <v>61328</v>
+        <v>61335</v>
       </c>
       <c r="F16" s="22">
-        <v>393541</v>
+        <v>393548</v>
       </c>
       <c r="G16" s="5">
         <f t="shared" si="1"/>
-        <v>0.95919635762719302</v>
+        <v>0.95921341906298596</v>
       </c>
       <c r="H16" s="9">
         <v>416018</v>
@@ -2633,14 +2633,14 @@
       </c>
       <c r="J16" s="4">
         <f t="shared" si="2"/>
-        <v>74113</v>
+        <v>74120</v>
       </c>
       <c r="K16" s="22">
-        <v>400753</v>
+        <v>400760</v>
       </c>
       <c r="L16" s="5">
         <f t="shared" si="3"/>
-        <v>0.96330687614478216</v>
+        <v>0.96332370233980258</v>
       </c>
       <c r="M16" s="4">
         <v>750813</v>
@@ -2650,14 +2650,14 @@
       </c>
       <c r="O16" s="4">
         <f t="shared" si="4"/>
-        <v>121065</v>
+        <v>121079</v>
       </c>
       <c r="P16" s="8">
-        <v>719531</v>
+        <v>719545</v>
       </c>
       <c r="Q16" s="5">
         <f t="shared" si="5"/>
-        <v>0.95833583062626782</v>
+        <v>0.9583544770801784</v>
       </c>
       <c r="R16" s="9">
         <v>419109</v>
@@ -2667,14 +2667,14 @@
       </c>
       <c r="T16" s="4">
         <f t="shared" si="6"/>
-        <v>73002</v>
+        <v>73010</v>
       </c>
       <c r="U16" s="22">
-        <v>401885</v>
+        <v>401893</v>
       </c>
       <c r="V16" s="5">
         <f t="shared" si="7"/>
-        <v>0.95890329246091111</v>
+        <v>0.95892238057402723</v>
       </c>
       <c r="W16" s="9">
         <v>423539</v>
@@ -2684,14 +2684,14 @@
       </c>
       <c r="Y16" s="4">
         <f t="shared" si="8"/>
-        <v>73334</v>
+        <v>73342</v>
       </c>
       <c r="Z16" s="22">
-        <v>407289</v>
+        <v>407297</v>
       </c>
       <c r="AA16" s="5">
         <f t="shared" si="9"/>
-        <v>0.96163281303492709</v>
+        <v>0.96165170149620227</v>
       </c>
       <c r="AB16" s="9">
         <v>762171</v>
@@ -2701,14 +2701,14 @@
       </c>
       <c r="AD16" s="4">
         <f t="shared" si="10"/>
-        <v>150551</v>
+        <v>150569</v>
       </c>
       <c r="AE16" s="8">
-        <v>731043</v>
+        <v>731061</v>
       </c>
       <c r="AF16" s="5">
         <f t="shared" si="11"/>
-        <v>0.95915877145679906</v>
+        <v>0.95918238820422186</v>
       </c>
       <c r="AG16" s="9">
         <v>429452</v>
@@ -2718,14 +2718,14 @@
       </c>
       <c r="AI16" s="4">
         <f t="shared" si="12"/>
-        <v>79973</v>
+        <v>79983</v>
       </c>
       <c r="AJ16" s="22">
-        <v>411517</v>
+        <v>411527</v>
       </c>
       <c r="AK16" s="5">
         <f t="shared" si="13"/>
-        <v>0.95823747473524401</v>
+        <v>0.95826076022465845</v>
       </c>
       <c r="AL16" s="9">
         <v>434676</v>
@@ -2735,14 +2735,14 @@
       </c>
       <c r="AN16" s="4">
         <f t="shared" si="14"/>
-        <v>70930</v>
+        <v>70941</v>
       </c>
       <c r="AO16" s="22">
-        <v>417029</v>
+        <v>417040</v>
       </c>
       <c r="AP16" s="5">
         <f t="shared" si="15"/>
-        <v>0.95940194535700152</v>
+        <v>0.95942725156208297</v>
       </c>
       <c r="AQ16" s="15">
         <v>772632</v>
@@ -2752,14 +2752,14 @@
       </c>
       <c r="AS16" s="4">
         <f t="shared" si="16"/>
-        <v>110147</v>
+        <v>110168</v>
       </c>
       <c r="AT16" s="8">
-        <v>741452</v>
+        <v>741473</v>
       </c>
       <c r="AU16" s="5">
         <f t="shared" si="17"/>
-        <v>0.9596444361610702</v>
+        <v>0.95967161598277062</v>
       </c>
       <c r="AV16" s="9">
         <v>448203</v>
@@ -2769,14 +2769,14 @@
       </c>
       <c r="AX16" s="4">
         <f t="shared" si="18"/>
-        <v>69522</v>
+        <v>69537</v>
       </c>
       <c r="AY16" s="22">
-        <v>419978</v>
+        <v>419993</v>
       </c>
       <c r="AZ16" s="5">
         <f t="shared" si="19"/>
-        <v>0.93702630281368038</v>
+        <v>0.93705976979181305</v>
       </c>
       <c r="BA16" s="9">
         <v>429555</v>
@@ -2786,14 +2786,14 @@
       </c>
       <c r="BC16" s="4">
         <f t="shared" si="20"/>
-        <v>70915</v>
+        <v>70929</v>
       </c>
       <c r="BD16" s="8">
-        <v>424787</v>
+        <v>424801</v>
       </c>
       <c r="BE16" s="5">
         <f t="shared" si="21"/>
-        <v>0.98890014084343103</v>
+        <v>0.98893273271175985</v>
       </c>
       <c r="BF16" s="9">
         <v>753579</v>
@@ -2803,14 +2803,14 @@
       </c>
       <c r="BH16" s="4">
         <f t="shared" si="22"/>
-        <v>147942</v>
+        <v>147976</v>
       </c>
       <c r="BI16" s="8">
-        <v>751144</v>
+        <v>751178</v>
       </c>
       <c r="BJ16" s="5">
         <f t="shared" si="23"/>
-        <v>0.99676875284475819</v>
+        <v>0.99681387087485185</v>
       </c>
     </row>
     <row r="17" spans="1:62" x14ac:dyDescent="0.3">
@@ -2828,14 +2828,14 @@
       </c>
       <c r="E17" s="4">
         <f t="shared" si="0"/>
-        <v>51271</v>
+        <v>51278</v>
       </c>
       <c r="F17" s="22">
-        <v>277323</v>
+        <v>277330</v>
       </c>
       <c r="G17" s="5">
         <f t="shared" si="1"/>
-        <v>0.9803868194335934</v>
+        <v>0.98041156569602395</v>
       </c>
       <c r="H17" s="9">
         <v>290053</v>
@@ -2845,14 +2845,14 @@
       </c>
       <c r="J17" s="4">
         <f t="shared" si="2"/>
-        <v>59533</v>
+        <v>59540</v>
       </c>
       <c r="K17" s="22">
-        <v>284820</v>
+        <v>284827</v>
       </c>
       <c r="L17" s="5">
         <f t="shared" si="3"/>
-        <v>0.98195846965899336</v>
+        <v>0.98198260317941899</v>
       </c>
       <c r="M17" s="4">
         <v>666005</v>
@@ -2862,14 +2862,14 @@
       </c>
       <c r="O17" s="4">
         <f t="shared" si="4"/>
-        <v>128101</v>
+        <v>128112</v>
       </c>
       <c r="P17" s="8">
-        <v>645965</v>
+        <v>645976</v>
       </c>
       <c r="Q17" s="5">
         <f t="shared" si="5"/>
-        <v>0.96991013580979124</v>
+        <v>0.96992665220231078</v>
       </c>
       <c r="R17" s="9">
         <v>287981</v>
@@ -2879,14 +2879,14 @@
       </c>
       <c r="T17" s="4">
         <f t="shared" si="6"/>
-        <v>55267</v>
+        <v>55275</v>
       </c>
       <c r="U17" s="22">
-        <v>280812</v>
+        <v>280820</v>
       </c>
       <c r="V17" s="5">
         <f t="shared" si="7"/>
-        <v>0.97510599657616304</v>
+        <v>0.97513377618662345</v>
       </c>
       <c r="W17" s="9">
         <v>293004</v>
@@ -2896,14 +2896,14 @@
       </c>
       <c r="Y17" s="4">
         <f t="shared" si="8"/>
-        <v>60464</v>
+        <v>60470</v>
       </c>
       <c r="Z17" s="22">
-        <v>286651</v>
+        <v>286657</v>
       </c>
       <c r="AA17" s="5">
         <f t="shared" si="9"/>
-        <v>0.97831770214741098</v>
+        <v>0.97833817968355385</v>
       </c>
       <c r="AB17" s="9">
         <v>677720</v>
@@ -2913,14 +2913,14 @@
       </c>
       <c r="AD17" s="4">
         <f t="shared" si="10"/>
-        <v>145657</v>
+        <v>145671</v>
       </c>
       <c r="AE17" s="8">
-        <v>658918</v>
+        <v>658932</v>
       </c>
       <c r="AF17" s="5">
         <f t="shared" si="11"/>
-        <v>0.97225697928347987</v>
+        <v>0.97227763678215195</v>
       </c>
       <c r="AG17" s="9">
         <v>295677</v>
@@ -2930,14 +2930,14 @@
       </c>
       <c r="AI17" s="4">
         <f t="shared" si="12"/>
-        <v>59661</v>
+        <v>59670</v>
       </c>
       <c r="AJ17" s="22">
-        <v>288105</v>
+        <v>288114</v>
       </c>
       <c r="AK17" s="5">
         <f t="shared" si="13"/>
-        <v>0.97439097393439467</v>
+        <v>0.97442141255491632</v>
       </c>
       <c r="AL17" s="9">
         <v>303084</v>
@@ -2947,14 +2947,14 @@
       </c>
       <c r="AN17" s="4">
         <f t="shared" si="14"/>
-        <v>51536</v>
+        <v>51544</v>
       </c>
       <c r="AO17" s="22">
-        <v>296044</v>
+        <v>296052</v>
       </c>
       <c r="AP17" s="5">
         <f t="shared" si="15"/>
-        <v>0.97677211598104818</v>
+        <v>0.97679851130379691</v>
       </c>
       <c r="AQ17" s="15">
         <v>690105</v>
@@ -2964,14 +2964,14 @@
       </c>
       <c r="AS17" s="4">
         <f t="shared" si="16"/>
-        <v>105773</v>
+        <v>105793</v>
       </c>
       <c r="AT17" s="8">
-        <v>672918</v>
+        <v>672938</v>
       </c>
       <c r="AU17" s="5">
         <f t="shared" si="17"/>
-        <v>0.9750950942247919</v>
+        <v>0.97512407532187129</v>
       </c>
       <c r="AV17" s="9">
         <v>311697</v>
@@ -2981,14 +2981,14 @@
       </c>
       <c r="AX17" s="4">
         <f t="shared" si="18"/>
-        <v>48998</v>
+        <v>49010</v>
       </c>
       <c r="AY17" s="22">
-        <v>294841</v>
+        <v>294853</v>
       </c>
       <c r="AZ17" s="5">
         <f t="shared" si="19"/>
-        <v>0.94592184076202213</v>
+        <v>0.9459603396888645</v>
       </c>
       <c r="BA17" s="9">
         <v>307540</v>
@@ -2998,14 +2998,14 @@
       </c>
       <c r="BC17" s="4">
         <f t="shared" si="20"/>
-        <v>49201</v>
+        <v>49210</v>
       </c>
       <c r="BD17" s="8">
-        <v>301974</v>
+        <v>301983</v>
       </c>
       <c r="BE17" s="5">
         <f t="shared" si="21"/>
-        <v>0.98190154126292517</v>
+        <v>0.98193080574884573</v>
       </c>
       <c r="BF17" s="9">
         <v>689646</v>
@@ -3015,14 +3015,14 @@
       </c>
       <c r="BH17" s="4">
         <f t="shared" si="22"/>
-        <v>153164</v>
+        <v>153193</v>
       </c>
       <c r="BI17" s="8">
-        <v>687184</v>
+        <v>687213</v>
       </c>
       <c r="BJ17" s="5">
         <f t="shared" si="23"/>
-        <v>0.99643005251969852</v>
+        <v>0.99647210307897094</v>
       </c>
     </row>
     <row r="18" spans="1:62" x14ac:dyDescent="0.3">
@@ -3040,14 +3040,14 @@
       </c>
       <c r="E18" s="4">
         <f t="shared" si="0"/>
-        <v>141557</v>
+        <v>141567</v>
       </c>
       <c r="F18" s="22">
-        <v>822070</v>
+        <v>822080</v>
       </c>
       <c r="G18" s="5">
         <f t="shared" si="1"/>
-        <v>0.97807373952854193</v>
+        <v>0.97808563722264985</v>
       </c>
       <c r="H18" s="9">
         <v>861805</v>
@@ -3057,14 +3057,14 @@
       </c>
       <c r="J18" s="4">
         <f t="shared" si="2"/>
-        <v>162031</v>
+        <v>162040</v>
       </c>
       <c r="K18" s="22">
-        <v>837265</v>
+        <v>837274</v>
       </c>
       <c r="L18" s="5">
         <f t="shared" si="3"/>
-        <v>0.97152488091853728</v>
+        <v>0.97153532411624444</v>
       </c>
       <c r="M18" s="4">
         <v>1358945</v>
@@ -3074,14 +3074,14 @@
       </c>
       <c r="O18" s="4">
         <f t="shared" si="4"/>
-        <v>245587</v>
+        <v>245599</v>
       </c>
       <c r="P18" s="8">
-        <v>1303820</v>
+        <v>1303832</v>
       </c>
       <c r="Q18" s="5">
         <f t="shared" si="5"/>
-        <v>0.95943544440724238</v>
+        <v>0.95944427478669114</v>
       </c>
       <c r="R18" s="9">
         <v>869959</v>
@@ -3091,14 +3091,14 @@
       </c>
       <c r="T18" s="4">
         <f t="shared" si="6"/>
-        <v>158461</v>
+        <v>158471</v>
       </c>
       <c r="U18" s="22">
-        <v>839476</v>
+        <v>839486</v>
       </c>
       <c r="V18" s="5">
         <f t="shared" si="7"/>
-        <v>0.96496041767485596</v>
+        <v>0.96497191246943825</v>
       </c>
       <c r="W18" s="9">
         <v>883450</v>
@@ -3108,14 +3108,14 @@
       </c>
       <c r="Y18" s="4">
         <f t="shared" si="8"/>
-        <v>163341</v>
+        <v>163350</v>
       </c>
       <c r="Z18" s="22">
-        <v>853920</v>
+        <v>853929</v>
       </c>
       <c r="AA18" s="5">
         <f t="shared" si="9"/>
-        <v>0.9665742260456166</v>
+        <v>0.96658441337936496</v>
       </c>
       <c r="AB18" s="9">
         <v>1397129</v>
@@ -3125,14 +3125,14 @@
       </c>
       <c r="AD18" s="4">
         <f t="shared" si="10"/>
-        <v>289631</v>
+        <v>289644</v>
       </c>
       <c r="AE18" s="8">
-        <v>1339760</v>
+        <v>1339773</v>
       </c>
       <c r="AF18" s="5">
         <f t="shared" si="11"/>
-        <v>0.95893793629650514</v>
+        <v>0.95894724109226848</v>
       </c>
       <c r="AG18" s="9">
         <v>899515</v>
@@ -3142,14 +3142,14 @@
       </c>
       <c r="AI18" s="4">
         <f t="shared" si="12"/>
-        <v>168535</v>
+        <v>168545</v>
       </c>
       <c r="AJ18" s="22">
-        <v>864912</v>
+        <v>864922</v>
       </c>
       <c r="AK18" s="5">
         <f t="shared" si="13"/>
-        <v>0.96153149197067311</v>
+        <v>0.96154260907266698</v>
       </c>
       <c r="AL18" s="9">
         <v>914748</v>
@@ -3159,14 +3159,14 @@
       </c>
       <c r="AN18" s="4">
         <f t="shared" si="14"/>
-        <v>146468</v>
+        <v>146479</v>
       </c>
       <c r="AO18" s="22">
-        <v>880794</v>
+        <v>880805</v>
       </c>
       <c r="AP18" s="5">
         <f t="shared" si="15"/>
-        <v>0.96288158050085926</v>
+        <v>0.96289360567063276</v>
       </c>
       <c r="AQ18" s="15">
         <v>1436617</v>
@@ -3176,14 +3176,14 @@
       </c>
       <c r="AS18" s="4">
         <f t="shared" si="16"/>
-        <v>219809</v>
+        <v>219826</v>
       </c>
       <c r="AT18" s="8">
-        <v>1375231</v>
+        <v>1375248</v>
       </c>
       <c r="AU18" s="5">
         <f t="shared" si="17"/>
-        <v>0.95727044856075072</v>
+        <v>0.95728228191647458</v>
       </c>
       <c r="AV18" s="9">
         <v>954168</v>
@@ -3193,14 +3193,14 @@
       </c>
       <c r="AX18" s="4">
         <f t="shared" si="18"/>
-        <v>153008</v>
+        <v>153020</v>
       </c>
       <c r="AY18" s="22">
-        <v>894795</v>
+        <v>894807</v>
       </c>
       <c r="AZ18" s="5">
         <f t="shared" si="19"/>
-        <v>0.93777510878587422</v>
+        <v>0.9377876851875141</v>
       </c>
       <c r="BA18" s="9">
         <v>922519</v>
@@ -3210,14 +3210,14 @@
       </c>
       <c r="BC18" s="4">
         <f t="shared" si="20"/>
-        <v>158389</v>
+        <v>158402</v>
       </c>
       <c r="BD18" s="8">
-        <v>911433</v>
+        <v>911446</v>
       </c>
       <c r="BE18" s="5">
         <f t="shared" si="21"/>
-        <v>0.9879829033331563</v>
+        <v>0.98799699518383899</v>
       </c>
       <c r="BF18" s="9">
         <v>1428140</v>
@@ -3227,14 +3227,14 @@
       </c>
       <c r="BH18" s="4">
         <f t="shared" si="22"/>
-        <v>327714</v>
+        <v>327751</v>
       </c>
       <c r="BI18" s="8">
-        <v>1413368</v>
+        <v>1413405</v>
       </c>
       <c r="BJ18" s="5">
         <f t="shared" si="23"/>
-        <v>0.98965647625582931</v>
+        <v>0.98968238407999221</v>
       </c>
     </row>
     <row r="19" spans="1:62" x14ac:dyDescent="0.3">
@@ -3252,14 +3252,14 @@
       </c>
       <c r="E19" s="4">
         <f t="shared" si="0"/>
-        <v>54810</v>
+        <v>54814</v>
       </c>
       <c r="F19" s="22">
-        <v>245680</v>
+        <v>245684</v>
       </c>
       <c r="G19" s="5">
         <f t="shared" si="1"/>
-        <v>0.8886895374242183</v>
+        <v>0.88870400648213799</v>
       </c>
       <c r="H19" s="9">
         <v>280982</v>
@@ -3269,14 +3269,14 @@
       </c>
       <c r="J19" s="4">
         <f t="shared" si="2"/>
-        <v>89968</v>
+        <v>89972</v>
       </c>
       <c r="K19" s="22">
-        <v>250782</v>
+        <v>250786</v>
       </c>
       <c r="L19" s="5">
         <f t="shared" si="3"/>
-        <v>0.89251980553914489</v>
+        <v>0.89253404132649061</v>
       </c>
       <c r="M19" s="4">
         <v>470659</v>
@@ -3286,14 +3286,14 @@
       </c>
       <c r="O19" s="4">
         <f t="shared" si="4"/>
-        <v>92072</v>
+        <v>92078</v>
       </c>
       <c r="P19" s="8">
-        <v>424563</v>
+        <v>424569</v>
       </c>
       <c r="Q19" s="5">
         <f t="shared" si="5"/>
-        <v>0.90206072761808442</v>
+        <v>0.90207347570109142</v>
       </c>
       <c r="R19" s="9">
         <v>282327</v>
@@ -3303,14 +3303,14 @@
       </c>
       <c r="T19" s="4">
         <f t="shared" si="6"/>
-        <v>55602</v>
+        <v>55606</v>
       </c>
       <c r="U19" s="22">
-        <v>249692</v>
+        <v>249696</v>
       </c>
       <c r="V19" s="5">
         <f t="shared" si="7"/>
-        <v>0.88440708823456493</v>
+        <v>0.88442125620291367</v>
       </c>
       <c r="W19" s="9">
         <v>286093</v>
@@ -3320,14 +3320,14 @@
       </c>
       <c r="Y19" s="4">
         <f t="shared" si="8"/>
-        <v>58849</v>
+        <v>58854</v>
       </c>
       <c r="Z19" s="22">
-        <v>254762</v>
+        <v>254767</v>
       </c>
       <c r="AA19" s="5">
         <f t="shared" si="9"/>
-        <v>0.89048665993225984</v>
+        <v>0.89050413676671569</v>
       </c>
       <c r="AB19" s="9">
         <v>481143</v>
@@ -3337,14 +3337,14 @@
       </c>
       <c r="AD19" s="4">
         <f t="shared" si="10"/>
-        <v>107371</v>
+        <v>107379</v>
       </c>
       <c r="AE19" s="8">
-        <v>435525</v>
+        <v>435533</v>
       </c>
       <c r="AF19" s="5">
         <f t="shared" si="11"/>
-        <v>0.90518827043103611</v>
+        <v>0.90520489750448407</v>
       </c>
       <c r="AG19" s="9">
         <v>287213</v>
@@ -3354,14 +3354,14 @@
       </c>
       <c r="AI19" s="4">
         <f t="shared" si="12"/>
-        <v>57866</v>
+        <v>57872</v>
       </c>
       <c r="AJ19" s="22">
-        <v>254652</v>
+        <v>254658</v>
       </c>
       <c r="AK19" s="5">
         <f t="shared" si="13"/>
-        <v>0.88663117616542431</v>
+        <v>0.88665206658472984</v>
       </c>
       <c r="AL19" s="9">
         <v>292666</v>
@@ -3371,14 +3371,14 @@
       </c>
       <c r="AN19" s="4">
         <f t="shared" si="14"/>
-        <v>53083</v>
+        <v>53088</v>
       </c>
       <c r="AO19" s="22">
-        <v>260277</v>
+        <v>260282</v>
       </c>
       <c r="AP19" s="5">
         <f t="shared" si="15"/>
-        <v>0.8893311829867494</v>
+        <v>0.88934826730812599</v>
       </c>
       <c r="AQ19" s="15">
         <v>495564</v>
@@ -3388,14 +3388,14 @@
       </c>
       <c r="AS19" s="4">
         <f t="shared" si="16"/>
-        <v>83361</v>
+        <v>83371</v>
       </c>
       <c r="AT19" s="8">
-        <v>446761</v>
+        <v>446771</v>
       </c>
       <c r="AU19" s="5">
         <f t="shared" si="17"/>
-        <v>0.90152028799509243</v>
+        <v>0.90154046702343194</v>
       </c>
       <c r="AV19" s="9">
         <v>310298</v>
@@ -3405,14 +3405,14 @@
       </c>
       <c r="AX19" s="4">
         <f t="shared" si="18"/>
-        <v>52445</v>
+        <v>52452</v>
       </c>
       <c r="AY19" s="22">
-        <v>264459</v>
+        <v>264466</v>
       </c>
       <c r="AZ19" s="5">
         <f t="shared" si="19"/>
-        <v>0.85227426538359896</v>
+        <v>0.85229682434305087</v>
       </c>
       <c r="BA19" s="9">
         <v>280202</v>
@@ -3422,14 +3422,14 @@
       </c>
       <c r="BC19" s="4">
         <f t="shared" si="20"/>
-        <v>55896</v>
+        <v>55905</v>
       </c>
       <c r="BD19" s="8">
-        <v>272803</v>
+        <v>272812</v>
       </c>
       <c r="BE19" s="5">
         <f t="shared" si="21"/>
-        <v>0.97359405000678079</v>
+        <v>0.97362616969186511</v>
       </c>
       <c r="BF19" s="9">
         <v>473091</v>
@@ -3439,14 +3439,14 @@
       </c>
       <c r="BH19" s="4">
         <f t="shared" si="22"/>
-        <v>125818</v>
+        <v>125841</v>
       </c>
       <c r="BI19" s="8">
-        <v>463144</v>
+        <v>463167</v>
       </c>
       <c r="BJ19" s="5">
         <f t="shared" si="23"/>
-        <v>0.97897444677662437</v>
+        <v>0.97902306321616772</v>
       </c>
     </row>
     <row r="20" spans="1:62" x14ac:dyDescent="0.3">
@@ -3464,14 +3464,14 @@
       </c>
       <c r="E20" s="4">
         <f t="shared" si="0"/>
-        <v>1349</v>
+        <v>1351</v>
       </c>
       <c r="F20" s="22">
-        <v>5174</v>
+        <v>5176</v>
       </c>
       <c r="G20" s="5">
         <f t="shared" si="1"/>
-        <v>0.85719019218025183</v>
+        <v>0.85752153744201454</v>
       </c>
       <c r="H20" s="9">
         <v>6124</v>
@@ -3481,14 +3481,14 @@
       </c>
       <c r="J20" s="4">
         <f t="shared" si="2"/>
-        <v>1455</v>
+        <v>1457</v>
       </c>
       <c r="K20" s="22">
-        <v>5232</v>
+        <v>5234</v>
       </c>
       <c r="L20" s="5">
         <f t="shared" si="3"/>
-        <v>0.85434356629653818</v>
+        <v>0.8546701502286087</v>
       </c>
       <c r="M20" s="4">
         <v>9262</v>
@@ -3498,14 +3498,14 @@
       </c>
       <c r="O20" s="4">
         <f t="shared" si="4"/>
-        <v>1950</v>
+        <v>1953</v>
       </c>
       <c r="P20" s="8">
-        <v>8208</v>
+        <v>8211</v>
       </c>
       <c r="Q20" s="5">
         <f t="shared" si="5"/>
-        <v>0.88620168430144675</v>
+        <v>0.88652558842582596</v>
       </c>
       <c r="R20" s="9">
         <v>6202</v>
@@ -3515,14 +3515,14 @@
       </c>
       <c r="T20" s="4">
         <f t="shared" si="6"/>
-        <v>1440</v>
+        <v>1442</v>
       </c>
       <c r="U20" s="22">
-        <v>5285</v>
+        <v>5287</v>
       </c>
       <c r="V20" s="5">
         <f t="shared" si="7"/>
-        <v>0.85214446952595935</v>
+        <v>0.85246694614640439</v>
       </c>
       <c r="W20" s="9">
         <v>6226</v>
@@ -3532,14 +3532,14 @@
       </c>
       <c r="Y20" s="4">
         <f t="shared" si="8"/>
-        <v>1480</v>
+        <v>1482</v>
       </c>
       <c r="Z20" s="22">
-        <v>5371</v>
+        <v>5373</v>
       </c>
       <c r="AA20" s="5">
         <f t="shared" si="9"/>
-        <v>0.86267266302601997</v>
+        <v>0.86299389656280112</v>
       </c>
       <c r="AB20" s="9">
         <v>9386</v>
@@ -3549,14 +3549,14 @@
       </c>
       <c r="AD20" s="4">
         <f t="shared" si="10"/>
-        <v>2418</v>
+        <v>2421</v>
       </c>
       <c r="AE20" s="8">
-        <v>8433</v>
+        <v>8436</v>
       </c>
       <c r="AF20" s="5">
         <f t="shared" si="11"/>
-        <v>0.89846580012784993</v>
+        <v>0.89878542510121462</v>
       </c>
       <c r="AG20" s="9">
         <v>6315</v>
@@ -3566,14 +3566,14 @@
       </c>
       <c r="AI20" s="4">
         <f t="shared" si="12"/>
-        <v>1688</v>
+        <v>1690</v>
       </c>
       <c r="AJ20" s="22">
-        <v>5456</v>
+        <v>5458</v>
       </c>
       <c r="AK20" s="5">
         <f t="shared" si="13"/>
-        <v>0.86397466349960417</v>
+        <v>0.86429136975455267</v>
       </c>
       <c r="AL20" s="9">
         <v>6446</v>
@@ -3583,14 +3583,14 @@
       </c>
       <c r="AN20" s="4">
         <f t="shared" si="14"/>
-        <v>1576</v>
+        <v>1578</v>
       </c>
       <c r="AO20" s="22">
-        <v>5570</v>
+        <v>5572</v>
       </c>
       <c r="AP20" s="5">
         <f t="shared" si="15"/>
-        <v>0.86410176853862863</v>
+        <v>0.86441203847347192</v>
       </c>
       <c r="AQ20" s="15">
         <v>9604</v>
@@ -3600,14 +3600,14 @@
       </c>
       <c r="AS20" s="4">
         <f t="shared" si="16"/>
-        <v>2138</v>
+        <v>2142</v>
       </c>
       <c r="AT20" s="8">
-        <v>8614</v>
+        <v>8618</v>
       </c>
       <c r="AU20" s="5">
         <f t="shared" si="17"/>
-        <v>0.89691795085381087</v>
+        <v>0.89733444398167428</v>
       </c>
       <c r="AV20" s="9">
         <v>6642</v>
@@ -3617,14 +3617,14 @@
       </c>
       <c r="AX20" s="4">
         <f t="shared" si="18"/>
-        <v>1453</v>
+        <v>1455</v>
       </c>
       <c r="AY20" s="22">
-        <v>5617</v>
+        <v>5619</v>
       </c>
       <c r="AZ20" s="5">
         <f t="shared" si="19"/>
-        <v>0.84567901234567899</v>
+        <v>0.8459801264679313</v>
       </c>
       <c r="BA20" s="9">
         <v>5628</v>
@@ -3634,14 +3634,14 @@
       </c>
       <c r="BC20" s="4">
         <f t="shared" si="20"/>
-        <v>1461</v>
+        <v>1463</v>
       </c>
       <c r="BD20" s="8">
-        <v>5724</v>
+        <v>5726</v>
       </c>
       <c r="BE20" s="5">
         <f t="shared" si="21"/>
-        <v>1.0170575692963753</v>
+        <v>1.0174129353233832</v>
       </c>
       <c r="BF20" s="9">
         <v>8802</v>
@@ -3651,14 +3651,14 @@
       </c>
       <c r="BH20" s="4">
         <f t="shared" si="22"/>
-        <v>2687</v>
+        <v>2692</v>
       </c>
       <c r="BI20" s="8">
-        <v>8955</v>
+        <v>8960</v>
       </c>
       <c r="BJ20" s="5">
         <f t="shared" si="23"/>
-        <v>1.0173824130879345</v>
+        <v>1.0179504658032266</v>
       </c>
     </row>
     <row r="21" spans="1:62" x14ac:dyDescent="0.3">
@@ -3676,14 +3676,14 @@
       </c>
       <c r="E21" s="4">
         <f t="shared" si="0"/>
-        <v>3316</v>
+        <v>3320</v>
       </c>
       <c r="F21" s="22">
-        <v>8594</v>
+        <v>8598</v>
       </c>
       <c r="G21" s="5">
         <f t="shared" si="1"/>
-        <v>0.80945653197701795</v>
+        <v>0.8098332862390506</v>
       </c>
       <c r="H21" s="9">
         <v>10811</v>
@@ -3693,14 +3693,14 @@
       </c>
       <c r="J21" s="4">
         <f t="shared" si="2"/>
-        <v>3216</v>
+        <v>3220</v>
       </c>
       <c r="K21" s="22">
-        <v>8736</v>
+        <v>8740</v>
       </c>
       <c r="L21" s="5">
         <f t="shared" si="3"/>
-        <v>0.80806585884747018</v>
+        <v>0.80843585237258353</v>
       </c>
       <c r="M21" s="4">
         <v>14133</v>
@@ -3710,14 +3710,14 @@
       </c>
       <c r="O21" s="4">
         <f t="shared" si="4"/>
-        <v>3833</v>
+        <v>3837</v>
       </c>
       <c r="P21" s="8">
-        <v>11803</v>
+        <v>11807</v>
       </c>
       <c r="Q21" s="5">
         <f t="shared" si="5"/>
-        <v>0.83513762117031065</v>
+        <v>0.83542064671336591</v>
       </c>
       <c r="R21" s="9">
         <v>11019</v>
@@ -3727,14 +3727,14 @@
       </c>
       <c r="T21" s="4">
         <f t="shared" si="6"/>
-        <v>3077</v>
+        <v>3081</v>
       </c>
       <c r="U21" s="22">
-        <v>8890</v>
+        <v>8894</v>
       </c>
       <c r="V21" s="5">
         <f t="shared" si="7"/>
-        <v>0.80678827479807602</v>
+        <v>0.80715128414556669</v>
       </c>
       <c r="W21" s="9">
         <v>11175</v>
@@ -3744,14 +3744,14 @@
       </c>
       <c r="Y21" s="4">
         <f t="shared" si="8"/>
-        <v>3189</v>
+        <v>3193</v>
       </c>
       <c r="Z21" s="22">
-        <v>9088</v>
+        <v>9092</v>
       </c>
       <c r="AA21" s="5">
         <f t="shared" si="9"/>
-        <v>0.81324384787472037</v>
+        <v>0.8136017897091723</v>
       </c>
       <c r="AB21" s="9">
         <v>14571</v>
@@ -3761,14 +3761,14 @@
       </c>
       <c r="AD21" s="4">
         <f t="shared" si="10"/>
-        <v>4480</v>
+        <v>4484</v>
       </c>
       <c r="AE21" s="8">
-        <v>12214</v>
+        <v>12218</v>
       </c>
       <c r="AF21" s="5">
         <f t="shared" si="11"/>
-        <v>0.83824034040216866</v>
+        <v>0.83851485828014549</v>
       </c>
       <c r="AG21" s="9">
         <v>11345</v>
@@ -3778,14 +3778,14 @@
       </c>
       <c r="AI21" s="4">
         <f t="shared" si="12"/>
-        <v>3230</v>
+        <v>3234</v>
       </c>
       <c r="AJ21" s="22">
-        <v>9220</v>
+        <v>9224</v>
       </c>
       <c r="AK21" s="5">
         <f t="shared" si="13"/>
-        <v>0.81269281621859846</v>
+        <v>0.81304539444689294</v>
       </c>
       <c r="AL21" s="9">
         <v>11441</v>
@@ -3795,14 +3795,14 @@
       </c>
       <c r="AN21" s="4">
         <f t="shared" si="14"/>
-        <v>3094</v>
+        <v>3098</v>
       </c>
       <c r="AO21" s="22">
-        <v>9342</v>
+        <v>9346</v>
       </c>
       <c r="AP21" s="5">
         <f t="shared" si="15"/>
-        <v>0.81653701599510531</v>
+        <v>0.81688663578358534</v>
       </c>
       <c r="AQ21" s="15">
         <v>14790</v>
@@ -3812,14 +3812,14 @@
       </c>
       <c r="AS21" s="4">
         <f t="shared" si="16"/>
-        <v>4009</v>
+        <v>4015</v>
       </c>
       <c r="AT21" s="8">
-        <v>12494</v>
+        <v>12500</v>
       </c>
       <c r="AU21" s="5">
         <f t="shared" si="17"/>
-        <v>0.84475997295469907</v>
+        <v>0.84516565246788367</v>
       </c>
       <c r="AV21" s="9">
         <v>11740</v>
@@ -3829,14 +3829,14 @@
       </c>
       <c r="AX21" s="4">
         <f t="shared" si="18"/>
-        <v>3221</v>
+        <v>3225</v>
       </c>
       <c r="AY21" s="22">
-        <v>9481</v>
+        <v>9485</v>
       </c>
       <c r="AZ21" s="5">
         <f t="shared" si="19"/>
-        <v>0.80758091993185688</v>
+        <v>0.80792163543441231</v>
       </c>
       <c r="BA21" s="9">
         <v>9242</v>
@@ -3863,14 +3863,14 @@
       </c>
       <c r="BH21" s="4">
         <f t="shared" si="22"/>
-        <v>5678</v>
+        <v>5684</v>
       </c>
       <c r="BI21" s="8">
-        <v>12900</v>
+        <v>12906</v>
       </c>
       <c r="BJ21" s="5">
         <f t="shared" si="23"/>
-        <v>1.0283801020408163</v>
+        <v>1.028858418367347</v>
       </c>
     </row>
     <row r="22" spans="1:62" x14ac:dyDescent="0.3">
@@ -3888,14 +3888,14 @@
       </c>
       <c r="E22" s="4">
         <f t="shared" si="0"/>
-        <v>1580</v>
+        <v>1583</v>
       </c>
       <c r="F22" s="22">
-        <v>5596</v>
+        <v>5599</v>
       </c>
       <c r="G22" s="5">
         <f t="shared" si="1"/>
-        <v>0.91647559777268262</v>
+        <v>0.91696691778578443</v>
       </c>
       <c r="H22" s="9">
         <v>6184</v>
@@ -3905,14 +3905,14 @@
       </c>
       <c r="J22" s="4">
         <f t="shared" si="2"/>
-        <v>1611</v>
+        <v>1614</v>
       </c>
       <c r="K22" s="22">
-        <v>5665</v>
+        <v>5668</v>
       </c>
       <c r="L22" s="5">
         <f t="shared" si="3"/>
-        <v>0.91607373868046571</v>
+        <v>0.91655886157826649</v>
       </c>
       <c r="M22" s="4">
         <v>7446</v>
@@ -3922,14 +3922,14 @@
       </c>
       <c r="O22" s="4">
         <f t="shared" si="4"/>
-        <v>1912</v>
+        <v>1916</v>
       </c>
       <c r="P22" s="8">
-        <v>6873</v>
+        <v>6877</v>
       </c>
       <c r="Q22" s="5">
         <f t="shared" si="5"/>
-        <v>0.92304593070104757</v>
+        <v>0.9235831318828901</v>
       </c>
       <c r="R22" s="9">
         <v>6325</v>
@@ -3939,14 +3939,14 @@
       </c>
       <c r="T22" s="4">
         <f t="shared" si="6"/>
-        <v>1599</v>
+        <v>1603</v>
       </c>
       <c r="U22" s="22">
-        <v>5798</v>
+        <v>5802</v>
       </c>
       <c r="V22" s="5">
         <f t="shared" si="7"/>
-        <v>0.91667984189723317</v>
+        <v>0.91731225296442687</v>
       </c>
       <c r="W22" s="9">
         <v>6418</v>
@@ -3956,14 +3956,14 @@
       </c>
       <c r="Y22" s="4">
         <f t="shared" si="8"/>
-        <v>1576</v>
+        <v>1580</v>
       </c>
       <c r="Z22" s="22">
-        <v>5875</v>
+        <v>5879</v>
       </c>
       <c r="AA22" s="5">
         <f t="shared" si="9"/>
-        <v>0.91539420380180747</v>
+        <v>0.91601745091928954</v>
       </c>
       <c r="AB22" s="9">
         <v>7662</v>
@@ -3973,14 +3973,14 @@
       </c>
       <c r="AD22" s="4">
         <f t="shared" si="10"/>
-        <v>2089</v>
+        <v>2093</v>
       </c>
       <c r="AE22" s="8">
-        <v>7093</v>
+        <v>7097</v>
       </c>
       <c r="AF22" s="5">
         <f t="shared" si="11"/>
-        <v>0.92573740537718607</v>
+        <v>0.92625946228138867</v>
       </c>
       <c r="AG22" s="9">
         <v>6546</v>
@@ -3990,14 +3990,14 @@
       </c>
       <c r="AI22" s="4">
         <f t="shared" si="12"/>
-        <v>1766</v>
+        <v>1770</v>
       </c>
       <c r="AJ22" s="22">
-        <v>6006</v>
+        <v>6010</v>
       </c>
       <c r="AK22" s="5">
         <f t="shared" si="13"/>
-        <v>0.91750687442713108</v>
+        <v>0.91811793461655977</v>
       </c>
       <c r="AL22" s="9">
         <v>6648</v>
@@ -4007,14 +4007,14 @@
       </c>
       <c r="AN22" s="4">
         <f t="shared" si="14"/>
-        <v>1592</v>
+        <v>1598</v>
       </c>
       <c r="AO22" s="22">
-        <v>6065</v>
+        <v>6071</v>
       </c>
       <c r="AP22" s="5">
         <f t="shared" si="15"/>
-        <v>0.91230445246690739</v>
+        <v>0.91320697954271957</v>
       </c>
       <c r="AQ22" s="15">
         <v>7880</v>
@@ -4024,14 +4024,14 @@
       </c>
       <c r="AS22" s="4">
         <f t="shared" si="16"/>
-        <v>2017</v>
+        <v>2023</v>
       </c>
       <c r="AT22" s="8">
-        <v>7254</v>
+        <v>7260</v>
       </c>
       <c r="AU22" s="5">
         <f t="shared" si="17"/>
-        <v>0.92055837563451781</v>
+        <v>0.92131979695431476</v>
       </c>
       <c r="AV22" s="9">
         <v>6715</v>
@@ -4041,14 +4041,14 @@
       </c>
       <c r="AX22" s="4">
         <f t="shared" si="18"/>
-        <v>1669</v>
+        <v>1675</v>
       </c>
       <c r="AY22" s="22">
-        <v>6089</v>
+        <v>6095</v>
       </c>
       <c r="AZ22" s="5">
         <f t="shared" si="19"/>
-        <v>0.90677587490692479</v>
+        <v>0.90766939687267312</v>
       </c>
       <c r="BA22" s="9">
         <v>6117</v>
@@ -4058,14 +4058,14 @@
       </c>
       <c r="BC22" s="4">
         <f t="shared" si="20"/>
-        <v>1680</v>
+        <v>1685</v>
       </c>
       <c r="BD22" s="8">
-        <v>6138</v>
+        <v>6143</v>
       </c>
       <c r="BE22" s="5">
         <f t="shared" si="21"/>
-        <v>1.0034330554193231</v>
+        <v>1.004250449566781</v>
       </c>
       <c r="BF22" s="9">
         <v>7349</v>
@@ -4075,14 +4075,14 @@
       </c>
       <c r="BH22" s="4">
         <f t="shared" si="22"/>
-        <v>2550</v>
+        <v>2555</v>
       </c>
       <c r="BI22" s="8">
-        <v>7396</v>
+        <v>7401</v>
       </c>
       <c r="BJ22" s="5">
         <f t="shared" si="23"/>
-        <v>1.006395427949381</v>
+        <v>1.0070757926248468</v>
       </c>
     </row>
     <row r="23" spans="1:62" x14ac:dyDescent="0.3">
@@ -4100,14 +4100,14 @@
       </c>
       <c r="E23" s="4">
         <f t="shared" si="0"/>
-        <v>2765</v>
+        <v>2766</v>
       </c>
       <c r="F23" s="22">
-        <v>7706</v>
+        <v>7707</v>
       </c>
       <c r="G23" s="5">
         <f t="shared" si="1"/>
-        <v>0.85508211273857082</v>
+        <v>0.85519307589880156</v>
       </c>
       <c r="H23" s="9">
         <v>9118</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="J23" s="4">
         <f t="shared" si="2"/>
-        <v>2979</v>
+        <v>2980</v>
       </c>
       <c r="K23" s="22">
-        <v>7829</v>
+        <v>7830</v>
       </c>
       <c r="L23" s="5">
         <f t="shared" si="3"/>
-        <v>0.8586312787892082</v>
+        <v>0.85874095196314981</v>
       </c>
       <c r="M23" s="4">
         <v>11079</v>
@@ -4134,14 +4134,14 @@
       </c>
       <c r="O23" s="4">
         <f t="shared" si="4"/>
-        <v>3335</v>
+        <v>3336</v>
       </c>
       <c r="P23" s="8">
-        <v>9655</v>
+        <v>9656</v>
       </c>
       <c r="Q23" s="5">
         <f t="shared" si="5"/>
-        <v>0.87146854409242713</v>
+        <v>0.87155880494629479</v>
       </c>
       <c r="R23" s="9">
         <v>9156</v>
@@ -4151,14 +4151,14 @@
       </c>
       <c r="T23" s="4">
         <f t="shared" si="6"/>
-        <v>2804</v>
+        <v>2805</v>
       </c>
       <c r="U23" s="22">
-        <v>7939</v>
+        <v>7940</v>
       </c>
       <c r="V23" s="5">
         <f t="shared" si="7"/>
-        <v>0.86708169506334642</v>
+        <v>0.86719091306247265</v>
       </c>
       <c r="W23" s="9">
         <v>9166</v>
@@ -4168,14 +4168,14 @@
       </c>
       <c r="Y23" s="4">
         <f t="shared" si="8"/>
-        <v>3178</v>
+        <v>3180</v>
       </c>
       <c r="Z23" s="22">
-        <v>8110</v>
+        <v>8112</v>
       </c>
       <c r="AA23" s="5">
         <f t="shared" si="9"/>
-        <v>0.88479162120881516</v>
+        <v>0.88500981889591968</v>
       </c>
       <c r="AB23" s="9">
         <v>11322</v>
@@ -4185,14 +4185,14 @@
       </c>
       <c r="AD23" s="4">
         <f t="shared" si="10"/>
-        <v>3785</v>
+        <v>3787</v>
       </c>
       <c r="AE23" s="8">
-        <v>10051</v>
+        <v>10053</v>
       </c>
       <c r="AF23" s="5">
         <f t="shared" si="11"/>
-        <v>0.88774068185832888</v>
+        <v>0.88791732909379972</v>
       </c>
       <c r="AG23" s="9">
         <v>9569</v>
@@ -4202,14 +4202,14 @@
       </c>
       <c r="AI23" s="4">
         <f t="shared" si="12"/>
-        <v>3118</v>
+        <v>3120</v>
       </c>
       <c r="AJ23" s="22">
-        <v>8226</v>
+        <v>8228</v>
       </c>
       <c r="AK23" s="5">
         <f t="shared" si="13"/>
-        <v>0.85965095621277043</v>
+        <v>0.85985996446859647</v>
       </c>
       <c r="AL23" s="9">
         <v>9502</v>
@@ -4219,14 +4219,14 @@
       </c>
       <c r="AN23" s="4">
         <f t="shared" si="14"/>
-        <v>2849</v>
+        <v>2851</v>
       </c>
       <c r="AO23" s="22">
-        <v>8340</v>
+        <v>8342</v>
       </c>
       <c r="AP23" s="5">
         <f t="shared" si="15"/>
-        <v>0.8777099557987792</v>
+        <v>0.8779204378025679</v>
       </c>
       <c r="AQ23" s="15">
         <v>11767</v>
@@ -4236,14 +4236,14 @@
       </c>
       <c r="AS23" s="4">
         <f t="shared" si="16"/>
-        <v>3218</v>
+        <v>3220</v>
       </c>
       <c r="AT23" s="8">
-        <v>10344</v>
+        <v>10346</v>
       </c>
       <c r="AU23" s="5">
         <f t="shared" si="17"/>
-        <v>0.87906858162658286</v>
+        <v>0.87923854848304583</v>
       </c>
       <c r="AV23" s="9">
         <v>9805</v>
@@ -4253,14 +4253,14 @@
       </c>
       <c r="AX23" s="4">
         <f t="shared" si="18"/>
-        <v>2846</v>
+        <v>2848</v>
       </c>
       <c r="AY23" s="22">
-        <v>8434</v>
+        <v>8436</v>
       </c>
       <c r="AZ23" s="5">
         <f t="shared" si="19"/>
-        <v>0.86017338092809792</v>
+        <v>0.86037735849056607</v>
       </c>
       <c r="BA23" s="9">
         <v>8694</v>
@@ -4270,14 +4270,14 @@
       </c>
       <c r="BC23" s="4">
         <f t="shared" si="20"/>
-        <v>2851</v>
+        <v>2853</v>
       </c>
       <c r="BD23" s="8">
-        <v>8533</v>
+        <v>8535</v>
       </c>
       <c r="BE23" s="5">
         <f t="shared" si="21"/>
-        <v>0.98148148148148151</v>
+        <v>0.98171152518978611</v>
       </c>
       <c r="BF23" s="9">
         <v>11229</v>
@@ -4287,14 +4287,14 @@
       </c>
       <c r="BH23" s="4">
         <f t="shared" si="22"/>
-        <v>4616</v>
+        <v>4619</v>
       </c>
       <c r="BI23" s="8">
-        <v>10602</v>
+        <v>10605</v>
       </c>
       <c r="BJ23" s="5">
         <f t="shared" si="23"/>
-        <v>0.9441624365482234</v>
+        <v>0.94442960192359071</v>
       </c>
     </row>
     <row r="24" spans="1:62" x14ac:dyDescent="0.3">
@@ -4524,14 +4524,14 @@
       </c>
       <c r="E25" s="4">
         <f t="shared" si="0"/>
-        <v>3222</v>
+        <v>3223</v>
       </c>
       <c r="F25" s="22">
-        <v>17484</v>
+        <v>17485</v>
       </c>
       <c r="G25" s="5">
         <f t="shared" si="1"/>
-        <v>0.92132581546082104</v>
+        <v>0.9213785108288981</v>
       </c>
       <c r="H25" s="9">
         <v>19277</v>
@@ -4541,14 +4541,14 @@
       </c>
       <c r="J25" s="4">
         <f t="shared" si="2"/>
-        <v>3666</v>
+        <v>3667</v>
       </c>
       <c r="K25" s="22">
-        <v>17702</v>
+        <v>17703</v>
       </c>
       <c r="L25" s="5">
         <f t="shared" si="3"/>
-        <v>0.91829641541733675</v>
+        <v>0.91834829070913526</v>
       </c>
       <c r="M25" s="4">
         <v>26614</v>
@@ -4558,14 +4558,14 @@
       </c>
       <c r="O25" s="4">
         <f t="shared" si="4"/>
-        <v>4368</v>
+        <v>4372</v>
       </c>
       <c r="P25" s="8">
-        <v>24773</v>
+        <v>24777</v>
       </c>
       <c r="Q25" s="5">
         <f t="shared" si="5"/>
-        <v>0.93082588111520248</v>
+        <v>0.93097617795145415</v>
       </c>
       <c r="R25" s="9">
         <v>19402</v>
@@ -4575,14 +4575,14 @@
       </c>
       <c r="T25" s="4">
         <f t="shared" si="6"/>
-        <v>3188</v>
+        <v>3190</v>
       </c>
       <c r="U25" s="22">
-        <v>17848</v>
+        <v>17850</v>
       </c>
       <c r="V25" s="5">
         <f t="shared" si="7"/>
-        <v>0.91990516441603953</v>
+        <v>0.92000824657251834</v>
       </c>
       <c r="W25" s="9">
         <v>19474</v>
@@ -4592,14 +4592,14 @@
       </c>
       <c r="Y25" s="4">
         <f t="shared" si="8"/>
-        <v>3575</v>
+        <v>3577</v>
       </c>
       <c r="Z25" s="22">
-        <v>18046</v>
+        <v>18048</v>
       </c>
       <c r="AA25" s="5">
         <f t="shared" si="9"/>
-        <v>0.92667145938173978</v>
+        <v>0.92677416041902028</v>
       </c>
       <c r="AB25" s="9">
         <v>27081</v>
@@ -4609,14 +4609,14 @@
       </c>
       <c r="AD25" s="4">
         <f t="shared" si="10"/>
-        <v>5527</v>
+        <v>5531</v>
       </c>
       <c r="AE25" s="8">
-        <v>25179</v>
+        <v>25183</v>
       </c>
       <c r="AF25" s="5">
         <f t="shared" si="11"/>
-        <v>0.92976625678519997</v>
+        <v>0.92991396181824892</v>
       </c>
       <c r="AG25" s="9">
         <v>19543</v>
@@ -4626,14 +4626,14 @@
       </c>
       <c r="AI25" s="4">
         <f t="shared" si="12"/>
-        <v>3606</v>
+        <v>3608</v>
       </c>
       <c r="AJ25" s="22">
-        <v>18110</v>
+        <v>18112</v>
       </c>
       <c r="AK25" s="5">
         <f t="shared" si="13"/>
-        <v>0.92667451261321188</v>
+        <v>0.9267768510464105</v>
       </c>
       <c r="AL25" s="9">
         <v>19594</v>
@@ -4643,14 +4643,14 @@
       </c>
       <c r="AN25" s="4">
         <f t="shared" si="14"/>
-        <v>3307</v>
+        <v>3309</v>
       </c>
       <c r="AO25" s="22">
-        <v>18301</v>
+        <v>18303</v>
       </c>
       <c r="AP25" s="5">
         <f t="shared" si="15"/>
-        <v>0.93401041135041341</v>
+        <v>0.93411248341328978</v>
       </c>
       <c r="AQ25" s="15">
         <v>26830</v>
@@ -4660,14 +4660,14 @@
       </c>
       <c r="AS25" s="4">
         <f t="shared" si="16"/>
-        <v>4452</v>
+        <v>4457</v>
       </c>
       <c r="AT25" s="8">
-        <v>25418</v>
+        <v>25423</v>
       </c>
       <c r="AU25" s="5">
         <f t="shared" si="17"/>
-        <v>0.94737234439060758</v>
+        <v>0.9475587029444652</v>
       </c>
       <c r="AV25" s="9">
         <v>19719</v>
@@ -4677,14 +4677,14 @@
       </c>
       <c r="AX25" s="4">
         <f t="shared" si="18"/>
-        <v>3485</v>
+        <v>3488</v>
       </c>
       <c r="AY25" s="22">
-        <v>18385</v>
+        <v>18388</v>
       </c>
       <c r="AZ25" s="5">
         <f t="shared" si="19"/>
-        <v>0.93234951062427096</v>
+        <v>0.93250164815660019</v>
       </c>
       <c r="BA25" s="9">
         <v>18241</v>
@@ -4694,14 +4694,14 @@
       </c>
       <c r="BC25" s="4">
         <f t="shared" si="20"/>
-        <v>3477</v>
+        <v>3480</v>
       </c>
       <c r="BD25" s="8">
-        <v>18398</v>
+        <v>18401</v>
       </c>
       <c r="BE25" s="5">
         <f t="shared" si="21"/>
-        <v>1.0086069842662135</v>
+        <v>1.0087714489337207</v>
       </c>
       <c r="BF25" s="9">
         <v>25358</v>
@@ -4711,14 +4711,14 @@
       </c>
       <c r="BH25" s="4">
         <f t="shared" si="22"/>
-        <v>7378</v>
+        <v>7385</v>
       </c>
       <c r="BI25" s="8">
-        <v>25651</v>
+        <v>25658</v>
       </c>
       <c r="BJ25" s="5">
         <f t="shared" si="23"/>
-        <v>1.0115545390014986</v>
+        <v>1.0118305860083603</v>
       </c>
     </row>
     <row r="26" spans="1:62" x14ac:dyDescent="0.3">
@@ -4770,14 +4770,14 @@
       </c>
       <c r="O26" s="4">
         <f t="shared" si="4"/>
-        <v>5023</v>
+        <v>5024</v>
       </c>
       <c r="P26" s="8">
-        <v>24136</v>
+        <v>24137</v>
       </c>
       <c r="Q26" s="5">
         <f t="shared" si="5"/>
-        <v>0.87735368956742998</v>
+        <v>0.87739003998545984</v>
       </c>
       <c r="R26" s="9">
         <v>16566</v>
@@ -4821,14 +4821,14 @@
       </c>
       <c r="AD26" s="4">
         <f t="shared" si="10"/>
-        <v>5968</v>
+        <v>5969</v>
       </c>
       <c r="AE26" s="8">
-        <v>24941</v>
+        <v>24942</v>
       </c>
       <c r="AF26" s="5">
         <f t="shared" si="11"/>
-        <v>0.88317988668555236</v>
+        <v>0.88321529745042493</v>
       </c>
       <c r="AG26" s="9">
         <v>16538</v>
@@ -4872,14 +4872,14 @@
       </c>
       <c r="AS26" s="4">
         <f t="shared" si="16"/>
-        <v>5529</v>
+        <v>5531</v>
       </c>
       <c r="AT26" s="8">
-        <v>25073</v>
+        <v>25075</v>
       </c>
       <c r="AU26" s="5">
         <f t="shared" si="17"/>
-        <v>0.88266563402098153</v>
+        <v>0.8827360416813349</v>
       </c>
       <c r="AV26" s="9">
         <v>16717</v>
@@ -4889,14 +4889,14 @@
       </c>
       <c r="AX26" s="4">
         <f t="shared" si="18"/>
-        <v>3333</v>
+        <v>3334</v>
       </c>
       <c r="AY26" s="22">
-        <v>13304</v>
+        <v>13305</v>
       </c>
       <c r="AZ26" s="5">
         <f t="shared" si="19"/>
-        <v>0.7958365735478854</v>
+        <v>0.7958963928934617</v>
       </c>
       <c r="BA26" s="9">
         <v>13719</v>
@@ -4906,14 +4906,14 @@
       </c>
       <c r="BC26" s="4">
         <f t="shared" si="20"/>
-        <v>3274</v>
+        <v>3275</v>
       </c>
       <c r="BD26" s="8">
-        <v>13412</v>
+        <v>13413</v>
       </c>
       <c r="BE26" s="5">
         <f t="shared" si="21"/>
-        <v>0.97762227567606963</v>
+        <v>0.97769516728624539</v>
       </c>
       <c r="BF26" s="9">
         <v>25779</v>
@@ -4923,14 +4923,14 @@
       </c>
       <c r="BH26" s="4">
         <f t="shared" si="22"/>
-        <v>6613</v>
+        <v>6616</v>
       </c>
       <c r="BI26" s="8">
-        <v>25111</v>
+        <v>25114</v>
       </c>
       <c r="BJ26" s="5">
         <f t="shared" si="23"/>
-        <v>0.97408743550952326</v>
+        <v>0.97420380930214512</v>
       </c>
     </row>
     <row r="27" spans="1:62" x14ac:dyDescent="0.3">
@@ -4948,14 +4948,14 @@
       </c>
       <c r="E27" s="4">
         <f t="shared" si="0"/>
-        <v>32539</v>
+        <v>32552</v>
       </c>
       <c r="F27" s="22">
-        <v>112741</v>
+        <v>112754</v>
       </c>
       <c r="G27" s="5">
         <f t="shared" si="1"/>
-        <v>0.95135267412620461</v>
+        <v>0.95146237321317062</v>
       </c>
       <c r="H27" s="9">
         <v>121212</v>
@@ -4965,14 +4965,14 @@
       </c>
       <c r="J27" s="4">
         <f t="shared" si="2"/>
-        <v>34879</v>
+        <v>34892</v>
       </c>
       <c r="K27" s="22">
-        <v>114761</v>
+        <v>114774</v>
       </c>
       <c r="L27" s="5">
         <f t="shared" si="3"/>
-        <v>0.94677919677919675</v>
+        <v>0.94688644688644685</v>
       </c>
       <c r="M27" s="4">
         <v>178312</v>
@@ -4982,14 +4982,14 @@
       </c>
       <c r="O27" s="4">
         <f t="shared" si="4"/>
-        <v>46469</v>
+        <v>46487</v>
       </c>
       <c r="P27" s="8">
-        <v>168557</v>
+        <v>168575</v>
       </c>
       <c r="Q27" s="5">
         <f t="shared" si="5"/>
-        <v>0.9452925209744717</v>
+        <v>0.9453934676297725</v>
       </c>
       <c r="R27" s="9">
         <v>121489</v>
@@ -4999,14 +4999,14 @@
       </c>
       <c r="T27" s="4">
         <f t="shared" si="6"/>
-        <v>32047</v>
+        <v>32060</v>
       </c>
       <c r="U27" s="22">
-        <v>114981</v>
+        <v>114994</v>
       </c>
       <c r="V27" s="5">
         <f t="shared" si="7"/>
-        <v>0.9464313641564257</v>
+        <v>0.94653836972894667</v>
       </c>
       <c r="W27" s="9">
         <v>123451</v>
@@ -5016,14 +5016,14 @@
       </c>
       <c r="Y27" s="4">
         <f t="shared" si="8"/>
-        <v>35397</v>
+        <v>35411</v>
       </c>
       <c r="Z27" s="22">
-        <v>116882</v>
+        <v>116896</v>
       </c>
       <c r="AA27" s="5">
         <f t="shared" si="9"/>
-        <v>0.94678860438554568</v>
+        <v>0.94690200970425509</v>
       </c>
       <c r="AB27" s="9">
         <v>182601</v>
@@ -5033,14 +5033,14 @@
       </c>
       <c r="AD27" s="4">
         <f t="shared" si="10"/>
-        <v>53444</v>
+        <v>53462</v>
       </c>
       <c r="AE27" s="8">
-        <v>173141</v>
+        <v>173159</v>
       </c>
       <c r="AF27" s="5">
         <f t="shared" si="11"/>
-        <v>0.94819305480254767</v>
+        <v>0.94829163038537578</v>
       </c>
       <c r="AG27" s="9">
         <v>124689</v>
@@ -5050,14 +5050,14 @@
       </c>
       <c r="AI27" s="4">
         <f t="shared" si="12"/>
-        <v>33807</v>
+        <v>33822</v>
       </c>
       <c r="AJ27" s="22">
-        <v>117371</v>
+        <v>117386</v>
       </c>
       <c r="AK27" s="5">
         <f t="shared" si="13"/>
-        <v>0.94130997922832005</v>
+        <v>0.94143027853299011</v>
       </c>
       <c r="AL27" s="9">
         <v>127177</v>
@@ -5067,14 +5067,14 @@
       </c>
       <c r="AN27" s="4">
         <f t="shared" si="14"/>
-        <v>31097</v>
+        <v>31112</v>
       </c>
       <c r="AO27" s="22">
-        <v>119307</v>
+        <v>119322</v>
       </c>
       <c r="AP27" s="5">
         <f t="shared" si="15"/>
-        <v>0.93811774141550752</v>
+        <v>0.938235687270497</v>
       </c>
       <c r="AQ27" s="15">
         <v>185152</v>
@@ -5084,14 +5084,14 @@
       </c>
       <c r="AS27" s="4">
         <f t="shared" si="16"/>
-        <v>44003</v>
+        <v>44026</v>
       </c>
       <c r="AT27" s="8">
-        <v>176363</v>
+        <v>176386</v>
       </c>
       <c r="AU27" s="5">
         <f t="shared" si="17"/>
-        <v>0.95253089353612164</v>
+        <v>0.95265511579675077</v>
       </c>
       <c r="AV27" s="9">
         <v>127611</v>
@@ -5101,14 +5101,14 @@
       </c>
       <c r="AX27" s="4">
         <f t="shared" si="18"/>
-        <v>30383</v>
+        <v>30400</v>
       </c>
       <c r="AY27" s="22">
-        <v>119183</v>
+        <v>119200</v>
       </c>
       <c r="AZ27" s="5">
         <f t="shared" si="19"/>
-        <v>0.93395553674839948</v>
+        <v>0.93408875410427006</v>
       </c>
       <c r="BA27" s="9">
         <v>122070</v>
@@ -5118,14 +5118,14 @@
       </c>
       <c r="BC27" s="4">
         <f t="shared" si="20"/>
-        <v>31259</v>
+        <v>31278</v>
       </c>
       <c r="BD27" s="8">
-        <v>120850</v>
+        <v>120869</v>
       </c>
       <c r="BE27" s="5">
         <f t="shared" si="21"/>
-        <v>0.99000573441468009</v>
+        <v>0.99016138281314003</v>
       </c>
       <c r="BF27" s="9">
         <v>180737</v>
@@ -5135,14 +5135,14 @@
       </c>
       <c r="BH27" s="4">
         <f t="shared" si="22"/>
-        <v>65887</v>
+        <v>65920</v>
       </c>
       <c r="BI27" s="8">
-        <v>179290</v>
+        <v>179323</v>
       </c>
       <c r="BJ27" s="5">
         <f t="shared" si="23"/>
-        <v>0.99199389167685648</v>
+        <v>0.99217647742299586</v>
       </c>
     </row>
     <row r="28" spans="1:62" x14ac:dyDescent="0.3">
@@ -5160,14 +5160,14 @@
       </c>
       <c r="E28" s="4">
         <f t="shared" si="0"/>
-        <v>55190</v>
+        <v>55194</v>
       </c>
       <c r="F28" s="22">
-        <v>349845</v>
+        <v>349849</v>
       </c>
       <c r="G28" s="5">
         <f t="shared" si="1"/>
-        <v>0.96016302557909761</v>
+        <v>0.96017400373257222</v>
       </c>
       <c r="H28" s="9">
         <v>368904</v>
@@ -5177,14 +5177,14 @@
       </c>
       <c r="J28" s="4">
         <f t="shared" si="2"/>
-        <v>63520</v>
+        <v>63524</v>
       </c>
       <c r="K28" s="22">
-        <v>354981</v>
+        <v>354985</v>
       </c>
       <c r="L28" s="5">
         <f t="shared" si="3"/>
-        <v>0.9622584737492681</v>
+        <v>0.96226931667859383</v>
       </c>
       <c r="M28" s="4">
         <v>633580</v>
@@ -5194,14 +5194,14 @@
       </c>
       <c r="O28" s="4">
         <f t="shared" si="4"/>
-        <v>99949</v>
+        <v>99954</v>
       </c>
       <c r="P28" s="8">
-        <v>609208</v>
+        <v>609213</v>
       </c>
       <c r="Q28" s="5">
         <f t="shared" si="5"/>
-        <v>0.96153287666908682</v>
+        <v>0.96154076833233371</v>
       </c>
       <c r="R28" s="9">
         <v>370844</v>
@@ -5211,14 +5211,14 @@
       </c>
       <c r="T28" s="4">
         <f t="shared" si="6"/>
-        <v>61803</v>
+        <v>61807</v>
       </c>
       <c r="U28" s="22">
-        <v>357050</v>
+        <v>357054</v>
       </c>
       <c r="V28" s="5">
         <f t="shared" si="7"/>
-        <v>0.96280376654334432</v>
+        <v>0.96281455274994332</v>
       </c>
       <c r="W28" s="9">
         <v>375522</v>
@@ -5228,14 +5228,14 @@
       </c>
       <c r="Y28" s="4">
         <f t="shared" si="8"/>
-        <v>66526</v>
+        <v>66531</v>
       </c>
       <c r="Z28" s="22">
-        <v>361720</v>
+        <v>361725</v>
       </c>
       <c r="AA28" s="5">
         <f t="shared" si="9"/>
-        <v>0.96324582847343165</v>
+        <v>0.96325914327256457</v>
       </c>
       <c r="AB28" s="9">
         <v>643156</v>
@@ -5245,14 +5245,14 @@
       </c>
       <c r="AD28" s="4">
         <f t="shared" si="10"/>
-        <v>116191</v>
+        <v>116196</v>
       </c>
       <c r="AE28" s="8">
-        <v>620718</v>
+        <v>620723</v>
       </c>
       <c r="AF28" s="5">
         <f t="shared" si="11"/>
-        <v>0.96511266317969513</v>
+        <v>0.96512043734335062</v>
       </c>
       <c r="AG28" s="9">
         <v>378725</v>
@@ -5262,14 +5262,14 @@
       </c>
       <c r="AI28" s="4">
         <f t="shared" si="12"/>
-        <v>65127</v>
+        <v>65131</v>
       </c>
       <c r="AJ28" s="22">
-        <v>363071</v>
+        <v>363075</v>
       </c>
       <c r="AK28" s="5">
         <f t="shared" si="13"/>
-        <v>0.95866657865205629</v>
+        <v>0.95867714040530727</v>
       </c>
       <c r="AL28" s="9">
         <v>382864</v>
@@ -5279,14 +5279,14 @@
       </c>
       <c r="AN28" s="4">
         <f t="shared" si="14"/>
-        <v>58054</v>
+        <v>58059</v>
       </c>
       <c r="AO28" s="22">
-        <v>368524</v>
+        <v>368529</v>
       </c>
       <c r="AP28" s="5">
         <f t="shared" si="15"/>
-        <v>0.96254544694721889</v>
+        <v>0.96255850641481044</v>
       </c>
       <c r="AQ28" s="15">
         <v>653033</v>
@@ -5296,14 +5296,14 @@
       </c>
       <c r="AS28" s="4">
         <f t="shared" si="16"/>
-        <v>88390</v>
+        <v>88400</v>
       </c>
       <c r="AT28" s="8">
-        <v>628951</v>
+        <v>628961</v>
       </c>
       <c r="AU28" s="5">
         <f t="shared" si="17"/>
-        <v>0.9631228437154018</v>
+        <v>0.96313815687721749</v>
       </c>
       <c r="AV28" s="9">
         <v>393378</v>
@@ -5313,14 +5313,14 @@
       </c>
       <c r="AX28" s="4">
         <f t="shared" si="18"/>
-        <v>54863</v>
+        <v>54870</v>
       </c>
       <c r="AY28" s="22">
-        <v>371527</v>
+        <v>371534</v>
       </c>
       <c r="AZ28" s="5">
         <f t="shared" si="19"/>
-        <v>0.94445291805845777</v>
+        <v>0.94447071264788574</v>
       </c>
       <c r="BA28" s="9">
         <v>381893</v>
@@ -5330,14 +5330,14 @@
       </c>
       <c r="BC28" s="4">
         <f t="shared" si="20"/>
-        <v>57989</v>
+        <v>57996</v>
       </c>
       <c r="BD28" s="8">
-        <v>376646</v>
+        <v>376653</v>
       </c>
       <c r="BE28" s="5">
         <f t="shared" si="21"/>
-        <v>0.98626054942091113</v>
+        <v>0.98627887916248791</v>
       </c>
       <c r="BF28" s="9">
         <v>643514</v>
@@ -5347,14 +5347,14 @@
       </c>
       <c r="BH28" s="4">
         <f t="shared" si="22"/>
-        <v>133737</v>
+        <v>133751</v>
       </c>
       <c r="BI28" s="8">
-        <v>639612</v>
+        <v>639626</v>
       </c>
       <c r="BJ28" s="5">
         <f t="shared" si="23"/>
-        <v>0.99393641785571096</v>
+        <v>0.99395817340415282</v>
       </c>
     </row>
     <row r="29" spans="1:62" x14ac:dyDescent="0.3">
@@ -5406,14 +5406,14 @@
       </c>
       <c r="O29" s="4">
         <f t="shared" si="4"/>
-        <v>30925</v>
+        <v>30926</v>
       </c>
       <c r="P29" s="8">
-        <v>162689</v>
+        <v>162690</v>
       </c>
       <c r="Q29" s="5">
         <f t="shared" si="5"/>
-        <v>0.96324387052463922</v>
+        <v>0.96324979129291821</v>
       </c>
       <c r="R29" s="9">
         <v>122532</v>
@@ -5457,14 +5457,14 @@
       </c>
       <c r="AD29" s="4">
         <f t="shared" si="10"/>
-        <v>37470</v>
+        <v>37472</v>
       </c>
       <c r="AE29" s="8">
-        <v>166134</v>
+        <v>166136</v>
       </c>
       <c r="AF29" s="5">
         <f t="shared" si="11"/>
-        <v>0.96213073265652416</v>
+        <v>0.96214231524326332</v>
       </c>
       <c r="AG29" s="9">
         <v>125793</v>
@@ -5474,14 +5474,14 @@
       </c>
       <c r="AI29" s="4">
         <f t="shared" si="12"/>
-        <v>24705</v>
+        <v>24706</v>
       </c>
       <c r="AJ29" s="22">
-        <v>120784</v>
+        <v>120785</v>
       </c>
       <c r="AK29" s="5">
         <f t="shared" si="13"/>
-        <v>0.96018061418361911</v>
+        <v>0.96018856375156014</v>
       </c>
       <c r="AL29" s="9">
         <v>126934</v>
@@ -5491,14 +5491,14 @@
       </c>
       <c r="AN29" s="4">
         <f t="shared" si="14"/>
-        <v>21695</v>
+        <v>21696</v>
       </c>
       <c r="AO29" s="22">
-        <v>122155</v>
+        <v>122156</v>
       </c>
       <c r="AP29" s="5">
         <f t="shared" si="15"/>
-        <v>0.96235051286495343</v>
+        <v>0.96235839097483733</v>
       </c>
       <c r="AQ29" s="15">
         <v>175834</v>
@@ -5508,14 +5508,14 @@
       </c>
       <c r="AS29" s="4">
         <f t="shared" si="16"/>
-        <v>28293</v>
+        <v>28295</v>
       </c>
       <c r="AT29" s="8">
-        <v>169049</v>
+        <v>169051</v>
       </c>
       <c r="AU29" s="5">
         <f t="shared" si="17"/>
-        <v>0.96141246857831819</v>
+        <v>0.96142384294277561</v>
       </c>
       <c r="AV29" s="9">
         <v>130198</v>
@@ -5525,14 +5525,14 @@
       </c>
       <c r="AX29" s="4">
         <f t="shared" si="18"/>
-        <v>22058</v>
+        <v>22059</v>
       </c>
       <c r="AY29" s="22">
-        <v>123785</v>
+        <v>123786</v>
       </c>
       <c r="AZ29" s="5">
         <f t="shared" si="19"/>
-        <v>0.95074425106376437</v>
+        <v>0.95075193167329763</v>
       </c>
       <c r="BA29" s="9">
         <v>127545</v>
@@ -5542,14 +5542,14 @@
       </c>
       <c r="BC29" s="4">
         <f t="shared" si="20"/>
-        <v>22788</v>
+        <v>22789</v>
       </c>
       <c r="BD29" s="8">
-        <v>125575</v>
+        <v>125576</v>
       </c>
       <c r="BE29" s="5">
         <f t="shared" si="21"/>
-        <v>0.98455447097102988</v>
+        <v>0.98456231134109529</v>
       </c>
       <c r="BF29" s="9">
         <v>174166</v>
@@ -5559,14 +5559,14 @@
       </c>
       <c r="BH29" s="4">
         <f t="shared" si="22"/>
-        <v>42581</v>
+        <v>42586</v>
       </c>
       <c r="BI29" s="8">
-        <v>172587</v>
+        <v>172592</v>
       </c>
       <c r="BJ29" s="5">
         <f t="shared" si="23"/>
-        <v>0.99093393658923101</v>
+        <v>0.99096264483309027</v>
       </c>
     </row>
     <row r="30" spans="1:62" x14ac:dyDescent="0.3">
@@ -5584,14 +5584,14 @@
       </c>
       <c r="E30" s="4">
         <f t="shared" si="0"/>
-        <v>33465</v>
+        <v>33471</v>
       </c>
       <c r="F30" s="22">
-        <v>151934</v>
+        <v>151940</v>
       </c>
       <c r="G30" s="5">
         <f t="shared" si="1"/>
-        <v>0.95781271670470158</v>
+        <v>0.95785054152534899</v>
       </c>
       <c r="H30" s="9">
         <v>160653</v>
@@ -5601,14 +5601,14 @@
       </c>
       <c r="J30" s="4">
         <f t="shared" si="2"/>
-        <v>39616</v>
+        <v>39622</v>
       </c>
       <c r="K30" s="22">
-        <v>155054</v>
+        <v>155060</v>
       </c>
       <c r="L30" s="5">
         <f t="shared" si="3"/>
-        <v>0.96514848773443385</v>
+        <v>0.96518583530964253</v>
       </c>
       <c r="M30" s="4">
         <v>275749</v>
@@ -5618,14 +5618,14 @@
       </c>
       <c r="O30" s="4">
         <f t="shared" si="4"/>
-        <v>59330</v>
+        <v>59342</v>
       </c>
       <c r="P30" s="8">
-        <v>264929</v>
+        <v>264941</v>
       </c>
       <c r="Q30" s="5">
         <f t="shared" si="5"/>
-        <v>0.96076141708582807</v>
+        <v>0.96080493492270147</v>
       </c>
       <c r="R30" s="9">
         <v>161454</v>
@@ -5635,14 +5635,14 @@
       </c>
       <c r="T30" s="4">
         <f t="shared" si="6"/>
-        <v>35697</v>
+        <v>35705</v>
       </c>
       <c r="U30" s="22">
-        <v>154870</v>
+        <v>154878</v>
       </c>
       <c r="V30" s="5">
         <f t="shared" si="7"/>
-        <v>0.95922058295241985</v>
+        <v>0.95927013266936711</v>
       </c>
       <c r="W30" s="9">
         <v>163696</v>
@@ -5652,14 +5652,14 @@
       </c>
       <c r="Y30" s="4">
         <f t="shared" si="8"/>
-        <v>38329</v>
+        <v>38336</v>
       </c>
       <c r="Z30" s="22">
-        <v>157855</v>
+        <v>157862</v>
       </c>
       <c r="AA30" s="5">
         <f t="shared" si="9"/>
-        <v>0.96431800410517055</v>
+        <v>0.96436076629850453</v>
       </c>
       <c r="AB30" s="9">
         <v>281667</v>
@@ -5669,14 +5669,14 @@
       </c>
       <c r="AD30" s="4">
         <f t="shared" si="10"/>
-        <v>68176</v>
+        <v>68188</v>
       </c>
       <c r="AE30" s="8">
-        <v>270975</v>
+        <v>270987</v>
       </c>
       <c r="AF30" s="5">
         <f t="shared" si="11"/>
-        <v>0.96204028160913424</v>
+        <v>0.96208288510901174</v>
       </c>
       <c r="AG30" s="9">
         <v>165324</v>
@@ -5686,14 +5686,14 @@
       </c>
       <c r="AI30" s="4">
         <f t="shared" si="12"/>
-        <v>38745</v>
+        <v>38752</v>
       </c>
       <c r="AJ30" s="22">
-        <v>158457</v>
+        <v>158464</v>
       </c>
       <c r="AK30" s="5">
         <f t="shared" si="13"/>
-        <v>0.95846338099731432</v>
+        <v>0.95850572209721518</v>
       </c>
       <c r="AL30" s="9">
         <v>168552</v>
@@ -5703,14 +5703,14 @@
       </c>
       <c r="AN30" s="4">
         <f t="shared" si="14"/>
-        <v>34428</v>
+        <v>34436</v>
       </c>
       <c r="AO30" s="22">
-        <v>161920</v>
+        <v>161928</v>
       </c>
       <c r="AP30" s="5">
         <f t="shared" si="15"/>
-        <v>0.96065309222079831</v>
+        <v>0.96070055531824006</v>
       </c>
       <c r="AQ30" s="15">
         <v>288456</v>
@@ -5720,14 +5720,14 @@
       </c>
       <c r="AS30" s="4">
         <f t="shared" si="16"/>
-        <v>55831</v>
+        <v>55844</v>
       </c>
       <c r="AT30" s="8">
-        <v>277204</v>
+        <v>277217</v>
       </c>
       <c r="AU30" s="5">
         <f t="shared" si="17"/>
-        <v>0.96099231771916682</v>
+        <v>0.96103738525113014</v>
       </c>
       <c r="AV30" s="9">
         <v>173481</v>
@@ -5737,14 +5737,14 @@
       </c>
       <c r="AX30" s="4">
         <f t="shared" si="18"/>
-        <v>35281</v>
+        <v>35289</v>
       </c>
       <c r="AY30" s="22">
-        <v>162963</v>
+        <v>162971</v>
       </c>
       <c r="AZ30" s="5">
         <f t="shared" si="19"/>
-        <v>0.93937088211389141</v>
+        <v>0.93941699667398737</v>
       </c>
       <c r="BA30" s="9">
         <v>168414</v>
@@ -5754,14 +5754,14 @@
       </c>
       <c r="BC30" s="4">
         <f t="shared" si="20"/>
-        <v>35310</v>
+        <v>35318</v>
       </c>
       <c r="BD30" s="8">
-        <v>165830</v>
+        <v>165838</v>
       </c>
       <c r="BE30" s="5">
         <f t="shared" si="21"/>
-        <v>0.98465685750590803</v>
+        <v>0.98470435949505386</v>
       </c>
       <c r="BF30" s="9">
         <v>284492</v>
@@ -5771,14 +5771,14 @@
       </c>
       <c r="BH30" s="4">
         <f t="shared" si="22"/>
-        <v>78341</v>
+        <v>78359</v>
       </c>
       <c r="BI30" s="8">
-        <v>283021</v>
+        <v>283039</v>
       </c>
       <c r="BJ30" s="5">
         <f t="shared" si="23"/>
-        <v>0.99482938008801658</v>
+        <v>0.99489265075995104</v>
       </c>
     </row>
     <row r="31" spans="1:62" x14ac:dyDescent="0.3">
@@ -5796,14 +5796,14 @@
       </c>
       <c r="E31" s="4">
         <f t="shared" si="0"/>
-        <v>20666</v>
+        <v>20669</v>
       </c>
       <c r="F31" s="22">
-        <v>71426</v>
+        <v>71429</v>
       </c>
       <c r="G31" s="5">
         <f t="shared" si="1"/>
-        <v>0.96067249495628781</v>
+        <v>0.96071284465366513</v>
       </c>
       <c r="H31" s="9">
         <v>75353</v>
@@ -5813,14 +5813,14 @@
       </c>
       <c r="J31" s="4">
         <f t="shared" si="2"/>
-        <v>22529</v>
+        <v>22532</v>
       </c>
       <c r="K31" s="22">
-        <v>72499</v>
+        <v>72502</v>
       </c>
       <c r="L31" s="5">
         <f t="shared" si="3"/>
-        <v>0.96212493198678217</v>
+        <v>0.96216474460207291</v>
       </c>
       <c r="M31" s="4">
         <v>132153</v>
@@ -5830,14 +5830,14 @@
       </c>
       <c r="O31" s="4">
         <f t="shared" si="4"/>
-        <v>36841</v>
+        <v>36844</v>
       </c>
       <c r="P31" s="8">
-        <v>126925</v>
+        <v>126928</v>
       </c>
       <c r="Q31" s="5">
         <f t="shared" si="5"/>
-        <v>0.96043979326992202</v>
+        <v>0.9604624942301726</v>
       </c>
       <c r="R31" s="9">
         <v>74474</v>
@@ -5847,14 +5847,14 @@
       </c>
       <c r="T31" s="4">
         <f t="shared" si="6"/>
-        <v>20038</v>
+        <v>20041</v>
       </c>
       <c r="U31" s="22">
-        <v>71224</v>
+        <v>71227</v>
       </c>
       <c r="V31" s="5">
         <f t="shared" si="7"/>
-        <v>0.95636060907162235</v>
+        <v>0.95640089158632546</v>
       </c>
       <c r="W31" s="9">
         <v>75697</v>
@@ -5864,14 +5864,14 @@
       </c>
       <c r="Y31" s="4">
         <f t="shared" si="8"/>
-        <v>22603</v>
+        <v>22606</v>
       </c>
       <c r="Z31" s="22">
-        <v>72496</v>
+        <v>72499</v>
       </c>
       <c r="AA31" s="5">
         <f t="shared" si="9"/>
-        <v>0.95771298730464882</v>
+        <v>0.95775261899414776</v>
       </c>
       <c r="AB31" s="9">
         <v>133809</v>
@@ -5881,14 +5881,14 @@
       </c>
       <c r="AD31" s="4">
         <f t="shared" si="10"/>
-        <v>38780</v>
+        <v>38783</v>
       </c>
       <c r="AE31" s="8">
-        <v>129171</v>
+        <v>129174</v>
       </c>
       <c r="AF31" s="5">
         <f t="shared" si="11"/>
-        <v>0.96533865435060418</v>
+        <v>0.96536107436719498</v>
       </c>
       <c r="AG31" s="9">
         <v>75434</v>
@@ -5898,14 +5898,14 @@
       </c>
       <c r="AI31" s="4">
         <f t="shared" si="12"/>
-        <v>21523</v>
+        <v>21526</v>
       </c>
       <c r="AJ31" s="22">
-        <v>72289</v>
+        <v>72292</v>
       </c>
       <c r="AK31" s="5">
         <f t="shared" si="13"/>
-        <v>0.95830792480844185</v>
+        <v>0.95834769467348946</v>
       </c>
       <c r="AL31" s="9">
         <v>76990</v>
@@ -5915,14 +5915,14 @@
       </c>
       <c r="AN31" s="4">
         <f t="shared" si="14"/>
-        <v>18792</v>
+        <v>18796</v>
       </c>
       <c r="AO31" s="22">
-        <v>73391</v>
+        <v>73395</v>
       </c>
       <c r="AP31" s="5">
         <f t="shared" si="15"/>
-        <v>0.95325366930770228</v>
+        <v>0.95330562410702691</v>
       </c>
       <c r="AQ31" s="15">
         <v>135546</v>
@@ -5932,14 +5932,14 @@
       </c>
       <c r="AS31" s="4">
         <f t="shared" si="16"/>
-        <v>32606</v>
+        <v>32611</v>
       </c>
       <c r="AT31" s="8">
-        <v>131023</v>
+        <v>131028</v>
       </c>
       <c r="AU31" s="5">
         <f t="shared" si="17"/>
-        <v>0.96663125433432195</v>
+        <v>0.96666814218051433</v>
       </c>
       <c r="AV31" s="9">
         <v>78435</v>
@@ -5949,14 +5949,14 @@
       </c>
       <c r="AX31" s="4">
         <f t="shared" si="18"/>
-        <v>18412</v>
+        <v>18416</v>
       </c>
       <c r="AY31" s="22">
-        <v>73381</v>
+        <v>73385</v>
       </c>
       <c r="AZ31" s="5">
         <f t="shared" si="19"/>
-        <v>0.93556448014279336</v>
+        <v>0.93561547778415244</v>
       </c>
       <c r="BA31" s="9">
         <v>76166</v>
@@ -5966,14 +5966,14 @@
       </c>
       <c r="BC31" s="4">
         <f t="shared" si="20"/>
-        <v>19437</v>
+        <v>19440</v>
       </c>
       <c r="BD31" s="8">
-        <v>74500</v>
+        <v>74503</v>
       </c>
       <c r="BE31" s="5">
         <f t="shared" si="21"/>
-        <v>0.97812672320983118</v>
+        <v>0.97816611086311478</v>
       </c>
       <c r="BF31" s="9">
         <v>132970</v>
@@ -5983,14 +5983,14 @@
       </c>
       <c r="BH31" s="4">
         <f t="shared" si="22"/>
-        <v>49518</v>
+        <v>49524</v>
       </c>
       <c r="BI31" s="8">
-        <v>132940</v>
+        <v>132946</v>
       </c>
       <c r="BJ31" s="5">
         <f t="shared" si="23"/>
-        <v>0.9997743851996691</v>
+        <v>0.9998195081597353</v>
       </c>
     </row>
     <row r="32" spans="1:62" x14ac:dyDescent="0.3">
@@ -6008,14 +6008,14 @@
       </c>
       <c r="E32" s="4">
         <f t="shared" si="0"/>
-        <v>38780</v>
+        <v>38781</v>
       </c>
       <c r="F32" s="22">
-        <v>188994</v>
+        <v>188995</v>
       </c>
       <c r="G32" s="5">
         <f t="shared" si="1"/>
-        <v>0.98435400368753845</v>
+        <v>0.98435921207512578</v>
       </c>
       <c r="H32" s="9">
         <v>196288</v>
@@ -6025,14 +6025,14 @@
       </c>
       <c r="J32" s="4">
         <f t="shared" si="2"/>
-        <v>46871</v>
+        <v>46872</v>
       </c>
       <c r="K32" s="22">
-        <v>192871</v>
+        <v>192872</v>
       </c>
       <c r="L32" s="5">
         <f t="shared" si="3"/>
-        <v>0.98259190577111188</v>
+        <v>0.98259700032605146</v>
       </c>
       <c r="M32" s="4">
         <v>418497</v>
@@ -6042,14 +6042,14 @@
       </c>
       <c r="O32" s="4">
         <f t="shared" si="4"/>
-        <v>94437</v>
+        <v>94440</v>
       </c>
       <c r="P32" s="8">
-        <v>409067</v>
+        <v>409070</v>
       </c>
       <c r="Q32" s="5">
         <f t="shared" si="5"/>
-        <v>0.97746698303691548</v>
+        <v>0.97747415154708395</v>
       </c>
       <c r="R32" s="9">
         <v>194320</v>
@@ -6059,14 +6059,14 @@
       </c>
       <c r="T32" s="4">
         <f t="shared" si="6"/>
-        <v>42837</v>
+        <v>42838</v>
       </c>
       <c r="U32" s="22">
-        <v>190343</v>
+        <v>190344</v>
       </c>
       <c r="V32" s="5">
         <f t="shared" si="7"/>
-        <v>0.97953375874845616</v>
+        <v>0.97953890489913542</v>
       </c>
       <c r="W32" s="9">
         <v>198209</v>
@@ -6076,14 +6076,14 @@
       </c>
       <c r="Y32" s="4">
         <f t="shared" si="8"/>
-        <v>47428</v>
+        <v>47430</v>
       </c>
       <c r="Z32" s="22">
-        <v>194351</v>
+        <v>194353</v>
       </c>
       <c r="AA32" s="5">
         <f t="shared" si="9"/>
-        <v>0.98053569716814071</v>
+        <v>0.98054578752730703</v>
       </c>
       <c r="AB32" s="9">
         <v>426405</v>
@@ -6093,14 +6093,14 @@
       </c>
       <c r="AD32" s="4">
         <f t="shared" si="10"/>
-        <v>98659</v>
+        <v>98664</v>
       </c>
       <c r="AE32" s="8">
-        <v>418373</v>
+        <v>418378</v>
       </c>
       <c r="AF32" s="5">
         <f t="shared" si="11"/>
-        <v>0.98116344789577981</v>
+        <v>0.98117517383707975</v>
       </c>
       <c r="AG32" s="9">
         <v>199136</v>
@@ -6110,14 +6110,14 @@
       </c>
       <c r="AI32" s="4">
         <f t="shared" si="12"/>
-        <v>44762</v>
+        <v>44765</v>
       </c>
       <c r="AJ32" s="22">
-        <v>195375</v>
+        <v>195378</v>
       </c>
       <c r="AK32" s="5">
         <f t="shared" si="13"/>
-        <v>0.98111340993090146</v>
+        <v>0.98112847501205203</v>
       </c>
       <c r="AL32" s="9">
         <v>204506</v>
@@ -6127,14 +6127,14 @@
       </c>
       <c r="AN32" s="4">
         <f t="shared" si="14"/>
-        <v>38338</v>
+        <v>38340</v>
       </c>
       <c r="AO32" s="22">
-        <v>199943</v>
+        <v>199945</v>
       </c>
       <c r="AP32" s="5">
         <f t="shared" si="15"/>
-        <v>0.97768769620451235</v>
+        <v>0.97769747586867872</v>
       </c>
       <c r="AQ32" s="15">
         <v>435626</v>
@@ -6144,14 +6144,14 @@
       </c>
       <c r="AS32" s="4">
         <f t="shared" si="16"/>
-        <v>82512</v>
+        <v>82517</v>
       </c>
       <c r="AT32" s="8">
-        <v>426558</v>
+        <v>426563</v>
       </c>
       <c r="AU32" s="5">
         <f t="shared" si="17"/>
-        <v>0.97918397891769549</v>
+        <v>0.97919545665318419</v>
       </c>
       <c r="AV32" s="9">
         <v>208760</v>
@@ -6161,14 +6161,14 @@
       </c>
       <c r="AX32" s="4">
         <f t="shared" si="18"/>
-        <v>38562</v>
+        <v>38565</v>
       </c>
       <c r="AY32" s="22">
-        <v>199576</v>
+        <v>199579</v>
       </c>
       <c r="AZ32" s="5">
         <f t="shared" si="19"/>
-        <v>0.95600689787315574</v>
+        <v>0.95602126844223034</v>
       </c>
       <c r="BA32" s="9">
         <v>206539</v>
@@ -6178,14 +6178,14 @@
       </c>
       <c r="BC32" s="4">
         <f t="shared" si="20"/>
-        <v>40472</v>
+        <v>40475</v>
       </c>
       <c r="BD32" s="8">
-        <v>203793</v>
+        <v>203796</v>
       </c>
       <c r="BE32" s="5">
         <f t="shared" si="21"/>
-        <v>0.98670469015537021</v>
+        <v>0.98671921525716688</v>
       </c>
       <c r="BF32" s="9">
         <v>435831</v>
@@ -6195,14 +6195,14 @@
       </c>
       <c r="BH32" s="4">
         <f t="shared" si="22"/>
-        <v>128630</v>
+        <v>128638</v>
       </c>
       <c r="BI32" s="8">
-        <v>435162</v>
+        <v>435170</v>
       </c>
       <c r="BJ32" s="5">
         <f t="shared" si="23"/>
-        <v>0.99846500134226335</v>
+        <v>0.99848335708107039</v>
       </c>
     </row>
     <row r="33" spans="1:62" x14ac:dyDescent="0.3">
@@ -6220,14 +6220,14 @@
       </c>
       <c r="E33" s="4">
         <f t="shared" si="0"/>
-        <v>71712</v>
+        <v>71715</v>
       </c>
       <c r="F33" s="22">
-        <v>581080</v>
+        <v>581083</v>
       </c>
       <c r="G33" s="5">
         <f t="shared" si="1"/>
-        <v>0.99074691350657362</v>
+        <v>0.99075202853503874</v>
       </c>
       <c r="H33" s="9">
         <v>594451</v>
@@ -6237,14 +6237,14 @@
       </c>
       <c r="J33" s="4">
         <f t="shared" si="2"/>
-        <v>83844</v>
+        <v>83846</v>
       </c>
       <c r="K33" s="22">
-        <v>590877</v>
+        <v>590879</v>
       </c>
       <c r="L33" s="5">
         <f t="shared" si="3"/>
-        <v>0.99398772985494177</v>
+        <v>0.99399109430381982</v>
       </c>
       <c r="M33" s="4">
         <v>1006436</v>
@@ -6254,14 +6254,14 @@
       </c>
       <c r="O33" s="4">
         <f t="shared" si="4"/>
-        <v>139349</v>
+        <v>139355</v>
       </c>
       <c r="P33" s="8">
-        <v>991598</v>
+        <v>991604</v>
       </c>
       <c r="Q33" s="5">
         <f t="shared" si="5"/>
-        <v>0.98525688667734457</v>
+        <v>0.98526284830828781</v>
       </c>
       <c r="R33" s="9">
         <v>599279</v>
@@ -6271,14 +6271,14 @@
       </c>
       <c r="T33" s="4">
         <f t="shared" si="6"/>
-        <v>86660</v>
+        <v>86663</v>
       </c>
       <c r="U33" s="22">
-        <v>593524</v>
+        <v>593527</v>
       </c>
       <c r="V33" s="5">
         <f t="shared" si="7"/>
-        <v>0.99039679348016529</v>
+        <v>0.99040179949572738</v>
       </c>
       <c r="W33" s="9">
         <v>608923</v>
@@ -6288,14 +6288,14 @@
       </c>
       <c r="Y33" s="4">
         <f t="shared" si="8"/>
-        <v>85225</v>
+        <v>85229</v>
       </c>
       <c r="Z33" s="22">
-        <v>601213</v>
+        <v>601217</v>
       </c>
       <c r="AA33" s="5">
         <f t="shared" si="9"/>
-        <v>0.98733830057330729</v>
+        <v>0.98734486954836653</v>
       </c>
       <c r="AB33" s="9">
         <v>1019860</v>
@@ -6305,14 +6305,14 @@
       </c>
       <c r="AD33" s="4">
         <f t="shared" si="10"/>
-        <v>135709</v>
+        <v>135719</v>
       </c>
       <c r="AE33" s="8">
-        <v>1006170</v>
+        <v>1006180</v>
       </c>
       <c r="AF33" s="5">
         <f t="shared" si="11"/>
-        <v>0.98657658894358047</v>
+        <v>0.98658639421097016</v>
       </c>
       <c r="AG33" s="9">
         <v>610453</v>
@@ -6322,14 +6322,14 @@
       </c>
       <c r="AI33" s="4">
         <f t="shared" si="12"/>
-        <v>86826</v>
+        <v>86831</v>
       </c>
       <c r="AJ33" s="22">
-        <v>602917</v>
+        <v>602922</v>
       </c>
       <c r="AK33" s="5">
         <f t="shared" si="13"/>
-        <v>0.98765506926823199</v>
+        <v>0.98766325990698711</v>
       </c>
       <c r="AL33" s="9">
         <v>617988</v>
@@ -6339,14 +6339,14 @@
       </c>
       <c r="AN33" s="4">
         <f t="shared" si="14"/>
-        <v>70934</v>
+        <v>70939</v>
       </c>
       <c r="AO33" s="22">
-        <v>608860</v>
+        <v>608865</v>
       </c>
       <c r="AP33" s="5">
         <f t="shared" si="15"/>
-        <v>0.98522948665669885</v>
+        <v>0.98523757742868789</v>
       </c>
       <c r="AQ33" s="15">
         <v>1027609</v>
@@ -6356,14 +6356,14 @@
       </c>
       <c r="AS33" s="4">
         <f t="shared" si="16"/>
-        <v>122606</v>
+        <v>122616</v>
       </c>
       <c r="AT33" s="8">
-        <v>1015111</v>
+        <v>1015121</v>
       </c>
       <c r="AU33" s="5">
         <f t="shared" si="17"/>
-        <v>0.98783778655111043</v>
+        <v>0.98784751787888192</v>
       </c>
       <c r="AV33" s="9">
         <v>625585</v>
@@ -6373,14 +6373,14 @@
       </c>
       <c r="AX33" s="4">
         <f t="shared" si="18"/>
-        <v>71270</v>
+        <v>71277</v>
       </c>
       <c r="AY33" s="22">
-        <v>611817</v>
+        <v>611824</v>
       </c>
       <c r="AZ33" s="5">
         <f t="shared" si="19"/>
-        <v>0.97799179967550376</v>
+        <v>0.97800298920210682</v>
       </c>
       <c r="BA33" s="9">
         <v>617039</v>
@@ -6390,14 +6390,14 @@
       </c>
       <c r="BC33" s="4">
         <f t="shared" si="20"/>
-        <v>71303</v>
+        <v>71308</v>
       </c>
       <c r="BD33" s="8">
-        <v>617607</v>
+        <v>617612</v>
       </c>
       <c r="BE33" s="5">
         <f t="shared" si="21"/>
-        <v>1.0009205252828428</v>
+        <v>1.0009286284983607</v>
       </c>
       <c r="BF33" s="9">
         <v>1025594</v>
@@ -6407,14 +6407,14 @@
       </c>
       <c r="BH33" s="4">
         <f t="shared" si="22"/>
-        <v>171332</v>
+        <v>171344</v>
       </c>
       <c r="BI33" s="8">
-        <v>1028372</v>
+        <v>1028384</v>
       </c>
       <c r="BJ33" s="5">
         <f t="shared" si="23"/>
-        <v>1.0027086741927118</v>
+        <v>1.0027203747291813</v>
       </c>
     </row>
     <row r="34" spans="1:62" x14ac:dyDescent="0.3">
@@ -6832,14 +6832,14 @@
       </c>
       <c r="E36" s="4">
         <f t="shared" si="0"/>
-        <v>170273</v>
+        <v>170284</v>
       </c>
       <c r="F36" s="22">
-        <v>777364</v>
+        <v>777375</v>
       </c>
       <c r="G36" s="5">
         <f t="shared" si="24"/>
-        <v>0.96668909197401975</v>
+        <v>0.96670277099698942</v>
       </c>
       <c r="H36" s="9">
         <v>814447</v>
@@ -6849,14 +6849,14 @@
       </c>
       <c r="J36" s="4">
         <f t="shared" si="2"/>
-        <v>192010</v>
+        <v>192024</v>
       </c>
       <c r="K36" s="22">
-        <v>789140</v>
+        <v>789154</v>
       </c>
       <c r="L36" s="5">
         <f t="shared" si="3"/>
-        <v>0.96892738262894951</v>
+        <v>0.96894457220666297</v>
       </c>
       <c r="M36" s="4">
         <v>1485608</v>
@@ -6866,14 +6866,14 @@
       </c>
       <c r="O36" s="4">
         <f t="shared" si="4"/>
-        <v>325412</v>
+        <v>325435</v>
       </c>
       <c r="P36" s="8">
-        <v>1435354</v>
+        <v>1435377</v>
       </c>
       <c r="Q36" s="5">
         <f t="shared" si="5"/>
-        <v>0.96617277235986887</v>
+        <v>0.96618825423664922</v>
       </c>
       <c r="R36" s="9">
         <v>815623</v>
@@ -6883,14 +6883,14 @@
       </c>
       <c r="T36" s="4">
         <f t="shared" si="6"/>
-        <v>178477</v>
+        <v>178495</v>
       </c>
       <c r="U36" s="22">
-        <v>787739</v>
+        <v>787757</v>
       </c>
       <c r="V36" s="5">
         <f t="shared" si="7"/>
-        <v>0.96581263647543047</v>
+        <v>0.96583470549506323</v>
       </c>
       <c r="W36" s="9">
         <v>826349</v>
@@ -6900,14 +6900,14 @@
       </c>
       <c r="Y36" s="4">
         <f t="shared" si="8"/>
-        <v>192793</v>
+        <v>192810</v>
       </c>
       <c r="Z36" s="22">
-        <v>797781</v>
+        <v>797798</v>
       </c>
       <c r="AA36" s="5">
         <f t="shared" si="9"/>
-        <v>0.96542865060646288</v>
+        <v>0.96544922302804259</v>
       </c>
       <c r="AB36" s="9">
         <v>1500292</v>
@@ -6917,14 +6917,14 @@
       </c>
       <c r="AD36" s="4">
         <f t="shared" si="10"/>
-        <v>350402</v>
+        <v>350426</v>
       </c>
       <c r="AE36" s="8">
-        <v>1453874</v>
+        <v>1453898</v>
       </c>
       <c r="AF36" s="5">
         <f t="shared" si="11"/>
-        <v>0.96906068951910695</v>
+        <v>0.96907668640504652</v>
       </c>
       <c r="AG36" s="9">
         <v>833041</v>
@@ -6934,14 +6934,14 @@
       </c>
       <c r="AI36" s="4">
         <f t="shared" si="12"/>
-        <v>198216</v>
+        <v>198234</v>
       </c>
       <c r="AJ36" s="22">
-        <v>803812</v>
+        <v>803830</v>
       </c>
       <c r="AK36" s="5">
         <f t="shared" si="13"/>
-        <v>0.96491289144231795</v>
+        <v>0.96493449902225703</v>
       </c>
       <c r="AL36" s="9">
         <v>845911</v>
@@ -6951,14 +6951,14 @@
       </c>
       <c r="AN36" s="4">
         <f t="shared" si="14"/>
-        <v>169622</v>
+        <v>169642</v>
       </c>
       <c r="AO36" s="22">
-        <v>816431</v>
+        <v>816451</v>
       </c>
       <c r="AP36" s="5">
         <f t="shared" si="15"/>
-        <v>0.96514999804944024</v>
+        <v>0.96517364119866034</v>
       </c>
       <c r="AQ36" s="15">
         <v>1519147</v>
@@ -6968,14 +6968,14 @@
       </c>
       <c r="AS36" s="4">
         <f t="shared" si="16"/>
-        <v>287886</v>
+        <v>287912</v>
       </c>
       <c r="AT36" s="8">
-        <v>1474512</v>
+        <v>1474538</v>
       </c>
       <c r="AU36" s="5">
         <f t="shared" si="17"/>
-        <v>0.97061837991978395</v>
+        <v>0.97063549478753541</v>
       </c>
       <c r="AV36" s="9">
         <v>864672</v>
@@ -6985,14 +6985,14 @@
       </c>
       <c r="AX36" s="4">
         <f t="shared" si="18"/>
-        <v>160463</v>
+        <v>160487</v>
       </c>
       <c r="AY36" s="22">
-        <v>819017</v>
+        <v>819041</v>
       </c>
       <c r="AZ36" s="5">
         <f t="shared" si="19"/>
-        <v>0.94719963176788424</v>
+        <v>0.94722738795751449</v>
       </c>
       <c r="BA36" s="9">
         <v>838532</v>
@@ -7002,14 +7002,14 @@
       </c>
       <c r="BC36" s="4">
         <f t="shared" si="20"/>
-        <v>161085</v>
+        <v>161104</v>
       </c>
       <c r="BD36" s="8">
-        <v>830627</v>
+        <v>830646</v>
       </c>
       <c r="BE36" s="5">
         <f t="shared" si="21"/>
-        <v>0.99057281057848712</v>
+        <v>0.99059546922478803</v>
       </c>
       <c r="BF36" s="9">
         <v>1502094</v>
@@ -7019,14 +7019,14 @@
       </c>
       <c r="BH36" s="4">
         <f t="shared" si="22"/>
-        <v>388446</v>
+        <v>388479</v>
       </c>
       <c r="BI36" s="8">
-        <v>1495165</v>
+        <v>1495198</v>
       </c>
       <c r="BJ36" s="5">
         <f t="shared" si="23"/>
-        <v>0.99538710626631888</v>
+        <v>0.9954090755971331</v>
       </c>
     </row>
     <row r="37" spans="1:62" x14ac:dyDescent="0.3">
@@ -7044,14 +7044,14 @@
       </c>
       <c r="E37" s="4">
         <f t="shared" si="0"/>
-        <v>111274</v>
+        <v>111280</v>
       </c>
       <c r="F37" s="22">
-        <v>621122</v>
+        <v>621128</v>
       </c>
       <c r="G37" s="5">
         <f t="shared" si="24"/>
-        <v>0.95463676366391703</v>
+        <v>0.95464598539585055</v>
       </c>
       <c r="H37" s="9">
         <v>656039</v>
@@ -7061,14 +7061,14 @@
       </c>
       <c r="J37" s="4">
         <f t="shared" si="2"/>
-        <v>125851</v>
+        <v>125857</v>
       </c>
       <c r="K37" s="22">
-        <v>626345</v>
+        <v>626351</v>
       </c>
       <c r="L37" s="5">
         <f t="shared" si="3"/>
-        <v>0.9547374470115344</v>
+        <v>0.95474659280926899</v>
       </c>
       <c r="M37" s="4">
         <v>844882</v>
@@ -7078,14 +7078,14 @@
       </c>
       <c r="O37" s="4">
         <f t="shared" si="4"/>
-        <v>156034</v>
+        <v>156042</v>
       </c>
       <c r="P37" s="8">
-        <v>804112</v>
+        <v>804120</v>
       </c>
       <c r="Q37" s="5">
         <f t="shared" si="5"/>
-        <v>0.9517447406856816</v>
+        <v>0.95175420946357003</v>
       </c>
       <c r="R37" s="9">
         <v>664863</v>
@@ -7095,14 +7095,14 @@
       </c>
       <c r="T37" s="4">
         <f t="shared" si="6"/>
-        <v>120144</v>
+        <v>120151</v>
       </c>
       <c r="U37" s="22">
-        <v>632142</v>
+        <v>632149</v>
       </c>
       <c r="V37" s="5">
         <f t="shared" si="7"/>
-        <v>0.95078534976378593</v>
+        <v>0.95079587824860157</v>
       </c>
       <c r="W37" s="9">
         <v>670009</v>
@@ -7112,14 +7112,14 @@
       </c>
       <c r="Y37" s="4">
         <f t="shared" si="8"/>
-        <v>127238</v>
+        <v>127245</v>
       </c>
       <c r="Z37" s="22">
-        <v>638008</v>
+        <v>638015</v>
       </c>
       <c r="AA37" s="5">
         <f t="shared" si="9"/>
-        <v>0.9522379550125446</v>
+        <v>0.95224840263339749</v>
       </c>
       <c r="AB37" s="9">
         <v>858143</v>
@@ -7129,14 +7129,14 @@
       </c>
       <c r="AD37" s="4">
         <f t="shared" si="10"/>
-        <v>183034</v>
+        <v>183045</v>
       </c>
       <c r="AE37" s="8">
-        <v>818651</v>
+        <v>818662</v>
       </c>
       <c r="AF37" s="5">
         <f t="shared" si="11"/>
-        <v>0.9539796980223576</v>
+        <v>0.95399251639878202</v>
       </c>
       <c r="AG37" s="9">
         <v>675943</v>
@@ -7146,14 +7146,14 @@
       </c>
       <c r="AI37" s="4">
         <f t="shared" si="12"/>
-        <v>129751</v>
+        <v>129762</v>
       </c>
       <c r="AJ37" s="22">
-        <v>644458</v>
+        <v>644469</v>
       </c>
       <c r="AK37" s="5">
         <f t="shared" si="13"/>
-        <v>0.95342062866247601</v>
+        <v>0.95343690222400412</v>
       </c>
       <c r="AL37" s="9">
         <v>678429</v>
@@ -7163,14 +7163,14 @@
       </c>
       <c r="AN37" s="4">
         <f t="shared" si="14"/>
-        <v>111949</v>
+        <v>111957</v>
       </c>
       <c r="AO37" s="22">
-        <v>650663</v>
+        <v>650671</v>
       </c>
       <c r="AP37" s="5">
         <f t="shared" si="15"/>
-        <v>0.95907309386833406</v>
+        <v>0.95908488581708629</v>
       </c>
       <c r="AQ37" s="15">
         <v>865622</v>
@@ -7180,14 +7180,14 @@
       </c>
       <c r="AS37" s="4">
         <f t="shared" si="16"/>
-        <v>140827</v>
+        <v>140838</v>
       </c>
       <c r="AT37" s="8">
-        <v>832568</v>
+        <v>832579</v>
       </c>
       <c r="AU37" s="5">
         <f t="shared" si="17"/>
-        <v>0.96181474130740674</v>
+        <v>0.96182744893267502</v>
       </c>
       <c r="AV37" s="9">
         <v>690116</v>
@@ -7197,14 +7197,14 @@
       </c>
       <c r="AX37" s="4">
         <f t="shared" si="18"/>
-        <v>115266</v>
+        <v>115274</v>
       </c>
       <c r="AY37" s="22">
-        <v>658554</v>
+        <v>658562</v>
       </c>
       <c r="AZ37" s="5">
         <f t="shared" si="19"/>
-        <v>0.9542656596861977</v>
+        <v>0.95427725194025348</v>
       </c>
       <c r="BA37" s="9">
         <v>673244</v>
@@ -7214,14 +7214,14 @@
       </c>
       <c r="BC37" s="4">
         <f t="shared" si="20"/>
-        <v>114846</v>
+        <v>114854</v>
       </c>
       <c r="BD37" s="8">
-        <v>664865</v>
+        <v>664873</v>
       </c>
       <c r="BE37" s="5">
         <f t="shared" si="21"/>
-        <v>0.98755428938096734</v>
+        <v>0.98756617214561138</v>
       </c>
       <c r="BF37" s="9">
         <v>856336</v>
@@ -7231,14 +7231,14 @@
       </c>
       <c r="BH37" s="4">
         <f t="shared" si="22"/>
-        <v>202696</v>
+        <v>202714</v>
       </c>
       <c r="BI37" s="8">
-        <v>846511</v>
+        <v>846529</v>
       </c>
       <c r="BJ37" s="5">
         <f t="shared" si="23"/>
-        <v>0.98852669980007846</v>
+        <v>0.98854771958670429</v>
       </c>
     </row>
     <row r="38" spans="1:62" x14ac:dyDescent="0.3">
@@ -7256,14 +7256,14 @@
       </c>
       <c r="E38" s="4">
         <f t="shared" si="0"/>
-        <v>5676</v>
+        <v>5677</v>
       </c>
       <c r="F38" s="22">
-        <v>21134</v>
+        <v>21135</v>
       </c>
       <c r="G38" s="5">
         <f t="shared" si="24"/>
-        <v>0.84407700295550758</v>
+        <v>0.84411694224778333</v>
       </c>
       <c r="H38" s="9">
         <v>25302</v>
@@ -7273,14 +7273,14 @@
       </c>
       <c r="J38" s="4">
         <f t="shared" si="2"/>
-        <v>6213</v>
+        <v>6214</v>
       </c>
       <c r="K38" s="22">
-        <v>21385</v>
+        <v>21386</v>
       </c>
       <c r="L38" s="5">
         <f t="shared" si="3"/>
-        <v>0.8451901035491266</v>
+        <v>0.84522962611651253</v>
       </c>
       <c r="M38" s="4">
         <v>37823</v>
@@ -7290,14 +7290,14 @@
       </c>
       <c r="O38" s="4">
         <f t="shared" si="4"/>
-        <v>9112</v>
+        <v>9113</v>
       </c>
       <c r="P38" s="8">
-        <v>33468</v>
+        <v>33469</v>
       </c>
       <c r="Q38" s="5">
         <f t="shared" si="5"/>
-        <v>0.88485841948021049</v>
+        <v>0.88488485841948017</v>
       </c>
       <c r="R38" s="9">
         <v>25469</v>
@@ -7307,14 +7307,14 @@
       </c>
       <c r="T38" s="4">
         <f t="shared" si="6"/>
-        <v>5837</v>
+        <v>5838</v>
       </c>
       <c r="U38" s="22">
-        <v>21459</v>
+        <v>21460</v>
       </c>
       <c r="V38" s="5">
         <f t="shared" si="7"/>
-        <v>0.84255369272448855</v>
+        <v>0.84259295614276175</v>
       </c>
       <c r="W38" s="9">
         <v>25404</v>
@@ -7324,14 +7324,14 @@
       </c>
       <c r="Y38" s="4">
         <f t="shared" si="8"/>
-        <v>6248</v>
+        <v>6249</v>
       </c>
       <c r="Z38" s="22">
-        <v>21668</v>
+        <v>21669</v>
       </c>
       <c r="AA38" s="5">
         <f t="shared" si="9"/>
-        <v>0.85293654542591713</v>
+        <v>0.85297590930562117</v>
       </c>
       <c r="AB38" s="9">
         <v>37238</v>
@@ -7341,14 +7341,14 @@
       </c>
       <c r="AD38" s="4">
         <f t="shared" si="10"/>
-        <v>9660</v>
+        <v>9662</v>
       </c>
       <c r="AE38" s="8">
-        <v>34014</v>
+        <v>34016</v>
       </c>
       <c r="AF38" s="5">
         <f t="shared" si="11"/>
-        <v>0.91342177345722109</v>
+        <v>0.91347548203448092</v>
       </c>
       <c r="AG38" s="9">
         <v>24904</v>
@@ -7358,14 +7358,14 @@
       </c>
       <c r="AI38" s="4">
         <f t="shared" si="12"/>
-        <v>6179</v>
+        <v>6181</v>
       </c>
       <c r="AJ38" s="22">
-        <v>21953</v>
+        <v>21955</v>
       </c>
       <c r="AK38" s="5">
         <f t="shared" si="13"/>
-        <v>0.88150497911982006</v>
+        <v>0.88158528750401544</v>
       </c>
       <c r="AL38" s="9">
         <v>25338</v>
@@ -7375,14 +7375,14 @@
       </c>
       <c r="AN38" s="4">
         <f t="shared" si="14"/>
-        <v>6176</v>
+        <v>6177</v>
       </c>
       <c r="AO38" s="22">
-        <v>22401</v>
+        <v>22402</v>
       </c>
       <c r="AP38" s="5">
         <f t="shared" si="15"/>
-        <v>0.8840871418422922</v>
+        <v>0.88412660825637379</v>
       </c>
       <c r="AQ38" s="15">
         <v>38074</v>
@@ -7392,14 +7392,14 @@
       </c>
       <c r="AS38" s="4">
         <f t="shared" si="16"/>
-        <v>8480</v>
+        <v>8481</v>
       </c>
       <c r="AT38" s="8">
-        <v>34878</v>
+        <v>34879</v>
       </c>
       <c r="AU38" s="5">
         <f t="shared" si="17"/>
-        <v>0.91605820244786473</v>
+        <v>0.91608446709040292</v>
       </c>
       <c r="AV38" s="9">
         <v>25812</v>
@@ -7409,14 +7409,14 @@
       </c>
       <c r="AX38" s="4">
         <f t="shared" si="18"/>
-        <v>5569</v>
+        <v>5570</v>
       </c>
       <c r="AY38" s="22">
-        <v>22501</v>
+        <v>22502</v>
       </c>
       <c r="AZ38" s="5">
         <f t="shared" si="19"/>
-        <v>0.87172632883929957</v>
+        <v>0.87176507050984042</v>
       </c>
       <c r="BA38" s="9">
         <v>22633</v>
@@ -7443,14 +7443,14 @@
       </c>
       <c r="BH38" s="4">
         <f t="shared" si="22"/>
-        <v>10843</v>
+        <v>10844</v>
       </c>
       <c r="BI38" s="8">
-        <v>35483</v>
+        <v>35484</v>
       </c>
       <c r="BJ38" s="5">
         <f t="shared" si="23"/>
-        <v>0.99856475488264762</v>
+        <v>0.99859289694377218</v>
       </c>
     </row>
     <row r="39" spans="1:62" x14ac:dyDescent="0.3">
@@ -7680,14 +7680,14 @@
       </c>
       <c r="E40" s="4">
         <f t="shared" si="0"/>
-        <v>50298</v>
+        <v>50303</v>
       </c>
       <c r="F40" s="22">
-        <v>260466</v>
+        <v>260471</v>
       </c>
       <c r="G40" s="5">
         <f t="shared" si="24"/>
-        <v>0.95241682176693643</v>
+        <v>0.95243510470639425</v>
       </c>
       <c r="H40" s="9">
         <v>275367</v>
@@ -7697,14 +7697,14 @@
       </c>
       <c r="J40" s="4">
         <f t="shared" si="2"/>
-        <v>57008</v>
+        <v>57012</v>
       </c>
       <c r="K40" s="22">
-        <v>262120</v>
+        <v>262124</v>
       </c>
       <c r="L40" s="5">
         <f t="shared" si="3"/>
-        <v>0.95189329149825508</v>
+        <v>0.95190781756710141</v>
       </c>
       <c r="M40" s="4">
         <v>339208</v>
@@ -7714,14 +7714,14 @@
       </c>
       <c r="O40" s="4">
         <f t="shared" si="4"/>
-        <v>69714</v>
+        <v>69720</v>
       </c>
       <c r="P40" s="8">
-        <v>323314</v>
+        <v>323320</v>
       </c>
       <c r="Q40" s="5">
         <f t="shared" si="5"/>
-        <v>0.9531437937784486</v>
+        <v>0.95316148204051787</v>
       </c>
       <c r="R40" s="9">
         <v>277547</v>
@@ -7731,14 +7731,14 @@
       </c>
       <c r="T40" s="4">
         <f t="shared" si="6"/>
-        <v>54025</v>
+        <v>54030</v>
       </c>
       <c r="U40" s="22">
-        <v>264287</v>
+        <v>264292</v>
       </c>
       <c r="V40" s="5">
         <f t="shared" si="7"/>
-        <v>0.95222430795504909</v>
+        <v>0.95224232292188349</v>
       </c>
       <c r="W40" s="9">
         <v>278758</v>
@@ -7748,14 +7748,14 @@
       </c>
       <c r="Y40" s="4">
         <f t="shared" si="8"/>
-        <v>62686</v>
+        <v>62691</v>
       </c>
       <c r="Z40" s="22">
-        <v>266731</v>
+        <v>266736</v>
       </c>
       <c r="AA40" s="5">
         <f t="shared" si="9"/>
-        <v>0.95685504989991321</v>
+        <v>0.95687298660486875</v>
       </c>
       <c r="AB40" s="9">
         <v>343140</v>
@@ -7765,14 +7765,14 @@
       </c>
       <c r="AD40" s="4">
         <f t="shared" si="10"/>
-        <v>81788</v>
+        <v>81795</v>
       </c>
       <c r="AE40" s="8">
-        <v>328045</v>
+        <v>328052</v>
       </c>
       <c r="AF40" s="5">
         <f t="shared" si="11"/>
-        <v>0.95600920906918463</v>
+        <v>0.95602960890598587</v>
       </c>
       <c r="AG40" s="9">
         <v>282101</v>
@@ -7782,14 +7782,14 @@
       </c>
       <c r="AI40" s="4">
         <f t="shared" si="12"/>
-        <v>62405</v>
+        <v>62414</v>
       </c>
       <c r="AJ40" s="22">
-        <v>268603</v>
+        <v>268612</v>
       </c>
       <c r="AK40" s="5">
         <f t="shared" si="13"/>
-        <v>0.95215188886249957</v>
+        <v>0.95218379232969752</v>
       </c>
       <c r="AL40" s="9">
         <v>282756</v>
@@ -7799,14 +7799,14 @@
       </c>
       <c r="AN40" s="4">
         <f t="shared" si="14"/>
-        <v>55714</v>
+        <v>55724</v>
       </c>
       <c r="AO40" s="22">
-        <v>270829</v>
+        <v>270839</v>
       </c>
       <c r="AP40" s="5">
         <f t="shared" si="15"/>
-        <v>0.95781875539334271</v>
+        <v>0.95785412157478533</v>
       </c>
       <c r="AQ40" s="15">
         <v>343988</v>
@@ -7816,14 +7816,14 @@
       </c>
       <c r="AS40" s="4">
         <f t="shared" si="16"/>
-        <v>66665</v>
+        <v>66678</v>
       </c>
       <c r="AT40" s="8">
-        <v>332146</v>
+        <v>332159</v>
       </c>
       <c r="AU40" s="5">
         <f t="shared" si="17"/>
-        <v>0.96557438050164546</v>
+        <v>0.96561217251764597</v>
       </c>
       <c r="AV40" s="9">
         <v>285285</v>
@@ -7833,14 +7833,14 @@
       </c>
       <c r="AX40" s="4">
         <f t="shared" si="18"/>
-        <v>56491</v>
+        <v>56506</v>
       </c>
       <c r="AY40" s="22">
-        <v>273343</v>
+        <v>273358</v>
       </c>
       <c r="AZ40" s="5">
         <f t="shared" si="19"/>
-        <v>0.95814010550852657</v>
+        <v>0.95819268450847395</v>
       </c>
       <c r="BA40" s="9">
         <v>276279</v>
@@ -7850,14 +7850,14 @@
       </c>
       <c r="BC40" s="4">
         <f t="shared" si="20"/>
-        <v>55316</v>
+        <v>55329</v>
       </c>
       <c r="BD40" s="8">
-        <v>275269</v>
+        <v>275282</v>
       </c>
       <c r="BE40" s="5">
         <f t="shared" si="21"/>
-        <v>0.99634427517111324</v>
+        <v>0.99639132905504946</v>
       </c>
       <c r="BF40" s="9">
         <v>339189</v>
@@ -7867,14 +7867,14 @@
       </c>
       <c r="BH40" s="4">
         <f t="shared" si="22"/>
-        <v>95103</v>
+        <v>95125</v>
       </c>
       <c r="BI40" s="8">
-        <v>336877</v>
+        <v>336899</v>
       </c>
       <c r="BJ40" s="5">
         <f t="shared" si="23"/>
-        <v>0.993183741218023</v>
+        <v>0.99324860181196917</v>
       </c>
     </row>
     <row r="41" spans="1:62" x14ac:dyDescent="0.3">
@@ -7892,14 +7892,14 @@
       </c>
       <c r="E41" s="4">
         <f t="shared" si="0"/>
-        <v>119469</v>
+        <v>119504</v>
       </c>
       <c r="F41" s="22">
-        <v>840917</v>
+        <v>840952</v>
       </c>
       <c r="G41" s="5">
         <f t="shared" si="24"/>
-        <v>0.96359188256998474</v>
+        <v>0.9636319884495067</v>
       </c>
       <c r="H41" s="9">
         <v>878008</v>
@@ -7909,14 +7909,14 @@
       </c>
       <c r="J41" s="4">
         <f t="shared" si="2"/>
-        <v>149459</v>
+        <v>149494</v>
       </c>
       <c r="K41" s="22">
-        <v>847983</v>
+        <v>848018</v>
       </c>
       <c r="L41" s="5">
         <f t="shared" si="3"/>
-        <v>0.9658032728631174</v>
+        <v>0.96584313582564163</v>
       </c>
       <c r="M41" s="4">
         <v>999035</v>
@@ -7926,14 +7926,14 @@
       </c>
       <c r="O41" s="4">
         <f t="shared" si="4"/>
-        <v>161241</v>
+        <v>161283</v>
       </c>
       <c r="P41" s="8">
-        <v>960728</v>
+        <v>960770</v>
       </c>
       <c r="Q41" s="5">
         <f t="shared" si="5"/>
-        <v>0.96165599803810675</v>
+        <v>0.961698038607256</v>
       </c>
       <c r="R41" s="9">
         <v>889467</v>
@@ -7943,14 +7943,14 @@
       </c>
       <c r="T41" s="4">
         <f t="shared" si="6"/>
-        <v>146270</v>
+        <v>146310</v>
       </c>
       <c r="U41" s="22">
-        <v>856964</v>
+        <v>857004</v>
       </c>
       <c r="V41" s="5">
         <f t="shared" si="7"/>
-        <v>0.96345789107409263</v>
+        <v>0.96350286182623979</v>
       </c>
       <c r="W41" s="9">
         <v>894020</v>
@@ -7960,14 +7960,14 @@
       </c>
       <c r="Y41" s="4">
         <f t="shared" si="8"/>
-        <v>152995</v>
+        <v>153033</v>
       </c>
       <c r="Z41" s="22">
-        <v>862371</v>
+        <v>862409</v>
       </c>
       <c r="AA41" s="5">
         <f t="shared" si="9"/>
-        <v>0.96459922596809911</v>
+        <v>0.96464173061005343</v>
       </c>
       <c r="AB41" s="9">
         <v>1012178</v>
@@ -7977,14 +7977,14 @@
       </c>
       <c r="AD41" s="4">
         <f t="shared" si="10"/>
-        <v>189442</v>
+        <v>189484</v>
       </c>
       <c r="AE41" s="8">
-        <v>976646</v>
+        <v>976688</v>
       </c>
       <c r="AF41" s="5">
         <f t="shared" si="11"/>
-        <v>0.96489550256970613</v>
+        <v>0.96493699724751969</v>
       </c>
       <c r="AG41" s="9">
         <v>904846</v>
@@ -7994,14 +7994,14 @@
       </c>
       <c r="AI41" s="4">
         <f t="shared" si="12"/>
-        <v>152668</v>
+        <v>152711</v>
       </c>
       <c r="AJ41" s="22">
-        <v>872423</v>
+        <v>872466</v>
       </c>
       <c r="AK41" s="5">
         <f t="shared" si="13"/>
-        <v>0.96416738317901607</v>
+        <v>0.96421490507777019</v>
       </c>
       <c r="AL41" s="9">
         <v>910192</v>
@@ -8011,14 +8011,14 @@
       </c>
       <c r="AN41" s="4">
         <f t="shared" si="14"/>
-        <v>133923</v>
+        <v>133969</v>
       </c>
       <c r="AO41" s="22">
-        <v>878329</v>
+        <v>878375</v>
       </c>
       <c r="AP41" s="5">
         <f t="shared" si="15"/>
-        <v>0.96499310035684782</v>
+        <v>0.96504363914426849</v>
       </c>
       <c r="AQ41" s="15">
         <v>1025826</v>
@@ -8028,14 +8028,14 @@
       </c>
       <c r="AS41" s="4">
         <f t="shared" si="16"/>
-        <v>163875</v>
+        <v>163930</v>
       </c>
       <c r="AT41" s="8">
-        <v>991839</v>
+        <v>991894</v>
       </c>
       <c r="AU41" s="5">
         <f t="shared" si="17"/>
-        <v>0.96686865023892943</v>
+        <v>0.96692226556940453</v>
       </c>
       <c r="AV41" s="9">
         <v>923071</v>
@@ -8045,14 +8045,14 @@
       </c>
       <c r="AX41" s="4">
         <f t="shared" si="18"/>
-        <v>137780</v>
+        <v>137828</v>
       </c>
       <c r="AY41" s="22">
-        <v>890319</v>
+        <v>890367</v>
       </c>
       <c r="AZ41" s="5">
         <f t="shared" si="19"/>
-        <v>0.96451843899331691</v>
+        <v>0.96457043932698572</v>
       </c>
       <c r="BA41" s="9">
         <v>907892</v>
@@ -8062,14 +8062,14 @@
       </c>
       <c r="BC41" s="4">
         <f t="shared" si="20"/>
-        <v>135468</v>
+        <v>135516</v>
       </c>
       <c r="BD41" s="8">
-        <v>897155</v>
+        <v>897203</v>
       </c>
       <c r="BE41" s="5">
         <f t="shared" si="21"/>
-        <v>0.98817370348014966</v>
+        <v>0.98822657320474239</v>
       </c>
       <c r="BF41" s="9">
         <v>1023930</v>
@@ -8079,14 +8079,14 @@
       </c>
       <c r="BH41" s="4">
         <f t="shared" si="22"/>
-        <v>214716</v>
+        <v>214772</v>
       </c>
       <c r="BI41" s="8">
-        <v>1010431</v>
+        <v>1010487</v>
       </c>
       <c r="BJ41" s="5">
         <f t="shared" si="23"/>
-        <v>0.98681648159542157</v>
+        <v>0.98687117283408043</v>
       </c>
     </row>
     <row r="42" spans="1:62" x14ac:dyDescent="0.3">
@@ -8121,14 +8121,14 @@
       </c>
       <c r="J42" s="4">
         <f t="shared" si="2"/>
-        <v>3795</v>
+        <v>3796</v>
       </c>
       <c r="K42" s="22">
-        <v>17357</v>
+        <v>17358</v>
       </c>
       <c r="L42" s="5">
         <f t="shared" si="3"/>
-        <v>0.9629937860630271</v>
+        <v>0.96304926764314247</v>
       </c>
       <c r="M42" s="4">
         <v>20468</v>
@@ -8138,14 +8138,14 @@
       </c>
       <c r="O42" s="4">
         <f t="shared" si="4"/>
-        <v>4296</v>
+        <v>4297</v>
       </c>
       <c r="P42" s="8">
-        <v>19582</v>
+        <v>19583</v>
       </c>
       <c r="Q42" s="5">
         <f t="shared" si="5"/>
-        <v>0.95671291772522959</v>
+        <v>0.95676177447723276</v>
       </c>
       <c r="R42" s="9">
         <v>18235</v>
@@ -8155,14 +8155,14 @@
       </c>
       <c r="T42" s="4">
         <f t="shared" si="6"/>
-        <v>3775</v>
+        <v>3776</v>
       </c>
       <c r="U42" s="22">
-        <v>17516</v>
+        <v>17517</v>
       </c>
       <c r="V42" s="5">
         <f t="shared" si="7"/>
-        <v>0.96057033177954487</v>
+        <v>0.96062517137373182</v>
       </c>
       <c r="W42" s="9">
         <v>18317</v>
@@ -8172,14 +8172,14 @@
       </c>
       <c r="Y42" s="4">
         <f t="shared" si="8"/>
-        <v>3861</v>
+        <v>3862</v>
       </c>
       <c r="Z42" s="22">
-        <v>17574</v>
+        <v>17575</v>
       </c>
       <c r="AA42" s="5">
         <f t="shared" si="9"/>
-        <v>0.95943658896107442</v>
+        <v>0.95949118305399361</v>
       </c>
       <c r="AB42" s="9">
         <v>20712</v>
@@ -8189,14 +8189,14 @@
       </c>
       <c r="AD42" s="4">
         <f t="shared" si="10"/>
-        <v>4968</v>
+        <v>4969</v>
       </c>
       <c r="AE42" s="8">
-        <v>19815</v>
+        <v>19816</v>
       </c>
       <c r="AF42" s="5">
         <f t="shared" si="11"/>
-        <v>0.95669177288528384</v>
+        <v>0.95674005407493246</v>
       </c>
       <c r="AG42" s="9">
         <v>18585</v>
@@ -8206,14 +8206,14 @@
       </c>
       <c r="AI42" s="4">
         <f t="shared" si="12"/>
-        <v>3796</v>
+        <v>3797</v>
       </c>
       <c r="AJ42" s="22">
-        <v>17748</v>
+        <v>17749</v>
       </c>
       <c r="AK42" s="5">
         <f t="shared" si="13"/>
-        <v>0.9549636803874092</v>
+        <v>0.95501748722087709</v>
       </c>
       <c r="AL42" s="9">
         <v>18498</v>
@@ -8223,14 +8223,14 @@
       </c>
       <c r="AN42" s="4">
         <f t="shared" si="14"/>
-        <v>3450</v>
+        <v>3451</v>
       </c>
       <c r="AO42" s="22">
-        <v>17806</v>
+        <v>17807</v>
       </c>
       <c r="AP42" s="5">
         <f t="shared" si="15"/>
-        <v>0.96259055032976537</v>
+        <v>0.96264461022813275</v>
       </c>
       <c r="AQ42" s="15">
         <v>20775</v>
@@ -8240,14 +8240,14 @@
       </c>
       <c r="AS42" s="4">
         <f t="shared" si="16"/>
-        <v>4077</v>
+        <v>4078</v>
       </c>
       <c r="AT42" s="8">
-        <v>20022</v>
+        <v>20023</v>
       </c>
       <c r="AU42" s="5">
         <f t="shared" si="17"/>
-        <v>0.96375451263537903</v>
+        <v>0.96380264741275568</v>
       </c>
       <c r="AV42" s="9">
         <v>18672</v>
@@ -8257,14 +8257,14 @@
       </c>
       <c r="AX42" s="4">
         <f t="shared" si="18"/>
-        <v>3582</v>
+        <v>3583</v>
       </c>
       <c r="AY42" s="22">
-        <v>17978</v>
+        <v>17979</v>
       </c>
       <c r="AZ42" s="5">
         <f t="shared" si="19"/>
-        <v>0.96283204798628963</v>
+        <v>0.96288560411311053</v>
       </c>
       <c r="BA42" s="9">
         <v>18422</v>
@@ -8274,14 +8274,14 @@
       </c>
       <c r="BC42" s="4">
         <f t="shared" si="20"/>
-        <v>3450</v>
+        <v>3451</v>
       </c>
       <c r="BD42" s="8">
-        <v>18092</v>
+        <v>18093</v>
       </c>
       <c r="BE42" s="5">
         <f t="shared" si="21"/>
-        <v>0.98208663554445774</v>
+        <v>0.98214091846705032</v>
       </c>
       <c r="BF42" s="9">
         <v>20562</v>
@@ -8291,14 +8291,14 @@
       </c>
       <c r="BH42" s="4">
         <f t="shared" si="22"/>
-        <v>5002</v>
+        <v>5003</v>
       </c>
       <c r="BI42" s="8">
-        <v>20390</v>
+        <v>20391</v>
       </c>
       <c r="BJ42" s="5">
         <f t="shared" si="23"/>
-        <v>0.99163505495574356</v>
+        <v>0.9916836883571637</v>
       </c>
     </row>
     <row r="43" spans="1:62" x14ac:dyDescent="0.3">
@@ -8528,14 +8528,14 @@
       </c>
       <c r="E44" s="4">
         <f t="shared" si="0"/>
-        <v>67398</v>
+        <v>67402</v>
       </c>
       <c r="F44" s="22">
-        <v>304556</v>
+        <v>304560</v>
       </c>
       <c r="G44" s="5">
         <f t="shared" si="24"/>
-        <v>0.89536582712768298</v>
+        <v>0.89537758674925838</v>
       </c>
       <c r="H44" s="9">
         <v>343940</v>
@@ -8545,14 +8545,14 @@
       </c>
       <c r="J44" s="4">
         <f t="shared" si="2"/>
-        <v>78202</v>
+        <v>78206</v>
       </c>
       <c r="K44" s="22">
-        <v>307768</v>
+        <v>307772</v>
       </c>
       <c r="L44" s="5">
         <f t="shared" si="3"/>
-        <v>0.89483049369076006</v>
+        <v>0.89484212362621385</v>
       </c>
       <c r="M44" s="4">
         <v>415294</v>
@@ -8562,14 +8562,14 @@
       </c>
       <c r="O44" s="4">
         <f t="shared" si="4"/>
-        <v>88830</v>
+        <v>88836</v>
       </c>
       <c r="P44" s="8">
-        <v>373537</v>
+        <v>373543</v>
       </c>
       <c r="Q44" s="5">
         <f t="shared" si="5"/>
-        <v>0.89945195451896731</v>
+        <v>0.89946640211512807</v>
       </c>
       <c r="R44" s="9">
         <v>349377</v>
@@ -8579,14 +8579,14 @@
       </c>
       <c r="T44" s="4">
         <f t="shared" si="6"/>
-        <v>76581</v>
+        <v>76585</v>
       </c>
       <c r="U44" s="22">
-        <v>311982</v>
+        <v>311986</v>
       </c>
       <c r="V44" s="5">
         <f t="shared" si="7"/>
-        <v>0.89296662344687827</v>
+        <v>0.89297807239743887</v>
       </c>
       <c r="W44" s="9">
         <v>352323</v>
@@ -8596,14 +8596,14 @@
       </c>
       <c r="Y44" s="4">
         <f t="shared" si="8"/>
-        <v>77405</v>
+        <v>77410</v>
       </c>
       <c r="Z44" s="22">
-        <v>315066</v>
+        <v>315071</v>
       </c>
       <c r="AA44" s="5">
         <f t="shared" si="9"/>
-        <v>0.894253284628026</v>
+        <v>0.89426747615114544</v>
       </c>
       <c r="AB44" s="9">
         <v>424236</v>
@@ -8613,14 +8613,14 @@
       </c>
       <c r="AD44" s="4">
         <f t="shared" si="10"/>
-        <v>99647</v>
+        <v>99654</v>
       </c>
       <c r="AE44" s="8">
-        <v>382529</v>
+        <v>382536</v>
       </c>
       <c r="AF44" s="5">
         <f t="shared" si="11"/>
-        <v>0.90168915415004858</v>
+        <v>0.90170565439990946</v>
       </c>
       <c r="AG44" s="9">
         <v>358309</v>
@@ -8630,14 +8630,14 @@
       </c>
       <c r="AI44" s="4">
         <f t="shared" si="12"/>
-        <v>80220</v>
+        <v>80225</v>
       </c>
       <c r="AJ44" s="22">
-        <v>319560</v>
+        <v>319565</v>
       </c>
       <c r="AK44" s="5">
         <f t="shared" si="13"/>
-        <v>0.89185591207588977</v>
+        <v>0.89186986651186551</v>
       </c>
       <c r="AL44" s="9">
         <v>359722</v>
@@ -8647,14 +8647,14 @@
       </c>
       <c r="AN44" s="4">
         <f t="shared" si="14"/>
-        <v>71137</v>
+        <v>71143</v>
       </c>
       <c r="AO44" s="22">
-        <v>323319</v>
+        <v>323325</v>
       </c>
       <c r="AP44" s="5">
         <f t="shared" si="15"/>
-        <v>0.89880240852658444</v>
+        <v>0.89881908807356792</v>
       </c>
       <c r="AQ44" s="15">
         <v>432157</v>
@@ -8664,14 +8664,14 @@
       </c>
       <c r="AS44" s="4">
         <f t="shared" si="16"/>
-        <v>82567</v>
+        <v>82575</v>
       </c>
       <c r="AT44" s="8">
-        <v>390799</v>
+        <v>390807</v>
       </c>
       <c r="AU44" s="5">
         <f t="shared" si="17"/>
-        <v>0.904298669233635</v>
+        <v>0.90431718102448877</v>
       </c>
       <c r="AV44" s="9">
         <v>367733</v>
@@ -8681,14 +8681,14 @@
       </c>
       <c r="AX44" s="4">
         <f t="shared" si="18"/>
-        <v>71238</v>
+        <v>71246</v>
       </c>
       <c r="AY44" s="22">
-        <v>327451</v>
+        <v>327459</v>
       </c>
       <c r="AZ44" s="5">
         <f t="shared" si="19"/>
-        <v>0.89045856640551702</v>
+        <v>0.89048032132008825</v>
       </c>
       <c r="BA44" s="9">
         <v>337773</v>
@@ -8698,14 +8698,14 @@
       </c>
       <c r="BC44" s="4">
         <f t="shared" si="20"/>
-        <v>71551</v>
+        <v>71558</v>
       </c>
       <c r="BD44" s="8">
-        <v>331153</v>
+        <v>331160</v>
       </c>
       <c r="BE44" s="5">
         <f t="shared" si="21"/>
-        <v>0.98040103856732186</v>
+        <v>0.98042176254466762</v>
       </c>
       <c r="BF44" s="9">
         <v>408499</v>
@@ -8715,14 +8715,14 @@
       </c>
       <c r="BH44" s="4">
         <f t="shared" si="22"/>
-        <v>111923</v>
+        <v>111938</v>
       </c>
       <c r="BI44" s="8">
-        <v>399273</v>
+        <v>399288</v>
       </c>
       <c r="BJ44" s="5">
         <f t="shared" si="23"/>
-        <v>0.97741487739260069</v>
+        <v>0.97745159718873242</v>
       </c>
     </row>
     <row r="45" spans="1:62" x14ac:dyDescent="0.3">
@@ -8740,14 +8740,14 @@
       </c>
       <c r="E45" s="4">
         <f t="shared" si="0"/>
-        <v>45800</v>
+        <v>45805</v>
       </c>
       <c r="F45" s="22">
-        <v>235570</v>
+        <v>235575</v>
       </c>
       <c r="G45" s="5">
         <f t="shared" si="24"/>
-        <v>0.94163215707593173</v>
+        <v>0.94165214332539215</v>
       </c>
       <c r="H45" s="9">
         <v>249985</v>
@@ -8757,14 +8757,14 @@
       </c>
       <c r="J45" s="4">
         <f t="shared" si="2"/>
-        <v>49306</v>
+        <v>49310</v>
       </c>
       <c r="K45" s="22">
-        <v>237252</v>
+        <v>237256</v>
       </c>
       <c r="L45" s="5">
         <f t="shared" si="3"/>
-        <v>0.94906494389663376</v>
+        <v>0.94908094485669137</v>
       </c>
       <c r="M45" s="4">
         <v>300587</v>
@@ -8774,14 +8774,14 @@
       </c>
       <c r="O45" s="4">
         <f t="shared" si="4"/>
-        <v>59167</v>
+        <v>59177</v>
       </c>
       <c r="P45" s="8">
-        <v>288713</v>
+        <v>288723</v>
       </c>
       <c r="Q45" s="5">
         <f t="shared" si="5"/>
-        <v>0.96049729362879965</v>
+        <v>0.9605305618672797</v>
       </c>
       <c r="R45" s="9">
         <v>247712</v>
@@ -8791,14 +8791,14 @@
       </c>
       <c r="T45" s="4">
         <f t="shared" si="6"/>
-        <v>49695</v>
+        <v>49701</v>
       </c>
       <c r="U45" s="22">
-        <v>238329</v>
+        <v>238335</v>
       </c>
       <c r="V45" s="5">
         <f t="shared" si="7"/>
-        <v>0.96212133445291304</v>
+        <v>0.96214555612969899</v>
       </c>
       <c r="W45" s="9">
         <v>250023</v>
@@ -8808,14 +8808,14 @@
       </c>
       <c r="Y45" s="4">
         <f t="shared" si="8"/>
-        <v>53048</v>
+        <v>53055</v>
       </c>
       <c r="Z45" s="22">
-        <v>240160</v>
+        <v>240167</v>
       </c>
       <c r="AA45" s="5">
         <f t="shared" si="9"/>
-        <v>0.96055162925010895</v>
+        <v>0.96057962667434593</v>
       </c>
       <c r="AB45" s="9">
         <v>306096</v>
@@ -8825,14 +8825,14 @@
       </c>
       <c r="AD45" s="4">
         <f t="shared" si="10"/>
-        <v>69229</v>
+        <v>69240</v>
       </c>
       <c r="AE45" s="8">
-        <v>293543</v>
+        <v>293554</v>
       </c>
       <c r="AF45" s="5">
         <f t="shared" si="11"/>
-        <v>0.9589899900684753</v>
+        <v>0.95902592650671681</v>
       </c>
       <c r="AG45" s="9">
         <v>252706</v>
@@ -8842,14 +8842,14 @@
       </c>
       <c r="AI45" s="4">
         <f t="shared" si="12"/>
-        <v>51712</v>
+        <v>51719</v>
       </c>
       <c r="AJ45" s="22">
-        <v>243550</v>
+        <v>243557</v>
       </c>
       <c r="AK45" s="5">
         <f t="shared" si="13"/>
-        <v>0.96376817329228437</v>
+        <v>0.96379587346560824</v>
       </c>
       <c r="AL45" s="9">
         <v>254538</v>
@@ -8859,14 +8859,14 @@
       </c>
       <c r="AN45" s="4">
         <f t="shared" si="14"/>
-        <v>44670</v>
+        <v>44677</v>
       </c>
       <c r="AO45" s="22">
-        <v>245883</v>
+        <v>245890</v>
       </c>
       <c r="AP45" s="5">
         <f t="shared" si="15"/>
-        <v>0.96599721848997011</v>
+        <v>0.96602471929535083</v>
       </c>
       <c r="AQ45" s="15">
         <v>310997</v>
@@ -8876,14 +8876,14 @@
       </c>
       <c r="AS45" s="4">
         <f t="shared" si="16"/>
-        <v>57323</v>
+        <v>57335</v>
       </c>
       <c r="AT45" s="8">
-        <v>299335</v>
+        <v>299347</v>
       </c>
       <c r="AU45" s="5">
         <f t="shared" si="17"/>
-        <v>0.96250124599272657</v>
+        <v>0.96253983157393797</v>
       </c>
       <c r="AV45" s="9">
         <v>259359</v>
@@ -8893,14 +8893,14 @@
       </c>
       <c r="AX45" s="4">
         <f t="shared" si="18"/>
-        <v>47780</v>
+        <v>47790</v>
       </c>
       <c r="AY45" s="22">
-        <v>248460</v>
+        <v>248470</v>
       </c>
       <c r="AZ45" s="5">
         <f t="shared" si="19"/>
-        <v>0.95797716678426426</v>
+        <v>0.95801572337956264</v>
       </c>
       <c r="BA45" s="9">
         <v>254394</v>
@@ -8910,14 +8910,14 @@
       </c>
       <c r="BC45" s="4">
         <f t="shared" si="20"/>
-        <v>46284</v>
+        <v>46291</v>
       </c>
       <c r="BD45" s="8">
-        <v>250266</v>
+        <v>250273</v>
       </c>
       <c r="BE45" s="5">
         <f t="shared" si="21"/>
-        <v>0.983773202198165</v>
+        <v>0.98380071857040652</v>
       </c>
       <c r="BF45" s="9">
         <v>309142</v>
@@ -8927,14 +8927,14 @@
       </c>
       <c r="BH45" s="4">
         <f t="shared" si="22"/>
-        <v>80304</v>
+        <v>80315</v>
       </c>
       <c r="BI45" s="8">
-        <v>304198</v>
+        <v>304209</v>
       </c>
       <c r="BJ45" s="5">
         <f t="shared" si="23"/>
-        <v>0.98400734937342715</v>
+        <v>0.9840429317271675</v>
       </c>
     </row>
     <row r="46" spans="1:62" x14ac:dyDescent="0.3">
@@ -8986,14 +8986,14 @@
       </c>
       <c r="O46" s="4">
         <f t="shared" si="4"/>
-        <v>1731</v>
+        <v>1732</v>
       </c>
       <c r="P46" s="8">
-        <v>5902</v>
+        <v>5903</v>
       </c>
       <c r="Q46" s="5">
         <f t="shared" si="5"/>
-        <v>1.0066518847006651</v>
+        <v>1.006822445846836</v>
       </c>
       <c r="R46" s="9">
         <v>2354</v>
@@ -9037,14 +9037,14 @@
       </c>
       <c r="AD46" s="4">
         <f t="shared" si="10"/>
-        <v>1761</v>
+        <v>1762</v>
       </c>
       <c r="AE46" s="8">
-        <v>6170</v>
+        <v>6171</v>
       </c>
       <c r="AF46" s="5">
         <f t="shared" si="11"/>
-        <v>1.0053772201401336</v>
+        <v>1.0055401662049861</v>
       </c>
       <c r="AG46" s="9">
         <v>2383</v>
@@ -9071,14 +9071,14 @@
       </c>
       <c r="AN46" s="4">
         <f t="shared" si="14"/>
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="AO46" s="22">
-        <v>2479</v>
+        <v>2480</v>
       </c>
       <c r="AP46" s="5">
         <f t="shared" si="15"/>
-        <v>1.0044570502431118</v>
+        <v>1.0048622366288493</v>
       </c>
       <c r="AQ46" s="15">
         <v>6357</v>
@@ -9088,14 +9088,14 @@
       </c>
       <c r="AS46" s="4">
         <f t="shared" si="16"/>
-        <v>1416</v>
+        <v>1417</v>
       </c>
       <c r="AT46" s="8">
-        <v>6387</v>
+        <v>6388</v>
       </c>
       <c r="AU46" s="5">
         <f t="shared" si="17"/>
-        <v>1.004719207173195</v>
+        <v>1.0048765140789682</v>
       </c>
       <c r="AV46" s="9">
         <v>2401</v>
@@ -9139,14 +9139,14 @@
       </c>
       <c r="BH46" s="4">
         <f t="shared" si="22"/>
-        <v>1960</v>
+        <v>1961</v>
       </c>
       <c r="BI46" s="8">
-        <v>6589</v>
+        <v>6590</v>
       </c>
       <c r="BJ46" s="5">
         <f t="shared" si="23"/>
-        <v>1.0327586206896551</v>
+        <v>1.0329153605015673</v>
       </c>
     </row>
     <row r="47" spans="1:62" x14ac:dyDescent="0.3">
@@ -9362,10 +9362,10 @@
       </c>
     </row>
     <row r="48" spans="1:62" x14ac:dyDescent="0.3">
-      <c r="A48" s="30" t="s">
+      <c r="A48" s="36" t="s">
         <v>44</v>
       </c>
-      <c r="B48" s="30"/>
+      <c r="B48" s="36"/>
       <c r="C48" s="11">
         <f>SUM(C10:C47)</f>
         <v>7396603</v>
@@ -9376,15 +9376,15 @@
       </c>
       <c r="E48" s="13">
         <f t="shared" ref="E48" si="25">F48-D48</f>
-        <v>1277811</v>
+        <v>1277953</v>
       </c>
       <c r="F48" s="12">
         <f>SUM(F10:F47)</f>
-        <v>7088073</v>
+        <v>7088215</v>
       </c>
       <c r="G48" s="14">
         <f t="shared" ref="G48" si="26">F48/C48</f>
-        <v>0.95828760851434103</v>
+        <v>0.95830680651645084</v>
       </c>
       <c r="H48" s="11">
         <f>SUM(H10:H47)</f>
@@ -9396,15 +9396,15 @@
       </c>
       <c r="J48" s="13">
         <f t="shared" ref="J48" si="27">K48-I48</f>
-        <v>1509046</v>
+        <v>1509188</v>
       </c>
       <c r="K48" s="12">
         <f>SUM(K10:K47)</f>
-        <v>7194179</v>
+        <v>7194321</v>
       </c>
       <c r="L48" s="14">
         <f t="shared" ref="L48" si="28">K48/H48</f>
-        <v>0.95978950261354024</v>
+        <v>0.95980844711149771</v>
       </c>
       <c r="M48" s="11">
         <f>SUM(M10:M47)</f>
@@ -9416,15 +9416,15 @@
       </c>
       <c r="O48" s="13">
         <f t="shared" si="4"/>
-        <v>2205022</v>
+        <v>2205237</v>
       </c>
       <c r="P48" s="12">
         <f>SUM(P10:P47)</f>
-        <v>11346359</v>
+        <v>11346574</v>
       </c>
       <c r="Q48" s="14">
         <f t="shared" si="5"/>
-        <v>0.95820982746266115</v>
+        <v>0.95822798439854728</v>
       </c>
       <c r="R48" s="11">
         <f>SUM(R10:R47)</f>
@@ -9436,15 +9436,15 @@
       </c>
       <c r="T48" s="13">
         <f t="shared" si="6"/>
-        <v>1415708</v>
+        <v>1415869</v>
       </c>
       <c r="U48" s="12">
         <f>SUM(U10:U47)</f>
-        <v>7214093</v>
+        <v>7214254</v>
       </c>
       <c r="V48" s="14">
         <f t="shared" si="7"/>
-        <v>0.95634235448346316</v>
+        <v>0.95636369758495521</v>
       </c>
       <c r="W48" s="11">
         <f>SUM(W10:W47)</f>
@@ -9456,15 +9456,15 @@
       </c>
       <c r="Y48" s="13">
         <f t="shared" ref="Y48" si="29">Z48-X48</f>
-        <v>1498545</v>
+        <v>1498708</v>
       </c>
       <c r="Z48" s="12">
         <f>SUM(Z10:Z47)</f>
-        <v>7308562</v>
+        <v>7308725</v>
       </c>
       <c r="AA48" s="14">
         <f t="shared" ref="AA48" si="30">Z48/W48</f>
-        <v>0.95773675953430426</v>
+        <v>0.95775811956269341</v>
       </c>
       <c r="AB48" s="11">
         <f>SUM(AB10:AB47)</f>
@@ -9476,15 +9476,15 @@
       </c>
       <c r="AD48" s="13">
         <f t="shared" si="10"/>
-        <v>2512656</v>
+        <v>2512903</v>
       </c>
       <c r="AE48" s="12">
         <f>SUM(AE10:AE47)</f>
-        <v>11559292</v>
+        <v>11559539</v>
       </c>
       <c r="AF48" s="14">
         <f t="shared" si="11"/>
-        <v>0.9600404371208916</v>
+        <v>0.96006095135203728</v>
       </c>
       <c r="AG48" s="11">
         <f>SUM(AG10:AG47)</f>
@@ -9496,15 +9496,15 @@
       </c>
       <c r="AI48" s="13">
         <f t="shared" si="12"/>
-        <v>1514477</v>
+        <v>1514668</v>
       </c>
       <c r="AJ48" s="12">
         <f>SUM(AJ10:AJ47)</f>
-        <v>7364769</v>
+        <v>7364960</v>
       </c>
       <c r="AK48" s="14">
         <f t="shared" si="13"/>
-        <v>0.95564859887010634</v>
+        <v>0.95567338293086701</v>
       </c>
       <c r="AL48" s="11">
         <f>SUM(AL10:AL47)</f>
@@ -9516,15 +9516,15 @@
       </c>
       <c r="AN48" s="13">
         <f t="shared" si="14"/>
-        <v>1322295</v>
+        <v>1322495</v>
       </c>
       <c r="AO48" s="12">
         <f>SUM(AO10:AO47)</f>
-        <v>7467508</v>
+        <v>7467708</v>
       </c>
       <c r="AP48" s="14">
         <f t="shared" si="15"/>
-        <v>0.95746746248892034</v>
+        <v>0.95749310604932869</v>
       </c>
       <c r="AQ48" s="11">
         <f>SUM(AQ10:AQ47)</f>
@@ -9536,15 +9536,15 @@
       </c>
       <c r="AS48" s="13">
         <f t="shared" si="16"/>
-        <v>1994162</v>
+        <v>1994469</v>
       </c>
       <c r="AT48" s="12">
         <f>SUM(AT10:AT47)</f>
-        <v>11756831</v>
+        <v>11757138</v>
       </c>
       <c r="AU48" s="14">
         <f t="shared" si="17"/>
-        <v>0.96129106426352162</v>
+        <v>0.96131616595603797</v>
       </c>
       <c r="AV48" s="11">
         <f>SUM(AV10:AV47)</f>
@@ -9556,15 +9556,15 @@
       </c>
       <c r="AX48" s="13">
         <f t="shared" si="18"/>
-        <v>1322719</v>
+        <v>1322953</v>
       </c>
       <c r="AY48" s="12">
         <f>SUM(AY10:AY47)</f>
-        <v>7529403</v>
+        <v>7529637</v>
       </c>
       <c r="AZ48" s="14">
         <f t="shared" si="19"/>
-        <v>0.942779396295372</v>
+        <v>0.94280869614540441</v>
       </c>
       <c r="BA48" s="11">
         <f>SUM(BA10:BA47)</f>
@@ -9576,15 +9576,15 @@
       </c>
       <c r="BC48" s="13">
         <f t="shared" si="20"/>
-        <v>1344390</v>
+        <v>1344607</v>
       </c>
       <c r="BD48" s="12">
         <f>SUM(BD10:BD47)</f>
-        <v>7632870</v>
+        <v>7633087</v>
       </c>
       <c r="BE48" s="14">
         <f t="shared" si="21"/>
-        <v>0.98852780539204288</v>
+        <v>0.98855590891454093</v>
       </c>
       <c r="BF48" s="11">
         <f>SUM(BF10:BF47)</f>
@@ -9596,15 +9596,15 @@
       </c>
       <c r="BH48" s="13">
         <f t="shared" si="22"/>
-        <v>2841433</v>
+        <v>2841870</v>
       </c>
       <c r="BI48" s="12">
         <f>SUM(BI10:BI47)</f>
-        <v>11979321</v>
+        <v>11979758</v>
       </c>
       <c r="BJ48" s="14">
         <f t="shared" si="23"/>
-        <v>0.9927000095215105</v>
+        <v>0.99273622275130557</v>
       </c>
     </row>
     <row r="49" spans="1:63" x14ac:dyDescent="0.3">
@@ -10122,13 +10122,13 @@
       <c r="BJ57" s="1"/>
     </row>
     <row r="58" spans="1:63" x14ac:dyDescent="0.3">
-      <c r="A58" s="29" t="s">
+      <c r="A58" s="35" t="s">
         <v>45</v>
       </c>
-      <c r="B58" s="29"/>
-      <c r="C58" s="29"/>
-      <c r="D58" s="29"/>
-      <c r="E58" s="29"/>
+      <c r="B58" s="35"/>
+      <c r="C58" s="35"/>
+      <c r="D58" s="35"/>
+      <c r="E58" s="35"/>
       <c r="F58" s="6"/>
       <c r="G58" s="1"/>
       <c r="H58" s="1"/>
@@ -10164,6 +10164,14 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A58:E58"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="AB8:AF8"/>
+    <mergeCell ref="AG8:AK8"/>
+    <mergeCell ref="W8:AA8"/>
+    <mergeCell ref="R8:V8"/>
+    <mergeCell ref="M8:Q8"/>
     <mergeCell ref="BF8:BJ8"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A5:C5"/>
@@ -10175,14 +10183,6 @@
     <mergeCell ref="AV8:AZ8"/>
     <mergeCell ref="AQ8:AU8"/>
     <mergeCell ref="AL8:AP8"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A58:E58"/>
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="AB8:AF8"/>
-    <mergeCell ref="AG8:AK8"/>
-    <mergeCell ref="W8:AA8"/>
-    <mergeCell ref="R8:V8"/>
-    <mergeCell ref="M8:Q8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/gstdatabase/GSTR-3B-2022-2023.xlsx
+++ b/gstdatabase/GSTR-3B-2022-2023.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\May-26\GST Statistics Downloads 31st May 26\Downloads\GSTR 3B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Jun-26\GST Statistics Downloads 31st May 26\Downloads\GSTR 3B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D6F5D85-E649-4638-B797-696BEA5E0392}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AED42A04-18A8-4FD7-B69E-48FB9EF1B5C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -185,10 +185,10 @@
     <t>-</t>
   </si>
   <si>
-    <t>Data Considered upto 31st May 2026</t>
+    <t>Data Considered upto 30th Jun 2026</t>
   </si>
   <si>
-    <t>Filing %age as on 31st May 2026</t>
+    <t>Filing %age as on 30th Jun 2026</t>
   </si>
 </sst>
 </file>
@@ -448,6 +448,15 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="17" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -465,15 +474,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="11">
@@ -775,12 +775,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:62" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
@@ -855,10 +855,10 @@
       <c r="AK2" s="1"/>
     </row>
     <row r="3" spans="1:62" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="31" t="s">
+      <c r="A3" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="B3" s="31"/>
+      <c r="B3" s="34"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -935,11 +935,11 @@
       <c r="AK4" s="1"/>
     </row>
     <row r="5" spans="1:62" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="31" t="s">
+      <c r="A5" s="34" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="31"/>
-      <c r="C5" s="31"/>
+      <c r="B5" s="34"/>
+      <c r="C5" s="34"/>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
@@ -1054,100 +1054,100 @@
       <c r="AK7" s="1"/>
     </row>
     <row r="8" spans="1:62" s="24" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="32" t="s">
+      <c r="A8" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="33" t="s">
+      <c r="B8" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="C8" s="28">
+      <c r="C8" s="31">
         <v>44652</v>
       </c>
-      <c r="D8" s="29"/>
-      <c r="E8" s="29"/>
-      <c r="F8" s="29"/>
-      <c r="G8" s="30"/>
-      <c r="H8" s="28">
+      <c r="D8" s="32"/>
+      <c r="E8" s="32"/>
+      <c r="F8" s="32"/>
+      <c r="G8" s="33"/>
+      <c r="H8" s="31">
         <v>44682</v>
       </c>
-      <c r="I8" s="29"/>
-      <c r="J8" s="29"/>
-      <c r="K8" s="29"/>
-      <c r="L8" s="30"/>
-      <c r="M8" s="28">
+      <c r="I8" s="32"/>
+      <c r="J8" s="32"/>
+      <c r="K8" s="32"/>
+      <c r="L8" s="33"/>
+      <c r="M8" s="31">
         <v>44713</v>
       </c>
-      <c r="N8" s="29"/>
-      <c r="O8" s="29"/>
-      <c r="P8" s="29"/>
-      <c r="Q8" s="30"/>
-      <c r="R8" s="28">
+      <c r="N8" s="32"/>
+      <c r="O8" s="32"/>
+      <c r="P8" s="32"/>
+      <c r="Q8" s="33"/>
+      <c r="R8" s="31">
         <v>44743</v>
       </c>
-      <c r="S8" s="29"/>
-      <c r="T8" s="29"/>
-      <c r="U8" s="29"/>
-      <c r="V8" s="30"/>
-      <c r="W8" s="28">
+      <c r="S8" s="32"/>
+      <c r="T8" s="32"/>
+      <c r="U8" s="32"/>
+      <c r="V8" s="33"/>
+      <c r="W8" s="31">
         <v>44774</v>
       </c>
-      <c r="X8" s="29"/>
-      <c r="Y8" s="29"/>
-      <c r="Z8" s="29"/>
-      <c r="AA8" s="30"/>
-      <c r="AB8" s="28">
+      <c r="X8" s="32"/>
+      <c r="Y8" s="32"/>
+      <c r="Z8" s="32"/>
+      <c r="AA8" s="33"/>
+      <c r="AB8" s="31">
         <v>44805</v>
       </c>
-      <c r="AC8" s="29"/>
-      <c r="AD8" s="29"/>
-      <c r="AE8" s="29"/>
-      <c r="AF8" s="30"/>
-      <c r="AG8" s="28">
+      <c r="AC8" s="32"/>
+      <c r="AD8" s="32"/>
+      <c r="AE8" s="32"/>
+      <c r="AF8" s="33"/>
+      <c r="AG8" s="31">
         <v>44835</v>
       </c>
-      <c r="AH8" s="29"/>
-      <c r="AI8" s="29"/>
-      <c r="AJ8" s="29"/>
-      <c r="AK8" s="30"/>
-      <c r="AL8" s="28">
+      <c r="AH8" s="32"/>
+      <c r="AI8" s="32"/>
+      <c r="AJ8" s="32"/>
+      <c r="AK8" s="33"/>
+      <c r="AL8" s="31">
         <v>44866</v>
       </c>
-      <c r="AM8" s="29"/>
-      <c r="AN8" s="29"/>
-      <c r="AO8" s="29"/>
-      <c r="AP8" s="30"/>
-      <c r="AQ8" s="28">
+      <c r="AM8" s="32"/>
+      <c r="AN8" s="32"/>
+      <c r="AO8" s="32"/>
+      <c r="AP8" s="33"/>
+      <c r="AQ8" s="31">
         <v>44896</v>
       </c>
-      <c r="AR8" s="29"/>
-      <c r="AS8" s="29"/>
-      <c r="AT8" s="29"/>
-      <c r="AU8" s="30"/>
-      <c r="AV8" s="28">
+      <c r="AR8" s="32"/>
+      <c r="AS8" s="32"/>
+      <c r="AT8" s="32"/>
+      <c r="AU8" s="33"/>
+      <c r="AV8" s="31">
         <v>44927</v>
       </c>
-      <c r="AW8" s="29"/>
-      <c r="AX8" s="29"/>
-      <c r="AY8" s="29"/>
-      <c r="AZ8" s="30"/>
-      <c r="BA8" s="28">
+      <c r="AW8" s="32"/>
+      <c r="AX8" s="32"/>
+      <c r="AY8" s="32"/>
+      <c r="AZ8" s="33"/>
+      <c r="BA8" s="31">
         <v>44958</v>
       </c>
-      <c r="BB8" s="29"/>
-      <c r="BC8" s="29"/>
-      <c r="BD8" s="29"/>
-      <c r="BE8" s="30"/>
-      <c r="BF8" s="28">
+      <c r="BB8" s="32"/>
+      <c r="BC8" s="32"/>
+      <c r="BD8" s="32"/>
+      <c r="BE8" s="33"/>
+      <c r="BF8" s="31">
         <v>44986</v>
       </c>
-      <c r="BG8" s="29"/>
-      <c r="BH8" s="29"/>
-      <c r="BI8" s="29"/>
-      <c r="BJ8" s="30"/>
+      <c r="BG8" s="32"/>
+      <c r="BH8" s="32"/>
+      <c r="BI8" s="32"/>
+      <c r="BJ8" s="33"/>
     </row>
     <row r="9" spans="1:62" s="24" customFormat="1" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="32"/>
-      <c r="B9" s="33"/>
+      <c r="A9" s="35"/>
+      <c r="B9" s="36"/>
       <c r="C9" s="25" t="s">
         <v>2</v>
       </c>
@@ -1480,14 +1480,14 @@
       </c>
       <c r="AS10" s="4">
         <f>AT10-AR10</f>
-        <v>20530</v>
+        <v>20531</v>
       </c>
       <c r="AT10" s="8">
-        <v>114704</v>
+        <v>114705</v>
       </c>
       <c r="AU10" s="5">
         <f>AT10/AQ10</f>
-        <v>0.98983448680554353</v>
+        <v>0.98984311627345056</v>
       </c>
       <c r="AV10" s="9">
         <v>70382</v>
@@ -1590,14 +1590,14 @@
       </c>
       <c r="O11" s="4">
         <f t="shared" ref="O11:O48" si="4">P11-N11</f>
-        <v>17698</v>
+        <v>17699</v>
       </c>
       <c r="P11" s="8">
-        <v>96226</v>
+        <v>96227</v>
       </c>
       <c r="Q11" s="5">
         <f t="shared" ref="Q11:Q48" si="5">P11/M11</f>
-        <v>0.97231372390517956</v>
+        <v>0.97232382838550613</v>
       </c>
       <c r="R11" s="9">
         <v>44504</v>
@@ -1641,14 +1641,14 @@
       </c>
       <c r="AD11" s="4">
         <f t="shared" ref="AD11:AD48" si="10">AE11-AC11</f>
-        <v>20291</v>
+        <v>20292</v>
       </c>
       <c r="AE11" s="8">
-        <v>97413</v>
+        <v>97414</v>
       </c>
       <c r="AF11" s="5">
         <f t="shared" ref="AF11:AF48" si="11">AE11/AB11</f>
-        <v>0.97522224891878906</v>
+        <v>0.97523226013134712</v>
       </c>
       <c r="AG11" s="9">
         <v>44744</v>
@@ -1692,14 +1692,14 @@
       </c>
       <c r="AS11" s="4">
         <f t="shared" ref="AS11:AS48" si="16">AT11-AR11</f>
-        <v>14773</v>
+        <v>14774</v>
       </c>
       <c r="AT11" s="8">
-        <v>98355</v>
+        <v>98356</v>
       </c>
       <c r="AU11" s="5">
         <f t="shared" ref="AU11:AU48" si="17">AT11/AQ11</f>
-        <v>0.97604421994859525</v>
+        <v>0.97605414363544341</v>
       </c>
       <c r="AV11" s="9">
         <v>46153</v>
@@ -1802,14 +1802,14 @@
       </c>
       <c r="O12" s="4">
         <f t="shared" si="4"/>
-        <v>51792</v>
+        <v>51793</v>
       </c>
       <c r="P12" s="8">
-        <v>327299</v>
+        <v>327300</v>
       </c>
       <c r="Q12" s="5">
         <f t="shared" si="5"/>
-        <v>0.95575983577116597</v>
+        <v>0.95576275591401927</v>
       </c>
       <c r="R12" s="9">
         <v>167538</v>
@@ -1853,14 +1853,14 @@
       </c>
       <c r="AD12" s="4">
         <f t="shared" si="10"/>
-        <v>64281</v>
+        <v>64282</v>
       </c>
       <c r="AE12" s="8">
-        <v>331748</v>
+        <v>331749</v>
       </c>
       <c r="AF12" s="5">
         <f t="shared" si="11"/>
-        <v>0.95605437510987124</v>
+        <v>0.95605725697916699</v>
       </c>
       <c r="AG12" s="9">
         <v>170493</v>
@@ -2192,14 +2192,14 @@
       </c>
       <c r="E14" s="4">
         <f t="shared" si="0"/>
-        <v>15674</v>
+        <v>15675</v>
       </c>
       <c r="F14" s="22">
-        <v>78890</v>
+        <v>78891</v>
       </c>
       <c r="G14" s="5">
         <f t="shared" si="1"/>
-        <v>0.95277777777777772</v>
+        <v>0.95278985507246372</v>
       </c>
       <c r="H14" s="9">
         <v>84757</v>
@@ -2209,14 +2209,14 @@
       </c>
       <c r="J14" s="4">
         <f t="shared" si="2"/>
-        <v>18866</v>
+        <v>18867</v>
       </c>
       <c r="K14" s="22">
-        <v>80623</v>
+        <v>80624</v>
       </c>
       <c r="L14" s="5">
         <f t="shared" si="3"/>
-        <v>0.95122526752952563</v>
+        <v>0.95123706596505309</v>
       </c>
       <c r="M14" s="4">
         <v>154914</v>
@@ -2226,14 +2226,14 @@
       </c>
       <c r="O14" s="4">
         <f t="shared" si="4"/>
-        <v>31307</v>
+        <v>31308</v>
       </c>
       <c r="P14" s="8">
-        <v>147541</v>
+        <v>147542</v>
       </c>
       <c r="Q14" s="5">
         <f t="shared" si="5"/>
-        <v>0.95240585098829023</v>
+        <v>0.95241230618278527</v>
       </c>
       <c r="R14" s="9">
         <v>85475</v>
@@ -2243,14 +2243,14 @@
       </c>
       <c r="T14" s="4">
         <f t="shared" si="6"/>
-        <v>18031</v>
+        <v>18032</v>
       </c>
       <c r="U14" s="22">
-        <v>80370</v>
+        <v>80371</v>
       </c>
       <c r="V14" s="5">
         <f t="shared" si="7"/>
-        <v>0.94027493419128405</v>
+        <v>0.94028663351857267</v>
       </c>
       <c r="W14" s="9">
         <v>86445</v>
@@ -2260,14 +2260,14 @@
       </c>
       <c r="Y14" s="4">
         <f t="shared" si="8"/>
-        <v>19187</v>
+        <v>19190</v>
       </c>
       <c r="Z14" s="22">
-        <v>81630</v>
+        <v>81633</v>
       </c>
       <c r="AA14" s="5">
         <f t="shared" si="9"/>
-        <v>0.9442998438313378</v>
+        <v>0.94433454797848337</v>
       </c>
       <c r="AB14" s="9">
         <v>156524</v>
@@ -2277,14 +2277,14 @@
       </c>
       <c r="AD14" s="4">
         <f t="shared" si="10"/>
-        <v>37393</v>
+        <v>37396</v>
       </c>
       <c r="AE14" s="8">
-        <v>149076</v>
+        <v>149079</v>
       </c>
       <c r="AF14" s="5">
         <f t="shared" si="11"/>
-        <v>0.95241624287649174</v>
+        <v>0.95243540926631065</v>
       </c>
       <c r="AG14" s="9">
         <v>86459</v>
@@ -2294,14 +2294,14 @@
       </c>
       <c r="AI14" s="4">
         <f t="shared" si="12"/>
-        <v>19484</v>
+        <v>19486</v>
       </c>
       <c r="AJ14" s="22">
-        <v>81561</v>
+        <v>81563</v>
       </c>
       <c r="AK14" s="5">
         <f t="shared" si="13"/>
-        <v>0.94334887056292582</v>
+        <v>0.94337200291467627</v>
       </c>
       <c r="AL14" s="9">
         <v>87786</v>
@@ -2311,14 +2311,14 @@
       </c>
       <c r="AN14" s="4">
         <f t="shared" si="14"/>
-        <v>16941</v>
+        <v>16943</v>
       </c>
       <c r="AO14" s="22">
-        <v>83042</v>
+        <v>83044</v>
       </c>
       <c r="AP14" s="5">
         <f t="shared" si="15"/>
-        <v>0.94595949240197752</v>
+        <v>0.94598227507803068</v>
       </c>
       <c r="AQ14" s="15">
         <v>158597</v>
@@ -2328,14 +2328,14 @@
       </c>
       <c r="AS14" s="4">
         <f t="shared" si="16"/>
-        <v>28223</v>
+        <v>28226</v>
       </c>
       <c r="AT14" s="8">
-        <v>151377</v>
+        <v>151380</v>
       </c>
       <c r="AU14" s="5">
         <f t="shared" si="17"/>
-        <v>0.95447580975680502</v>
+        <v>0.95449472562532711</v>
       </c>
       <c r="AV14" s="9">
         <v>90863</v>
@@ -2345,14 +2345,14 @@
       </c>
       <c r="AX14" s="4">
         <f t="shared" si="18"/>
-        <v>17156</v>
+        <v>17158</v>
       </c>
       <c r="AY14" s="22">
-        <v>83730</v>
+        <v>83732</v>
       </c>
       <c r="AZ14" s="5">
         <f t="shared" si="19"/>
-        <v>0.92149719907993355</v>
+        <v>0.92151921023959149</v>
       </c>
       <c r="BA14" s="9">
         <v>86219</v>
@@ -2362,14 +2362,14 @@
       </c>
       <c r="BC14" s="4">
         <f t="shared" si="20"/>
-        <v>17696</v>
+        <v>17698</v>
       </c>
       <c r="BD14" s="8">
-        <v>85365</v>
+        <v>85367</v>
       </c>
       <c r="BE14" s="5">
         <f t="shared" si="21"/>
-        <v>0.99009499066331086</v>
+        <v>0.99011818740648816</v>
       </c>
       <c r="BF14" s="9">
         <v>155639</v>
@@ -2379,14 +2379,14 @@
       </c>
       <c r="BH14" s="4">
         <f t="shared" si="22"/>
-        <v>40052</v>
+        <v>40056</v>
       </c>
       <c r="BI14" s="8">
-        <v>154739</v>
+        <v>154743</v>
       </c>
       <c r="BJ14" s="5">
         <f t="shared" si="23"/>
-        <v>0.99421738767275558</v>
+        <v>0.9942430881719877</v>
       </c>
     </row>
     <row r="15" spans="1:62" x14ac:dyDescent="0.3">
@@ -2616,14 +2616,14 @@
       </c>
       <c r="E16" s="4">
         <f t="shared" si="0"/>
-        <v>61335</v>
+        <v>61337</v>
       </c>
       <c r="F16" s="22">
-        <v>393548</v>
+        <v>393550</v>
       </c>
       <c r="G16" s="5">
         <f t="shared" si="1"/>
-        <v>0.95921341906298596</v>
+        <v>0.95921829375892675</v>
       </c>
       <c r="H16" s="9">
         <v>416018</v>
@@ -2633,14 +2633,14 @@
       </c>
       <c r="J16" s="4">
         <f t="shared" si="2"/>
-        <v>74120</v>
+        <v>74123</v>
       </c>
       <c r="K16" s="22">
-        <v>400760</v>
+        <v>400763</v>
       </c>
       <c r="L16" s="5">
         <f t="shared" si="3"/>
-        <v>0.96332370233980258</v>
+        <v>0.9633309135662399</v>
       </c>
       <c r="M16" s="4">
         <v>750813</v>
@@ -2650,14 +2650,14 @@
       </c>
       <c r="O16" s="4">
         <f t="shared" si="4"/>
-        <v>121079</v>
+        <v>121083</v>
       </c>
       <c r="P16" s="8">
-        <v>719545</v>
+        <v>719549</v>
       </c>
       <c r="Q16" s="5">
         <f t="shared" si="5"/>
-        <v>0.9583544770801784</v>
+        <v>0.95835980463843862</v>
       </c>
       <c r="R16" s="9">
         <v>419109</v>
@@ -2667,14 +2667,14 @@
       </c>
       <c r="T16" s="4">
         <f t="shared" si="6"/>
-        <v>73010</v>
+        <v>73012</v>
       </c>
       <c r="U16" s="22">
-        <v>401893</v>
+        <v>401895</v>
       </c>
       <c r="V16" s="5">
         <f t="shared" si="7"/>
-        <v>0.95892238057402723</v>
+        <v>0.95892715260230632</v>
       </c>
       <c r="W16" s="9">
         <v>423539</v>
@@ -2684,14 +2684,14 @@
       </c>
       <c r="Y16" s="4">
         <f t="shared" si="8"/>
-        <v>73342</v>
+        <v>73344</v>
       </c>
       <c r="Z16" s="22">
-        <v>407297</v>
+        <v>407299</v>
       </c>
       <c r="AA16" s="5">
         <f t="shared" si="9"/>
-        <v>0.96165170149620227</v>
+        <v>0.96165642361152104</v>
       </c>
       <c r="AB16" s="9">
         <v>762171</v>
@@ -2701,14 +2701,14 @@
       </c>
       <c r="AD16" s="4">
         <f t="shared" si="10"/>
-        <v>150569</v>
+        <v>150574</v>
       </c>
       <c r="AE16" s="8">
-        <v>731061</v>
+        <v>731066</v>
       </c>
       <c r="AF16" s="5">
         <f t="shared" si="11"/>
-        <v>0.95918238820422186</v>
+        <v>0.95918894841183933</v>
       </c>
       <c r="AG16" s="9">
         <v>429452</v>
@@ -2718,14 +2718,14 @@
       </c>
       <c r="AI16" s="4">
         <f t="shared" si="12"/>
-        <v>79983</v>
+        <v>79987</v>
       </c>
       <c r="AJ16" s="22">
-        <v>411527</v>
+        <v>411531</v>
       </c>
       <c r="AK16" s="5">
         <f t="shared" si="13"/>
-        <v>0.95826076022465845</v>
+        <v>0.95827007442042422</v>
       </c>
       <c r="AL16" s="9">
         <v>434676</v>
@@ -2735,14 +2735,14 @@
       </c>
       <c r="AN16" s="4">
         <f t="shared" si="14"/>
-        <v>70941</v>
+        <v>70945</v>
       </c>
       <c r="AO16" s="22">
-        <v>417040</v>
+        <v>417044</v>
       </c>
       <c r="AP16" s="5">
         <f t="shared" si="15"/>
-        <v>0.95942725156208297</v>
+        <v>0.95943645381847631</v>
       </c>
       <c r="AQ16" s="15">
         <v>772632</v>
@@ -2752,14 +2752,14 @@
       </c>
       <c r="AS16" s="4">
         <f t="shared" si="16"/>
-        <v>110168</v>
+        <v>110175</v>
       </c>
       <c r="AT16" s="8">
-        <v>741473</v>
+        <v>741480</v>
       </c>
       <c r="AU16" s="5">
         <f t="shared" si="17"/>
-        <v>0.95967161598277062</v>
+        <v>0.95968067592333739</v>
       </c>
       <c r="AV16" s="9">
         <v>448203</v>
@@ -2769,14 +2769,14 @@
       </c>
       <c r="AX16" s="4">
         <f t="shared" si="18"/>
-        <v>69537</v>
+        <v>69543</v>
       </c>
       <c r="AY16" s="22">
-        <v>419993</v>
+        <v>419999</v>
       </c>
       <c r="AZ16" s="5">
         <f t="shared" si="19"/>
-        <v>0.93705976979181305</v>
+        <v>0.93707315658306611</v>
       </c>
       <c r="BA16" s="9">
         <v>429555</v>
@@ -2786,14 +2786,14 @@
       </c>
       <c r="BC16" s="4">
         <f t="shared" si="20"/>
-        <v>70929</v>
+        <v>70935</v>
       </c>
       <c r="BD16" s="8">
-        <v>424801</v>
+        <v>424807</v>
       </c>
       <c r="BE16" s="5">
         <f t="shared" si="21"/>
-        <v>0.98893273271175985</v>
+        <v>0.9889467006553293</v>
       </c>
       <c r="BF16" s="9">
         <v>753579</v>
@@ -2803,14 +2803,14 @@
       </c>
       <c r="BH16" s="4">
         <f t="shared" si="22"/>
-        <v>147976</v>
+        <v>147984</v>
       </c>
       <c r="BI16" s="8">
-        <v>751178</v>
+        <v>751186</v>
       </c>
       <c r="BJ16" s="5">
         <f t="shared" si="23"/>
-        <v>0.99681387087485185</v>
+        <v>0.9968244868819327</v>
       </c>
     </row>
     <row r="17" spans="1:62" x14ac:dyDescent="0.3">
@@ -2828,14 +2828,14 @@
       </c>
       <c r="E17" s="4">
         <f t="shared" si="0"/>
-        <v>51278</v>
+        <v>51282</v>
       </c>
       <c r="F17" s="22">
-        <v>277330</v>
+        <v>277334</v>
       </c>
       <c r="G17" s="5">
         <f t="shared" si="1"/>
-        <v>0.98041156569602395</v>
+        <v>0.98042570641741289</v>
       </c>
       <c r="H17" s="9">
         <v>290053</v>
@@ -2845,14 +2845,14 @@
       </c>
       <c r="J17" s="4">
         <f t="shared" si="2"/>
-        <v>59540</v>
+        <v>59544</v>
       </c>
       <c r="K17" s="22">
-        <v>284827</v>
+        <v>284831</v>
       </c>
       <c r="L17" s="5">
         <f t="shared" si="3"/>
-        <v>0.98198260317941899</v>
+        <v>0.98199639376251924</v>
       </c>
       <c r="M17" s="4">
         <v>666005</v>
@@ -2862,14 +2862,14 @@
       </c>
       <c r="O17" s="4">
         <f t="shared" si="4"/>
-        <v>128112</v>
+        <v>128120</v>
       </c>
       <c r="P17" s="8">
-        <v>645976</v>
+        <v>645984</v>
       </c>
       <c r="Q17" s="5">
         <f t="shared" si="5"/>
-        <v>0.96992665220231078</v>
+        <v>0.9699386641241432</v>
       </c>
       <c r="R17" s="9">
         <v>287981</v>
@@ -2879,14 +2879,14 @@
       </c>
       <c r="T17" s="4">
         <f t="shared" si="6"/>
-        <v>55275</v>
+        <v>55280</v>
       </c>
       <c r="U17" s="22">
-        <v>280820</v>
+        <v>280825</v>
       </c>
       <c r="V17" s="5">
         <f t="shared" si="7"/>
-        <v>0.97513377618662345</v>
+        <v>0.97515113844316115</v>
       </c>
       <c r="W17" s="9">
         <v>293004</v>
@@ -2896,14 +2896,14 @@
       </c>
       <c r="Y17" s="4">
         <f t="shared" si="8"/>
-        <v>60470</v>
+        <v>60475</v>
       </c>
       <c r="Z17" s="22">
-        <v>286657</v>
+        <v>286662</v>
       </c>
       <c r="AA17" s="5">
         <f t="shared" si="9"/>
-        <v>0.97833817968355385</v>
+        <v>0.97835524429700615</v>
       </c>
       <c r="AB17" s="9">
         <v>677720</v>
@@ -2913,14 +2913,14 @@
       </c>
       <c r="AD17" s="4">
         <f t="shared" si="10"/>
-        <v>145671</v>
+        <v>145679</v>
       </c>
       <c r="AE17" s="8">
-        <v>658932</v>
+        <v>658940</v>
       </c>
       <c r="AF17" s="5">
         <f t="shared" si="11"/>
-        <v>0.97227763678215195</v>
+        <v>0.97228944106710735</v>
       </c>
       <c r="AG17" s="9">
         <v>295677</v>
@@ -2930,14 +2930,14 @@
       </c>
       <c r="AI17" s="4">
         <f t="shared" si="12"/>
-        <v>59670</v>
+        <v>59675</v>
       </c>
       <c r="AJ17" s="22">
-        <v>288114</v>
+        <v>288119</v>
       </c>
       <c r="AK17" s="5">
         <f t="shared" si="13"/>
-        <v>0.97442141255491632</v>
+        <v>0.9744383228996506</v>
       </c>
       <c r="AL17" s="9">
         <v>303084</v>
@@ -2947,14 +2947,14 @@
       </c>
       <c r="AN17" s="4">
         <f t="shared" si="14"/>
-        <v>51544</v>
+        <v>51549</v>
       </c>
       <c r="AO17" s="22">
-        <v>296052</v>
+        <v>296057</v>
       </c>
       <c r="AP17" s="5">
         <f t="shared" si="15"/>
-        <v>0.97679851130379691</v>
+        <v>0.97681500838051494</v>
       </c>
       <c r="AQ17" s="15">
         <v>690105</v>
@@ -2964,14 +2964,14 @@
       </c>
       <c r="AS17" s="4">
         <f t="shared" si="16"/>
-        <v>105793</v>
+        <v>105800</v>
       </c>
       <c r="AT17" s="8">
-        <v>672938</v>
+        <v>672945</v>
       </c>
       <c r="AU17" s="5">
         <f t="shared" si="17"/>
-        <v>0.97512407532187129</v>
+        <v>0.97513421870584915</v>
       </c>
       <c r="AV17" s="9">
         <v>311697</v>
@@ -2981,14 +2981,14 @@
       </c>
       <c r="AX17" s="4">
         <f t="shared" si="18"/>
-        <v>49010</v>
+        <v>49016</v>
       </c>
       <c r="AY17" s="22">
-        <v>294853</v>
+        <v>294859</v>
       </c>
       <c r="AZ17" s="5">
         <f t="shared" si="19"/>
-        <v>0.9459603396888645</v>
+        <v>0.94597958915228575</v>
       </c>
       <c r="BA17" s="9">
         <v>307540</v>
@@ -2998,14 +2998,14 @@
       </c>
       <c r="BC17" s="4">
         <f t="shared" si="20"/>
-        <v>49210</v>
+        <v>49215</v>
       </c>
       <c r="BD17" s="8">
-        <v>301983</v>
+        <v>301988</v>
       </c>
       <c r="BE17" s="5">
         <f t="shared" si="21"/>
-        <v>0.98193080574884573</v>
+        <v>0.98194706379657926</v>
       </c>
       <c r="BF17" s="9">
         <v>689646</v>
@@ -3015,14 +3015,14 @@
       </c>
       <c r="BH17" s="4">
         <f t="shared" si="22"/>
-        <v>153193</v>
+        <v>153200</v>
       </c>
       <c r="BI17" s="8">
-        <v>687213</v>
+        <v>687220</v>
       </c>
       <c r="BJ17" s="5">
         <f t="shared" si="23"/>
-        <v>0.99647210307897094</v>
+        <v>0.99648225321396777</v>
       </c>
     </row>
     <row r="18" spans="1:62" x14ac:dyDescent="0.3">
@@ -3040,14 +3040,14 @@
       </c>
       <c r="E18" s="4">
         <f t="shared" si="0"/>
-        <v>141567</v>
+        <v>141571</v>
       </c>
       <c r="F18" s="22">
-        <v>822080</v>
+        <v>822084</v>
       </c>
       <c r="G18" s="5">
         <f t="shared" si="1"/>
-        <v>0.97808563722264985</v>
+        <v>0.97809039630029304</v>
       </c>
       <c r="H18" s="9">
         <v>861805</v>
@@ -3057,14 +3057,14 @@
       </c>
       <c r="J18" s="4">
         <f t="shared" si="2"/>
-        <v>162040</v>
+        <v>162044</v>
       </c>
       <c r="K18" s="22">
-        <v>837274</v>
+        <v>837278</v>
       </c>
       <c r="L18" s="5">
         <f t="shared" si="3"/>
-        <v>0.97153532411624444</v>
+        <v>0.97153996553744759</v>
       </c>
       <c r="M18" s="4">
         <v>1358945</v>
@@ -3074,14 +3074,14 @@
       </c>
       <c r="O18" s="4">
         <f t="shared" si="4"/>
-        <v>245599</v>
+        <v>245603</v>
       </c>
       <c r="P18" s="8">
-        <v>1303832</v>
+        <v>1303836</v>
       </c>
       <c r="Q18" s="5">
         <f t="shared" si="5"/>
-        <v>0.95944427478669114</v>
+        <v>0.95944721824650736</v>
       </c>
       <c r="R18" s="9">
         <v>869959</v>
@@ -3091,14 +3091,14 @@
       </c>
       <c r="T18" s="4">
         <f t="shared" si="6"/>
-        <v>158471</v>
+        <v>158474</v>
       </c>
       <c r="U18" s="22">
-        <v>839486</v>
+        <v>839489</v>
       </c>
       <c r="V18" s="5">
         <f t="shared" si="7"/>
-        <v>0.96497191246943825</v>
+        <v>0.96497536090781288</v>
       </c>
       <c r="W18" s="9">
         <v>883450</v>
@@ -3108,14 +3108,14 @@
       </c>
       <c r="Y18" s="4">
         <f t="shared" si="8"/>
-        <v>163350</v>
+        <v>163353</v>
       </c>
       <c r="Z18" s="22">
-        <v>853929</v>
+        <v>853932</v>
       </c>
       <c r="AA18" s="5">
         <f t="shared" si="9"/>
-        <v>0.96658441337936496</v>
+        <v>0.96658780915728115</v>
       </c>
       <c r="AB18" s="9">
         <v>1397129</v>
@@ -3125,14 +3125,14 @@
       </c>
       <c r="AD18" s="4">
         <f t="shared" si="10"/>
-        <v>289644</v>
+        <v>289649</v>
       </c>
       <c r="AE18" s="8">
-        <v>1339773</v>
+        <v>1339778</v>
       </c>
       <c r="AF18" s="5">
         <f t="shared" si="11"/>
-        <v>0.95894724109226848</v>
+        <v>0.95895081985986974</v>
       </c>
       <c r="AG18" s="9">
         <v>899515</v>
@@ -3142,14 +3142,14 @@
       </c>
       <c r="AI18" s="4">
         <f t="shared" si="12"/>
-        <v>168545</v>
+        <v>168548</v>
       </c>
       <c r="AJ18" s="22">
-        <v>864922</v>
+        <v>864925</v>
       </c>
       <c r="AK18" s="5">
         <f t="shared" si="13"/>
-        <v>0.96154260907266698</v>
+        <v>0.96154594420326511</v>
       </c>
       <c r="AL18" s="9">
         <v>914748</v>
@@ -3159,14 +3159,14 @@
       </c>
       <c r="AN18" s="4">
         <f t="shared" si="14"/>
-        <v>146479</v>
+        <v>146483</v>
       </c>
       <c r="AO18" s="22">
-        <v>880805</v>
+        <v>880809</v>
       </c>
       <c r="AP18" s="5">
         <f t="shared" si="15"/>
-        <v>0.96289360567063276</v>
+        <v>0.96289797845964131</v>
       </c>
       <c r="AQ18" s="15">
         <v>1436617</v>
@@ -3176,14 +3176,14 @@
       </c>
       <c r="AS18" s="4">
         <f t="shared" si="16"/>
-        <v>219826</v>
+        <v>219831</v>
       </c>
       <c r="AT18" s="8">
-        <v>1375248</v>
+        <v>1375253</v>
       </c>
       <c r="AU18" s="5">
         <f t="shared" si="17"/>
-        <v>0.95728228191647458</v>
+        <v>0.95728576231521689</v>
       </c>
       <c r="AV18" s="9">
         <v>954168</v>
@@ -3193,14 +3193,14 @@
       </c>
       <c r="AX18" s="4">
         <f t="shared" si="18"/>
-        <v>153020</v>
+        <v>153024</v>
       </c>
       <c r="AY18" s="22">
-        <v>894807</v>
+        <v>894811</v>
       </c>
       <c r="AZ18" s="5">
         <f t="shared" si="19"/>
-        <v>0.9377876851875141</v>
+        <v>0.93779187732139413</v>
       </c>
       <c r="BA18" s="9">
         <v>922519</v>
@@ -3210,14 +3210,14 @@
       </c>
       <c r="BC18" s="4">
         <f t="shared" si="20"/>
-        <v>158402</v>
+        <v>158406</v>
       </c>
       <c r="BD18" s="8">
-        <v>911446</v>
+        <v>911450</v>
       </c>
       <c r="BE18" s="5">
         <f t="shared" si="21"/>
-        <v>0.98799699518383899</v>
+        <v>0.98800133113789523</v>
       </c>
       <c r="BF18" s="9">
         <v>1428140</v>
@@ -3227,14 +3227,14 @@
       </c>
       <c r="BH18" s="4">
         <f t="shared" si="22"/>
-        <v>327751</v>
+        <v>327759</v>
       </c>
       <c r="BI18" s="8">
-        <v>1413405</v>
+        <v>1413413</v>
       </c>
       <c r="BJ18" s="5">
         <f t="shared" si="23"/>
-        <v>0.98968238407999221</v>
+        <v>0.98968798577170303</v>
       </c>
     </row>
     <row r="19" spans="1:62" x14ac:dyDescent="0.3">
@@ -3252,14 +3252,14 @@
       </c>
       <c r="E19" s="4">
         <f t="shared" si="0"/>
-        <v>54814</v>
+        <v>54817</v>
       </c>
       <c r="F19" s="22">
-        <v>245684</v>
+        <v>245687</v>
       </c>
       <c r="G19" s="5">
         <f t="shared" si="1"/>
-        <v>0.88870400648213799</v>
+        <v>0.88871485827557772</v>
       </c>
       <c r="H19" s="9">
         <v>280982</v>
@@ -3269,14 +3269,14 @@
       </c>
       <c r="J19" s="4">
         <f t="shared" si="2"/>
-        <v>89972</v>
+        <v>89975</v>
       </c>
       <c r="K19" s="22">
-        <v>250786</v>
+        <v>250789</v>
       </c>
       <c r="L19" s="5">
         <f t="shared" si="3"/>
-        <v>0.89253404132649061</v>
+        <v>0.89254471816699998</v>
       </c>
       <c r="M19" s="4">
         <v>470659</v>
@@ -3286,14 +3286,14 @@
       </c>
       <c r="O19" s="4">
         <f t="shared" si="4"/>
-        <v>92078</v>
+        <v>92082</v>
       </c>
       <c r="P19" s="8">
-        <v>424569</v>
+        <v>424573</v>
       </c>
       <c r="Q19" s="5">
         <f t="shared" si="5"/>
-        <v>0.90207347570109142</v>
+        <v>0.90208197442309612</v>
       </c>
       <c r="R19" s="9">
         <v>282327</v>
@@ -3303,14 +3303,14 @@
       </c>
       <c r="T19" s="4">
         <f t="shared" si="6"/>
-        <v>55606</v>
+        <v>55609</v>
       </c>
       <c r="U19" s="22">
-        <v>249696</v>
+        <v>249699</v>
       </c>
       <c r="V19" s="5">
         <f t="shared" si="7"/>
-        <v>0.88442125620291367</v>
+        <v>0.88443188217917523</v>
       </c>
       <c r="W19" s="9">
         <v>286093</v>
@@ -3320,14 +3320,14 @@
       </c>
       <c r="Y19" s="4">
         <f t="shared" si="8"/>
-        <v>58854</v>
+        <v>58857</v>
       </c>
       <c r="Z19" s="22">
-        <v>254767</v>
+        <v>254770</v>
       </c>
       <c r="AA19" s="5">
         <f t="shared" si="9"/>
-        <v>0.89050413676671569</v>
+        <v>0.89051462286738925</v>
       </c>
       <c r="AB19" s="9">
         <v>481143</v>
@@ -3337,14 +3337,14 @@
       </c>
       <c r="AD19" s="4">
         <f t="shared" si="10"/>
-        <v>107379</v>
+        <v>107383</v>
       </c>
       <c r="AE19" s="8">
-        <v>435533</v>
+        <v>435537</v>
       </c>
       <c r="AF19" s="5">
         <f t="shared" si="11"/>
-        <v>0.90520489750448407</v>
+        <v>0.90521321104120811</v>
       </c>
       <c r="AG19" s="9">
         <v>287213</v>
@@ -3354,14 +3354,14 @@
       </c>
       <c r="AI19" s="4">
         <f t="shared" si="12"/>
-        <v>57872</v>
+        <v>57875</v>
       </c>
       <c r="AJ19" s="22">
-        <v>254658</v>
+        <v>254661</v>
       </c>
       <c r="AK19" s="5">
         <f t="shared" si="13"/>
-        <v>0.88665206658472984</v>
+        <v>0.8866625117943826</v>
       </c>
       <c r="AL19" s="9">
         <v>292666</v>
@@ -3371,14 +3371,14 @@
       </c>
       <c r="AN19" s="4">
         <f t="shared" si="14"/>
-        <v>53088</v>
+        <v>53092</v>
       </c>
       <c r="AO19" s="22">
-        <v>260282</v>
+        <v>260286</v>
       </c>
       <c r="AP19" s="5">
         <f t="shared" si="15"/>
-        <v>0.88934826730812599</v>
+        <v>0.88936193476522729</v>
       </c>
       <c r="AQ19" s="15">
         <v>495564</v>
@@ -3388,14 +3388,14 @@
       </c>
       <c r="AS19" s="4">
         <f t="shared" si="16"/>
-        <v>83371</v>
+        <v>83376</v>
       </c>
       <c r="AT19" s="8">
-        <v>446771</v>
+        <v>446776</v>
       </c>
       <c r="AU19" s="5">
         <f t="shared" si="17"/>
-        <v>0.90154046702343194</v>
+        <v>0.90155055653760163</v>
       </c>
       <c r="AV19" s="9">
         <v>310298</v>
@@ -3405,14 +3405,14 @@
       </c>
       <c r="AX19" s="4">
         <f t="shared" si="18"/>
-        <v>52452</v>
+        <v>52457</v>
       </c>
       <c r="AY19" s="22">
-        <v>264466</v>
+        <v>264471</v>
       </c>
       <c r="AZ19" s="5">
         <f t="shared" si="19"/>
-        <v>0.85229682434305087</v>
+        <v>0.85231293788551654</v>
       </c>
       <c r="BA19" s="9">
         <v>280202</v>
@@ -3422,14 +3422,14 @@
       </c>
       <c r="BC19" s="4">
         <f t="shared" si="20"/>
-        <v>55905</v>
+        <v>55913</v>
       </c>
       <c r="BD19" s="8">
-        <v>272812</v>
+        <v>272820</v>
       </c>
       <c r="BE19" s="5">
         <f t="shared" si="21"/>
-        <v>0.97362616969186511</v>
+        <v>0.97365472052305124</v>
       </c>
       <c r="BF19" s="9">
         <v>473091</v>
@@ -3439,14 +3439,14 @@
       </c>
       <c r="BH19" s="4">
         <f t="shared" si="22"/>
-        <v>125841</v>
+        <v>125849</v>
       </c>
       <c r="BI19" s="8">
-        <v>463167</v>
+        <v>463175</v>
       </c>
       <c r="BJ19" s="5">
         <f t="shared" si="23"/>
-        <v>0.97902306321616772</v>
+        <v>0.9790399732820958</v>
       </c>
     </row>
     <row r="20" spans="1:62" x14ac:dyDescent="0.3">
@@ -3676,14 +3676,14 @@
       </c>
       <c r="E21" s="4">
         <f t="shared" si="0"/>
-        <v>3320</v>
+        <v>3321</v>
       </c>
       <c r="F21" s="22">
-        <v>8598</v>
+        <v>8599</v>
       </c>
       <c r="G21" s="5">
         <f t="shared" si="1"/>
-        <v>0.8098332862390506</v>
+        <v>0.80992747480455873</v>
       </c>
       <c r="H21" s="9">
         <v>10811</v>
@@ -3693,14 +3693,14 @@
       </c>
       <c r="J21" s="4">
         <f t="shared" si="2"/>
-        <v>3220</v>
+        <v>3222</v>
       </c>
       <c r="K21" s="22">
-        <v>8740</v>
+        <v>8742</v>
       </c>
       <c r="L21" s="5">
         <f t="shared" si="3"/>
-        <v>0.80843585237258353</v>
+        <v>0.8086208491351401</v>
       </c>
       <c r="M21" s="4">
         <v>14133</v>
@@ -3710,14 +3710,14 @@
       </c>
       <c r="O21" s="4">
         <f t="shared" si="4"/>
-        <v>3837</v>
+        <v>3839</v>
       </c>
       <c r="P21" s="8">
-        <v>11807</v>
+        <v>11809</v>
       </c>
       <c r="Q21" s="5">
         <f t="shared" si="5"/>
-        <v>0.83542064671336591</v>
+        <v>0.83556215948489354</v>
       </c>
       <c r="R21" s="9">
         <v>11019</v>
@@ -3727,14 +3727,14 @@
       </c>
       <c r="T21" s="4">
         <f t="shared" si="6"/>
-        <v>3081</v>
+        <v>3083</v>
       </c>
       <c r="U21" s="22">
-        <v>8894</v>
+        <v>8896</v>
       </c>
       <c r="V21" s="5">
         <f t="shared" si="7"/>
-        <v>0.80715128414556669</v>
+        <v>0.80733278881931214</v>
       </c>
       <c r="W21" s="9">
         <v>11175</v>
@@ -3744,14 +3744,14 @@
       </c>
       <c r="Y21" s="4">
         <f t="shared" si="8"/>
-        <v>3193</v>
+        <v>3195</v>
       </c>
       <c r="Z21" s="22">
-        <v>9092</v>
+        <v>9094</v>
       </c>
       <c r="AA21" s="5">
         <f t="shared" si="9"/>
-        <v>0.8136017897091723</v>
+        <v>0.81378076062639826</v>
       </c>
       <c r="AB21" s="9">
         <v>14571</v>
@@ -3761,14 +3761,14 @@
       </c>
       <c r="AD21" s="4">
         <f t="shared" si="10"/>
-        <v>4484</v>
+        <v>4487</v>
       </c>
       <c r="AE21" s="8">
-        <v>12218</v>
+        <v>12221</v>
       </c>
       <c r="AF21" s="5">
         <f t="shared" si="11"/>
-        <v>0.83851485828014549</v>
+        <v>0.83872074668862806</v>
       </c>
       <c r="AG21" s="9">
         <v>11345</v>
@@ -3778,14 +3778,14 @@
       </c>
       <c r="AI21" s="4">
         <f t="shared" si="12"/>
-        <v>3234</v>
+        <v>3237</v>
       </c>
       <c r="AJ21" s="22">
-        <v>9224</v>
+        <v>9227</v>
       </c>
       <c r="AK21" s="5">
         <f t="shared" si="13"/>
-        <v>0.81304539444689294</v>
+        <v>0.8133098281181137</v>
       </c>
       <c r="AL21" s="9">
         <v>11441</v>
@@ -3795,14 +3795,14 @@
       </c>
       <c r="AN21" s="4">
         <f t="shared" si="14"/>
-        <v>3098</v>
+        <v>3101</v>
       </c>
       <c r="AO21" s="22">
-        <v>9346</v>
+        <v>9349</v>
       </c>
       <c r="AP21" s="5">
         <f t="shared" si="15"/>
-        <v>0.81688663578358534</v>
+        <v>0.81714885062494536</v>
       </c>
       <c r="AQ21" s="15">
         <v>14790</v>
@@ -3812,14 +3812,14 @@
       </c>
       <c r="AS21" s="4">
         <f t="shared" si="16"/>
-        <v>4015</v>
+        <v>4020</v>
       </c>
       <c r="AT21" s="8">
-        <v>12500</v>
+        <v>12505</v>
       </c>
       <c r="AU21" s="5">
         <f t="shared" si="17"/>
-        <v>0.84516565246788367</v>
+        <v>0.84550371872887087</v>
       </c>
       <c r="AV21" s="9">
         <v>11740</v>
@@ -3829,14 +3829,14 @@
       </c>
       <c r="AX21" s="4">
         <f t="shared" si="18"/>
-        <v>3225</v>
+        <v>3229</v>
       </c>
       <c r="AY21" s="22">
-        <v>9485</v>
+        <v>9489</v>
       </c>
       <c r="AZ21" s="5">
         <f t="shared" si="19"/>
-        <v>0.80792163543441231</v>
+        <v>0.80826235093696763</v>
       </c>
       <c r="BA21" s="9">
         <v>9242</v>
@@ -3846,14 +3846,14 @@
       </c>
       <c r="BC21" s="4">
         <f t="shared" si="20"/>
-        <v>3127</v>
+        <v>3131</v>
       </c>
       <c r="BD21" s="8">
-        <v>9580</v>
+        <v>9584</v>
       </c>
       <c r="BE21" s="5">
         <f t="shared" si="21"/>
-        <v>1.0365721705258601</v>
+        <v>1.0370049772776455</v>
       </c>
       <c r="BF21" s="9">
         <v>12544</v>
@@ -3863,14 +3863,14 @@
       </c>
       <c r="BH21" s="4">
         <f t="shared" si="22"/>
-        <v>5684</v>
+        <v>5689</v>
       </c>
       <c r="BI21" s="8">
-        <v>12906</v>
+        <v>12911</v>
       </c>
       <c r="BJ21" s="5">
         <f t="shared" si="23"/>
-        <v>1.028858418367347</v>
+        <v>1.0292570153061225</v>
       </c>
     </row>
     <row r="22" spans="1:62" x14ac:dyDescent="0.3">
@@ -3888,14 +3888,14 @@
       </c>
       <c r="E22" s="4">
         <f t="shared" si="0"/>
-        <v>1583</v>
+        <v>1584</v>
       </c>
       <c r="F22" s="22">
-        <v>5599</v>
+        <v>5600</v>
       </c>
       <c r="G22" s="5">
         <f t="shared" si="1"/>
-        <v>0.91696691778578443</v>
+        <v>0.91713069112348511</v>
       </c>
       <c r="H22" s="9">
         <v>6184</v>
@@ -3905,14 +3905,14 @@
       </c>
       <c r="J22" s="4">
         <f t="shared" si="2"/>
-        <v>1614</v>
+        <v>1615</v>
       </c>
       <c r="K22" s="22">
-        <v>5668</v>
+        <v>5669</v>
       </c>
       <c r="L22" s="5">
         <f t="shared" si="3"/>
-        <v>0.91655886157826649</v>
+        <v>0.91672056921086675</v>
       </c>
       <c r="M22" s="4">
         <v>7446</v>
@@ -3922,14 +3922,14 @@
       </c>
       <c r="O22" s="4">
         <f t="shared" si="4"/>
-        <v>1916</v>
+        <v>1917</v>
       </c>
       <c r="P22" s="8">
-        <v>6877</v>
+        <v>6878</v>
       </c>
       <c r="Q22" s="5">
         <f t="shared" si="5"/>
-        <v>0.9235831318828901</v>
+        <v>0.92371743217835078</v>
       </c>
       <c r="R22" s="9">
         <v>6325</v>
@@ -3939,14 +3939,14 @@
       </c>
       <c r="T22" s="4">
         <f t="shared" si="6"/>
-        <v>1603</v>
+        <v>1604</v>
       </c>
       <c r="U22" s="22">
-        <v>5802</v>
+        <v>5803</v>
       </c>
       <c r="V22" s="5">
         <f t="shared" si="7"/>
-        <v>0.91731225296442687</v>
+        <v>0.91747035573122526</v>
       </c>
       <c r="W22" s="9">
         <v>6418</v>
@@ -3956,14 +3956,14 @@
       </c>
       <c r="Y22" s="4">
         <f t="shared" si="8"/>
-        <v>1580</v>
+        <v>1581</v>
       </c>
       <c r="Z22" s="22">
-        <v>5879</v>
+        <v>5880</v>
       </c>
       <c r="AA22" s="5">
         <f t="shared" si="9"/>
-        <v>0.91601745091928954</v>
+        <v>0.91617326269866006</v>
       </c>
       <c r="AB22" s="9">
         <v>7662</v>
@@ -3973,14 +3973,14 @@
       </c>
       <c r="AD22" s="4">
         <f t="shared" si="10"/>
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="AE22" s="8">
-        <v>7097</v>
+        <v>7098</v>
       </c>
       <c r="AF22" s="5">
         <f t="shared" si="11"/>
-        <v>0.92625946228138867</v>
+        <v>0.92638997650743926</v>
       </c>
       <c r="AG22" s="9">
         <v>6546</v>
@@ -3990,14 +3990,14 @@
       </c>
       <c r="AI22" s="4">
         <f t="shared" si="12"/>
-        <v>1770</v>
+        <v>1771</v>
       </c>
       <c r="AJ22" s="22">
-        <v>6010</v>
+        <v>6011</v>
       </c>
       <c r="AK22" s="5">
         <f t="shared" si="13"/>
-        <v>0.91811793461655977</v>
+        <v>0.91827069966391694</v>
       </c>
       <c r="AL22" s="9">
         <v>6648</v>
@@ -4007,14 +4007,14 @@
       </c>
       <c r="AN22" s="4">
         <f t="shared" si="14"/>
-        <v>1598</v>
+        <v>1599</v>
       </c>
       <c r="AO22" s="22">
-        <v>6071</v>
+        <v>6072</v>
       </c>
       <c r="AP22" s="5">
         <f t="shared" si="15"/>
-        <v>0.91320697954271957</v>
+        <v>0.91335740072202165</v>
       </c>
       <c r="AQ22" s="15">
         <v>7880</v>
@@ -4024,14 +4024,14 @@
       </c>
       <c r="AS22" s="4">
         <f t="shared" si="16"/>
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="AT22" s="8">
-        <v>7260</v>
+        <v>7262</v>
       </c>
       <c r="AU22" s="5">
         <f t="shared" si="17"/>
-        <v>0.92131979695431476</v>
+        <v>0.92157360406091371</v>
       </c>
       <c r="AV22" s="9">
         <v>6715</v>
@@ -4041,14 +4041,14 @@
       </c>
       <c r="AX22" s="4">
         <f t="shared" si="18"/>
-        <v>1675</v>
+        <v>1676</v>
       </c>
       <c r="AY22" s="22">
-        <v>6095</v>
+        <v>6096</v>
       </c>
       <c r="AZ22" s="5">
         <f t="shared" si="19"/>
-        <v>0.90766939687267312</v>
+        <v>0.90781831720029782</v>
       </c>
       <c r="BA22" s="9">
         <v>6117</v>
@@ -4058,14 +4058,14 @@
       </c>
       <c r="BC22" s="4">
         <f t="shared" si="20"/>
-        <v>1685</v>
+        <v>1686</v>
       </c>
       <c r="BD22" s="8">
-        <v>6143</v>
+        <v>6144</v>
       </c>
       <c r="BE22" s="5">
         <f t="shared" si="21"/>
-        <v>1.004250449566781</v>
+        <v>1.0044139283962727</v>
       </c>
       <c r="BF22" s="9">
         <v>7349</v>
@@ -4075,14 +4075,14 @@
       </c>
       <c r="BH22" s="4">
         <f t="shared" si="22"/>
-        <v>2555</v>
+        <v>2556</v>
       </c>
       <c r="BI22" s="8">
-        <v>7401</v>
+        <v>7402</v>
       </c>
       <c r="BJ22" s="5">
         <f t="shared" si="23"/>
-        <v>1.0070757926248468</v>
+        <v>1.00721186555994</v>
       </c>
     </row>
     <row r="23" spans="1:62" x14ac:dyDescent="0.3">
@@ -4287,14 +4287,14 @@
       </c>
       <c r="BH23" s="4">
         <f t="shared" si="22"/>
-        <v>4619</v>
+        <v>4620</v>
       </c>
       <c r="BI23" s="8">
-        <v>10605</v>
+        <v>10606</v>
       </c>
       <c r="BJ23" s="5">
         <f t="shared" si="23"/>
-        <v>0.94442960192359071</v>
+        <v>0.94451865704871318</v>
       </c>
     </row>
     <row r="24" spans="1:62" x14ac:dyDescent="0.3">
@@ -4736,14 +4736,14 @@
       </c>
       <c r="E26" s="4">
         <f t="shared" si="0"/>
-        <v>3348</v>
+        <v>3349</v>
       </c>
       <c r="F26" s="22">
-        <v>12922</v>
+        <v>12923</v>
       </c>
       <c r="G26" s="5">
         <f t="shared" si="1"/>
-        <v>0.80722138930534737</v>
+        <v>0.80728385807096448</v>
       </c>
       <c r="H26" s="9">
         <v>16365</v>
@@ -4753,14 +4753,14 @@
       </c>
       <c r="J26" s="4">
         <f t="shared" si="2"/>
-        <v>3589</v>
+        <v>3590</v>
       </c>
       <c r="K26" s="22">
-        <v>13396</v>
+        <v>13397</v>
       </c>
       <c r="L26" s="5">
         <f t="shared" si="3"/>
-        <v>0.8185762297586312</v>
+        <v>0.81863733577757414</v>
       </c>
       <c r="M26" s="4">
         <v>27510</v>
@@ -4770,14 +4770,14 @@
       </c>
       <c r="O26" s="4">
         <f t="shared" si="4"/>
-        <v>5024</v>
+        <v>5026</v>
       </c>
       <c r="P26" s="8">
-        <v>24137</v>
+        <v>24139</v>
       </c>
       <c r="Q26" s="5">
         <f t="shared" si="5"/>
-        <v>0.87739003998545984</v>
+        <v>0.87746274082151943</v>
       </c>
       <c r="R26" s="9">
         <v>16566</v>
@@ -4787,14 +4787,14 @@
       </c>
       <c r="T26" s="4">
         <f t="shared" si="6"/>
-        <v>3645</v>
+        <v>3646</v>
       </c>
       <c r="U26" s="22">
-        <v>13599</v>
+        <v>13600</v>
       </c>
       <c r="V26" s="5">
         <f t="shared" si="7"/>
-        <v>0.82089822528069545</v>
+        <v>0.82095858988289272</v>
       </c>
       <c r="W26" s="9">
         <v>16728</v>
@@ -4804,14 +4804,14 @@
       </c>
       <c r="Y26" s="4">
         <f t="shared" si="8"/>
-        <v>3629</v>
+        <v>3630</v>
       </c>
       <c r="Z26" s="22">
-        <v>13810</v>
+        <v>13811</v>
       </c>
       <c r="AA26" s="5">
         <f t="shared" si="9"/>
-        <v>0.82556193208990913</v>
+        <v>0.82562171209947388</v>
       </c>
       <c r="AB26" s="9">
         <v>28240</v>
@@ -4821,14 +4821,14 @@
       </c>
       <c r="AD26" s="4">
         <f t="shared" si="10"/>
-        <v>5969</v>
+        <v>5972</v>
       </c>
       <c r="AE26" s="8">
-        <v>24942</v>
+        <v>24945</v>
       </c>
       <c r="AF26" s="5">
         <f t="shared" si="11"/>
-        <v>0.88321529745042493</v>
+        <v>0.88332152974504252</v>
       </c>
       <c r="AG26" s="9">
         <v>16538</v>
@@ -4838,14 +4838,14 @@
       </c>
       <c r="AI26" s="4">
         <f t="shared" si="12"/>
-        <v>3545</v>
+        <v>3547</v>
       </c>
       <c r="AJ26" s="22">
-        <v>13498</v>
+        <v>13500</v>
       </c>
       <c r="AK26" s="5">
         <f t="shared" si="13"/>
-        <v>0.81618091667674442</v>
+        <v>0.816301850284194</v>
       </c>
       <c r="AL26" s="9">
         <v>16671</v>
@@ -4855,14 +4855,14 @@
       </c>
       <c r="AN26" s="4">
         <f t="shared" si="14"/>
-        <v>3414</v>
+        <v>3416</v>
       </c>
       <c r="AO26" s="22">
-        <v>13611</v>
+        <v>13613</v>
       </c>
       <c r="AP26" s="5">
         <f t="shared" si="15"/>
-        <v>0.81644772359186613</v>
+        <v>0.81656769239997595</v>
       </c>
       <c r="AQ26" s="15">
         <v>28406</v>
@@ -4872,14 +4872,14 @@
       </c>
       <c r="AS26" s="4">
         <f t="shared" si="16"/>
-        <v>5531</v>
+        <v>5536</v>
       </c>
       <c r="AT26" s="8">
-        <v>25075</v>
+        <v>25080</v>
       </c>
       <c r="AU26" s="5">
         <f t="shared" si="17"/>
-        <v>0.8827360416813349</v>
+        <v>0.88291206083221851</v>
       </c>
       <c r="AV26" s="9">
         <v>16717</v>
@@ -4889,14 +4889,14 @@
       </c>
       <c r="AX26" s="4">
         <f t="shared" si="18"/>
-        <v>3334</v>
+        <v>3337</v>
       </c>
       <c r="AY26" s="22">
-        <v>13305</v>
+        <v>13308</v>
       </c>
       <c r="AZ26" s="5">
         <f t="shared" si="19"/>
-        <v>0.7958963928934617</v>
+        <v>0.79607585093019084</v>
       </c>
       <c r="BA26" s="9">
         <v>13719</v>
@@ -4906,14 +4906,14 @@
       </c>
       <c r="BC26" s="4">
         <f t="shared" si="20"/>
-        <v>3275</v>
+        <v>3278</v>
       </c>
       <c r="BD26" s="8">
-        <v>13413</v>
+        <v>13416</v>
       </c>
       <c r="BE26" s="5">
         <f t="shared" si="21"/>
-        <v>0.97769516728624539</v>
+        <v>0.97791384211677235</v>
       </c>
       <c r="BF26" s="9">
         <v>25779</v>
@@ -4923,14 +4923,14 @@
       </c>
       <c r="BH26" s="4">
         <f t="shared" si="22"/>
-        <v>6616</v>
+        <v>6621</v>
       </c>
       <c r="BI26" s="8">
-        <v>25114</v>
+        <v>25119</v>
       </c>
       <c r="BJ26" s="5">
         <f t="shared" si="23"/>
-        <v>0.97420380930214512</v>
+        <v>0.9743977656231817</v>
       </c>
     </row>
     <row r="27" spans="1:62" x14ac:dyDescent="0.3">
@@ -4948,14 +4948,14 @@
       </c>
       <c r="E27" s="4">
         <f t="shared" si="0"/>
-        <v>32552</v>
+        <v>32557</v>
       </c>
       <c r="F27" s="22">
-        <v>112754</v>
+        <v>112759</v>
       </c>
       <c r="G27" s="5">
         <f t="shared" si="1"/>
-        <v>0.95146237321317062</v>
+        <v>0.95150456516969606</v>
       </c>
       <c r="H27" s="9">
         <v>121212</v>
@@ -4965,14 +4965,14 @@
       </c>
       <c r="J27" s="4">
         <f t="shared" si="2"/>
-        <v>34892</v>
+        <v>34897</v>
       </c>
       <c r="K27" s="22">
-        <v>114774</v>
+        <v>114779</v>
       </c>
       <c r="L27" s="5">
         <f t="shared" si="3"/>
-        <v>0.94688644688644685</v>
+        <v>0.94692769692769696</v>
       </c>
       <c r="M27" s="4">
         <v>178312</v>
@@ -4982,14 +4982,14 @@
       </c>
       <c r="O27" s="4">
         <f t="shared" si="4"/>
-        <v>46487</v>
+        <v>46493</v>
       </c>
       <c r="P27" s="8">
-        <v>168575</v>
+        <v>168581</v>
       </c>
       <c r="Q27" s="5">
         <f t="shared" si="5"/>
-        <v>0.9453934676297725</v>
+        <v>0.94542711651487277</v>
       </c>
       <c r="R27" s="9">
         <v>121489</v>
@@ -4999,14 +4999,14 @@
       </c>
       <c r="T27" s="4">
         <f t="shared" si="6"/>
-        <v>32060</v>
+        <v>32065</v>
       </c>
       <c r="U27" s="22">
-        <v>114994</v>
+        <v>114999</v>
       </c>
       <c r="V27" s="5">
         <f t="shared" si="7"/>
-        <v>0.94653836972894667</v>
+        <v>0.94657952571837778</v>
       </c>
       <c r="W27" s="9">
         <v>123451</v>
@@ -5016,14 +5016,14 @@
       </c>
       <c r="Y27" s="4">
         <f t="shared" si="8"/>
-        <v>35411</v>
+        <v>35416</v>
       </c>
       <c r="Z27" s="22">
-        <v>116896</v>
+        <v>116901</v>
       </c>
       <c r="AA27" s="5">
         <f t="shared" si="9"/>
-        <v>0.94690200970425509</v>
+        <v>0.94694251160379417</v>
       </c>
       <c r="AB27" s="9">
         <v>182601</v>
@@ -5033,14 +5033,14 @@
       </c>
       <c r="AD27" s="4">
         <f t="shared" si="10"/>
-        <v>53462</v>
+        <v>53468</v>
       </c>
       <c r="AE27" s="8">
-        <v>173159</v>
+        <v>173165</v>
       </c>
       <c r="AF27" s="5">
         <f t="shared" si="11"/>
-        <v>0.94829163038537578</v>
+        <v>0.94832448891298515</v>
       </c>
       <c r="AG27" s="9">
         <v>124689</v>
@@ -5050,14 +5050,14 @@
       </c>
       <c r="AI27" s="4">
         <f t="shared" si="12"/>
-        <v>33822</v>
+        <v>33827</v>
       </c>
       <c r="AJ27" s="22">
-        <v>117386</v>
+        <v>117391</v>
       </c>
       <c r="AK27" s="5">
         <f t="shared" si="13"/>
-        <v>0.94143027853299011</v>
+        <v>0.94147037830121338</v>
       </c>
       <c r="AL27" s="9">
         <v>127177</v>
@@ -5067,14 +5067,14 @@
       </c>
       <c r="AN27" s="4">
         <f t="shared" si="14"/>
-        <v>31112</v>
+        <v>31118</v>
       </c>
       <c r="AO27" s="22">
-        <v>119322</v>
+        <v>119328</v>
       </c>
       <c r="AP27" s="5">
         <f t="shared" si="15"/>
-        <v>0.938235687270497</v>
+        <v>0.93828286561249286</v>
       </c>
       <c r="AQ27" s="15">
         <v>185152</v>
@@ -5084,14 +5084,14 @@
       </c>
       <c r="AS27" s="4">
         <f t="shared" si="16"/>
-        <v>44026</v>
+        <v>44035</v>
       </c>
       <c r="AT27" s="8">
-        <v>176386</v>
+        <v>176395</v>
       </c>
       <c r="AU27" s="5">
         <f t="shared" si="17"/>
-        <v>0.95265511579675077</v>
+        <v>0.95270372450743168</v>
       </c>
       <c r="AV27" s="9">
         <v>127611</v>
@@ -5101,14 +5101,14 @@
       </c>
       <c r="AX27" s="4">
         <f t="shared" si="18"/>
-        <v>30400</v>
+        <v>30407</v>
       </c>
       <c r="AY27" s="22">
-        <v>119200</v>
+        <v>119207</v>
       </c>
       <c r="AZ27" s="5">
         <f t="shared" si="19"/>
-        <v>0.93408875410427006</v>
+        <v>0.9341436083096285</v>
       </c>
       <c r="BA27" s="9">
         <v>122070</v>
@@ -5118,14 +5118,14 @@
       </c>
       <c r="BC27" s="4">
         <f t="shared" si="20"/>
-        <v>31278</v>
+        <v>31284</v>
       </c>
       <c r="BD27" s="8">
-        <v>120869</v>
+        <v>120875</v>
       </c>
       <c r="BE27" s="5">
         <f t="shared" si="21"/>
-        <v>0.99016138281314003</v>
+        <v>0.99021053493896949</v>
       </c>
       <c r="BF27" s="9">
         <v>180737</v>
@@ -5135,14 +5135,14 @@
       </c>
       <c r="BH27" s="4">
         <f t="shared" si="22"/>
-        <v>65920</v>
+        <v>65930</v>
       </c>
       <c r="BI27" s="8">
-        <v>179323</v>
+        <v>179333</v>
       </c>
       <c r="BJ27" s="5">
         <f t="shared" si="23"/>
-        <v>0.99217647742299586</v>
+        <v>0.9922318064369775</v>
       </c>
     </row>
     <row r="28" spans="1:62" x14ac:dyDescent="0.3">
@@ -5160,14 +5160,14 @@
       </c>
       <c r="E28" s="4">
         <f t="shared" si="0"/>
-        <v>55194</v>
+        <v>55196</v>
       </c>
       <c r="F28" s="22">
-        <v>349849</v>
+        <v>349851</v>
       </c>
       <c r="G28" s="5">
         <f t="shared" si="1"/>
-        <v>0.96017400373257222</v>
+        <v>0.96017949280930948</v>
       </c>
       <c r="H28" s="9">
         <v>368904</v>
@@ -5177,14 +5177,14 @@
       </c>
       <c r="J28" s="4">
         <f t="shared" si="2"/>
-        <v>63524</v>
+        <v>63526</v>
       </c>
       <c r="K28" s="22">
-        <v>354985</v>
+        <v>354987</v>
       </c>
       <c r="L28" s="5">
         <f t="shared" si="3"/>
-        <v>0.96226931667859383</v>
+        <v>0.96227473814325681</v>
       </c>
       <c r="M28" s="4">
         <v>633580</v>
@@ -5194,14 +5194,14 @@
       </c>
       <c r="O28" s="4">
         <f t="shared" si="4"/>
-        <v>99954</v>
+        <v>99956</v>
       </c>
       <c r="P28" s="8">
-        <v>609213</v>
+        <v>609215</v>
       </c>
       <c r="Q28" s="5">
         <f t="shared" si="5"/>
-        <v>0.96154076833233371</v>
+        <v>0.96154392499763253</v>
       </c>
       <c r="R28" s="9">
         <v>370844</v>
@@ -5211,14 +5211,14 @@
       </c>
       <c r="T28" s="4">
         <f t="shared" si="6"/>
-        <v>61807</v>
+        <v>61809</v>
       </c>
       <c r="U28" s="22">
-        <v>357054</v>
+        <v>357056</v>
       </c>
       <c r="V28" s="5">
         <f t="shared" si="7"/>
-        <v>0.96281455274994332</v>
+        <v>0.96281994585324282</v>
       </c>
       <c r="W28" s="9">
         <v>375522</v>
@@ -5228,14 +5228,14 @@
       </c>
       <c r="Y28" s="4">
         <f t="shared" si="8"/>
-        <v>66531</v>
+        <v>66534</v>
       </c>
       <c r="Z28" s="22">
-        <v>361725</v>
+        <v>361728</v>
       </c>
       <c r="AA28" s="5">
         <f t="shared" si="9"/>
-        <v>0.96325914327256457</v>
+        <v>0.9632671321520444</v>
       </c>
       <c r="AB28" s="9">
         <v>643156</v>
@@ -5245,14 +5245,14 @@
       </c>
       <c r="AD28" s="4">
         <f t="shared" si="10"/>
-        <v>116196</v>
+        <v>116200</v>
       </c>
       <c r="AE28" s="8">
-        <v>620723</v>
+        <v>620727</v>
       </c>
       <c r="AF28" s="5">
         <f t="shared" si="11"/>
-        <v>0.96512043734335062</v>
+        <v>0.965126656674275</v>
       </c>
       <c r="AG28" s="9">
         <v>378725</v>
@@ -5262,14 +5262,14 @@
       </c>
       <c r="AI28" s="4">
         <f t="shared" si="12"/>
-        <v>65131</v>
+        <v>65134</v>
       </c>
       <c r="AJ28" s="22">
-        <v>363075</v>
+        <v>363078</v>
       </c>
       <c r="AK28" s="5">
         <f t="shared" si="13"/>
-        <v>0.95867714040530727</v>
+        <v>0.95868506172024559</v>
       </c>
       <c r="AL28" s="9">
         <v>382864</v>
@@ -5279,14 +5279,14 @@
       </c>
       <c r="AN28" s="4">
         <f t="shared" si="14"/>
-        <v>58059</v>
+        <v>58061</v>
       </c>
       <c r="AO28" s="22">
-        <v>368529</v>
+        <v>368531</v>
       </c>
       <c r="AP28" s="5">
         <f t="shared" si="15"/>
-        <v>0.96255850641481044</v>
+        <v>0.96256373020184716</v>
       </c>
       <c r="AQ28" s="15">
         <v>653033</v>
@@ -5296,14 +5296,14 @@
       </c>
       <c r="AS28" s="4">
         <f t="shared" si="16"/>
-        <v>88400</v>
+        <v>88404</v>
       </c>
       <c r="AT28" s="8">
-        <v>628961</v>
+        <v>628965</v>
       </c>
       <c r="AU28" s="5">
         <f t="shared" si="17"/>
-        <v>0.96313815687721749</v>
+        <v>0.96314428214194381</v>
       </c>
       <c r="AV28" s="9">
         <v>393378</v>
@@ -5313,14 +5313,14 @@
       </c>
       <c r="AX28" s="4">
         <f t="shared" si="18"/>
-        <v>54870</v>
+        <v>54872</v>
       </c>
       <c r="AY28" s="22">
-        <v>371534</v>
+        <v>371536</v>
       </c>
       <c r="AZ28" s="5">
         <f t="shared" si="19"/>
-        <v>0.94447071264788574</v>
+        <v>0.94447579681629379</v>
       </c>
       <c r="BA28" s="9">
         <v>381893</v>
@@ -5330,14 +5330,14 @@
       </c>
       <c r="BC28" s="4">
         <f t="shared" si="20"/>
-        <v>57996</v>
+        <v>57998</v>
       </c>
       <c r="BD28" s="8">
-        <v>376653</v>
+        <v>376655</v>
       </c>
       <c r="BE28" s="5">
         <f t="shared" si="21"/>
-        <v>0.98627887916248791</v>
+        <v>0.98628411623150991</v>
       </c>
       <c r="BF28" s="9">
         <v>643514</v>
@@ -5347,14 +5347,14 @@
       </c>
       <c r="BH28" s="4">
         <f t="shared" si="22"/>
-        <v>133751</v>
+        <v>133755</v>
       </c>
       <c r="BI28" s="8">
-        <v>639626</v>
+        <v>639630</v>
       </c>
       <c r="BJ28" s="5">
         <f t="shared" si="23"/>
-        <v>0.99395817340415282</v>
+        <v>0.9939643892751362</v>
       </c>
     </row>
     <row r="29" spans="1:62" x14ac:dyDescent="0.3">
@@ -5406,14 +5406,14 @@
       </c>
       <c r="O29" s="4">
         <f t="shared" si="4"/>
-        <v>30926</v>
+        <v>30927</v>
       </c>
       <c r="P29" s="8">
-        <v>162690</v>
+        <v>162691</v>
       </c>
       <c r="Q29" s="5">
         <f t="shared" si="5"/>
-        <v>0.96324979129291821</v>
+        <v>0.96325571206119709</v>
       </c>
       <c r="R29" s="9">
         <v>122532</v>
@@ -5457,14 +5457,14 @@
       </c>
       <c r="AD29" s="4">
         <f t="shared" si="10"/>
-        <v>37472</v>
+        <v>37473</v>
       </c>
       <c r="AE29" s="8">
-        <v>166136</v>
+        <v>166137</v>
       </c>
       <c r="AF29" s="5">
         <f t="shared" si="11"/>
-        <v>0.96214231524326332</v>
+        <v>0.96214810653663285</v>
       </c>
       <c r="AG29" s="9">
         <v>125793</v>
@@ -5508,14 +5508,14 @@
       </c>
       <c r="AS29" s="4">
         <f t="shared" si="16"/>
-        <v>28295</v>
+        <v>28296</v>
       </c>
       <c r="AT29" s="8">
-        <v>169051</v>
+        <v>169052</v>
       </c>
       <c r="AU29" s="5">
         <f t="shared" si="17"/>
-        <v>0.96142384294277561</v>
+        <v>0.96142953012500432</v>
       </c>
       <c r="AV29" s="9">
         <v>130198</v>
@@ -5542,14 +5542,14 @@
       </c>
       <c r="BC29" s="4">
         <f t="shared" si="20"/>
-        <v>22789</v>
+        <v>22790</v>
       </c>
       <c r="BD29" s="8">
-        <v>125576</v>
+        <v>125577</v>
       </c>
       <c r="BE29" s="5">
         <f t="shared" si="21"/>
-        <v>0.98456231134109529</v>
+        <v>0.9845701517111608</v>
       </c>
       <c r="BF29" s="9">
         <v>174166</v>
@@ -5559,14 +5559,14 @@
       </c>
       <c r="BH29" s="4">
         <f t="shared" si="22"/>
-        <v>42586</v>
+        <v>42587</v>
       </c>
       <c r="BI29" s="8">
-        <v>172592</v>
+        <v>172593</v>
       </c>
       <c r="BJ29" s="5">
         <f t="shared" si="23"/>
-        <v>0.99096264483309027</v>
+        <v>0.99096838648186214</v>
       </c>
     </row>
     <row r="30" spans="1:62" x14ac:dyDescent="0.3">
@@ -5584,14 +5584,14 @@
       </c>
       <c r="E30" s="4">
         <f t="shared" si="0"/>
-        <v>33471</v>
+        <v>33472</v>
       </c>
       <c r="F30" s="22">
-        <v>151940</v>
+        <v>151941</v>
       </c>
       <c r="G30" s="5">
         <f t="shared" si="1"/>
-        <v>0.95785054152534899</v>
+        <v>0.95785684566212348</v>
       </c>
       <c r="H30" s="9">
         <v>160653</v>
@@ -5601,14 +5601,14 @@
       </c>
       <c r="J30" s="4">
         <f t="shared" si="2"/>
-        <v>39622</v>
+        <v>39623</v>
       </c>
       <c r="K30" s="22">
-        <v>155060</v>
+        <v>155061</v>
       </c>
       <c r="L30" s="5">
         <f t="shared" si="3"/>
-        <v>0.96518583530964253</v>
+        <v>0.9651920599055106</v>
       </c>
       <c r="M30" s="4">
         <v>275749</v>
@@ -5618,14 +5618,14 @@
       </c>
       <c r="O30" s="4">
         <f t="shared" si="4"/>
-        <v>59342</v>
+        <v>59345</v>
       </c>
       <c r="P30" s="8">
-        <v>264941</v>
+        <v>264944</v>
       </c>
       <c r="Q30" s="5">
         <f t="shared" si="5"/>
-        <v>0.96080493492270147</v>
+        <v>0.96081581438191976</v>
       </c>
       <c r="R30" s="9">
         <v>161454</v>
@@ -5635,14 +5635,14 @@
       </c>
       <c r="T30" s="4">
         <f t="shared" si="6"/>
-        <v>35705</v>
+        <v>35706</v>
       </c>
       <c r="U30" s="22">
-        <v>154878</v>
+        <v>154879</v>
       </c>
       <c r="V30" s="5">
         <f t="shared" si="7"/>
-        <v>0.95927013266936711</v>
+        <v>0.95927632638398552</v>
       </c>
       <c r="W30" s="9">
         <v>163696</v>
@@ -5652,14 +5652,14 @@
       </c>
       <c r="Y30" s="4">
         <f t="shared" si="8"/>
-        <v>38336</v>
+        <v>38337</v>
       </c>
       <c r="Z30" s="22">
-        <v>157862</v>
+        <v>157863</v>
       </c>
       <c r="AA30" s="5">
         <f t="shared" si="9"/>
-        <v>0.96436076629850453</v>
+        <v>0.96436687518326658</v>
       </c>
       <c r="AB30" s="9">
         <v>281667</v>
@@ -5669,14 +5669,14 @@
       </c>
       <c r="AD30" s="4">
         <f t="shared" si="10"/>
-        <v>68188</v>
+        <v>68191</v>
       </c>
       <c r="AE30" s="8">
-        <v>270987</v>
+        <v>270990</v>
       </c>
       <c r="AF30" s="5">
         <f t="shared" si="11"/>
-        <v>0.96208288510901174</v>
+        <v>0.96209353598398106</v>
       </c>
       <c r="AG30" s="9">
         <v>165324</v>
@@ -5686,14 +5686,14 @@
       </c>
       <c r="AI30" s="4">
         <f t="shared" si="12"/>
-        <v>38752</v>
+        <v>38753</v>
       </c>
       <c r="AJ30" s="22">
-        <v>158464</v>
+        <v>158465</v>
       </c>
       <c r="AK30" s="5">
         <f t="shared" si="13"/>
-        <v>0.95850572209721518</v>
+        <v>0.95851177082577244</v>
       </c>
       <c r="AL30" s="9">
         <v>168552</v>
@@ -5703,14 +5703,14 @@
       </c>
       <c r="AN30" s="4">
         <f t="shared" si="14"/>
-        <v>34436</v>
+        <v>34438</v>
       </c>
       <c r="AO30" s="22">
-        <v>161928</v>
+        <v>161930</v>
       </c>
       <c r="AP30" s="5">
         <f t="shared" si="15"/>
-        <v>0.96070055531824006</v>
+        <v>0.96071242109260047</v>
       </c>
       <c r="AQ30" s="15">
         <v>288456</v>
@@ -5720,14 +5720,14 @@
       </c>
       <c r="AS30" s="4">
         <f t="shared" si="16"/>
-        <v>55844</v>
+        <v>55846</v>
       </c>
       <c r="AT30" s="8">
-        <v>277217</v>
+        <v>277219</v>
       </c>
       <c r="AU30" s="5">
         <f t="shared" si="17"/>
-        <v>0.96103738525113014</v>
+        <v>0.961044318717586</v>
       </c>
       <c r="AV30" s="9">
         <v>173481</v>
@@ -5737,14 +5737,14 @@
       </c>
       <c r="AX30" s="4">
         <f t="shared" si="18"/>
-        <v>35289</v>
+        <v>35290</v>
       </c>
       <c r="AY30" s="22">
-        <v>162971</v>
+        <v>162972</v>
       </c>
       <c r="AZ30" s="5">
         <f t="shared" si="19"/>
-        <v>0.93941699667398737</v>
+        <v>0.93942276099399935</v>
       </c>
       <c r="BA30" s="9">
         <v>168414</v>
@@ -5754,14 +5754,14 @@
       </c>
       <c r="BC30" s="4">
         <f t="shared" si="20"/>
-        <v>35318</v>
+        <v>35319</v>
       </c>
       <c r="BD30" s="8">
-        <v>165838</v>
+        <v>165839</v>
       </c>
       <c r="BE30" s="5">
         <f t="shared" si="21"/>
-        <v>0.98470435949505386</v>
+        <v>0.98471029724369707</v>
       </c>
       <c r="BF30" s="9">
         <v>284492</v>
@@ -5771,14 +5771,14 @@
       </c>
       <c r="BH30" s="4">
         <f t="shared" si="22"/>
-        <v>78359</v>
+        <v>78362</v>
       </c>
       <c r="BI30" s="8">
-        <v>283039</v>
+        <v>283042</v>
       </c>
       <c r="BJ30" s="5">
         <f t="shared" si="23"/>
-        <v>0.99489265075995104</v>
+        <v>0.9949031958719402</v>
       </c>
     </row>
     <row r="31" spans="1:62" x14ac:dyDescent="0.3">
@@ -5796,14 +5796,14 @@
       </c>
       <c r="E31" s="4">
         <f t="shared" si="0"/>
-        <v>20669</v>
+        <v>20670</v>
       </c>
       <c r="F31" s="22">
-        <v>71429</v>
+        <v>71430</v>
       </c>
       <c r="G31" s="5">
         <f t="shared" si="1"/>
-        <v>0.96071284465366513</v>
+        <v>0.9607262945527909</v>
       </c>
       <c r="H31" s="9">
         <v>75353</v>
@@ -5813,14 +5813,14 @@
       </c>
       <c r="J31" s="4">
         <f t="shared" si="2"/>
-        <v>22532</v>
+        <v>22534</v>
       </c>
       <c r="K31" s="22">
-        <v>72502</v>
+        <v>72504</v>
       </c>
       <c r="L31" s="5">
         <f t="shared" si="3"/>
-        <v>0.96216474460207291</v>
+        <v>0.96219128634560003</v>
       </c>
       <c r="M31" s="4">
         <v>132153</v>
@@ -5830,14 +5830,14 @@
       </c>
       <c r="O31" s="4">
         <f t="shared" si="4"/>
-        <v>36844</v>
+        <v>36849</v>
       </c>
       <c r="P31" s="8">
-        <v>126928</v>
+        <v>126933</v>
       </c>
       <c r="Q31" s="5">
         <f t="shared" si="5"/>
-        <v>0.9604624942301726</v>
+        <v>0.96050032916392358</v>
       </c>
       <c r="R31" s="9">
         <v>74474</v>
@@ -5847,14 +5847,14 @@
       </c>
       <c r="T31" s="4">
         <f t="shared" si="6"/>
-        <v>20041</v>
+        <v>20043</v>
       </c>
       <c r="U31" s="22">
-        <v>71227</v>
+        <v>71229</v>
       </c>
       <c r="V31" s="5">
         <f t="shared" si="7"/>
-        <v>0.95640089158632546</v>
+        <v>0.9564277465961275</v>
       </c>
       <c r="W31" s="9">
         <v>75697</v>
@@ -5864,14 +5864,14 @@
       </c>
       <c r="Y31" s="4">
         <f t="shared" si="8"/>
-        <v>22606</v>
+        <v>22608</v>
       </c>
       <c r="Z31" s="22">
-        <v>72499</v>
+        <v>72501</v>
       </c>
       <c r="AA31" s="5">
         <f t="shared" si="9"/>
-        <v>0.95775261899414776</v>
+        <v>0.95777904012048032</v>
       </c>
       <c r="AB31" s="9">
         <v>133809</v>
@@ -5881,14 +5881,14 @@
       </c>
       <c r="AD31" s="4">
         <f t="shared" si="10"/>
-        <v>38783</v>
+        <v>38788</v>
       </c>
       <c r="AE31" s="8">
-        <v>129174</v>
+        <v>129179</v>
       </c>
       <c r="AF31" s="5">
         <f t="shared" si="11"/>
-        <v>0.96536107436719498</v>
+        <v>0.96539844106151307</v>
       </c>
       <c r="AG31" s="9">
         <v>75434</v>
@@ -5898,14 +5898,14 @@
       </c>
       <c r="AI31" s="4">
         <f t="shared" si="12"/>
-        <v>21526</v>
+        <v>21529</v>
       </c>
       <c r="AJ31" s="22">
-        <v>72292</v>
+        <v>72295</v>
       </c>
       <c r="AK31" s="5">
         <f t="shared" si="13"/>
-        <v>0.95834769467348946</v>
+        <v>0.95838746453853696</v>
       </c>
       <c r="AL31" s="9">
         <v>76990</v>
@@ -5915,14 +5915,14 @@
       </c>
       <c r="AN31" s="4">
         <f t="shared" si="14"/>
-        <v>18796</v>
+        <v>18800</v>
       </c>
       <c r="AO31" s="22">
-        <v>73395</v>
+        <v>73399</v>
       </c>
       <c r="AP31" s="5">
         <f t="shared" si="15"/>
-        <v>0.95330562410702691</v>
+        <v>0.95335757890635142</v>
       </c>
       <c r="AQ31" s="15">
         <v>135546</v>
@@ -5932,14 +5932,14 @@
       </c>
       <c r="AS31" s="4">
         <f t="shared" si="16"/>
-        <v>32611</v>
+        <v>32617</v>
       </c>
       <c r="AT31" s="8">
-        <v>131028</v>
+        <v>131034</v>
       </c>
       <c r="AU31" s="5">
         <f t="shared" si="17"/>
-        <v>0.96666814218051433</v>
+        <v>0.96671240759594523</v>
       </c>
       <c r="AV31" s="9">
         <v>78435</v>
@@ -5949,14 +5949,14 @@
       </c>
       <c r="AX31" s="4">
         <f t="shared" si="18"/>
-        <v>18416</v>
+        <v>18418</v>
       </c>
       <c r="AY31" s="22">
-        <v>73385</v>
+        <v>73387</v>
       </c>
       <c r="AZ31" s="5">
         <f t="shared" si="19"/>
-        <v>0.93561547778415244</v>
+        <v>0.93564097660483203</v>
       </c>
       <c r="BA31" s="9">
         <v>76166</v>
@@ -5966,14 +5966,14 @@
       </c>
       <c r="BC31" s="4">
         <f t="shared" si="20"/>
-        <v>19440</v>
+        <v>19443</v>
       </c>
       <c r="BD31" s="8">
-        <v>74503</v>
+        <v>74506</v>
       </c>
       <c r="BE31" s="5">
         <f t="shared" si="21"/>
-        <v>0.97816611086311478</v>
+        <v>0.97820549851639838</v>
       </c>
       <c r="BF31" s="9">
         <v>132970</v>
@@ -5983,14 +5983,14 @@
       </c>
       <c r="BH31" s="4">
         <f t="shared" si="22"/>
-        <v>49524</v>
+        <v>49530</v>
       </c>
       <c r="BI31" s="8">
-        <v>132946</v>
+        <v>132952</v>
       </c>
       <c r="BJ31" s="5">
         <f t="shared" si="23"/>
-        <v>0.9998195081597353</v>
+        <v>0.99986463111980151</v>
       </c>
     </row>
     <row r="32" spans="1:62" x14ac:dyDescent="0.3">
@@ -6042,14 +6042,14 @@
       </c>
       <c r="O32" s="4">
         <f t="shared" si="4"/>
-        <v>94440</v>
+        <v>94442</v>
       </c>
       <c r="P32" s="8">
-        <v>409070</v>
+        <v>409072</v>
       </c>
       <c r="Q32" s="5">
         <f t="shared" si="5"/>
-        <v>0.97747415154708395</v>
+        <v>0.97747893055386303</v>
       </c>
       <c r="R32" s="9">
         <v>194320</v>
@@ -6059,14 +6059,14 @@
       </c>
       <c r="T32" s="4">
         <f t="shared" si="6"/>
-        <v>42838</v>
+        <v>42839</v>
       </c>
       <c r="U32" s="22">
-        <v>190344</v>
+        <v>190345</v>
       </c>
       <c r="V32" s="5">
         <f t="shared" si="7"/>
-        <v>0.97953890489913542</v>
+        <v>0.97954405104981479</v>
       </c>
       <c r="W32" s="9">
         <v>198209</v>
@@ -6076,14 +6076,14 @@
       </c>
       <c r="Y32" s="4">
         <f t="shared" si="8"/>
-        <v>47430</v>
+        <v>47431</v>
       </c>
       <c r="Z32" s="22">
-        <v>194353</v>
+        <v>194354</v>
       </c>
       <c r="AA32" s="5">
         <f t="shared" si="9"/>
-        <v>0.98054578752730703</v>
+        <v>0.98055083270689025</v>
       </c>
       <c r="AB32" s="9">
         <v>426405</v>
@@ -6093,14 +6093,14 @@
       </c>
       <c r="AD32" s="4">
         <f t="shared" si="10"/>
-        <v>98664</v>
+        <v>98666</v>
       </c>
       <c r="AE32" s="8">
-        <v>418378</v>
+        <v>418380</v>
       </c>
       <c r="AF32" s="5">
         <f t="shared" si="11"/>
-        <v>0.98117517383707975</v>
+        <v>0.98117986421359971</v>
       </c>
       <c r="AG32" s="9">
         <v>199136</v>
@@ -6110,14 +6110,14 @@
       </c>
       <c r="AI32" s="4">
         <f t="shared" si="12"/>
-        <v>44765</v>
+        <v>44767</v>
       </c>
       <c r="AJ32" s="22">
-        <v>195378</v>
+        <v>195380</v>
       </c>
       <c r="AK32" s="5">
         <f t="shared" si="13"/>
-        <v>0.98112847501205203</v>
+        <v>0.98113851839948574</v>
       </c>
       <c r="AL32" s="9">
         <v>204506</v>
@@ -6127,14 +6127,14 @@
       </c>
       <c r="AN32" s="4">
         <f t="shared" si="14"/>
-        <v>38340</v>
+        <v>38342</v>
       </c>
       <c r="AO32" s="22">
-        <v>199945</v>
+        <v>199947</v>
       </c>
       <c r="AP32" s="5">
         <f t="shared" si="15"/>
-        <v>0.97769747586867872</v>
+        <v>0.97770725553284499</v>
       </c>
       <c r="AQ32" s="15">
         <v>435626</v>
@@ -6144,14 +6144,14 @@
       </c>
       <c r="AS32" s="4">
         <f t="shared" si="16"/>
-        <v>82517</v>
+        <v>82518</v>
       </c>
       <c r="AT32" s="8">
-        <v>426563</v>
+        <v>426564</v>
       </c>
       <c r="AU32" s="5">
         <f t="shared" si="17"/>
-        <v>0.97919545665318419</v>
+        <v>0.97919775220028193</v>
       </c>
       <c r="AV32" s="9">
         <v>208760</v>
@@ -6161,14 +6161,14 @@
       </c>
       <c r="AX32" s="4">
         <f t="shared" si="18"/>
-        <v>38565</v>
+        <v>38566</v>
       </c>
       <c r="AY32" s="22">
-        <v>199579</v>
+        <v>199580</v>
       </c>
       <c r="AZ32" s="5">
         <f t="shared" si="19"/>
-        <v>0.95602126844223034</v>
+        <v>0.9560260586319218</v>
       </c>
       <c r="BA32" s="9">
         <v>206539</v>
@@ -6178,14 +6178,14 @@
       </c>
       <c r="BC32" s="4">
         <f t="shared" si="20"/>
-        <v>40475</v>
+        <v>40476</v>
       </c>
       <c r="BD32" s="8">
-        <v>203796</v>
+        <v>203797</v>
       </c>
       <c r="BE32" s="5">
         <f t="shared" si="21"/>
-        <v>0.98671921525716688</v>
+        <v>0.98672405695776588</v>
       </c>
       <c r="BF32" s="9">
         <v>435831</v>
@@ -6195,14 +6195,14 @@
       </c>
       <c r="BH32" s="4">
         <f t="shared" si="22"/>
-        <v>128638</v>
+        <v>128639</v>
       </c>
       <c r="BI32" s="8">
-        <v>435170</v>
+        <v>435171</v>
       </c>
       <c r="BJ32" s="5">
         <f t="shared" si="23"/>
-        <v>0.99848335708107039</v>
+        <v>0.99848565154842128</v>
       </c>
     </row>
     <row r="33" spans="1:62" x14ac:dyDescent="0.3">
@@ -6220,14 +6220,14 @@
       </c>
       <c r="E33" s="4">
         <f t="shared" si="0"/>
-        <v>71715</v>
+        <v>71716</v>
       </c>
       <c r="F33" s="22">
-        <v>581083</v>
+        <v>581084</v>
       </c>
       <c r="G33" s="5">
         <f t="shared" si="1"/>
-        <v>0.99075202853503874</v>
+        <v>0.99075373354452723</v>
       </c>
       <c r="H33" s="9">
         <v>594451</v>
@@ -6237,14 +6237,14 @@
       </c>
       <c r="J33" s="4">
         <f t="shared" si="2"/>
-        <v>83846</v>
+        <v>83847</v>
       </c>
       <c r="K33" s="22">
-        <v>590879</v>
+        <v>590880</v>
       </c>
       <c r="L33" s="5">
         <f t="shared" si="3"/>
-        <v>0.99399109430381982</v>
+        <v>0.99399277652825879</v>
       </c>
       <c r="M33" s="4">
         <v>1006436</v>
@@ -6254,14 +6254,14 @@
       </c>
       <c r="O33" s="4">
         <f t="shared" si="4"/>
-        <v>139355</v>
+        <v>139356</v>
       </c>
       <c r="P33" s="8">
-        <v>991604</v>
+        <v>991605</v>
       </c>
       <c r="Q33" s="5">
         <f t="shared" si="5"/>
-        <v>0.98526284830828781</v>
+        <v>0.98526384191344507</v>
       </c>
       <c r="R33" s="9">
         <v>599279</v>
@@ -6271,14 +6271,14 @@
       </c>
       <c r="T33" s="4">
         <f t="shared" si="6"/>
-        <v>86663</v>
+        <v>86664</v>
       </c>
       <c r="U33" s="22">
-        <v>593527</v>
+        <v>593528</v>
       </c>
       <c r="V33" s="5">
         <f t="shared" si="7"/>
-        <v>0.99040179949572738</v>
+        <v>0.9904034681675814</v>
       </c>
       <c r="W33" s="9">
         <v>608923</v>
@@ -6288,14 +6288,14 @@
       </c>
       <c r="Y33" s="4">
         <f t="shared" si="8"/>
-        <v>85229</v>
+        <v>85230</v>
       </c>
       <c r="Z33" s="22">
-        <v>601217</v>
+        <v>601218</v>
       </c>
       <c r="AA33" s="5">
         <f t="shared" si="9"/>
-        <v>0.98734486954836653</v>
+        <v>0.9873465117921314</v>
       </c>
       <c r="AB33" s="9">
         <v>1019860</v>
@@ -6305,14 +6305,14 @@
       </c>
       <c r="AD33" s="4">
         <f t="shared" si="10"/>
-        <v>135719</v>
+        <v>135720</v>
       </c>
       <c r="AE33" s="8">
-        <v>1006180</v>
+        <v>1006181</v>
       </c>
       <c r="AF33" s="5">
         <f t="shared" si="11"/>
-        <v>0.98658639421097016</v>
+        <v>0.98658737473770908</v>
       </c>
       <c r="AG33" s="9">
         <v>610453</v>
@@ -6322,14 +6322,14 @@
       </c>
       <c r="AI33" s="4">
         <f t="shared" si="12"/>
-        <v>86831</v>
+        <v>86832</v>
       </c>
       <c r="AJ33" s="22">
-        <v>602922</v>
+        <v>602923</v>
       </c>
       <c r="AK33" s="5">
         <f t="shared" si="13"/>
-        <v>0.98766325990698711</v>
+        <v>0.98766489803473811</v>
       </c>
       <c r="AL33" s="9">
         <v>617988</v>
@@ -6339,14 +6339,14 @@
       </c>
       <c r="AN33" s="4">
         <f t="shared" si="14"/>
-        <v>70939</v>
+        <v>70940</v>
       </c>
       <c r="AO33" s="22">
-        <v>608865</v>
+        <v>608866</v>
       </c>
       <c r="AP33" s="5">
         <f t="shared" si="15"/>
-        <v>0.98523757742868789</v>
+        <v>0.9852391955830857</v>
       </c>
       <c r="AQ33" s="15">
         <v>1027609</v>
@@ -6356,14 +6356,14 @@
       </c>
       <c r="AS33" s="4">
         <f t="shared" si="16"/>
-        <v>122616</v>
+        <v>122617</v>
       </c>
       <c r="AT33" s="8">
-        <v>1015121</v>
+        <v>1015122</v>
       </c>
       <c r="AU33" s="5">
         <f t="shared" si="17"/>
-        <v>0.98784751787888192</v>
+        <v>0.98784849101165906</v>
       </c>
       <c r="AV33" s="9">
         <v>625585</v>
@@ -6373,14 +6373,14 @@
       </c>
       <c r="AX33" s="4">
         <f t="shared" si="18"/>
-        <v>71277</v>
+        <v>71278</v>
       </c>
       <c r="AY33" s="22">
-        <v>611824</v>
+        <v>611825</v>
       </c>
       <c r="AZ33" s="5">
         <f t="shared" si="19"/>
-        <v>0.97800298920210682</v>
+        <v>0.97800458770590726</v>
       </c>
       <c r="BA33" s="9">
         <v>617039</v>
@@ -6390,14 +6390,14 @@
       </c>
       <c r="BC33" s="4">
         <f t="shared" si="20"/>
-        <v>71308</v>
+        <v>71309</v>
       </c>
       <c r="BD33" s="8">
-        <v>617612</v>
+        <v>617613</v>
       </c>
       <c r="BE33" s="5">
         <f t="shared" si="21"/>
-        <v>1.0009286284983607</v>
+        <v>1.0009302491414642</v>
       </c>
       <c r="BF33" s="9">
         <v>1025594</v>
@@ -6407,14 +6407,14 @@
       </c>
       <c r="BH33" s="4">
         <f t="shared" si="22"/>
-        <v>171344</v>
+        <v>171345</v>
       </c>
       <c r="BI33" s="8">
-        <v>1028384</v>
+        <v>1028385</v>
       </c>
       <c r="BJ33" s="5">
         <f t="shared" si="23"/>
-        <v>1.0027203747291813</v>
+        <v>1.0027213497738872</v>
       </c>
     </row>
     <row r="34" spans="1:62" x14ac:dyDescent="0.3">
@@ -6832,14 +6832,14 @@
       </c>
       <c r="E36" s="4">
         <f t="shared" si="0"/>
-        <v>170284</v>
+        <v>170295</v>
       </c>
       <c r="F36" s="22">
-        <v>777375</v>
+        <v>777386</v>
       </c>
       <c r="G36" s="5">
         <f t="shared" si="24"/>
-        <v>0.96670277099698942</v>
+        <v>0.96671645001995898</v>
       </c>
       <c r="H36" s="9">
         <v>814447</v>
@@ -6849,14 +6849,14 @@
       </c>
       <c r="J36" s="4">
         <f t="shared" si="2"/>
-        <v>192024</v>
+        <v>192035</v>
       </c>
       <c r="K36" s="22">
-        <v>789154</v>
+        <v>789165</v>
       </c>
       <c r="L36" s="5">
         <f t="shared" si="3"/>
-        <v>0.96894457220666297</v>
+        <v>0.96895807830343783</v>
       </c>
       <c r="M36" s="4">
         <v>1485608</v>
@@ -6866,14 +6866,14 @@
       </c>
       <c r="O36" s="4">
         <f t="shared" si="4"/>
-        <v>325435</v>
+        <v>325451</v>
       </c>
       <c r="P36" s="8">
-        <v>1435377</v>
+        <v>1435393</v>
       </c>
       <c r="Q36" s="5">
         <f t="shared" si="5"/>
-        <v>0.96618825423664922</v>
+        <v>0.96619902423788784</v>
       </c>
       <c r="R36" s="9">
         <v>815623</v>
@@ -6883,14 +6883,14 @@
       </c>
       <c r="T36" s="4">
         <f t="shared" si="6"/>
-        <v>178495</v>
+        <v>178507</v>
       </c>
       <c r="U36" s="22">
-        <v>787757</v>
+        <v>787769</v>
       </c>
       <c r="V36" s="5">
         <f t="shared" si="7"/>
-        <v>0.96583470549506323</v>
+        <v>0.96584941817481851</v>
       </c>
       <c r="W36" s="9">
         <v>826349</v>
@@ -6900,14 +6900,14 @@
       </c>
       <c r="Y36" s="4">
         <f t="shared" si="8"/>
-        <v>192810</v>
+        <v>192823</v>
       </c>
       <c r="Z36" s="22">
-        <v>797798</v>
+        <v>797811</v>
       </c>
       <c r="AA36" s="5">
         <f t="shared" si="9"/>
-        <v>0.96544922302804259</v>
+        <v>0.96546495487983885</v>
       </c>
       <c r="AB36" s="9">
         <v>1500292</v>
@@ -6917,14 +6917,14 @@
       </c>
       <c r="AD36" s="4">
         <f t="shared" si="10"/>
-        <v>350426</v>
+        <v>350445</v>
       </c>
       <c r="AE36" s="8">
-        <v>1453898</v>
+        <v>1453917</v>
       </c>
       <c r="AF36" s="5">
         <f t="shared" si="11"/>
-        <v>0.96907668640504652</v>
+        <v>0.96908935060641532</v>
       </c>
       <c r="AG36" s="9">
         <v>833041</v>
@@ -6934,14 +6934,14 @@
       </c>
       <c r="AI36" s="4">
         <f t="shared" si="12"/>
-        <v>198234</v>
+        <v>198245</v>
       </c>
       <c r="AJ36" s="22">
-        <v>803830</v>
+        <v>803841</v>
       </c>
       <c r="AK36" s="5">
         <f t="shared" si="13"/>
-        <v>0.96493449902225703</v>
+        <v>0.96494770365444194</v>
       </c>
       <c r="AL36" s="9">
         <v>845911</v>
@@ -6951,14 +6951,14 @@
       </c>
       <c r="AN36" s="4">
         <f t="shared" si="14"/>
-        <v>169642</v>
+        <v>169654</v>
       </c>
       <c r="AO36" s="22">
-        <v>816451</v>
+        <v>816463</v>
       </c>
       <c r="AP36" s="5">
         <f t="shared" si="15"/>
-        <v>0.96517364119866034</v>
+        <v>0.96518782708819251</v>
       </c>
       <c r="AQ36" s="15">
         <v>1519147</v>
@@ -6968,14 +6968,14 @@
       </c>
       <c r="AS36" s="4">
         <f t="shared" si="16"/>
-        <v>287912</v>
+        <v>287931</v>
       </c>
       <c r="AT36" s="8">
-        <v>1474538</v>
+        <v>1474557</v>
       </c>
       <c r="AU36" s="5">
         <f t="shared" si="17"/>
-        <v>0.97063549478753541</v>
+        <v>0.97064800180627686</v>
       </c>
       <c r="AV36" s="9">
         <v>864672</v>
@@ -6985,14 +6985,14 @@
       </c>
       <c r="AX36" s="4">
         <f t="shared" si="18"/>
-        <v>160487</v>
+        <v>160498</v>
       </c>
       <c r="AY36" s="22">
-        <v>819041</v>
+        <v>819052</v>
       </c>
       <c r="AZ36" s="5">
         <f t="shared" si="19"/>
-        <v>0.94722738795751449</v>
+        <v>0.94724010954442839</v>
       </c>
       <c r="BA36" s="9">
         <v>838532</v>
@@ -7002,14 +7002,14 @@
       </c>
       <c r="BC36" s="4">
         <f t="shared" si="20"/>
-        <v>161104</v>
+        <v>161113</v>
       </c>
       <c r="BD36" s="8">
-        <v>830646</v>
+        <v>830655</v>
       </c>
       <c r="BE36" s="5">
         <f t="shared" si="21"/>
-        <v>0.99059546922478803</v>
+        <v>0.99060620226777274</v>
       </c>
       <c r="BF36" s="9">
         <v>1502094</v>
@@ -7019,14 +7019,14 @@
       </c>
       <c r="BH36" s="4">
         <f t="shared" si="22"/>
-        <v>388479</v>
+        <v>388495</v>
       </c>
       <c r="BI36" s="8">
-        <v>1495198</v>
+        <v>1495214</v>
       </c>
       <c r="BJ36" s="5">
         <f t="shared" si="23"/>
-        <v>0.9954090755971331</v>
+        <v>0.99541972739389151</v>
       </c>
     </row>
     <row r="37" spans="1:62" x14ac:dyDescent="0.3">
@@ -7044,14 +7044,14 @@
       </c>
       <c r="E37" s="4">
         <f t="shared" si="0"/>
-        <v>111280</v>
+        <v>111288</v>
       </c>
       <c r="F37" s="22">
-        <v>621128</v>
+        <v>621136</v>
       </c>
       <c r="G37" s="5">
         <f t="shared" si="24"/>
-        <v>0.95464598539585055</v>
+        <v>0.95465828103842854</v>
       </c>
       <c r="H37" s="9">
         <v>656039</v>
@@ -7061,14 +7061,14 @@
       </c>
       <c r="J37" s="4">
         <f t="shared" si="2"/>
-        <v>125857</v>
+        <v>125865</v>
       </c>
       <c r="K37" s="22">
-        <v>626351</v>
+        <v>626359</v>
       </c>
       <c r="L37" s="5">
         <f t="shared" si="3"/>
-        <v>0.95474659280926899</v>
+        <v>0.9547587872062484</v>
       </c>
       <c r="M37" s="4">
         <v>844882</v>
@@ -7078,14 +7078,14 @@
       </c>
       <c r="O37" s="4">
         <f t="shared" si="4"/>
-        <v>156042</v>
+        <v>156051</v>
       </c>
       <c r="P37" s="8">
-        <v>804120</v>
+        <v>804129</v>
       </c>
       <c r="Q37" s="5">
         <f t="shared" si="5"/>
-        <v>0.95175420946357003</v>
+        <v>0.95176486183869469</v>
       </c>
       <c r="R37" s="9">
         <v>664863</v>
@@ -7095,14 +7095,14 @@
       </c>
       <c r="T37" s="4">
         <f t="shared" si="6"/>
-        <v>120151</v>
+        <v>120159</v>
       </c>
       <c r="U37" s="22">
-        <v>632149</v>
+        <v>632157</v>
       </c>
       <c r="V37" s="5">
         <f t="shared" si="7"/>
-        <v>0.95079587824860157</v>
+        <v>0.95080791080267668</v>
       </c>
       <c r="W37" s="9">
         <v>670009</v>
@@ -7112,14 +7112,14 @@
       </c>
       <c r="Y37" s="4">
         <f t="shared" si="8"/>
-        <v>127245</v>
+        <v>127254</v>
       </c>
       <c r="Z37" s="22">
-        <v>638015</v>
+        <v>638024</v>
       </c>
       <c r="AA37" s="5">
         <f t="shared" si="9"/>
-        <v>0.95224840263339749</v>
+        <v>0.95226183528877972</v>
       </c>
       <c r="AB37" s="9">
         <v>858143</v>
@@ -7129,14 +7129,14 @@
       </c>
       <c r="AD37" s="4">
         <f t="shared" si="10"/>
-        <v>183045</v>
+        <v>183055</v>
       </c>
       <c r="AE37" s="8">
-        <v>818662</v>
+        <v>818672</v>
       </c>
       <c r="AF37" s="5">
         <f t="shared" si="11"/>
-        <v>0.95399251639878202</v>
+        <v>0.95400416946825883</v>
       </c>
       <c r="AG37" s="9">
         <v>675943</v>
@@ -7146,14 +7146,14 @@
       </c>
       <c r="AI37" s="4">
         <f t="shared" si="12"/>
-        <v>129762</v>
+        <v>129771</v>
       </c>
       <c r="AJ37" s="22">
-        <v>644469</v>
+        <v>644478</v>
       </c>
       <c r="AK37" s="5">
         <f t="shared" si="13"/>
-        <v>0.95343690222400412</v>
+        <v>0.9534502169561635</v>
       </c>
       <c r="AL37" s="9">
         <v>678429</v>
@@ -7163,14 +7163,14 @@
       </c>
       <c r="AN37" s="4">
         <f t="shared" si="14"/>
-        <v>111957</v>
+        <v>111965</v>
       </c>
       <c r="AO37" s="22">
-        <v>650671</v>
+        <v>650679</v>
       </c>
       <c r="AP37" s="5">
         <f t="shared" si="15"/>
-        <v>0.95908488581708629</v>
+        <v>0.9590966777658384</v>
       </c>
       <c r="AQ37" s="15">
         <v>865622</v>
@@ -7180,14 +7180,14 @@
       </c>
       <c r="AS37" s="4">
         <f t="shared" si="16"/>
-        <v>140838</v>
+        <v>140847</v>
       </c>
       <c r="AT37" s="8">
-        <v>832579</v>
+        <v>832588</v>
       </c>
       <c r="AU37" s="5">
         <f t="shared" si="17"/>
-        <v>0.96182744893267502</v>
+        <v>0.96183784608062184</v>
       </c>
       <c r="AV37" s="9">
         <v>690116</v>
@@ -7197,14 +7197,14 @@
       </c>
       <c r="AX37" s="4">
         <f t="shared" si="18"/>
-        <v>115274</v>
+        <v>115283</v>
       </c>
       <c r="AY37" s="22">
-        <v>658562</v>
+        <v>658571</v>
       </c>
       <c r="AZ37" s="5">
         <f t="shared" si="19"/>
-        <v>0.95427725194025348</v>
+        <v>0.95429029322606629</v>
       </c>
       <c r="BA37" s="9">
         <v>673244</v>
@@ -7214,14 +7214,14 @@
       </c>
       <c r="BC37" s="4">
         <f t="shared" si="20"/>
-        <v>114854</v>
+        <v>114863</v>
       </c>
       <c r="BD37" s="8">
-        <v>664873</v>
+        <v>664882</v>
       </c>
       <c r="BE37" s="5">
         <f t="shared" si="21"/>
-        <v>0.98756617214561138</v>
+        <v>0.98757954025583594</v>
       </c>
       <c r="BF37" s="9">
         <v>856336</v>
@@ -7231,14 +7231,14 @@
       </c>
       <c r="BH37" s="4">
         <f t="shared" si="22"/>
-        <v>202714</v>
+        <v>202724</v>
       </c>
       <c r="BI37" s="8">
-        <v>846529</v>
+        <v>846539</v>
       </c>
       <c r="BJ37" s="5">
         <f t="shared" si="23"/>
-        <v>0.98854771958670429</v>
+        <v>0.98855939724594089</v>
       </c>
     </row>
     <row r="38" spans="1:62" x14ac:dyDescent="0.3">
@@ -7290,14 +7290,14 @@
       </c>
       <c r="O38" s="4">
         <f t="shared" si="4"/>
-        <v>9113</v>
+        <v>9114</v>
       </c>
       <c r="P38" s="8">
-        <v>33469</v>
+        <v>33470</v>
       </c>
       <c r="Q38" s="5">
         <f t="shared" si="5"/>
-        <v>0.88488485841948017</v>
+        <v>0.88491129735874996</v>
       </c>
       <c r="R38" s="9">
         <v>25469</v>
@@ -7341,14 +7341,14 @@
       </c>
       <c r="AD38" s="4">
         <f t="shared" si="10"/>
-        <v>9662</v>
+        <v>9663</v>
       </c>
       <c r="AE38" s="8">
-        <v>34016</v>
+        <v>34017</v>
       </c>
       <c r="AF38" s="5">
         <f t="shared" si="11"/>
-        <v>0.91347548203448092</v>
+        <v>0.91350233632311084</v>
       </c>
       <c r="AG38" s="9">
         <v>24904</v>
@@ -7392,14 +7392,14 @@
       </c>
       <c r="AS38" s="4">
         <f t="shared" si="16"/>
-        <v>8481</v>
+        <v>8482</v>
       </c>
       <c r="AT38" s="8">
-        <v>34879</v>
+        <v>34880</v>
       </c>
       <c r="AU38" s="5">
         <f t="shared" si="17"/>
-        <v>0.91608446709040292</v>
+        <v>0.91611073173294111</v>
       </c>
       <c r="AV38" s="9">
         <v>25812</v>
@@ -7443,14 +7443,14 @@
       </c>
       <c r="BH38" s="4">
         <f t="shared" si="22"/>
-        <v>10844</v>
+        <v>10845</v>
       </c>
       <c r="BI38" s="8">
-        <v>35484</v>
+        <v>35485</v>
       </c>
       <c r="BJ38" s="5">
         <f t="shared" si="23"/>
-        <v>0.99859289694377218</v>
+        <v>0.99862103900489674</v>
       </c>
     </row>
     <row r="39" spans="1:62" x14ac:dyDescent="0.3">
@@ -7680,14 +7680,14 @@
       </c>
       <c r="E40" s="4">
         <f t="shared" si="0"/>
-        <v>50303</v>
+        <v>50304</v>
       </c>
       <c r="F40" s="22">
-        <v>260471</v>
+        <v>260472</v>
       </c>
       <c r="G40" s="5">
         <f t="shared" si="24"/>
-        <v>0.95243510470639425</v>
+        <v>0.95243876129428584</v>
       </c>
       <c r="H40" s="9">
         <v>275367</v>
@@ -7697,14 +7697,14 @@
       </c>
       <c r="J40" s="4">
         <f t="shared" si="2"/>
-        <v>57012</v>
+        <v>57014</v>
       </c>
       <c r="K40" s="22">
-        <v>262124</v>
+        <v>262126</v>
       </c>
       <c r="L40" s="5">
         <f t="shared" si="3"/>
-        <v>0.95190781756710141</v>
+        <v>0.95191508060152452</v>
       </c>
       <c r="M40" s="4">
         <v>339208</v>
@@ -7714,14 +7714,14 @@
       </c>
       <c r="O40" s="4">
         <f t="shared" si="4"/>
-        <v>69720</v>
+        <v>69723</v>
       </c>
       <c r="P40" s="8">
-        <v>323320</v>
+        <v>323323</v>
       </c>
       <c r="Q40" s="5">
         <f t="shared" si="5"/>
-        <v>0.95316148204051787</v>
+        <v>0.95317032617155251</v>
       </c>
       <c r="R40" s="9">
         <v>277547</v>
@@ -7731,14 +7731,14 @@
       </c>
       <c r="T40" s="4">
         <f t="shared" si="6"/>
-        <v>54030</v>
+        <v>54033</v>
       </c>
       <c r="U40" s="22">
-        <v>264292</v>
+        <v>264295</v>
       </c>
       <c r="V40" s="5">
         <f t="shared" si="7"/>
-        <v>0.95224232292188349</v>
+        <v>0.95225313190198413</v>
       </c>
       <c r="W40" s="9">
         <v>278758</v>
@@ -7748,14 +7748,14 @@
       </c>
       <c r="Y40" s="4">
         <f t="shared" si="8"/>
-        <v>62691</v>
+        <v>62696</v>
       </c>
       <c r="Z40" s="22">
-        <v>266736</v>
+        <v>266741</v>
       </c>
       <c r="AA40" s="5">
         <f t="shared" si="9"/>
-        <v>0.95687298660486875</v>
+        <v>0.95689092330982428</v>
       </c>
       <c r="AB40" s="9">
         <v>343140</v>
@@ -7765,14 +7765,14 @@
       </c>
       <c r="AD40" s="4">
         <f t="shared" si="10"/>
-        <v>81795</v>
+        <v>81800</v>
       </c>
       <c r="AE40" s="8">
-        <v>328052</v>
+        <v>328057</v>
       </c>
       <c r="AF40" s="5">
         <f t="shared" si="11"/>
-        <v>0.95602960890598587</v>
+        <v>0.95604418021798687</v>
       </c>
       <c r="AG40" s="9">
         <v>282101</v>
@@ -7782,14 +7782,14 @@
       </c>
       <c r="AI40" s="4">
         <f t="shared" si="12"/>
-        <v>62414</v>
+        <v>62419</v>
       </c>
       <c r="AJ40" s="22">
-        <v>268612</v>
+        <v>268617</v>
       </c>
       <c r="AK40" s="5">
         <f t="shared" si="13"/>
-        <v>0.95218379232969752</v>
+        <v>0.95220151647814077</v>
       </c>
       <c r="AL40" s="9">
         <v>282756</v>
@@ -7799,14 +7799,14 @@
       </c>
       <c r="AN40" s="4">
         <f t="shared" si="14"/>
-        <v>55724</v>
+        <v>55727</v>
       </c>
       <c r="AO40" s="22">
-        <v>270839</v>
+        <v>270842</v>
       </c>
       <c r="AP40" s="5">
         <f t="shared" si="15"/>
-        <v>0.95785412157478533</v>
+        <v>0.95786473142921813</v>
       </c>
       <c r="AQ40" s="15">
         <v>343988</v>
@@ -7816,14 +7816,14 @@
       </c>
       <c r="AS40" s="4">
         <f t="shared" si="16"/>
-        <v>66678</v>
+        <v>66685</v>
       </c>
       <c r="AT40" s="8">
-        <v>332159</v>
+        <v>332166</v>
       </c>
       <c r="AU40" s="5">
         <f t="shared" si="17"/>
-        <v>0.96561217251764597</v>
+        <v>0.96563252206472316</v>
       </c>
       <c r="AV40" s="9">
         <v>285285</v>
@@ -7833,14 +7833,14 @@
       </c>
       <c r="AX40" s="4">
         <f t="shared" si="18"/>
-        <v>56506</v>
+        <v>56513</v>
       </c>
       <c r="AY40" s="22">
-        <v>273358</v>
+        <v>273365</v>
       </c>
       <c r="AZ40" s="5">
         <f t="shared" si="19"/>
-        <v>0.95819268450847395</v>
+        <v>0.95821722137511611</v>
       </c>
       <c r="BA40" s="9">
         <v>276279</v>
@@ -7850,14 +7850,14 @@
       </c>
       <c r="BC40" s="4">
         <f t="shared" si="20"/>
-        <v>55329</v>
+        <v>55338</v>
       </c>
       <c r="BD40" s="8">
-        <v>275282</v>
+        <v>275291</v>
       </c>
       <c r="BE40" s="5">
         <f t="shared" si="21"/>
-        <v>0.99639132905504946</v>
+        <v>0.99642390482085141</v>
       </c>
       <c r="BF40" s="9">
         <v>339189</v>
@@ -7867,14 +7867,14 @@
       </c>
       <c r="BH40" s="4">
         <f t="shared" si="22"/>
-        <v>95125</v>
+        <v>95133</v>
       </c>
       <c r="BI40" s="8">
-        <v>336899</v>
+        <v>336907</v>
       </c>
       <c r="BJ40" s="5">
         <f t="shared" si="23"/>
-        <v>0.99324860181196917</v>
+        <v>0.99327218748249502</v>
       </c>
     </row>
     <row r="41" spans="1:62" x14ac:dyDescent="0.3">
@@ -7892,14 +7892,14 @@
       </c>
       <c r="E41" s="4">
         <f t="shared" si="0"/>
-        <v>119504</v>
+        <v>119516</v>
       </c>
       <c r="F41" s="22">
-        <v>840952</v>
+        <v>840964</v>
       </c>
       <c r="G41" s="5">
         <f t="shared" si="24"/>
-        <v>0.9636319884495067</v>
+        <v>0.96364573903677131</v>
       </c>
       <c r="H41" s="9">
         <v>878008</v>
@@ -7909,14 +7909,14 @@
       </c>
       <c r="J41" s="4">
         <f t="shared" si="2"/>
-        <v>149494</v>
+        <v>149505</v>
       </c>
       <c r="K41" s="22">
-        <v>848018</v>
+        <v>848029</v>
       </c>
       <c r="L41" s="5">
         <f t="shared" si="3"/>
-        <v>0.96584313582564163</v>
+        <v>0.96585566418529212</v>
       </c>
       <c r="M41" s="4">
         <v>999035</v>
@@ -7926,14 +7926,14 @@
       </c>
       <c r="O41" s="4">
         <f t="shared" si="4"/>
-        <v>161283</v>
+        <v>161294</v>
       </c>
       <c r="P41" s="8">
-        <v>960770</v>
+        <v>960781</v>
       </c>
       <c r="Q41" s="5">
         <f t="shared" si="5"/>
-        <v>0.961698038607256</v>
+        <v>0.96170904923250933</v>
       </c>
       <c r="R41" s="9">
         <v>889467</v>
@@ -7943,14 +7943,14 @@
       </c>
       <c r="T41" s="4">
         <f t="shared" si="6"/>
-        <v>146310</v>
+        <v>146322</v>
       </c>
       <c r="U41" s="22">
-        <v>857004</v>
+        <v>857016</v>
       </c>
       <c r="V41" s="5">
         <f t="shared" si="7"/>
-        <v>0.96350286182623979</v>
+        <v>0.96351635305188388</v>
       </c>
       <c r="W41" s="9">
         <v>894020</v>
@@ -7960,14 +7960,14 @@
       </c>
       <c r="Y41" s="4">
         <f t="shared" si="8"/>
-        <v>153033</v>
+        <v>153046</v>
       </c>
       <c r="Z41" s="22">
-        <v>862409</v>
+        <v>862422</v>
       </c>
       <c r="AA41" s="5">
         <f t="shared" si="9"/>
-        <v>0.96464173061005343</v>
+        <v>0.9646562716717747</v>
       </c>
       <c r="AB41" s="9">
         <v>1012178</v>
@@ -7977,14 +7977,14 @@
       </c>
       <c r="AD41" s="4">
         <f t="shared" si="10"/>
-        <v>189484</v>
+        <v>189499</v>
       </c>
       <c r="AE41" s="8">
-        <v>976688</v>
+        <v>976703</v>
       </c>
       <c r="AF41" s="5">
         <f t="shared" si="11"/>
-        <v>0.96493699724751969</v>
+        <v>0.96495181677531028</v>
       </c>
       <c r="AG41" s="9">
         <v>904846</v>
@@ -7994,14 +7994,14 @@
       </c>
       <c r="AI41" s="4">
         <f t="shared" si="12"/>
-        <v>152711</v>
+        <v>152721</v>
       </c>
       <c r="AJ41" s="22">
-        <v>872466</v>
+        <v>872476</v>
       </c>
       <c r="AK41" s="5">
         <f t="shared" si="13"/>
-        <v>0.96421490507777019</v>
+        <v>0.96422595668213151</v>
       </c>
       <c r="AL41" s="9">
         <v>910192</v>
@@ -8011,14 +8011,14 @@
       </c>
       <c r="AN41" s="4">
         <f t="shared" si="14"/>
-        <v>133969</v>
+        <v>133982</v>
       </c>
       <c r="AO41" s="22">
-        <v>878375</v>
+        <v>878388</v>
       </c>
       <c r="AP41" s="5">
         <f t="shared" si="15"/>
-        <v>0.96504363914426849</v>
+        <v>0.96505792184506123</v>
       </c>
       <c r="AQ41" s="15">
         <v>1025826</v>
@@ -8028,14 +8028,14 @@
       </c>
       <c r="AS41" s="4">
         <f t="shared" si="16"/>
-        <v>163930</v>
+        <v>163951</v>
       </c>
       <c r="AT41" s="8">
-        <v>991894</v>
+        <v>991915</v>
       </c>
       <c r="AU41" s="5">
         <f t="shared" si="17"/>
-        <v>0.96692226556940453</v>
+        <v>0.96694273687740417</v>
       </c>
       <c r="AV41" s="9">
         <v>923071</v>
@@ -8045,14 +8045,14 @@
       </c>
       <c r="AX41" s="4">
         <f t="shared" si="18"/>
-        <v>137828</v>
+        <v>137843</v>
       </c>
       <c r="AY41" s="22">
-        <v>890367</v>
+        <v>890382</v>
       </c>
       <c r="AZ41" s="5">
         <f t="shared" si="19"/>
-        <v>0.96457043932698572</v>
+        <v>0.96458668943125714</v>
       </c>
       <c r="BA41" s="9">
         <v>907892</v>
@@ -8062,14 +8062,14 @@
       </c>
       <c r="BC41" s="4">
         <f t="shared" si="20"/>
-        <v>135516</v>
+        <v>135531</v>
       </c>
       <c r="BD41" s="8">
-        <v>897203</v>
+        <v>897218</v>
       </c>
       <c r="BE41" s="5">
         <f t="shared" si="21"/>
-        <v>0.98822657320474239</v>
+        <v>0.98824309499367768</v>
       </c>
       <c r="BF41" s="9">
         <v>1023930</v>
@@ -8079,14 +8079,14 @@
       </c>
       <c r="BH41" s="4">
         <f t="shared" si="22"/>
-        <v>214772</v>
+        <v>214791</v>
       </c>
       <c r="BI41" s="8">
-        <v>1010487</v>
+        <v>1010506</v>
       </c>
       <c r="BJ41" s="5">
         <f t="shared" si="23"/>
-        <v>0.98687117283408043</v>
+        <v>0.98688972879005399</v>
       </c>
     </row>
     <row r="42" spans="1:62" x14ac:dyDescent="0.3">
@@ -8172,14 +8172,14 @@
       </c>
       <c r="Y42" s="4">
         <f t="shared" si="8"/>
-        <v>3862</v>
+        <v>3863</v>
       </c>
       <c r="Z42" s="22">
-        <v>17575</v>
+        <v>17576</v>
       </c>
       <c r="AA42" s="5">
         <f t="shared" si="9"/>
-        <v>0.95949118305399361</v>
+        <v>0.95954577714691269</v>
       </c>
       <c r="AB42" s="9">
         <v>20712</v>
@@ -8189,14 +8189,14 @@
       </c>
       <c r="AD42" s="4">
         <f t="shared" si="10"/>
-        <v>4969</v>
+        <v>4970</v>
       </c>
       <c r="AE42" s="8">
-        <v>19816</v>
+        <v>19817</v>
       </c>
       <c r="AF42" s="5">
         <f t="shared" si="11"/>
-        <v>0.95674005407493246</v>
+        <v>0.95678833526458096</v>
       </c>
       <c r="AG42" s="9">
         <v>18585</v>
@@ -8206,14 +8206,14 @@
       </c>
       <c r="AI42" s="4">
         <f t="shared" si="12"/>
-        <v>3797</v>
+        <v>3798</v>
       </c>
       <c r="AJ42" s="22">
-        <v>17749</v>
+        <v>17750</v>
       </c>
       <c r="AK42" s="5">
         <f t="shared" si="13"/>
-        <v>0.95501748722087709</v>
+        <v>0.95507129405434488</v>
       </c>
       <c r="AL42" s="9">
         <v>18498</v>
@@ -8223,14 +8223,14 @@
       </c>
       <c r="AN42" s="4">
         <f t="shared" si="14"/>
-        <v>3451</v>
+        <v>3452</v>
       </c>
       <c r="AO42" s="22">
-        <v>17807</v>
+        <v>17808</v>
       </c>
       <c r="AP42" s="5">
         <f t="shared" si="15"/>
-        <v>0.96264461022813275</v>
+        <v>0.96269867012650012</v>
       </c>
       <c r="AQ42" s="15">
         <v>20775</v>
@@ -8240,14 +8240,14 @@
       </c>
       <c r="AS42" s="4">
         <f t="shared" si="16"/>
-        <v>4078</v>
+        <v>4079</v>
       </c>
       <c r="AT42" s="8">
-        <v>20023</v>
+        <v>20024</v>
       </c>
       <c r="AU42" s="5">
         <f t="shared" si="17"/>
-        <v>0.96380264741275568</v>
+        <v>0.96385078219013232</v>
       </c>
       <c r="AV42" s="9">
         <v>18672</v>
@@ -8257,14 +8257,14 @@
       </c>
       <c r="AX42" s="4">
         <f t="shared" si="18"/>
-        <v>3583</v>
+        <v>3584</v>
       </c>
       <c r="AY42" s="22">
-        <v>17979</v>
+        <v>17980</v>
       </c>
       <c r="AZ42" s="5">
         <f t="shared" si="19"/>
-        <v>0.96288560411311053</v>
+        <v>0.96293916023993142</v>
       </c>
       <c r="BA42" s="9">
         <v>18422</v>
@@ -8274,14 +8274,14 @@
       </c>
       <c r="BC42" s="4">
         <f t="shared" si="20"/>
-        <v>3451</v>
+        <v>3452</v>
       </c>
       <c r="BD42" s="8">
-        <v>18093</v>
+        <v>18094</v>
       </c>
       <c r="BE42" s="5">
         <f t="shared" si="21"/>
-        <v>0.98214091846705032</v>
+        <v>0.98219520138964278</v>
       </c>
       <c r="BF42" s="9">
         <v>20562</v>
@@ -8316,14 +8316,14 @@
       </c>
       <c r="E43" s="4">
         <f t="shared" si="0"/>
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="F43" s="22">
-        <v>3181</v>
+        <v>3182</v>
       </c>
       <c r="G43" s="5">
         <f t="shared" si="24"/>
-        <v>0.94785458879618589</v>
+        <v>0.94815256257449343</v>
       </c>
       <c r="H43" s="9">
         <v>3369</v>
@@ -8333,14 +8333,14 @@
       </c>
       <c r="J43" s="4">
         <f t="shared" si="2"/>
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="K43" s="22">
-        <v>3227</v>
+        <v>3228</v>
       </c>
       <c r="L43" s="5">
         <f t="shared" si="3"/>
-        <v>0.95785099436034427</v>
+        <v>0.9581478183437222</v>
       </c>
       <c r="M43" s="4">
         <v>4189</v>
@@ -8350,14 +8350,14 @@
       </c>
       <c r="O43" s="4">
         <f t="shared" si="4"/>
-        <v>1387</v>
+        <v>1388</v>
       </c>
       <c r="P43" s="8">
-        <v>4038</v>
+        <v>4039</v>
       </c>
       <c r="Q43" s="5">
         <f t="shared" si="5"/>
-        <v>0.96395321079016472</v>
+        <v>0.96419193124850799</v>
       </c>
       <c r="R43" s="9">
         <v>3398</v>
@@ -8367,14 +8367,14 @@
       </c>
       <c r="T43" s="4">
         <f t="shared" si="6"/>
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="U43" s="22">
-        <v>3282</v>
+        <v>3283</v>
       </c>
       <c r="V43" s="5">
         <f t="shared" si="7"/>
-        <v>0.96586227192466156</v>
+        <v>0.96615656268393169</v>
       </c>
       <c r="W43" s="9">
         <v>3433</v>
@@ -8384,14 +8384,14 @@
       </c>
       <c r="Y43" s="4">
         <f t="shared" si="8"/>
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="Z43" s="22">
-        <v>3338</v>
+        <v>3339</v>
       </c>
       <c r="AA43" s="5">
         <f t="shared" si="9"/>
-        <v>0.97232741042819693</v>
+        <v>0.97261870084474222</v>
       </c>
       <c r="AB43" s="9">
         <v>4306</v>
@@ -8401,14 +8401,14 @@
       </c>
       <c r="AD43" s="4">
         <f t="shared" si="10"/>
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="AE43" s="8">
-        <v>4181</v>
+        <v>4182</v>
       </c>
       <c r="AF43" s="5">
         <f t="shared" si="11"/>
-        <v>0.9709707385044124</v>
+        <v>0.97120297259637711</v>
       </c>
       <c r="AG43" s="9">
         <v>3505</v>
@@ -8418,14 +8418,14 @@
       </c>
       <c r="AI43" s="4">
         <f t="shared" si="12"/>
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="AJ43" s="22">
-        <v>3338</v>
+        <v>3339</v>
       </c>
       <c r="AK43" s="5">
         <f t="shared" si="13"/>
-        <v>0.95235378031383733</v>
+        <v>0.95263908701854494</v>
       </c>
       <c r="AL43" s="9">
         <v>3511</v>
@@ -8435,14 +8435,14 @@
       </c>
       <c r="AN43" s="4">
         <f t="shared" si="14"/>
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="AO43" s="22">
-        <v>3369</v>
+        <v>3370</v>
       </c>
       <c r="AP43" s="5">
         <f t="shared" si="15"/>
-        <v>0.95955568214183995</v>
+        <v>0.95984050128168608</v>
       </c>
       <c r="AQ43" s="15">
         <v>4405</v>
@@ -8452,14 +8452,14 @@
       </c>
       <c r="AS43" s="4">
         <f t="shared" si="16"/>
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="AT43" s="8">
-        <v>4261</v>
+        <v>4262</v>
       </c>
       <c r="AU43" s="5">
         <f t="shared" si="17"/>
-        <v>0.96730987514188427</v>
+        <v>0.96753688989784337</v>
       </c>
       <c r="AV43" s="9">
         <v>3534</v>
@@ -8469,14 +8469,14 @@
       </c>
       <c r="AX43" s="4">
         <f t="shared" si="18"/>
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="AY43" s="22">
-        <v>3397</v>
+        <v>3398</v>
       </c>
       <c r="AZ43" s="5">
         <f t="shared" si="19"/>
-        <v>0.96123372948500285</v>
+        <v>0.96151669496321446</v>
       </c>
       <c r="BA43" s="9">
         <v>3464</v>
@@ -8486,14 +8486,14 @@
       </c>
       <c r="BC43" s="4">
         <f t="shared" si="20"/>
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="BD43" s="8">
-        <v>3452</v>
+        <v>3453</v>
       </c>
       <c r="BE43" s="5">
         <f t="shared" si="21"/>
-        <v>0.99653579676674364</v>
+        <v>0.99682448036951499</v>
       </c>
       <c r="BF43" s="9">
         <v>4361</v>
@@ -8503,14 +8503,14 @@
       </c>
       <c r="BH43" s="4">
         <f t="shared" si="22"/>
-        <v>1683</v>
+        <v>1684</v>
       </c>
       <c r="BI43" s="8">
-        <v>4333</v>
+        <v>4334</v>
       </c>
       <c r="BJ43" s="5">
         <f t="shared" si="23"/>
-        <v>0.9935794542536116</v>
+        <v>0.99380875945883973</v>
       </c>
     </row>
     <row r="44" spans="1:62" x14ac:dyDescent="0.3">
@@ -8528,14 +8528,14 @@
       </c>
       <c r="E44" s="4">
         <f t="shared" si="0"/>
-        <v>67402</v>
+        <v>67403</v>
       </c>
       <c r="F44" s="22">
-        <v>304560</v>
+        <v>304561</v>
       </c>
       <c r="G44" s="5">
         <f t="shared" si="24"/>
-        <v>0.89537758674925838</v>
+        <v>0.89538052665465229</v>
       </c>
       <c r="H44" s="9">
         <v>343940</v>
@@ -8545,14 +8545,14 @@
       </c>
       <c r="J44" s="4">
         <f t="shared" si="2"/>
-        <v>78206</v>
+        <v>78207</v>
       </c>
       <c r="K44" s="22">
-        <v>307772</v>
+        <v>307773</v>
       </c>
       <c r="L44" s="5">
         <f t="shared" si="3"/>
-        <v>0.89484212362621385</v>
+        <v>0.89484503111007729</v>
       </c>
       <c r="M44" s="4">
         <v>415294</v>
@@ -8562,14 +8562,14 @@
       </c>
       <c r="O44" s="4">
         <f t="shared" si="4"/>
-        <v>88836</v>
+        <v>88837</v>
       </c>
       <c r="P44" s="8">
-        <v>373543</v>
+        <v>373544</v>
       </c>
       <c r="Q44" s="5">
         <f t="shared" si="5"/>
-        <v>0.89946640211512807</v>
+        <v>0.89946881004782153</v>
       </c>
       <c r="R44" s="9">
         <v>349377</v>
@@ -8579,14 +8579,14 @@
       </c>
       <c r="T44" s="4">
         <f t="shared" si="6"/>
-        <v>76585</v>
+        <v>76586</v>
       </c>
       <c r="U44" s="22">
-        <v>311986</v>
+        <v>311987</v>
       </c>
       <c r="V44" s="5">
         <f t="shared" si="7"/>
-        <v>0.89297807239743887</v>
+        <v>0.89298093463507899</v>
       </c>
       <c r="W44" s="9">
         <v>352323</v>
@@ -8596,14 +8596,14 @@
       </c>
       <c r="Y44" s="4">
         <f t="shared" si="8"/>
-        <v>77410</v>
+        <v>77411</v>
       </c>
       <c r="Z44" s="22">
-        <v>315071</v>
+        <v>315072</v>
       </c>
       <c r="AA44" s="5">
         <f t="shared" si="9"/>
-        <v>0.89426747615114544</v>
+        <v>0.89427031445576932</v>
       </c>
       <c r="AB44" s="9">
         <v>424236</v>
@@ -8613,14 +8613,14 @@
       </c>
       <c r="AD44" s="4">
         <f t="shared" si="10"/>
-        <v>99654</v>
+        <v>99655</v>
       </c>
       <c r="AE44" s="8">
-        <v>382536</v>
+        <v>382537</v>
       </c>
       <c r="AF44" s="5">
         <f t="shared" si="11"/>
-        <v>0.90170565439990946</v>
+        <v>0.90170801157846103</v>
       </c>
       <c r="AG44" s="9">
         <v>358309</v>
@@ -8630,14 +8630,14 @@
       </c>
       <c r="AI44" s="4">
         <f t="shared" si="12"/>
-        <v>80225</v>
+        <v>80226</v>
       </c>
       <c r="AJ44" s="22">
-        <v>319565</v>
+        <v>319566</v>
       </c>
       <c r="AK44" s="5">
         <f t="shared" si="13"/>
-        <v>0.89186986651186551</v>
+        <v>0.89187265739906063</v>
       </c>
       <c r="AL44" s="9">
         <v>359722</v>
@@ -8647,14 +8647,14 @@
       </c>
       <c r="AN44" s="4">
         <f t="shared" si="14"/>
-        <v>71143</v>
+        <v>71145</v>
       </c>
       <c r="AO44" s="22">
-        <v>323325</v>
+        <v>323327</v>
       </c>
       <c r="AP44" s="5">
         <f t="shared" si="15"/>
-        <v>0.89881908807356792</v>
+        <v>0.89882464792256245</v>
       </c>
       <c r="AQ44" s="15">
         <v>432157</v>
@@ -8664,14 +8664,14 @@
       </c>
       <c r="AS44" s="4">
         <f t="shared" si="16"/>
-        <v>82575</v>
+        <v>82578</v>
       </c>
       <c r="AT44" s="8">
-        <v>390807</v>
+        <v>390810</v>
       </c>
       <c r="AU44" s="5">
         <f t="shared" si="17"/>
-        <v>0.90431718102448877</v>
+        <v>0.90432412294605891</v>
       </c>
       <c r="AV44" s="9">
         <v>367733</v>
@@ -8681,14 +8681,14 @@
       </c>
       <c r="AX44" s="4">
         <f t="shared" si="18"/>
-        <v>71246</v>
+        <v>71249</v>
       </c>
       <c r="AY44" s="22">
-        <v>327459</v>
+        <v>327462</v>
       </c>
       <c r="AZ44" s="5">
         <f t="shared" si="19"/>
-        <v>0.89048032132008825</v>
+        <v>0.89048847941305243</v>
       </c>
       <c r="BA44" s="9">
         <v>337773</v>
@@ -8698,14 +8698,14 @@
       </c>
       <c r="BC44" s="4">
         <f t="shared" si="20"/>
-        <v>71558</v>
+        <v>71561</v>
       </c>
       <c r="BD44" s="8">
-        <v>331160</v>
+        <v>331163</v>
       </c>
       <c r="BE44" s="5">
         <f t="shared" si="21"/>
-        <v>0.98042176254466762</v>
+        <v>0.98043064424924431</v>
       </c>
       <c r="BF44" s="9">
         <v>408499</v>
@@ -8715,14 +8715,14 @@
       </c>
       <c r="BH44" s="4">
         <f t="shared" si="22"/>
-        <v>111938</v>
+        <v>111941</v>
       </c>
       <c r="BI44" s="8">
-        <v>399288</v>
+        <v>399291</v>
       </c>
       <c r="BJ44" s="5">
         <f t="shared" si="23"/>
-        <v>0.97745159718873242</v>
+        <v>0.97745894114795873</v>
       </c>
     </row>
     <row r="45" spans="1:62" x14ac:dyDescent="0.3">
@@ -8740,14 +8740,14 @@
       </c>
       <c r="E45" s="4">
         <f t="shared" si="0"/>
-        <v>45805</v>
+        <v>45806</v>
       </c>
       <c r="F45" s="22">
-        <v>235575</v>
+        <v>235576</v>
       </c>
       <c r="G45" s="5">
         <f t="shared" si="24"/>
-        <v>0.94165214332539215</v>
+        <v>0.94165614057528424</v>
       </c>
       <c r="H45" s="9">
         <v>249985</v>
@@ -8757,14 +8757,14 @@
       </c>
       <c r="J45" s="4">
         <f t="shared" si="2"/>
-        <v>49310</v>
+        <v>49311</v>
       </c>
       <c r="K45" s="22">
-        <v>237256</v>
+        <v>237257</v>
       </c>
       <c r="L45" s="5">
         <f t="shared" si="3"/>
-        <v>0.94908094485669137</v>
+        <v>0.94908494509670582</v>
       </c>
       <c r="M45" s="4">
         <v>300587</v>
@@ -8774,14 +8774,14 @@
       </c>
       <c r="O45" s="4">
         <f t="shared" si="4"/>
-        <v>59177</v>
+        <v>59178</v>
       </c>
       <c r="P45" s="8">
-        <v>288723</v>
+        <v>288724</v>
       </c>
       <c r="Q45" s="5">
         <f t="shared" si="5"/>
-        <v>0.9605305618672797</v>
+        <v>0.96053388869112766</v>
       </c>
       <c r="R45" s="9">
         <v>247712</v>
@@ -8791,14 +8791,14 @@
       </c>
       <c r="T45" s="4">
         <f t="shared" si="6"/>
-        <v>49701</v>
+        <v>49702</v>
       </c>
       <c r="U45" s="22">
-        <v>238335</v>
+        <v>238336</v>
       </c>
       <c r="V45" s="5">
         <f t="shared" si="7"/>
-        <v>0.96214555612969899</v>
+        <v>0.96214959307583003</v>
       </c>
       <c r="W45" s="9">
         <v>250023</v>
@@ -8808,14 +8808,14 @@
       </c>
       <c r="Y45" s="4">
         <f t="shared" si="8"/>
-        <v>53055</v>
+        <v>53056</v>
       </c>
       <c r="Z45" s="22">
-        <v>240167</v>
+        <v>240168</v>
       </c>
       <c r="AA45" s="5">
         <f t="shared" si="9"/>
-        <v>0.96057962667434593</v>
+        <v>0.96058362630637983</v>
       </c>
       <c r="AB45" s="9">
         <v>306096</v>
@@ -8825,14 +8825,14 @@
       </c>
       <c r="AD45" s="4">
         <f t="shared" si="10"/>
-        <v>69240</v>
+        <v>69241</v>
       </c>
       <c r="AE45" s="8">
-        <v>293554</v>
+        <v>293555</v>
       </c>
       <c r="AF45" s="5">
         <f t="shared" si="11"/>
-        <v>0.95902592650671681</v>
+        <v>0.95902919345564785</v>
       </c>
       <c r="AG45" s="9">
         <v>252706</v>
@@ -8876,14 +8876,14 @@
       </c>
       <c r="AS45" s="4">
         <f t="shared" si="16"/>
-        <v>57335</v>
+        <v>57336</v>
       </c>
       <c r="AT45" s="8">
-        <v>299347</v>
+        <v>299348</v>
       </c>
       <c r="AU45" s="5">
         <f t="shared" si="17"/>
-        <v>0.96253983157393797</v>
+        <v>0.96254304703903892</v>
       </c>
       <c r="AV45" s="9">
         <v>259359</v>
@@ -8893,14 +8893,14 @@
       </c>
       <c r="AX45" s="4">
         <f t="shared" si="18"/>
-        <v>47790</v>
+        <v>47791</v>
       </c>
       <c r="AY45" s="22">
-        <v>248470</v>
+        <v>248471</v>
       </c>
       <c r="AZ45" s="5">
         <f t="shared" si="19"/>
-        <v>0.95801572337956264</v>
+        <v>0.95801957903909252</v>
       </c>
       <c r="BA45" s="9">
         <v>254394</v>
@@ -8910,14 +8910,14 @@
       </c>
       <c r="BC45" s="4">
         <f t="shared" si="20"/>
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="BD45" s="8">
-        <v>250273</v>
+        <v>250274</v>
       </c>
       <c r="BE45" s="5">
         <f t="shared" si="21"/>
-        <v>0.98380071857040652</v>
+        <v>0.98380464948072677</v>
       </c>
       <c r="BF45" s="9">
         <v>309142</v>
@@ -8927,14 +8927,14 @@
       </c>
       <c r="BH45" s="4">
         <f t="shared" si="22"/>
-        <v>80315</v>
+        <v>80316</v>
       </c>
       <c r="BI45" s="8">
-        <v>304209</v>
+        <v>304210</v>
       </c>
       <c r="BJ45" s="5">
         <f t="shared" si="23"/>
-        <v>0.9840429317271675</v>
+        <v>0.98404616648659837</v>
       </c>
     </row>
     <row r="46" spans="1:62" x14ac:dyDescent="0.3">
@@ -8952,14 +8952,14 @@
       </c>
       <c r="E46" s="4">
         <f t="shared" si="0"/>
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="F46" s="22">
-        <v>2366</v>
+        <v>2367</v>
       </c>
       <c r="G46" s="5">
         <f t="shared" si="24"/>
-        <v>1.0413732394366197</v>
+        <v>1.0418133802816902</v>
       </c>
       <c r="H46" s="9">
         <v>2410</v>
@@ -8969,14 +8969,14 @@
       </c>
       <c r="J46" s="4">
         <f t="shared" si="2"/>
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="K46" s="22">
-        <v>2540</v>
+        <v>2541</v>
       </c>
       <c r="L46" s="5">
         <f t="shared" si="3"/>
-        <v>1.053941908713693</v>
+        <v>1.0543568464730291</v>
       </c>
       <c r="M46" s="4">
         <v>5863</v>
@@ -8986,14 +8986,14 @@
       </c>
       <c r="O46" s="4">
         <f t="shared" si="4"/>
-        <v>1732</v>
+        <v>1733</v>
       </c>
       <c r="P46" s="8">
-        <v>5903</v>
+        <v>5904</v>
       </c>
       <c r="Q46" s="5">
         <f t="shared" si="5"/>
-        <v>1.006822445846836</v>
+        <v>1.0069930069930071</v>
       </c>
       <c r="R46" s="9">
         <v>2354</v>
@@ -9003,14 +9003,14 @@
       </c>
       <c r="T46" s="4">
         <f t="shared" si="6"/>
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="U46" s="22">
-        <v>2406</v>
+        <v>2407</v>
       </c>
       <c r="V46" s="5">
         <f t="shared" si="7"/>
-        <v>1.0220900594732369</v>
+        <v>1.0225148683092609</v>
       </c>
       <c r="W46" s="9">
         <v>2487</v>
@@ -9020,14 +9020,14 @@
       </c>
       <c r="Y46" s="4">
         <f t="shared" si="8"/>
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="Z46" s="22">
-        <v>2508</v>
+        <v>2509</v>
       </c>
       <c r="AA46" s="5">
         <f t="shared" si="9"/>
-        <v>1.008443908323281</v>
+        <v>1.0088459991958183</v>
       </c>
       <c r="AB46" s="9">
         <v>6137</v>
@@ -9037,14 +9037,14 @@
       </c>
       <c r="AD46" s="4">
         <f t="shared" si="10"/>
-        <v>1762</v>
+        <v>1763</v>
       </c>
       <c r="AE46" s="8">
-        <v>6171</v>
+        <v>6172</v>
       </c>
       <c r="AF46" s="5">
         <f t="shared" si="11"/>
-        <v>1.0055401662049861</v>
+        <v>1.0057031122698388</v>
       </c>
       <c r="AG46" s="9">
         <v>2383</v>
@@ -9054,14 +9054,14 @@
       </c>
       <c r="AI46" s="4">
         <f t="shared" si="12"/>
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="AJ46" s="22">
-        <v>2393</v>
+        <v>2394</v>
       </c>
       <c r="AK46" s="5">
         <f t="shared" si="13"/>
-        <v>1.0041963911036509</v>
+        <v>1.0046160302140159</v>
       </c>
       <c r="AL46" s="9">
         <v>2468</v>
@@ -9071,14 +9071,14 @@
       </c>
       <c r="AN46" s="4">
         <f t="shared" si="14"/>
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="AO46" s="22">
-        <v>2480</v>
+        <v>2481</v>
       </c>
       <c r="AP46" s="5">
         <f t="shared" si="15"/>
-        <v>1.0048622366288493</v>
+        <v>1.0052674230145866</v>
       </c>
       <c r="AQ46" s="15">
         <v>6357</v>
@@ -9088,14 +9088,14 @@
       </c>
       <c r="AS46" s="4">
         <f t="shared" si="16"/>
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="AT46" s="8">
-        <v>6388</v>
+        <v>6389</v>
       </c>
       <c r="AU46" s="5">
         <f t="shared" si="17"/>
-        <v>1.0048765140789682</v>
+        <v>1.0050338209847411</v>
       </c>
       <c r="AV46" s="9">
         <v>2401</v>
@@ -9105,14 +9105,14 @@
       </c>
       <c r="AX46" s="4">
         <f t="shared" si="18"/>
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="AY46" s="22">
-        <v>2326</v>
+        <v>2327</v>
       </c>
       <c r="AZ46" s="5">
         <f t="shared" si="19"/>
-        <v>0.96876301541024568</v>
+        <v>0.96917950853810908</v>
       </c>
       <c r="BA46" s="9">
         <v>2316</v>
@@ -9122,14 +9122,14 @@
       </c>
       <c r="BC46" s="4">
         <f t="shared" si="20"/>
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="BD46" s="8">
-        <v>2398</v>
+        <v>2399</v>
       </c>
       <c r="BE46" s="5">
         <f t="shared" si="21"/>
-        <v>1.0354058721934369</v>
+        <v>1.0358376511226253</v>
       </c>
       <c r="BF46" s="9">
         <v>6380</v>
@@ -9139,14 +9139,14 @@
       </c>
       <c r="BH46" s="4">
         <f t="shared" si="22"/>
-        <v>1961</v>
+        <v>1962</v>
       </c>
       <c r="BI46" s="8">
-        <v>6590</v>
+        <v>6591</v>
       </c>
       <c r="BJ46" s="5">
         <f t="shared" si="23"/>
-        <v>1.0329153605015673</v>
+        <v>1.0330721003134795</v>
       </c>
     </row>
     <row r="47" spans="1:62" x14ac:dyDescent="0.3">
@@ -9362,10 +9362,10 @@
       </c>
     </row>
     <row r="48" spans="1:62" x14ac:dyDescent="0.3">
-      <c r="A48" s="36" t="s">
+      <c r="A48" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="B48" s="36"/>
+      <c r="B48" s="30"/>
       <c r="C48" s="11">
         <f>SUM(C10:C47)</f>
         <v>7396603</v>
@@ -9376,15 +9376,15 @@
       </c>
       <c r="E48" s="13">
         <f t="shared" ref="E48" si="25">F48-D48</f>
-        <v>1277953</v>
+        <v>1278016</v>
       </c>
       <c r="F48" s="12">
         <f>SUM(F10:F47)</f>
-        <v>7088215</v>
+        <v>7088278</v>
       </c>
       <c r="G48" s="14">
         <f t="shared" ref="G48" si="26">F48/C48</f>
-        <v>0.95830680651645084</v>
+        <v>0.95831532393992214</v>
       </c>
       <c r="H48" s="11">
         <f>SUM(H10:H47)</f>
@@ -9396,15 +9396,15 @@
       </c>
       <c r="J48" s="13">
         <f t="shared" ref="J48" si="27">K48-I48</f>
-        <v>1509188</v>
+        <v>1509254</v>
       </c>
       <c r="K48" s="12">
         <f>SUM(K10:K47)</f>
-        <v>7194321</v>
+        <v>7194387</v>
       </c>
       <c r="L48" s="14">
         <f t="shared" ref="L48" si="28">K48/H48</f>
-        <v>0.95980844711149771</v>
+        <v>0.95981725230068926</v>
       </c>
       <c r="M48" s="11">
         <f>SUM(M10:M47)</f>
@@ -9416,15 +9416,15 @@
       </c>
       <c r="O48" s="13">
         <f t="shared" si="4"/>
-        <v>2205237</v>
+        <v>2205329</v>
       </c>
       <c r="P48" s="12">
         <f>SUM(P10:P47)</f>
-        <v>11346574</v>
+        <v>11346666</v>
       </c>
       <c r="Q48" s="14">
         <f t="shared" si="5"/>
-        <v>0.95822798439854728</v>
+        <v>0.95823575387808924</v>
       </c>
       <c r="R48" s="11">
         <f>SUM(R10:R47)</f>
@@ -9436,15 +9436,15 @@
       </c>
       <c r="T48" s="13">
         <f t="shared" si="6"/>
-        <v>1415869</v>
+        <v>1415938</v>
       </c>
       <c r="U48" s="12">
         <f>SUM(U10:U47)</f>
-        <v>7214254</v>
+        <v>7214323</v>
       </c>
       <c r="V48" s="14">
         <f t="shared" si="7"/>
-        <v>0.95636369758495521</v>
+        <v>0.95637284462845173</v>
       </c>
       <c r="W48" s="11">
         <f>SUM(W10:W47)</f>
@@ -9456,15 +9456,15 @@
       </c>
       <c r="Y48" s="13">
         <f t="shared" ref="Y48" si="29">Z48-X48</f>
-        <v>1498708</v>
+        <v>1498786</v>
       </c>
       <c r="Z48" s="12">
         <f>SUM(Z10:Z47)</f>
-        <v>7308725</v>
+        <v>7308803</v>
       </c>
       <c r="AA48" s="14">
         <f t="shared" ref="AA48" si="30">Z48/W48</f>
-        <v>0.95775811956269341</v>
+        <v>0.95776834092597163</v>
       </c>
       <c r="AB48" s="11">
         <f>SUM(AB10:AB47)</f>
@@ -9476,15 +9476,15 @@
       </c>
       <c r="AD48" s="13">
         <f t="shared" si="10"/>
-        <v>2512903</v>
+        <v>2513014</v>
       </c>
       <c r="AE48" s="12">
         <f>SUM(AE10:AE47)</f>
-        <v>11559539</v>
+        <v>11559650</v>
       </c>
       <c r="AF48" s="14">
         <f t="shared" si="11"/>
-        <v>0.96006095135203728</v>
+        <v>0.96007017029801778</v>
       </c>
       <c r="AG48" s="11">
         <f>SUM(AG10:AG47)</f>
@@ -9496,15 +9496,15 @@
       </c>
       <c r="AI48" s="13">
         <f t="shared" si="12"/>
-        <v>1514668</v>
+        <v>1514745</v>
       </c>
       <c r="AJ48" s="12">
         <f>SUM(AJ10:AJ47)</f>
-        <v>7364960</v>
+        <v>7365037</v>
       </c>
       <c r="AK48" s="14">
         <f t="shared" si="13"/>
-        <v>0.95567338293086701</v>
+        <v>0.95568337441085949</v>
       </c>
       <c r="AL48" s="11">
         <f>SUM(AL10:AL47)</f>
@@ -9516,15 +9516,15 @@
       </c>
       <c r="AN48" s="13">
         <f t="shared" si="14"/>
-        <v>1322495</v>
+        <v>1322578</v>
       </c>
       <c r="AO48" s="12">
         <f>SUM(AO10:AO47)</f>
-        <v>7467708</v>
+        <v>7467791</v>
       </c>
       <c r="AP48" s="14">
         <f t="shared" si="15"/>
-        <v>0.95749310604932869</v>
+        <v>0.9575037481268982</v>
       </c>
       <c r="AQ48" s="11">
         <f>SUM(AQ10:AQ47)</f>
@@ -9536,15 +9536,15 @@
       </c>
       <c r="AS48" s="13">
         <f t="shared" si="16"/>
-        <v>1994469</v>
+        <v>1994598</v>
       </c>
       <c r="AT48" s="12">
         <f>SUM(AT10:AT47)</f>
-        <v>11757138</v>
+        <v>11757267</v>
       </c>
       <c r="AU48" s="14">
         <f t="shared" si="17"/>
-        <v>0.96131616595603797</v>
+        <v>0.96132671357276311</v>
       </c>
       <c r="AV48" s="11">
         <f>SUM(AV10:AV47)</f>
@@ -9556,15 +9556,15 @@
       </c>
       <c r="AX48" s="13">
         <f t="shared" si="18"/>
-        <v>1322953</v>
+        <v>1323047</v>
       </c>
       <c r="AY48" s="12">
         <f>SUM(AY10:AY47)</f>
-        <v>7529637</v>
+        <v>7529731</v>
       </c>
       <c r="AZ48" s="14">
         <f t="shared" si="19"/>
-        <v>0.94280869614540441</v>
+        <v>0.94282046617063109</v>
       </c>
       <c r="BA48" s="11">
         <f>SUM(BA10:BA47)</f>
@@ -9576,15 +9576,15 @@
       </c>
       <c r="BC48" s="13">
         <f t="shared" si="20"/>
-        <v>1344607</v>
+        <v>1344704</v>
       </c>
       <c r="BD48" s="12">
         <f>SUM(BD10:BD47)</f>
-        <v>7633087</v>
+        <v>7633184</v>
       </c>
       <c r="BE48" s="14">
         <f t="shared" si="21"/>
-        <v>0.98855590891454093</v>
+        <v>0.98856847131860692</v>
       </c>
       <c r="BF48" s="11">
         <f>SUM(BF10:BF47)</f>
@@ -9596,15 +9596,15 @@
       </c>
       <c r="BH48" s="13">
         <f t="shared" si="22"/>
-        <v>2841870</v>
+        <v>2842003</v>
       </c>
       <c r="BI48" s="12">
         <f>SUM(BI10:BI47)</f>
-        <v>11979758</v>
+        <v>11979891</v>
       </c>
       <c r="BJ48" s="14">
         <f t="shared" si="23"/>
-        <v>0.99273622275130557</v>
+        <v>0.99274724416906923</v>
       </c>
     </row>
     <row r="49" spans="1:63" x14ac:dyDescent="0.3">
@@ -10122,13 +10122,13 @@
       <c r="BJ57" s="1"/>
     </row>
     <row r="58" spans="1:63" x14ac:dyDescent="0.3">
-      <c r="A58" s="35" t="s">
+      <c r="A58" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="B58" s="35"/>
-      <c r="C58" s="35"/>
-      <c r="D58" s="35"/>
-      <c r="E58" s="35"/>
+      <c r="B58" s="29"/>
+      <c r="C58" s="29"/>
+      <c r="D58" s="29"/>
+      <c r="E58" s="29"/>
       <c r="F58" s="6"/>
       <c r="G58" s="1"/>
       <c r="H58" s="1"/>
@@ -10164,14 +10164,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A58:E58"/>
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="AB8:AF8"/>
-    <mergeCell ref="AG8:AK8"/>
-    <mergeCell ref="W8:AA8"/>
-    <mergeCell ref="R8:V8"/>
-    <mergeCell ref="M8:Q8"/>
     <mergeCell ref="BF8:BJ8"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A5:C5"/>
@@ -10183,6 +10175,14 @@
     <mergeCell ref="AV8:AZ8"/>
     <mergeCell ref="AQ8:AU8"/>
     <mergeCell ref="AL8:AP8"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A58:E58"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="AB8:AF8"/>
+    <mergeCell ref="AG8:AK8"/>
+    <mergeCell ref="W8:AA8"/>
+    <mergeCell ref="R8:V8"/>
+    <mergeCell ref="M8:Q8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/gstdatabase/GSTR-3B-2022-2023.xlsx
+++ b/gstdatabase/GSTR-3B-2022-2023.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Jun-26\GST Statistics Downloads 31st May 26\Downloads\GSTR 3B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Jul-26\GST Statistics Downloads 31st Jul 26\Downloads\GSTR 3B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AED42A04-18A8-4FD7-B69E-48FB9EF1B5C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09A121C3-5667-41CF-984C-90A37B780D95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -185,10 +185,10 @@
     <t>-</t>
   </si>
   <si>
-    <t>Data Considered upto 30th Jun 2026</t>
+    <t>Data Considered upto 31st Jul 2026</t>
   </si>
   <si>
-    <t>Filing %age as on 30th Jun 2026</t>
+    <t>Filing %age as on 31st Jul 2026</t>
   </si>
 </sst>
 </file>
@@ -448,15 +448,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="17" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -474,6 +465,15 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="11">
@@ -766,7 +766,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:BK58"/>
+  <dimension ref="A1:BJ56"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -775,12 +775,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:62" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="34" t="s">
         <v>47</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
@@ -855,10 +855,10 @@
       <c r="AK2" s="1"/>
     </row>
     <row r="3" spans="1:62" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="34" t="s">
+      <c r="A3" s="31" t="s">
         <v>46</v>
       </c>
-      <c r="B3" s="34"/>
+      <c r="B3" s="31"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -935,11 +935,11 @@
       <c r="AK4" s="1"/>
     </row>
     <row r="5" spans="1:62" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="34" t="s">
+      <c r="A5" s="31" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="34"/>
-      <c r="C5" s="34"/>
+      <c r="B5" s="31"/>
+      <c r="C5" s="31"/>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
@@ -1054,100 +1054,100 @@
       <c r="AK7" s="1"/>
     </row>
     <row r="8" spans="1:62" s="24" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="35" t="s">
+      <c r="A8" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="36" t="s">
+      <c r="B8" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="C8" s="31">
+      <c r="C8" s="28">
         <v>44652</v>
       </c>
-      <c r="D8" s="32"/>
-      <c r="E8" s="32"/>
-      <c r="F8" s="32"/>
-      <c r="G8" s="33"/>
-      <c r="H8" s="31">
+      <c r="D8" s="29"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="30"/>
+      <c r="H8" s="28">
         <v>44682</v>
       </c>
-      <c r="I8" s="32"/>
-      <c r="J8" s="32"/>
-      <c r="K8" s="32"/>
-      <c r="L8" s="33"/>
-      <c r="M8" s="31">
+      <c r="I8" s="29"/>
+      <c r="J8" s="29"/>
+      <c r="K8" s="29"/>
+      <c r="L8" s="30"/>
+      <c r="M8" s="28">
         <v>44713</v>
       </c>
-      <c r="N8" s="32"/>
-      <c r="O8" s="32"/>
-      <c r="P8" s="32"/>
-      <c r="Q8" s="33"/>
-      <c r="R8" s="31">
+      <c r="N8" s="29"/>
+      <c r="O8" s="29"/>
+      <c r="P8" s="29"/>
+      <c r="Q8" s="30"/>
+      <c r="R8" s="28">
         <v>44743</v>
       </c>
-      <c r="S8" s="32"/>
-      <c r="T8" s="32"/>
-      <c r="U8" s="32"/>
-      <c r="V8" s="33"/>
-      <c r="W8" s="31">
+      <c r="S8" s="29"/>
+      <c r="T8" s="29"/>
+      <c r="U8" s="29"/>
+      <c r="V8" s="30"/>
+      <c r="W8" s="28">
         <v>44774</v>
       </c>
-      <c r="X8" s="32"/>
-      <c r="Y8" s="32"/>
-      <c r="Z8" s="32"/>
-      <c r="AA8" s="33"/>
-      <c r="AB8" s="31">
+      <c r="X8" s="29"/>
+      <c r="Y8" s="29"/>
+      <c r="Z8" s="29"/>
+      <c r="AA8" s="30"/>
+      <c r="AB8" s="28">
         <v>44805</v>
       </c>
-      <c r="AC8" s="32"/>
-      <c r="AD8" s="32"/>
-      <c r="AE8" s="32"/>
-      <c r="AF8" s="33"/>
-      <c r="AG8" s="31">
+      <c r="AC8" s="29"/>
+      <c r="AD8" s="29"/>
+      <c r="AE8" s="29"/>
+      <c r="AF8" s="30"/>
+      <c r="AG8" s="28">
         <v>44835</v>
       </c>
-      <c r="AH8" s="32"/>
-      <c r="AI8" s="32"/>
-      <c r="AJ8" s="32"/>
-      <c r="AK8" s="33"/>
-      <c r="AL8" s="31">
+      <c r="AH8" s="29"/>
+      <c r="AI8" s="29"/>
+      <c r="AJ8" s="29"/>
+      <c r="AK8" s="30"/>
+      <c r="AL8" s="28">
         <v>44866</v>
       </c>
-      <c r="AM8" s="32"/>
-      <c r="AN8" s="32"/>
-      <c r="AO8" s="32"/>
-      <c r="AP8" s="33"/>
-      <c r="AQ8" s="31">
+      <c r="AM8" s="29"/>
+      <c r="AN8" s="29"/>
+      <c r="AO8" s="29"/>
+      <c r="AP8" s="30"/>
+      <c r="AQ8" s="28">
         <v>44896</v>
       </c>
-      <c r="AR8" s="32"/>
-      <c r="AS8" s="32"/>
-      <c r="AT8" s="32"/>
-      <c r="AU8" s="33"/>
-      <c r="AV8" s="31">
+      <c r="AR8" s="29"/>
+      <c r="AS8" s="29"/>
+      <c r="AT8" s="29"/>
+      <c r="AU8" s="30"/>
+      <c r="AV8" s="28">
         <v>44927</v>
       </c>
-      <c r="AW8" s="32"/>
-      <c r="AX8" s="32"/>
-      <c r="AY8" s="32"/>
-      <c r="AZ8" s="33"/>
-      <c r="BA8" s="31">
+      <c r="AW8" s="29"/>
+      <c r="AX8" s="29"/>
+      <c r="AY8" s="29"/>
+      <c r="AZ8" s="30"/>
+      <c r="BA8" s="28">
         <v>44958</v>
       </c>
-      <c r="BB8" s="32"/>
-      <c r="BC8" s="32"/>
-      <c r="BD8" s="32"/>
-      <c r="BE8" s="33"/>
-      <c r="BF8" s="31">
+      <c r="BB8" s="29"/>
+      <c r="BC8" s="29"/>
+      <c r="BD8" s="29"/>
+      <c r="BE8" s="30"/>
+      <c r="BF8" s="28">
         <v>44986</v>
       </c>
-      <c r="BG8" s="32"/>
-      <c r="BH8" s="32"/>
-      <c r="BI8" s="32"/>
-      <c r="BJ8" s="33"/>
+      <c r="BG8" s="29"/>
+      <c r="BH8" s="29"/>
+      <c r="BI8" s="29"/>
+      <c r="BJ8" s="30"/>
     </row>
     <row r="9" spans="1:62" s="24" customFormat="1" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="35"/>
-      <c r="B9" s="36"/>
+      <c r="A9" s="32"/>
+      <c r="B9" s="33"/>
       <c r="C9" s="25" t="s">
         <v>2</v>
       </c>
@@ -1397,7 +1397,7 @@
         <f>U10-S10</f>
         <v>13779</v>
       </c>
-      <c r="U10" s="22">
+      <c r="U10" s="8">
         <v>68413</v>
       </c>
       <c r="V10" s="5">
@@ -1531,14 +1531,14 @@
       </c>
       <c r="BH10" s="4">
         <f>BI10-BG10</f>
-        <v>32205</v>
+        <v>32206</v>
       </c>
       <c r="BI10" s="8">
-        <v>117481</v>
+        <v>117482</v>
       </c>
       <c r="BJ10" s="5">
         <f>BI10/BF10</f>
-        <v>0.99930250163741996</v>
+        <v>0.99931100771501236</v>
       </c>
     </row>
     <row r="11" spans="1:62" x14ac:dyDescent="0.3">
@@ -1609,7 +1609,7 @@
         <f t="shared" ref="T11:T48" si="6">U11-S11</f>
         <v>8459</v>
       </c>
-      <c r="U11" s="22">
+      <c r="U11" s="8">
         <v>43148</v>
       </c>
       <c r="V11" s="5">
@@ -1641,14 +1641,14 @@
       </c>
       <c r="AD11" s="4">
         <f t="shared" ref="AD11:AD48" si="10">AE11-AC11</f>
-        <v>20292</v>
+        <v>20293</v>
       </c>
       <c r="AE11" s="8">
-        <v>97414</v>
+        <v>97415</v>
       </c>
       <c r="AF11" s="5">
         <f t="shared" ref="AF11:AF48" si="11">AE11/AB11</f>
-        <v>0.97523226013134712</v>
+        <v>0.97524227134390518</v>
       </c>
       <c r="AG11" s="9">
         <v>44744</v>
@@ -1692,14 +1692,14 @@
       </c>
       <c r="AS11" s="4">
         <f t="shared" ref="AS11:AS48" si="16">AT11-AR11</f>
-        <v>14774</v>
+        <v>14776</v>
       </c>
       <c r="AT11" s="8">
-        <v>98356</v>
+        <v>98358</v>
       </c>
       <c r="AU11" s="5">
         <f t="shared" ref="AU11:AU48" si="17">AT11/AQ11</f>
-        <v>0.97605414363544341</v>
+        <v>0.97607399100913972</v>
       </c>
       <c r="AV11" s="9">
         <v>46153</v>
@@ -1709,14 +1709,14 @@
       </c>
       <c r="AX11" s="4">
         <f t="shared" ref="AX11:AX48" si="18">AY11-AW11</f>
-        <v>7691</v>
+        <v>7692</v>
       </c>
       <c r="AY11" s="22">
-        <v>43746</v>
+        <v>43747</v>
       </c>
       <c r="AZ11" s="5">
         <f t="shared" ref="AZ11:AZ48" si="19">AY11/AV11</f>
-        <v>0.94784737720191536</v>
+        <v>0.94786904426581153</v>
       </c>
       <c r="BA11" s="9">
         <v>44735</v>
@@ -1726,14 +1726,14 @@
       </c>
       <c r="BC11" s="4">
         <f t="shared" ref="BC11:BC48" si="20">BD11-BB11</f>
-        <v>7801</v>
+        <v>7802</v>
       </c>
       <c r="BD11" s="8">
-        <v>44766</v>
+        <v>44767</v>
       </c>
       <c r="BE11" s="5">
         <f t="shared" ref="BE11:BE48" si="21">BD11/BA11</f>
-        <v>1.0006929697105176</v>
+        <v>1.0007153235721471</v>
       </c>
       <c r="BF11" s="9">
         <v>99991</v>
@@ -1743,14 +1743,14 @@
       </c>
       <c r="BH11" s="4">
         <f t="shared" ref="BH11:BH48" si="22">BI11-BG11</f>
-        <v>21624</v>
+        <v>21626</v>
       </c>
       <c r="BI11" s="8">
-        <v>100717</v>
+        <v>100719</v>
       </c>
       <c r="BJ11" s="5">
         <f t="shared" ref="BJ11:BJ48" si="23">BI11/BF11</f>
-        <v>1.0072606534588113</v>
+        <v>1.0072806552589733</v>
       </c>
     </row>
     <row r="12" spans="1:62" x14ac:dyDescent="0.3">
@@ -1821,7 +1821,7 @@
         <f t="shared" si="6"/>
         <v>23861</v>
       </c>
-      <c r="U12" s="22">
+      <c r="U12" s="8">
         <v>158029</v>
       </c>
       <c r="V12" s="5">
@@ -2033,7 +2033,7 @@
         <f t="shared" si="6"/>
         <v>2399</v>
       </c>
-      <c r="U13" s="22">
+      <c r="U13" s="8">
         <v>15914</v>
       </c>
       <c r="V13" s="5">
@@ -2192,14 +2192,14 @@
       </c>
       <c r="E14" s="4">
         <f t="shared" si="0"/>
-        <v>15675</v>
+        <v>15677</v>
       </c>
       <c r="F14" s="22">
-        <v>78891</v>
+        <v>78893</v>
       </c>
       <c r="G14" s="5">
         <f t="shared" si="1"/>
-        <v>0.95278985507246372</v>
+        <v>0.95281400966183571</v>
       </c>
       <c r="H14" s="9">
         <v>84757</v>
@@ -2209,14 +2209,14 @@
       </c>
       <c r="J14" s="4">
         <f t="shared" si="2"/>
-        <v>18867</v>
+        <v>18869</v>
       </c>
       <c r="K14" s="22">
-        <v>80624</v>
+        <v>80626</v>
       </c>
       <c r="L14" s="5">
         <f t="shared" si="3"/>
-        <v>0.95123706596505309</v>
+        <v>0.95126066283610788</v>
       </c>
       <c r="M14" s="4">
         <v>154914</v>
@@ -2226,14 +2226,14 @@
       </c>
       <c r="O14" s="4">
         <f t="shared" si="4"/>
-        <v>31308</v>
+        <v>31311</v>
       </c>
       <c r="P14" s="8">
-        <v>147542</v>
+        <v>147545</v>
       </c>
       <c r="Q14" s="5">
         <f t="shared" si="5"/>
-        <v>0.95241230618278527</v>
+        <v>0.9524316717662703</v>
       </c>
       <c r="R14" s="9">
         <v>85475</v>
@@ -2243,14 +2243,14 @@
       </c>
       <c r="T14" s="4">
         <f t="shared" si="6"/>
-        <v>18032</v>
-      </c>
-      <c r="U14" s="22">
-        <v>80371</v>
+        <v>18034</v>
+      </c>
+      <c r="U14" s="8">
+        <v>80373</v>
       </c>
       <c r="V14" s="5">
         <f t="shared" si="7"/>
-        <v>0.94028663351857267</v>
+        <v>0.94031003217315001</v>
       </c>
       <c r="W14" s="9">
         <v>86445</v>
@@ -2260,14 +2260,14 @@
       </c>
       <c r="Y14" s="4">
         <f t="shared" si="8"/>
-        <v>19190</v>
+        <v>19191</v>
       </c>
       <c r="Z14" s="22">
-        <v>81633</v>
+        <v>81634</v>
       </c>
       <c r="AA14" s="5">
         <f t="shared" si="9"/>
-        <v>0.94433454797848337</v>
+        <v>0.94434611602753193</v>
       </c>
       <c r="AB14" s="9">
         <v>156524</v>
@@ -2277,14 +2277,14 @@
       </c>
       <c r="AD14" s="4">
         <f t="shared" si="10"/>
-        <v>37396</v>
+        <v>37399</v>
       </c>
       <c r="AE14" s="8">
-        <v>149079</v>
+        <v>149082</v>
       </c>
       <c r="AF14" s="5">
         <f t="shared" si="11"/>
-        <v>0.95243540926631065</v>
+        <v>0.95245457565612945</v>
       </c>
       <c r="AG14" s="9">
         <v>86459</v>
@@ -2294,14 +2294,14 @@
       </c>
       <c r="AI14" s="4">
         <f t="shared" si="12"/>
-        <v>19486</v>
+        <v>19488</v>
       </c>
       <c r="AJ14" s="22">
-        <v>81563</v>
+        <v>81565</v>
       </c>
       <c r="AK14" s="5">
         <f t="shared" si="13"/>
-        <v>0.94337200291467627</v>
+        <v>0.94339513526642682</v>
       </c>
       <c r="AL14" s="9">
         <v>87786</v>
@@ -2311,14 +2311,14 @@
       </c>
       <c r="AN14" s="4">
         <f t="shared" si="14"/>
-        <v>16943</v>
+        <v>16945</v>
       </c>
       <c r="AO14" s="22">
-        <v>83044</v>
+        <v>83046</v>
       </c>
       <c r="AP14" s="5">
         <f t="shared" si="15"/>
-        <v>0.94598227507803068</v>
+        <v>0.94600505775408383</v>
       </c>
       <c r="AQ14" s="15">
         <v>158597</v>
@@ -2328,14 +2328,14 @@
       </c>
       <c r="AS14" s="4">
         <f t="shared" si="16"/>
-        <v>28226</v>
+        <v>28229</v>
       </c>
       <c r="AT14" s="8">
-        <v>151380</v>
+        <v>151383</v>
       </c>
       <c r="AU14" s="5">
         <f t="shared" si="17"/>
-        <v>0.95449472562532711</v>
+        <v>0.95451364149384921</v>
       </c>
       <c r="AV14" s="9">
         <v>90863</v>
@@ -2345,14 +2345,14 @@
       </c>
       <c r="AX14" s="4">
         <f t="shared" si="18"/>
-        <v>17158</v>
+        <v>17160</v>
       </c>
       <c r="AY14" s="22">
-        <v>83732</v>
+        <v>83734</v>
       </c>
       <c r="AZ14" s="5">
         <f t="shared" si="19"/>
-        <v>0.92151921023959149</v>
+        <v>0.92154122139924943</v>
       </c>
       <c r="BA14" s="9">
         <v>86219</v>
@@ -2362,14 +2362,14 @@
       </c>
       <c r="BC14" s="4">
         <f t="shared" si="20"/>
-        <v>17698</v>
+        <v>17700</v>
       </c>
       <c r="BD14" s="8">
-        <v>85367</v>
+        <v>85369</v>
       </c>
       <c r="BE14" s="5">
         <f t="shared" si="21"/>
-        <v>0.99011818740648816</v>
+        <v>0.99014138414966535</v>
       </c>
       <c r="BF14" s="9">
         <v>155639</v>
@@ -2379,14 +2379,14 @@
       </c>
       <c r="BH14" s="4">
         <f t="shared" si="22"/>
-        <v>40056</v>
+        <v>40059</v>
       </c>
       <c r="BI14" s="8">
-        <v>154743</v>
+        <v>154746</v>
       </c>
       <c r="BJ14" s="5">
         <f t="shared" si="23"/>
-        <v>0.9942430881719877</v>
+        <v>0.99426236354641184</v>
       </c>
     </row>
     <row r="15" spans="1:62" x14ac:dyDescent="0.3">
@@ -2457,7 +2457,7 @@
         <f t="shared" si="6"/>
         <v>48254</v>
       </c>
-      <c r="U15" s="22">
+      <c r="U15" s="8">
         <v>264124</v>
       </c>
       <c r="V15" s="5">
@@ -2591,14 +2591,14 @@
       </c>
       <c r="BH15" s="4">
         <f t="shared" si="22"/>
-        <v>100955</v>
+        <v>100956</v>
       </c>
       <c r="BI15" s="8">
-        <v>481818</v>
+        <v>481819</v>
       </c>
       <c r="BJ15" s="5">
         <f t="shared" si="23"/>
-        <v>0.99318934206240905</v>
+        <v>0.99319140339955725</v>
       </c>
     </row>
     <row r="16" spans="1:62" x14ac:dyDescent="0.3">
@@ -2616,14 +2616,14 @@
       </c>
       <c r="E16" s="4">
         <f t="shared" si="0"/>
-        <v>61337</v>
+        <v>61339</v>
       </c>
       <c r="F16" s="22">
-        <v>393550</v>
+        <v>393552</v>
       </c>
       <c r="G16" s="5">
         <f t="shared" si="1"/>
-        <v>0.95921829375892675</v>
+        <v>0.95922316845486766</v>
       </c>
       <c r="H16" s="9">
         <v>416018</v>
@@ -2633,14 +2633,14 @@
       </c>
       <c r="J16" s="4">
         <f t="shared" si="2"/>
-        <v>74123</v>
+        <v>74126</v>
       </c>
       <c r="K16" s="22">
-        <v>400763</v>
+        <v>400766</v>
       </c>
       <c r="L16" s="5">
         <f t="shared" si="3"/>
-        <v>0.9633309135662399</v>
+        <v>0.96333812479267722</v>
       </c>
       <c r="M16" s="4">
         <v>750813</v>
@@ -2650,14 +2650,14 @@
       </c>
       <c r="O16" s="4">
         <f t="shared" si="4"/>
-        <v>121083</v>
+        <v>121086</v>
       </c>
       <c r="P16" s="8">
-        <v>719549</v>
+        <v>719552</v>
       </c>
       <c r="Q16" s="5">
         <f t="shared" si="5"/>
-        <v>0.95835980463843862</v>
+        <v>0.95836380030713375</v>
       </c>
       <c r="R16" s="9">
         <v>419109</v>
@@ -2667,14 +2667,14 @@
       </c>
       <c r="T16" s="4">
         <f t="shared" si="6"/>
-        <v>73012</v>
-      </c>
-      <c r="U16" s="22">
-        <v>401895</v>
+        <v>73016</v>
+      </c>
+      <c r="U16" s="8">
+        <v>401899</v>
       </c>
       <c r="V16" s="5">
         <f t="shared" si="7"/>
-        <v>0.95892715260230632</v>
+        <v>0.95893669665886438</v>
       </c>
       <c r="W16" s="9">
         <v>423539</v>
@@ -2684,14 +2684,14 @@
       </c>
       <c r="Y16" s="4">
         <f t="shared" si="8"/>
-        <v>73344</v>
+        <v>73348</v>
       </c>
       <c r="Z16" s="22">
-        <v>407299</v>
+        <v>407303</v>
       </c>
       <c r="AA16" s="5">
         <f t="shared" si="9"/>
-        <v>0.96165642361152104</v>
+        <v>0.96166586784215857</v>
       </c>
       <c r="AB16" s="9">
         <v>762171</v>
@@ -2701,14 +2701,14 @@
       </c>
       <c r="AD16" s="4">
         <f t="shared" si="10"/>
-        <v>150574</v>
+        <v>150579</v>
       </c>
       <c r="AE16" s="8">
-        <v>731066</v>
+        <v>731071</v>
       </c>
       <c r="AF16" s="5">
         <f t="shared" si="11"/>
-        <v>0.95918894841183933</v>
+        <v>0.95919550861945679</v>
       </c>
       <c r="AG16" s="9">
         <v>429452</v>
@@ -2718,14 +2718,14 @@
       </c>
       <c r="AI16" s="4">
         <f t="shared" si="12"/>
-        <v>79987</v>
+        <v>79992</v>
       </c>
       <c r="AJ16" s="22">
-        <v>411531</v>
+        <v>411536</v>
       </c>
       <c r="AK16" s="5">
         <f t="shared" si="13"/>
-        <v>0.95827007442042422</v>
+        <v>0.95828171716513133</v>
       </c>
       <c r="AL16" s="9">
         <v>434676</v>
@@ -2735,14 +2735,14 @@
       </c>
       <c r="AN16" s="4">
         <f t="shared" si="14"/>
-        <v>70945</v>
+        <v>70950</v>
       </c>
       <c r="AO16" s="22">
-        <v>417044</v>
+        <v>417049</v>
       </c>
       <c r="AP16" s="5">
         <f t="shared" si="15"/>
-        <v>0.95943645381847631</v>
+        <v>0.95944795663896787</v>
       </c>
       <c r="AQ16" s="15">
         <v>772632</v>
@@ -2752,14 +2752,14 @@
       </c>
       <c r="AS16" s="4">
         <f t="shared" si="16"/>
-        <v>110175</v>
+        <v>110182</v>
       </c>
       <c r="AT16" s="8">
-        <v>741480</v>
+        <v>741487</v>
       </c>
       <c r="AU16" s="5">
         <f t="shared" si="17"/>
-        <v>0.95968067592333739</v>
+        <v>0.95968973586390416</v>
       </c>
       <c r="AV16" s="9">
         <v>448203</v>
@@ -2769,14 +2769,14 @@
       </c>
       <c r="AX16" s="4">
         <f t="shared" si="18"/>
-        <v>69543</v>
+        <v>69550</v>
       </c>
       <c r="AY16" s="22">
-        <v>419999</v>
+        <v>420006</v>
       </c>
       <c r="AZ16" s="5">
         <f t="shared" si="19"/>
-        <v>0.93707315658306611</v>
+        <v>0.93708877450619477</v>
       </c>
       <c r="BA16" s="9">
         <v>429555</v>
@@ -2786,14 +2786,14 @@
       </c>
       <c r="BC16" s="4">
         <f t="shared" si="20"/>
-        <v>70935</v>
+        <v>70943</v>
       </c>
       <c r="BD16" s="8">
-        <v>424807</v>
+        <v>424815</v>
       </c>
       <c r="BE16" s="5">
         <f t="shared" si="21"/>
-        <v>0.9889467006553293</v>
+        <v>0.98896532458008868</v>
       </c>
       <c r="BF16" s="9">
         <v>753579</v>
@@ -2803,14 +2803,14 @@
       </c>
       <c r="BH16" s="4">
         <f t="shared" si="22"/>
-        <v>147984</v>
+        <v>147992</v>
       </c>
       <c r="BI16" s="8">
-        <v>751186</v>
+        <v>751194</v>
       </c>
       <c r="BJ16" s="5">
         <f t="shared" si="23"/>
-        <v>0.9968244868819327</v>
+        <v>0.99683510288901367</v>
       </c>
     </row>
     <row r="17" spans="1:62" x14ac:dyDescent="0.3">
@@ -2828,14 +2828,14 @@
       </c>
       <c r="E17" s="4">
         <f t="shared" si="0"/>
-        <v>51282</v>
+        <v>51284</v>
       </c>
       <c r="F17" s="22">
-        <v>277334</v>
+        <v>277336</v>
       </c>
       <c r="G17" s="5">
         <f t="shared" si="1"/>
-        <v>0.98042570641741289</v>
+        <v>0.98043277677810736</v>
       </c>
       <c r="H17" s="9">
         <v>290053</v>
@@ -2845,14 +2845,14 @@
       </c>
       <c r="J17" s="4">
         <f t="shared" si="2"/>
-        <v>59544</v>
+        <v>59548</v>
       </c>
       <c r="K17" s="22">
-        <v>284831</v>
+        <v>284835</v>
       </c>
       <c r="L17" s="5">
         <f t="shared" si="3"/>
-        <v>0.98199639376251924</v>
+        <v>0.9820101843456196</v>
       </c>
       <c r="M17" s="4">
         <v>666005</v>
@@ -2862,14 +2862,14 @@
       </c>
       <c r="O17" s="4">
         <f t="shared" si="4"/>
-        <v>128120</v>
+        <v>128129</v>
       </c>
       <c r="P17" s="8">
-        <v>645984</v>
+        <v>645993</v>
       </c>
       <c r="Q17" s="5">
         <f t="shared" si="5"/>
-        <v>0.9699386641241432</v>
+        <v>0.96995217753620466</v>
       </c>
       <c r="R17" s="9">
         <v>287981</v>
@@ -2879,14 +2879,14 @@
       </c>
       <c r="T17" s="4">
         <f t="shared" si="6"/>
-        <v>55280</v>
-      </c>
-      <c r="U17" s="22">
-        <v>280825</v>
+        <v>55282</v>
+      </c>
+      <c r="U17" s="8">
+        <v>280827</v>
       </c>
       <c r="V17" s="5">
         <f t="shared" si="7"/>
-        <v>0.97515113844316115</v>
+        <v>0.97515808334577625</v>
       </c>
       <c r="W17" s="9">
         <v>293004</v>
@@ -2896,14 +2896,14 @@
       </c>
       <c r="Y17" s="4">
         <f t="shared" si="8"/>
-        <v>60475</v>
+        <v>60477</v>
       </c>
       <c r="Z17" s="22">
-        <v>286662</v>
+        <v>286664</v>
       </c>
       <c r="AA17" s="5">
         <f t="shared" si="9"/>
-        <v>0.97835524429700615</v>
+        <v>0.97836207014238719</v>
       </c>
       <c r="AB17" s="9">
         <v>677720</v>
@@ -2913,14 +2913,14 @@
       </c>
       <c r="AD17" s="4">
         <f t="shared" si="10"/>
-        <v>145679</v>
+        <v>145686</v>
       </c>
       <c r="AE17" s="8">
-        <v>658940</v>
+        <v>658947</v>
       </c>
       <c r="AF17" s="5">
         <f t="shared" si="11"/>
-        <v>0.97228944106710735</v>
+        <v>0.97229976981644339</v>
       </c>
       <c r="AG17" s="9">
         <v>295677</v>
@@ -2930,14 +2930,14 @@
       </c>
       <c r="AI17" s="4">
         <f t="shared" si="12"/>
-        <v>59675</v>
+        <v>59677</v>
       </c>
       <c r="AJ17" s="22">
-        <v>288119</v>
+        <v>288121</v>
       </c>
       <c r="AK17" s="5">
         <f t="shared" si="13"/>
-        <v>0.9744383228996506</v>
+        <v>0.9744450870375444</v>
       </c>
       <c r="AL17" s="9">
         <v>303084</v>
@@ -2947,14 +2947,14 @@
       </c>
       <c r="AN17" s="4">
         <f t="shared" si="14"/>
-        <v>51549</v>
+        <v>51550</v>
       </c>
       <c r="AO17" s="22">
-        <v>296057</v>
+        <v>296058</v>
       </c>
       <c r="AP17" s="5">
         <f t="shared" si="15"/>
-        <v>0.97681500838051494</v>
+        <v>0.97681830779585854</v>
       </c>
       <c r="AQ17" s="15">
         <v>690105</v>
@@ -2964,14 +2964,14 @@
       </c>
       <c r="AS17" s="4">
         <f t="shared" si="16"/>
-        <v>105800</v>
+        <v>105810</v>
       </c>
       <c r="AT17" s="8">
-        <v>672945</v>
+        <v>672955</v>
       </c>
       <c r="AU17" s="5">
         <f t="shared" si="17"/>
-        <v>0.97513421870584915</v>
+        <v>0.97514870925438879</v>
       </c>
       <c r="AV17" s="9">
         <v>311697</v>
@@ -2981,14 +2981,14 @@
       </c>
       <c r="AX17" s="4">
         <f t="shared" si="18"/>
-        <v>49016</v>
+        <v>49019</v>
       </c>
       <c r="AY17" s="22">
-        <v>294859</v>
+        <v>294862</v>
       </c>
       <c r="AZ17" s="5">
         <f t="shared" si="19"/>
-        <v>0.94597958915228575</v>
+        <v>0.94598921388399637</v>
       </c>
       <c r="BA17" s="9">
         <v>307540</v>
@@ -2998,14 +2998,14 @@
       </c>
       <c r="BC17" s="4">
         <f t="shared" si="20"/>
-        <v>49215</v>
+        <v>49217</v>
       </c>
       <c r="BD17" s="8">
-        <v>301988</v>
+        <v>301990</v>
       </c>
       <c r="BE17" s="5">
         <f t="shared" si="21"/>
-        <v>0.98194706379657926</v>
+        <v>0.98195356701567271</v>
       </c>
       <c r="BF17" s="9">
         <v>689646</v>
@@ -3015,14 +3015,14 @@
       </c>
       <c r="BH17" s="4">
         <f t="shared" si="22"/>
-        <v>153200</v>
+        <v>153213</v>
       </c>
       <c r="BI17" s="8">
-        <v>687220</v>
+        <v>687233</v>
       </c>
       <c r="BJ17" s="5">
         <f t="shared" si="23"/>
-        <v>0.99648225321396777</v>
+        <v>0.99650110346467613</v>
       </c>
     </row>
     <row r="18" spans="1:62" x14ac:dyDescent="0.3">
@@ -3040,14 +3040,14 @@
       </c>
       <c r="E18" s="4">
         <f t="shared" si="0"/>
-        <v>141571</v>
+        <v>141576</v>
       </c>
       <c r="F18" s="22">
-        <v>822084</v>
+        <v>822089</v>
       </c>
       <c r="G18" s="5">
         <f t="shared" si="1"/>
-        <v>0.97809039630029304</v>
+        <v>0.978096345147347</v>
       </c>
       <c r="H18" s="9">
         <v>861805</v>
@@ -3057,14 +3057,14 @@
       </c>
       <c r="J18" s="4">
         <f t="shared" si="2"/>
-        <v>162044</v>
+        <v>162049</v>
       </c>
       <c r="K18" s="22">
-        <v>837278</v>
+        <v>837283</v>
       </c>
       <c r="L18" s="5">
         <f t="shared" si="3"/>
-        <v>0.97153996553744759</v>
+        <v>0.97154576731395148</v>
       </c>
       <c r="M18" s="4">
         <v>1358945</v>
@@ -3074,14 +3074,14 @@
       </c>
       <c r="O18" s="4">
         <f t="shared" si="4"/>
-        <v>245603</v>
+        <v>245611</v>
       </c>
       <c r="P18" s="8">
-        <v>1303836</v>
+        <v>1303844</v>
       </c>
       <c r="Q18" s="5">
         <f t="shared" si="5"/>
-        <v>0.95944721824650736</v>
+        <v>0.95945310516613991</v>
       </c>
       <c r="R18" s="9">
         <v>869959</v>
@@ -3091,14 +3091,14 @@
       </c>
       <c r="T18" s="4">
         <f t="shared" si="6"/>
-        <v>158474</v>
-      </c>
-      <c r="U18" s="22">
-        <v>839489</v>
+        <v>158479</v>
+      </c>
+      <c r="U18" s="8">
+        <v>839494</v>
       </c>
       <c r="V18" s="5">
         <f t="shared" si="7"/>
-        <v>0.96497536090781288</v>
+        <v>0.96498110830510408</v>
       </c>
       <c r="W18" s="9">
         <v>883450</v>
@@ -3108,14 +3108,14 @@
       </c>
       <c r="Y18" s="4">
         <f t="shared" si="8"/>
-        <v>163353</v>
+        <v>163358</v>
       </c>
       <c r="Z18" s="22">
-        <v>853932</v>
+        <v>853937</v>
       </c>
       <c r="AA18" s="5">
         <f t="shared" si="9"/>
-        <v>0.96658780915728115</v>
+        <v>0.96659346878714136</v>
       </c>
       <c r="AB18" s="9">
         <v>1397129</v>
@@ -3125,14 +3125,14 @@
       </c>
       <c r="AD18" s="4">
         <f t="shared" si="10"/>
-        <v>289649</v>
+        <v>289657</v>
       </c>
       <c r="AE18" s="8">
-        <v>1339778</v>
+        <v>1339786</v>
       </c>
       <c r="AF18" s="5">
         <f t="shared" si="11"/>
-        <v>0.95895081985986974</v>
+        <v>0.95895654588803181</v>
       </c>
       <c r="AG18" s="9">
         <v>899515</v>
@@ -3142,14 +3142,14 @@
       </c>
       <c r="AI18" s="4">
         <f t="shared" si="12"/>
-        <v>168548</v>
+        <v>168553</v>
       </c>
       <c r="AJ18" s="22">
-        <v>864925</v>
+        <v>864930</v>
       </c>
       <c r="AK18" s="5">
         <f t="shared" si="13"/>
-        <v>0.96154594420326511</v>
+        <v>0.96155150275426204</v>
       </c>
       <c r="AL18" s="9">
         <v>914748</v>
@@ -3159,14 +3159,14 @@
       </c>
       <c r="AN18" s="4">
         <f t="shared" si="14"/>
-        <v>146483</v>
+        <v>146488</v>
       </c>
       <c r="AO18" s="22">
-        <v>880809</v>
+        <v>880814</v>
       </c>
       <c r="AP18" s="5">
         <f t="shared" si="15"/>
-        <v>0.96289797845964131</v>
+        <v>0.96290344444590203</v>
       </c>
       <c r="AQ18" s="15">
         <v>1436617</v>
@@ -3176,14 +3176,14 @@
       </c>
       <c r="AS18" s="4">
         <f t="shared" si="16"/>
-        <v>219831</v>
+        <v>219839</v>
       </c>
       <c r="AT18" s="8">
-        <v>1375253</v>
+        <v>1375261</v>
       </c>
       <c r="AU18" s="5">
         <f t="shared" si="17"/>
-        <v>0.95728576231521689</v>
+        <v>0.95729133095320462</v>
       </c>
       <c r="AV18" s="9">
         <v>954168</v>
@@ -3193,14 +3193,14 @@
       </c>
       <c r="AX18" s="4">
         <f t="shared" si="18"/>
-        <v>153024</v>
+        <v>153030</v>
       </c>
       <c r="AY18" s="22">
-        <v>894811</v>
+        <v>894817</v>
       </c>
       <c r="AZ18" s="5">
         <f t="shared" si="19"/>
-        <v>0.93779187732139413</v>
+        <v>0.93779816552221407</v>
       </c>
       <c r="BA18" s="9">
         <v>922519</v>
@@ -3210,14 +3210,14 @@
       </c>
       <c r="BC18" s="4">
         <f t="shared" si="20"/>
-        <v>158406</v>
+        <v>158412</v>
       </c>
       <c r="BD18" s="8">
-        <v>911450</v>
+        <v>911456</v>
       </c>
       <c r="BE18" s="5">
         <f t="shared" si="21"/>
-        <v>0.98800133113789523</v>
+        <v>0.9880078350689796</v>
       </c>
       <c r="BF18" s="9">
         <v>1428140</v>
@@ -3227,14 +3227,14 @@
       </c>
       <c r="BH18" s="4">
         <f t="shared" si="22"/>
-        <v>327759</v>
+        <v>327770</v>
       </c>
       <c r="BI18" s="8">
-        <v>1413413</v>
+        <v>1413424</v>
       </c>
       <c r="BJ18" s="5">
         <f t="shared" si="23"/>
-        <v>0.98968798577170303</v>
+        <v>0.9896956880978055</v>
       </c>
     </row>
     <row r="19" spans="1:62" x14ac:dyDescent="0.3">
@@ -3305,7 +3305,7 @@
         <f t="shared" si="6"/>
         <v>55609</v>
       </c>
-      <c r="U19" s="22">
+      <c r="U19" s="8">
         <v>249699</v>
       </c>
       <c r="V19" s="5">
@@ -3354,14 +3354,14 @@
       </c>
       <c r="AI19" s="4">
         <f t="shared" si="12"/>
-        <v>57875</v>
+        <v>57876</v>
       </c>
       <c r="AJ19" s="22">
-        <v>254661</v>
+        <v>254662</v>
       </c>
       <c r="AK19" s="5">
         <f t="shared" si="13"/>
-        <v>0.8866625117943826</v>
+        <v>0.88666599353093345</v>
       </c>
       <c r="AL19" s="9">
         <v>292666</v>
@@ -3388,14 +3388,14 @@
       </c>
       <c r="AS19" s="4">
         <f t="shared" si="16"/>
-        <v>83376</v>
+        <v>83377</v>
       </c>
       <c r="AT19" s="8">
-        <v>446776</v>
+        <v>446777</v>
       </c>
       <c r="AU19" s="5">
         <f t="shared" si="17"/>
-        <v>0.90155055653760163</v>
+        <v>0.90155257444043557</v>
       </c>
       <c r="AV19" s="9">
         <v>310298</v>
@@ -3464,14 +3464,14 @@
       </c>
       <c r="E20" s="4">
         <f t="shared" si="0"/>
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="F20" s="22">
-        <v>5176</v>
+        <v>5177</v>
       </c>
       <c r="G20" s="5">
         <f t="shared" si="1"/>
-        <v>0.85752153744201454</v>
+        <v>0.85768721007289594</v>
       </c>
       <c r="H20" s="9">
         <v>6124</v>
@@ -3481,14 +3481,14 @@
       </c>
       <c r="J20" s="4">
         <f t="shared" si="2"/>
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="K20" s="22">
-        <v>5234</v>
+        <v>5235</v>
       </c>
       <c r="L20" s="5">
         <f t="shared" si="3"/>
-        <v>0.8546701502286087</v>
+        <v>0.85483344219464408</v>
       </c>
       <c r="M20" s="4">
         <v>9262</v>
@@ -3498,14 +3498,14 @@
       </c>
       <c r="O20" s="4">
         <f t="shared" si="4"/>
-        <v>1953</v>
+        <v>1954</v>
       </c>
       <c r="P20" s="8">
-        <v>8211</v>
+        <v>8212</v>
       </c>
       <c r="Q20" s="5">
         <f t="shared" si="5"/>
-        <v>0.88652558842582596</v>
+        <v>0.8866335564672857</v>
       </c>
       <c r="R20" s="9">
         <v>6202</v>
@@ -3515,14 +3515,14 @@
       </c>
       <c r="T20" s="4">
         <f t="shared" si="6"/>
-        <v>1442</v>
-      </c>
-      <c r="U20" s="22">
-        <v>5287</v>
+        <v>1443</v>
+      </c>
+      <c r="U20" s="8">
+        <v>5288</v>
       </c>
       <c r="V20" s="5">
         <f t="shared" si="7"/>
-        <v>0.85246694614640439</v>
+        <v>0.85262818445662691</v>
       </c>
       <c r="W20" s="9">
         <v>6226</v>
@@ -3532,14 +3532,14 @@
       </c>
       <c r="Y20" s="4">
         <f t="shared" si="8"/>
-        <v>1482</v>
+        <v>1483</v>
       </c>
       <c r="Z20" s="22">
-        <v>5373</v>
+        <v>5374</v>
       </c>
       <c r="AA20" s="5">
         <f t="shared" si="9"/>
-        <v>0.86299389656280112</v>
+        <v>0.86315451333119175</v>
       </c>
       <c r="AB20" s="9">
         <v>9386</v>
@@ -3549,14 +3549,14 @@
       </c>
       <c r="AD20" s="4">
         <f t="shared" si="10"/>
-        <v>2421</v>
+        <v>2422</v>
       </c>
       <c r="AE20" s="8">
-        <v>8436</v>
+        <v>8437</v>
       </c>
       <c r="AF20" s="5">
         <f t="shared" si="11"/>
-        <v>0.89878542510121462</v>
+        <v>0.89889196675900274</v>
       </c>
       <c r="AG20" s="9">
         <v>6315</v>
@@ -3566,14 +3566,14 @@
       </c>
       <c r="AI20" s="4">
         <f t="shared" si="12"/>
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="AJ20" s="22">
-        <v>5458</v>
+        <v>5459</v>
       </c>
       <c r="AK20" s="5">
         <f t="shared" si="13"/>
-        <v>0.86429136975455267</v>
+        <v>0.86444972288202693</v>
       </c>
       <c r="AL20" s="9">
         <v>6446</v>
@@ -3583,14 +3583,14 @@
       </c>
       <c r="AN20" s="4">
         <f t="shared" si="14"/>
-        <v>1578</v>
+        <v>1579</v>
       </c>
       <c r="AO20" s="22">
-        <v>5572</v>
+        <v>5573</v>
       </c>
       <c r="AP20" s="5">
         <f t="shared" si="15"/>
-        <v>0.86441203847347192</v>
+        <v>0.86456717344089362</v>
       </c>
       <c r="AQ20" s="15">
         <v>9604</v>
@@ -3600,14 +3600,14 @@
       </c>
       <c r="AS20" s="4">
         <f t="shared" si="16"/>
-        <v>2142</v>
+        <v>2143</v>
       </c>
       <c r="AT20" s="8">
-        <v>8618</v>
+        <v>8619</v>
       </c>
       <c r="AU20" s="5">
         <f t="shared" si="17"/>
-        <v>0.89733444398167428</v>
+        <v>0.89743856726364013</v>
       </c>
       <c r="AV20" s="9">
         <v>6642</v>
@@ -3617,14 +3617,14 @@
       </c>
       <c r="AX20" s="4">
         <f t="shared" si="18"/>
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="AY20" s="22">
-        <v>5619</v>
+        <v>5620</v>
       </c>
       <c r="AZ20" s="5">
         <f t="shared" si="19"/>
-        <v>0.8459801264679313</v>
+        <v>0.84613068352905751</v>
       </c>
       <c r="BA20" s="9">
         <v>5628</v>
@@ -3676,14 +3676,14 @@
       </c>
       <c r="E21" s="4">
         <f t="shared" si="0"/>
-        <v>3321</v>
+        <v>3322</v>
       </c>
       <c r="F21" s="22">
-        <v>8599</v>
+        <v>8600</v>
       </c>
       <c r="G21" s="5">
         <f t="shared" si="1"/>
-        <v>0.80992747480455873</v>
+        <v>0.81002166337006687</v>
       </c>
       <c r="H21" s="9">
         <v>10811</v>
@@ -3693,14 +3693,14 @@
       </c>
       <c r="J21" s="4">
         <f t="shared" si="2"/>
-        <v>3222</v>
+        <v>3223</v>
       </c>
       <c r="K21" s="22">
-        <v>8742</v>
+        <v>8743</v>
       </c>
       <c r="L21" s="5">
         <f t="shared" si="3"/>
-        <v>0.8086208491351401</v>
+        <v>0.80871334751641843</v>
       </c>
       <c r="M21" s="4">
         <v>14133</v>
@@ -3710,14 +3710,14 @@
       </c>
       <c r="O21" s="4">
         <f t="shared" si="4"/>
-        <v>3839</v>
+        <v>3840</v>
       </c>
       <c r="P21" s="8">
-        <v>11809</v>
+        <v>11810</v>
       </c>
       <c r="Q21" s="5">
         <f t="shared" si="5"/>
-        <v>0.83556215948489354</v>
+        <v>0.83563291587065736</v>
       </c>
       <c r="R21" s="9">
         <v>11019</v>
@@ -3727,14 +3727,14 @@
       </c>
       <c r="T21" s="4">
         <f t="shared" si="6"/>
-        <v>3083</v>
-      </c>
-      <c r="U21" s="22">
-        <v>8896</v>
+        <v>3084</v>
+      </c>
+      <c r="U21" s="8">
+        <v>8897</v>
       </c>
       <c r="V21" s="5">
         <f t="shared" si="7"/>
-        <v>0.80733278881931214</v>
+        <v>0.80742354115618475</v>
       </c>
       <c r="W21" s="9">
         <v>11175</v>
@@ -3744,14 +3744,14 @@
       </c>
       <c r="Y21" s="4">
         <f t="shared" si="8"/>
-        <v>3195</v>
+        <v>3196</v>
       </c>
       <c r="Z21" s="22">
-        <v>9094</v>
+        <v>9095</v>
       </c>
       <c r="AA21" s="5">
         <f t="shared" si="9"/>
-        <v>0.81378076062639826</v>
+        <v>0.81387024608501124</v>
       </c>
       <c r="AB21" s="9">
         <v>14571</v>
@@ -3761,14 +3761,14 @@
       </c>
       <c r="AD21" s="4">
         <f t="shared" si="10"/>
-        <v>4487</v>
+        <v>4488</v>
       </c>
       <c r="AE21" s="8">
-        <v>12221</v>
+        <v>12222</v>
       </c>
       <c r="AF21" s="5">
         <f t="shared" si="11"/>
-        <v>0.83872074668862806</v>
+        <v>0.83878937615812232</v>
       </c>
       <c r="AG21" s="9">
         <v>11345</v>
@@ -3778,14 +3778,14 @@
       </c>
       <c r="AI21" s="4">
         <f t="shared" si="12"/>
-        <v>3237</v>
+        <v>3238</v>
       </c>
       <c r="AJ21" s="22">
-        <v>9227</v>
+        <v>9228</v>
       </c>
       <c r="AK21" s="5">
         <f t="shared" si="13"/>
-        <v>0.8133098281181137</v>
+        <v>0.81339797267518732</v>
       </c>
       <c r="AL21" s="9">
         <v>11441</v>
@@ -3795,14 +3795,14 @@
       </c>
       <c r="AN21" s="4">
         <f t="shared" si="14"/>
-        <v>3101</v>
+        <v>3102</v>
       </c>
       <c r="AO21" s="22">
-        <v>9349</v>
+        <v>9350</v>
       </c>
       <c r="AP21" s="5">
         <f t="shared" si="15"/>
-        <v>0.81714885062494536</v>
+        <v>0.81723625557206536</v>
       </c>
       <c r="AQ21" s="15">
         <v>14790</v>
@@ -3812,14 +3812,14 @@
       </c>
       <c r="AS21" s="4">
         <f t="shared" si="16"/>
-        <v>4020</v>
+        <v>4021</v>
       </c>
       <c r="AT21" s="8">
-        <v>12505</v>
+        <v>12506</v>
       </c>
       <c r="AU21" s="5">
         <f t="shared" si="17"/>
-        <v>0.84550371872887087</v>
+        <v>0.84557133198106826</v>
       </c>
       <c r="AV21" s="9">
         <v>11740</v>
@@ -3829,14 +3829,14 @@
       </c>
       <c r="AX21" s="4">
         <f t="shared" si="18"/>
-        <v>3229</v>
+        <v>3230</v>
       </c>
       <c r="AY21" s="22">
-        <v>9489</v>
+        <v>9490</v>
       </c>
       <c r="AZ21" s="5">
         <f t="shared" si="19"/>
-        <v>0.80826235093696763</v>
+        <v>0.80834752981260649</v>
       </c>
       <c r="BA21" s="9">
         <v>9242</v>
@@ -3846,14 +3846,14 @@
       </c>
       <c r="BC21" s="4">
         <f t="shared" si="20"/>
-        <v>3131</v>
+        <v>3132</v>
       </c>
       <c r="BD21" s="8">
-        <v>9584</v>
+        <v>9585</v>
       </c>
       <c r="BE21" s="5">
         <f t="shared" si="21"/>
-        <v>1.0370049772776455</v>
+        <v>1.0371131789655919</v>
       </c>
       <c r="BF21" s="9">
         <v>12544</v>
@@ -3863,14 +3863,14 @@
       </c>
       <c r="BH21" s="4">
         <f t="shared" si="22"/>
-        <v>5689</v>
+        <v>5690</v>
       </c>
       <c r="BI21" s="8">
-        <v>12911</v>
+        <v>12912</v>
       </c>
       <c r="BJ21" s="5">
         <f t="shared" si="23"/>
-        <v>1.0292570153061225</v>
+        <v>1.0293367346938775</v>
       </c>
     </row>
     <row r="22" spans="1:62" x14ac:dyDescent="0.3">
@@ -3922,14 +3922,14 @@
       </c>
       <c r="O22" s="4">
         <f t="shared" si="4"/>
-        <v>1917</v>
+        <v>1919</v>
       </c>
       <c r="P22" s="8">
-        <v>6878</v>
+        <v>6880</v>
       </c>
       <c r="Q22" s="5">
         <f t="shared" si="5"/>
-        <v>0.92371743217835078</v>
+        <v>0.92398603276927205</v>
       </c>
       <c r="R22" s="9">
         <v>6325</v>
@@ -3941,7 +3941,7 @@
         <f t="shared" si="6"/>
         <v>1604</v>
       </c>
-      <c r="U22" s="22">
+      <c r="U22" s="8">
         <v>5803</v>
       </c>
       <c r="V22" s="5">
@@ -3973,14 +3973,14 @@
       </c>
       <c r="AD22" s="4">
         <f t="shared" si="10"/>
-        <v>2094</v>
+        <v>2097</v>
       </c>
       <c r="AE22" s="8">
-        <v>7098</v>
+        <v>7101</v>
       </c>
       <c r="AF22" s="5">
         <f t="shared" si="11"/>
-        <v>0.92638997650743926</v>
+        <v>0.92678151918559126</v>
       </c>
       <c r="AG22" s="9">
         <v>6546</v>
@@ -3990,14 +3990,14 @@
       </c>
       <c r="AI22" s="4">
         <f t="shared" si="12"/>
-        <v>1771</v>
+        <v>1772</v>
       </c>
       <c r="AJ22" s="22">
-        <v>6011</v>
+        <v>6012</v>
       </c>
       <c r="AK22" s="5">
         <f t="shared" si="13"/>
-        <v>0.91827069966391694</v>
+        <v>0.91842346471127401</v>
       </c>
       <c r="AL22" s="9">
         <v>6648</v>
@@ -4007,14 +4007,14 @@
       </c>
       <c r="AN22" s="4">
         <f t="shared" si="14"/>
-        <v>1599</v>
+        <v>1600</v>
       </c>
       <c r="AO22" s="22">
-        <v>6072</v>
+        <v>6073</v>
       </c>
       <c r="AP22" s="5">
         <f t="shared" si="15"/>
-        <v>0.91335740072202165</v>
+        <v>0.91350782190132374</v>
       </c>
       <c r="AQ22" s="15">
         <v>7880</v>
@@ -4024,14 +4024,14 @@
       </c>
       <c r="AS22" s="4">
         <f t="shared" si="16"/>
-        <v>2025</v>
+        <v>2028</v>
       </c>
       <c r="AT22" s="8">
-        <v>7262</v>
+        <v>7265</v>
       </c>
       <c r="AU22" s="5">
         <f t="shared" si="17"/>
-        <v>0.92157360406091371</v>
+        <v>0.92195431472081213</v>
       </c>
       <c r="AV22" s="9">
         <v>6715</v>
@@ -4041,14 +4041,14 @@
       </c>
       <c r="AX22" s="4">
         <f t="shared" si="18"/>
-        <v>1676</v>
+        <v>1677</v>
       </c>
       <c r="AY22" s="22">
-        <v>6096</v>
+        <v>6097</v>
       </c>
       <c r="AZ22" s="5">
         <f t="shared" si="19"/>
-        <v>0.90781831720029782</v>
+        <v>0.90796723752792252</v>
       </c>
       <c r="BA22" s="9">
         <v>6117</v>
@@ -4058,14 +4058,14 @@
       </c>
       <c r="BC22" s="4">
         <f t="shared" si="20"/>
-        <v>1686</v>
+        <v>1687</v>
       </c>
       <c r="BD22" s="8">
-        <v>6144</v>
+        <v>6145</v>
       </c>
       <c r="BE22" s="5">
         <f t="shared" si="21"/>
-        <v>1.0044139283962727</v>
+        <v>1.0045774072257643</v>
       </c>
       <c r="BF22" s="9">
         <v>7349</v>
@@ -4075,14 +4075,14 @@
       </c>
       <c r="BH22" s="4">
         <f t="shared" si="22"/>
-        <v>2556</v>
+        <v>2559</v>
       </c>
       <c r="BI22" s="8">
-        <v>7402</v>
+        <v>7405</v>
       </c>
       <c r="BJ22" s="5">
         <f t="shared" si="23"/>
-        <v>1.00721186555994</v>
+        <v>1.0076200843652197</v>
       </c>
     </row>
     <row r="23" spans="1:62" x14ac:dyDescent="0.3">
@@ -4100,14 +4100,14 @@
       </c>
       <c r="E23" s="4">
         <f t="shared" si="0"/>
-        <v>2766</v>
+        <v>2767</v>
       </c>
       <c r="F23" s="22">
-        <v>7707</v>
+        <v>7708</v>
       </c>
       <c r="G23" s="5">
         <f t="shared" si="1"/>
-        <v>0.85519307589880156</v>
+        <v>0.85530403905903241</v>
       </c>
       <c r="H23" s="9">
         <v>9118</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="J23" s="4">
         <f t="shared" si="2"/>
-        <v>2980</v>
+        <v>2981</v>
       </c>
       <c r="K23" s="22">
-        <v>7830</v>
+        <v>7831</v>
       </c>
       <c r="L23" s="5">
         <f t="shared" si="3"/>
-        <v>0.85874095196314981</v>
+        <v>0.85885062513709143</v>
       </c>
       <c r="M23" s="4">
         <v>11079</v>
@@ -4134,14 +4134,14 @@
       </c>
       <c r="O23" s="4">
         <f t="shared" si="4"/>
-        <v>3336</v>
+        <v>3337</v>
       </c>
       <c r="P23" s="8">
-        <v>9656</v>
+        <v>9657</v>
       </c>
       <c r="Q23" s="5">
         <f t="shared" si="5"/>
-        <v>0.87155880494629479</v>
+        <v>0.87164906580016244</v>
       </c>
       <c r="R23" s="9">
         <v>9156</v>
@@ -4151,14 +4151,14 @@
       </c>
       <c r="T23" s="4">
         <f t="shared" si="6"/>
-        <v>2805</v>
-      </c>
-      <c r="U23" s="22">
-        <v>7940</v>
+        <v>2806</v>
+      </c>
+      <c r="U23" s="8">
+        <v>7941</v>
       </c>
       <c r="V23" s="5">
         <f t="shared" si="7"/>
-        <v>0.86719091306247265</v>
+        <v>0.86730013106159898</v>
       </c>
       <c r="W23" s="9">
         <v>9166</v>
@@ -4168,14 +4168,14 @@
       </c>
       <c r="Y23" s="4">
         <f t="shared" si="8"/>
-        <v>3180</v>
+        <v>3181</v>
       </c>
       <c r="Z23" s="22">
-        <v>8112</v>
+        <v>8113</v>
       </c>
       <c r="AA23" s="5">
         <f t="shared" si="9"/>
-        <v>0.88500981889591968</v>
+        <v>0.88511891773947193</v>
       </c>
       <c r="AB23" s="9">
         <v>11322</v>
@@ -4185,14 +4185,14 @@
       </c>
       <c r="AD23" s="4">
         <f t="shared" si="10"/>
-        <v>3787</v>
+        <v>3788</v>
       </c>
       <c r="AE23" s="8">
-        <v>10053</v>
+        <v>10054</v>
       </c>
       <c r="AF23" s="5">
         <f t="shared" si="11"/>
-        <v>0.88791732909379972</v>
+        <v>0.88800565271153509</v>
       </c>
       <c r="AG23" s="9">
         <v>9569</v>
@@ -4202,14 +4202,14 @@
       </c>
       <c r="AI23" s="4">
         <f t="shared" si="12"/>
-        <v>3120</v>
+        <v>3121</v>
       </c>
       <c r="AJ23" s="22">
-        <v>8228</v>
+        <v>8229</v>
       </c>
       <c r="AK23" s="5">
         <f t="shared" si="13"/>
-        <v>0.85985996446859647</v>
+        <v>0.85996446859650955</v>
       </c>
       <c r="AL23" s="9">
         <v>9502</v>
@@ -4219,14 +4219,14 @@
       </c>
       <c r="AN23" s="4">
         <f t="shared" si="14"/>
-        <v>2851</v>
+        <v>2852</v>
       </c>
       <c r="AO23" s="22">
-        <v>8342</v>
+        <v>8343</v>
       </c>
       <c r="AP23" s="5">
         <f t="shared" si="15"/>
-        <v>0.8779204378025679</v>
+        <v>0.87802567880446225</v>
       </c>
       <c r="AQ23" s="15">
         <v>11767</v>
@@ -4236,14 +4236,14 @@
       </c>
       <c r="AS23" s="4">
         <f t="shared" si="16"/>
-        <v>3220</v>
+        <v>3221</v>
       </c>
       <c r="AT23" s="8">
-        <v>10346</v>
+        <v>10347</v>
       </c>
       <c r="AU23" s="5">
         <f t="shared" si="17"/>
-        <v>0.87923854848304583</v>
+        <v>0.87932353191127732</v>
       </c>
       <c r="AV23" s="9">
         <v>9805</v>
@@ -4253,14 +4253,14 @@
       </c>
       <c r="AX23" s="4">
         <f t="shared" si="18"/>
-        <v>2848</v>
+        <v>2849</v>
       </c>
       <c r="AY23" s="22">
-        <v>8436</v>
+        <v>8437</v>
       </c>
       <c r="AZ23" s="5">
         <f t="shared" si="19"/>
-        <v>0.86037735849056607</v>
+        <v>0.86047934727180009</v>
       </c>
       <c r="BA23" s="9">
         <v>8694</v>
@@ -4270,14 +4270,14 @@
       </c>
       <c r="BC23" s="4">
         <f t="shared" si="20"/>
-        <v>2853</v>
+        <v>2854</v>
       </c>
       <c r="BD23" s="8">
-        <v>8535</v>
+        <v>8536</v>
       </c>
       <c r="BE23" s="5">
         <f t="shared" si="21"/>
-        <v>0.98171152518978611</v>
+        <v>0.98182654704393835</v>
       </c>
       <c r="BF23" s="9">
         <v>11229</v>
@@ -4287,14 +4287,14 @@
       </c>
       <c r="BH23" s="4">
         <f t="shared" si="22"/>
-        <v>4620</v>
+        <v>4621</v>
       </c>
       <c r="BI23" s="8">
-        <v>10606</v>
+        <v>10607</v>
       </c>
       <c r="BJ23" s="5">
         <f t="shared" si="23"/>
-        <v>0.94451865704871318</v>
+        <v>0.94460771217383566</v>
       </c>
     </row>
     <row r="24" spans="1:62" x14ac:dyDescent="0.3">
@@ -4312,14 +4312,14 @@
       </c>
       <c r="E24" s="4">
         <f t="shared" si="0"/>
-        <v>1132</v>
+        <v>1134</v>
       </c>
       <c r="F24" s="22">
-        <v>5107</v>
+        <v>5109</v>
       </c>
       <c r="G24" s="5">
         <f t="shared" si="1"/>
-        <v>0.81089234677675448</v>
+        <v>0.8112099079072721</v>
       </c>
       <c r="H24" s="9">
         <v>6340</v>
@@ -4329,14 +4329,14 @@
       </c>
       <c r="J24" s="4">
         <f t="shared" si="2"/>
-        <v>1298</v>
+        <v>1300</v>
       </c>
       <c r="K24" s="22">
-        <v>5175</v>
+        <v>5177</v>
       </c>
       <c r="L24" s="5">
         <f t="shared" si="3"/>
-        <v>0.81624605678233442</v>
+        <v>0.81656151419558365</v>
       </c>
       <c r="M24" s="4">
         <v>7252</v>
@@ -4346,14 +4346,14 @@
       </c>
       <c r="O24" s="4">
         <f t="shared" si="4"/>
-        <v>1355</v>
+        <v>1357</v>
       </c>
       <c r="P24" s="8">
-        <v>6055</v>
+        <v>6057</v>
       </c>
       <c r="Q24" s="5">
         <f t="shared" si="5"/>
-        <v>0.83494208494208499</v>
+        <v>0.8352178709321566</v>
       </c>
       <c r="R24" s="9">
         <v>6353</v>
@@ -4363,14 +4363,14 @@
       </c>
       <c r="T24" s="4">
         <f t="shared" si="6"/>
-        <v>1166</v>
-      </c>
-      <c r="U24" s="22">
-        <v>5206</v>
+        <v>1168</v>
+      </c>
+      <c r="U24" s="8">
+        <v>5208</v>
       </c>
       <c r="V24" s="5">
         <f t="shared" si="7"/>
-        <v>0.81945537541319058</v>
+        <v>0.81977018731308049</v>
       </c>
       <c r="W24" s="9">
         <v>6421</v>
@@ -4380,14 +4380,14 @@
       </c>
       <c r="Y24" s="4">
         <f t="shared" si="8"/>
-        <v>1154</v>
+        <v>1156</v>
       </c>
       <c r="Z24" s="22">
-        <v>5276</v>
+        <v>5278</v>
       </c>
       <c r="AA24" s="5">
         <f t="shared" si="9"/>
-        <v>0.82167886622021491</v>
+        <v>0.82199034418314909</v>
       </c>
       <c r="AB24" s="9">
         <v>7434</v>
@@ -4397,14 +4397,14 @@
       </c>
       <c r="AD24" s="4">
         <f t="shared" si="10"/>
-        <v>1553</v>
+        <v>1555</v>
       </c>
       <c r="AE24" s="8">
-        <v>6221</v>
+        <v>6223</v>
       </c>
       <c r="AF24" s="5">
         <f t="shared" si="11"/>
-        <v>0.83683077750874357</v>
+        <v>0.83709981167608283</v>
       </c>
       <c r="AG24" s="9">
         <v>6545</v>
@@ -4414,14 +4414,14 @@
       </c>
       <c r="AI24" s="4">
         <f t="shared" si="12"/>
-        <v>1414</v>
+        <v>1416</v>
       </c>
       <c r="AJ24" s="22">
-        <v>5335</v>
+        <v>5337</v>
       </c>
       <c r="AK24" s="5">
         <f t="shared" si="13"/>
-        <v>0.81512605042016806</v>
+        <v>0.81543162719633311</v>
       </c>
       <c r="AL24" s="9">
         <v>6623</v>
@@ -4431,14 +4431,14 @@
       </c>
       <c r="AN24" s="4">
         <f t="shared" si="14"/>
-        <v>1304</v>
+        <v>1306</v>
       </c>
       <c r="AO24" s="22">
-        <v>5427</v>
+        <v>5429</v>
       </c>
       <c r="AP24" s="5">
         <f t="shared" si="15"/>
-        <v>0.81941718254567419</v>
+        <v>0.81971916050128346</v>
       </c>
       <c r="AQ24" s="15">
         <v>7610</v>
@@ -4448,14 +4448,14 @@
       </c>
       <c r="AS24" s="4">
         <f t="shared" si="16"/>
-        <v>1412</v>
+        <v>1414</v>
       </c>
       <c r="AT24" s="8">
-        <v>6381</v>
+        <v>6383</v>
       </c>
       <c r="AU24" s="5">
         <f t="shared" si="17"/>
-        <v>0.83850197109067015</v>
+        <v>0.83876478318002623</v>
       </c>
       <c r="AV24" s="9">
         <v>6365</v>
@@ -4558,14 +4558,14 @@
       </c>
       <c r="O25" s="4">
         <f t="shared" si="4"/>
-        <v>4372</v>
+        <v>4373</v>
       </c>
       <c r="P25" s="8">
-        <v>24777</v>
+        <v>24778</v>
       </c>
       <c r="Q25" s="5">
         <f t="shared" si="5"/>
-        <v>0.93097617795145415</v>
+        <v>0.93101375216051707</v>
       </c>
       <c r="R25" s="9">
         <v>19402</v>
@@ -4575,14 +4575,14 @@
       </c>
       <c r="T25" s="4">
         <f t="shared" si="6"/>
-        <v>3190</v>
-      </c>
-      <c r="U25" s="22">
-        <v>17850</v>
+        <v>3191</v>
+      </c>
+      <c r="U25" s="8">
+        <v>17851</v>
       </c>
       <c r="V25" s="5">
         <f t="shared" si="7"/>
-        <v>0.92000824657251834</v>
+        <v>0.92005978765075769</v>
       </c>
       <c r="W25" s="9">
         <v>19474</v>
@@ -4592,14 +4592,14 @@
       </c>
       <c r="Y25" s="4">
         <f t="shared" si="8"/>
-        <v>3577</v>
+        <v>3578</v>
       </c>
       <c r="Z25" s="22">
-        <v>18048</v>
+        <v>18049</v>
       </c>
       <c r="AA25" s="5">
         <f t="shared" si="9"/>
-        <v>0.92677416041902028</v>
+        <v>0.92682551093766052</v>
       </c>
       <c r="AB25" s="9">
         <v>27081</v>
@@ -4609,14 +4609,14 @@
       </c>
       <c r="AD25" s="4">
         <f t="shared" si="10"/>
-        <v>5531</v>
+        <v>5532</v>
       </c>
       <c r="AE25" s="8">
-        <v>25183</v>
+        <v>25184</v>
       </c>
       <c r="AF25" s="5">
         <f t="shared" si="11"/>
-        <v>0.92991396181824892</v>
+        <v>0.92995088807651116</v>
       </c>
       <c r="AG25" s="9">
         <v>19543</v>
@@ -4626,14 +4626,14 @@
       </c>
       <c r="AI25" s="4">
         <f t="shared" si="12"/>
-        <v>3608</v>
+        <v>3609</v>
       </c>
       <c r="AJ25" s="22">
-        <v>18112</v>
+        <v>18113</v>
       </c>
       <c r="AK25" s="5">
         <f t="shared" si="13"/>
-        <v>0.9267768510464105</v>
+        <v>0.92682802026300981</v>
       </c>
       <c r="AL25" s="9">
         <v>19594</v>
@@ -4643,14 +4643,14 @@
       </c>
       <c r="AN25" s="4">
         <f t="shared" si="14"/>
-        <v>3309</v>
+        <v>3310</v>
       </c>
       <c r="AO25" s="22">
-        <v>18303</v>
+        <v>18304</v>
       </c>
       <c r="AP25" s="5">
         <f t="shared" si="15"/>
-        <v>0.93411248341328978</v>
+        <v>0.93416351944472797</v>
       </c>
       <c r="AQ25" s="15">
         <v>26830</v>
@@ -4660,14 +4660,14 @@
       </c>
       <c r="AS25" s="4">
         <f t="shared" si="16"/>
-        <v>4457</v>
+        <v>4458</v>
       </c>
       <c r="AT25" s="8">
-        <v>25423</v>
+        <v>25424</v>
       </c>
       <c r="AU25" s="5">
         <f t="shared" si="17"/>
-        <v>0.9475587029444652</v>
+        <v>0.94759597465523671</v>
       </c>
       <c r="AV25" s="9">
         <v>19719</v>
@@ -4677,14 +4677,14 @@
       </c>
       <c r="AX25" s="4">
         <f t="shared" si="18"/>
-        <v>3488</v>
+        <v>3490</v>
       </c>
       <c r="AY25" s="22">
-        <v>18388</v>
+        <v>18390</v>
       </c>
       <c r="AZ25" s="5">
         <f t="shared" si="19"/>
-        <v>0.93250164815660019</v>
+        <v>0.93260307317815305</v>
       </c>
       <c r="BA25" s="9">
         <v>18241</v>
@@ -4694,14 +4694,14 @@
       </c>
       <c r="BC25" s="4">
         <f t="shared" si="20"/>
-        <v>3480</v>
+        <v>3481</v>
       </c>
       <c r="BD25" s="8">
-        <v>18401</v>
+        <v>18402</v>
       </c>
       <c r="BE25" s="5">
         <f t="shared" si="21"/>
-        <v>1.0087714489337207</v>
+        <v>1.0088262704895565</v>
       </c>
       <c r="BF25" s="9">
         <v>25358</v>
@@ -4711,14 +4711,14 @@
       </c>
       <c r="BH25" s="4">
         <f t="shared" si="22"/>
-        <v>7385</v>
+        <v>7386</v>
       </c>
       <c r="BI25" s="8">
-        <v>25658</v>
+        <v>25659</v>
       </c>
       <c r="BJ25" s="5">
         <f t="shared" si="23"/>
-        <v>1.0118305860083603</v>
+        <v>1.0118700212950549</v>
       </c>
     </row>
     <row r="26" spans="1:62" x14ac:dyDescent="0.3">
@@ -4770,14 +4770,14 @@
       </c>
       <c r="O26" s="4">
         <f t="shared" si="4"/>
-        <v>5026</v>
+        <v>5027</v>
       </c>
       <c r="P26" s="8">
-        <v>24139</v>
+        <v>24140</v>
       </c>
       <c r="Q26" s="5">
         <f t="shared" si="5"/>
-        <v>0.87746274082151943</v>
+        <v>0.87749909123954928</v>
       </c>
       <c r="R26" s="9">
         <v>16566</v>
@@ -4787,14 +4787,14 @@
       </c>
       <c r="T26" s="4">
         <f t="shared" si="6"/>
-        <v>3646</v>
-      </c>
-      <c r="U26" s="22">
-        <v>13600</v>
+        <v>3647</v>
+      </c>
+      <c r="U26" s="8">
+        <v>13601</v>
       </c>
       <c r="V26" s="5">
         <f t="shared" si="7"/>
-        <v>0.82095858988289272</v>
+        <v>0.82101895448508999</v>
       </c>
       <c r="W26" s="9">
         <v>16728</v>
@@ -4804,14 +4804,14 @@
       </c>
       <c r="Y26" s="4">
         <f t="shared" si="8"/>
-        <v>3630</v>
+        <v>3631</v>
       </c>
       <c r="Z26" s="22">
-        <v>13811</v>
+        <v>13812</v>
       </c>
       <c r="AA26" s="5">
         <f t="shared" si="9"/>
-        <v>0.82562171209947388</v>
+        <v>0.82568149210903874</v>
       </c>
       <c r="AB26" s="9">
         <v>28240</v>
@@ -4821,14 +4821,14 @@
       </c>
       <c r="AD26" s="4">
         <f t="shared" si="10"/>
-        <v>5972</v>
+        <v>5973</v>
       </c>
       <c r="AE26" s="8">
-        <v>24945</v>
+        <v>24946</v>
       </c>
       <c r="AF26" s="5">
         <f t="shared" si="11"/>
-        <v>0.88332152974504252</v>
+        <v>0.88335694050991498</v>
       </c>
       <c r="AG26" s="9">
         <v>16538</v>
@@ -4838,14 +4838,14 @@
       </c>
       <c r="AI26" s="4">
         <f t="shared" si="12"/>
-        <v>3547</v>
+        <v>3548</v>
       </c>
       <c r="AJ26" s="22">
-        <v>13500</v>
+        <v>13501</v>
       </c>
       <c r="AK26" s="5">
         <f t="shared" si="13"/>
-        <v>0.816301850284194</v>
+        <v>0.81636231708791873</v>
       </c>
       <c r="AL26" s="9">
         <v>16671</v>
@@ -4855,14 +4855,14 @@
       </c>
       <c r="AN26" s="4">
         <f t="shared" si="14"/>
-        <v>3416</v>
+        <v>3418</v>
       </c>
       <c r="AO26" s="22">
-        <v>13613</v>
+        <v>13615</v>
       </c>
       <c r="AP26" s="5">
         <f t="shared" si="15"/>
-        <v>0.81656769239997595</v>
+        <v>0.81668766120808589</v>
       </c>
       <c r="AQ26" s="15">
         <v>28406</v>
@@ -4872,14 +4872,14 @@
       </c>
       <c r="AS26" s="4">
         <f t="shared" si="16"/>
-        <v>5536</v>
+        <v>5538</v>
       </c>
       <c r="AT26" s="8">
-        <v>25080</v>
+        <v>25082</v>
       </c>
       <c r="AU26" s="5">
         <f t="shared" si="17"/>
-        <v>0.88291206083221851</v>
+        <v>0.882982468492572</v>
       </c>
       <c r="AV26" s="9">
         <v>16717</v>
@@ -4889,14 +4889,14 @@
       </c>
       <c r="AX26" s="4">
         <f t="shared" si="18"/>
-        <v>3337</v>
+        <v>3339</v>
       </c>
       <c r="AY26" s="22">
-        <v>13308</v>
+        <v>13310</v>
       </c>
       <c r="AZ26" s="5">
         <f t="shared" si="19"/>
-        <v>0.79607585093019084</v>
+        <v>0.79619548962134357</v>
       </c>
       <c r="BA26" s="9">
         <v>13719</v>
@@ -4906,14 +4906,14 @@
       </c>
       <c r="BC26" s="4">
         <f t="shared" si="20"/>
-        <v>3278</v>
+        <v>3280</v>
       </c>
       <c r="BD26" s="8">
-        <v>13416</v>
+        <v>13418</v>
       </c>
       <c r="BE26" s="5">
         <f t="shared" si="21"/>
-        <v>0.97791384211677235</v>
+        <v>0.97805962533712365</v>
       </c>
       <c r="BF26" s="9">
         <v>25779</v>
@@ -4923,14 +4923,14 @@
       </c>
       <c r="BH26" s="4">
         <f t="shared" si="22"/>
-        <v>6621</v>
+        <v>6623</v>
       </c>
       <c r="BI26" s="8">
-        <v>25119</v>
+        <v>25121</v>
       </c>
       <c r="BJ26" s="5">
         <f t="shared" si="23"/>
-        <v>0.9743977656231817</v>
+        <v>0.97447534815159631</v>
       </c>
     </row>
     <row r="27" spans="1:62" x14ac:dyDescent="0.3">
@@ -4948,14 +4948,14 @@
       </c>
       <c r="E27" s="4">
         <f t="shared" si="0"/>
-        <v>32557</v>
+        <v>32561</v>
       </c>
       <c r="F27" s="22">
-        <v>112759</v>
+        <v>112763</v>
       </c>
       <c r="G27" s="5">
         <f t="shared" si="1"/>
-        <v>0.95150456516969606</v>
+        <v>0.95153831873491634</v>
       </c>
       <c r="H27" s="9">
         <v>121212</v>
@@ -4965,14 +4965,14 @@
       </c>
       <c r="J27" s="4">
         <f t="shared" si="2"/>
-        <v>34897</v>
+        <v>34901</v>
       </c>
       <c r="K27" s="22">
-        <v>114779</v>
+        <v>114783</v>
       </c>
       <c r="L27" s="5">
         <f t="shared" si="3"/>
-        <v>0.94692769692769696</v>
+        <v>0.94696069696069696</v>
       </c>
       <c r="M27" s="4">
         <v>178312</v>
@@ -4982,14 +4982,14 @@
       </c>
       <c r="O27" s="4">
         <f t="shared" si="4"/>
-        <v>46493</v>
+        <v>46497</v>
       </c>
       <c r="P27" s="8">
-        <v>168581</v>
+        <v>168585</v>
       </c>
       <c r="Q27" s="5">
         <f t="shared" si="5"/>
-        <v>0.94542711651487277</v>
+        <v>0.94544954910493961</v>
       </c>
       <c r="R27" s="9">
         <v>121489</v>
@@ -4999,14 +4999,14 @@
       </c>
       <c r="T27" s="4">
         <f t="shared" si="6"/>
-        <v>32065</v>
-      </c>
-      <c r="U27" s="22">
-        <v>114999</v>
+        <v>32069</v>
+      </c>
+      <c r="U27" s="8">
+        <v>115003</v>
       </c>
       <c r="V27" s="5">
         <f t="shared" si="7"/>
-        <v>0.94657952571837778</v>
+        <v>0.94661245050992271</v>
       </c>
       <c r="W27" s="9">
         <v>123451</v>
@@ -5016,14 +5016,14 @@
       </c>
       <c r="Y27" s="4">
         <f t="shared" si="8"/>
-        <v>35416</v>
+        <v>35420</v>
       </c>
       <c r="Z27" s="22">
-        <v>116901</v>
+        <v>116905</v>
       </c>
       <c r="AA27" s="5">
         <f t="shared" si="9"/>
-        <v>0.94694251160379417</v>
+        <v>0.94697491312342552</v>
       </c>
       <c r="AB27" s="9">
         <v>182601</v>
@@ -5033,14 +5033,14 @@
       </c>
       <c r="AD27" s="4">
         <f t="shared" si="10"/>
-        <v>53468</v>
+        <v>53474</v>
       </c>
       <c r="AE27" s="8">
-        <v>173165</v>
+        <v>173171</v>
       </c>
       <c r="AF27" s="5">
         <f t="shared" si="11"/>
-        <v>0.94832448891298515</v>
+        <v>0.94835734744059452</v>
       </c>
       <c r="AG27" s="9">
         <v>124689</v>
@@ -5050,14 +5050,14 @@
       </c>
       <c r="AI27" s="4">
         <f t="shared" si="12"/>
-        <v>33827</v>
+        <v>33831</v>
       </c>
       <c r="AJ27" s="22">
-        <v>117391</v>
+        <v>117395</v>
       </c>
       <c r="AK27" s="5">
         <f t="shared" si="13"/>
-        <v>0.94147037830121338</v>
+        <v>0.94150245811579214</v>
       </c>
       <c r="AL27" s="9">
         <v>127177</v>
@@ -5067,14 +5067,14 @@
       </c>
       <c r="AN27" s="4">
         <f t="shared" si="14"/>
-        <v>31118</v>
+        <v>31122</v>
       </c>
       <c r="AO27" s="22">
-        <v>119328</v>
+        <v>119332</v>
       </c>
       <c r="AP27" s="5">
         <f t="shared" si="15"/>
-        <v>0.93828286561249286</v>
+        <v>0.93831431784049002</v>
       </c>
       <c r="AQ27" s="15">
         <v>185152</v>
@@ -5084,14 +5084,14 @@
       </c>
       <c r="AS27" s="4">
         <f t="shared" si="16"/>
-        <v>44035</v>
+        <v>44039</v>
       </c>
       <c r="AT27" s="8">
-        <v>176395</v>
+        <v>176399</v>
       </c>
       <c r="AU27" s="5">
         <f t="shared" si="17"/>
-        <v>0.95270372450743168</v>
+        <v>0.95272532837884549</v>
       </c>
       <c r="AV27" s="9">
         <v>127611</v>
@@ -5101,14 +5101,14 @@
       </c>
       <c r="AX27" s="4">
         <f t="shared" si="18"/>
-        <v>30407</v>
+        <v>30410</v>
       </c>
       <c r="AY27" s="22">
-        <v>119207</v>
+        <v>119210</v>
       </c>
       <c r="AZ27" s="5">
         <f t="shared" si="19"/>
-        <v>0.9341436083096285</v>
+        <v>0.93416711725478208</v>
       </c>
       <c r="BA27" s="9">
         <v>122070</v>
@@ -5118,14 +5118,14 @@
       </c>
       <c r="BC27" s="4">
         <f t="shared" si="20"/>
-        <v>31284</v>
+        <v>31288</v>
       </c>
       <c r="BD27" s="8">
-        <v>120875</v>
+        <v>120879</v>
       </c>
       <c r="BE27" s="5">
         <f t="shared" si="21"/>
-        <v>0.99021053493896949</v>
+        <v>0.99024330302285579</v>
       </c>
       <c r="BF27" s="9">
         <v>180737</v>
@@ -5135,14 +5135,14 @@
       </c>
       <c r="BH27" s="4">
         <f t="shared" si="22"/>
-        <v>65930</v>
+        <v>65936</v>
       </c>
       <c r="BI27" s="8">
-        <v>179333</v>
+        <v>179339</v>
       </c>
       <c r="BJ27" s="5">
         <f t="shared" si="23"/>
-        <v>0.9922318064369775</v>
+        <v>0.99226500384536642</v>
       </c>
     </row>
     <row r="28" spans="1:62" x14ac:dyDescent="0.3">
@@ -5160,14 +5160,14 @@
       </c>
       <c r="E28" s="4">
         <f t="shared" si="0"/>
-        <v>55196</v>
+        <v>55197</v>
       </c>
       <c r="F28" s="22">
-        <v>349851</v>
+        <v>349852</v>
       </c>
       <c r="G28" s="5">
         <f t="shared" si="1"/>
-        <v>0.96017949280930948</v>
+        <v>0.96018223734767816</v>
       </c>
       <c r="H28" s="9">
         <v>368904</v>
@@ -5177,14 +5177,14 @@
       </c>
       <c r="J28" s="4">
         <f t="shared" si="2"/>
-        <v>63526</v>
+        <v>63527</v>
       </c>
       <c r="K28" s="22">
-        <v>354987</v>
+        <v>354988</v>
       </c>
       <c r="L28" s="5">
         <f t="shared" si="3"/>
-        <v>0.96227473814325681</v>
+        <v>0.96227744887558819</v>
       </c>
       <c r="M28" s="4">
         <v>633580</v>
@@ -5194,14 +5194,14 @@
       </c>
       <c r="O28" s="4">
         <f t="shared" si="4"/>
-        <v>99956</v>
+        <v>99957</v>
       </c>
       <c r="P28" s="8">
-        <v>609215</v>
+        <v>609216</v>
       </c>
       <c r="Q28" s="5">
         <f t="shared" si="5"/>
-        <v>0.96154392499763253</v>
+        <v>0.96154550333028188</v>
       </c>
       <c r="R28" s="9">
         <v>370844</v>
@@ -5211,14 +5211,14 @@
       </c>
       <c r="T28" s="4">
         <f t="shared" si="6"/>
-        <v>61809</v>
-      </c>
-      <c r="U28" s="22">
-        <v>357056</v>
+        <v>61810</v>
+      </c>
+      <c r="U28" s="8">
+        <v>357057</v>
       </c>
       <c r="V28" s="5">
         <f t="shared" si="7"/>
-        <v>0.96281994585324282</v>
+        <v>0.96282264240489257</v>
       </c>
       <c r="W28" s="9">
         <v>375522</v>
@@ -5228,14 +5228,14 @@
       </c>
       <c r="Y28" s="4">
         <f t="shared" si="8"/>
-        <v>66534</v>
+        <v>66536</v>
       </c>
       <c r="Z28" s="22">
-        <v>361728</v>
+        <v>361730</v>
       </c>
       <c r="AA28" s="5">
         <f t="shared" si="9"/>
-        <v>0.9632671321520444</v>
+        <v>0.96327245807169748</v>
       </c>
       <c r="AB28" s="9">
         <v>643156</v>
@@ -5245,14 +5245,14 @@
       </c>
       <c r="AD28" s="4">
         <f t="shared" si="10"/>
-        <v>116200</v>
+        <v>116203</v>
       </c>
       <c r="AE28" s="8">
-        <v>620727</v>
+        <v>620730</v>
       </c>
       <c r="AF28" s="5">
         <f t="shared" si="11"/>
-        <v>0.965126656674275</v>
+        <v>0.96513132117246825</v>
       </c>
       <c r="AG28" s="9">
         <v>378725</v>
@@ -5262,14 +5262,14 @@
       </c>
       <c r="AI28" s="4">
         <f t="shared" si="12"/>
-        <v>65134</v>
+        <v>65137</v>
       </c>
       <c r="AJ28" s="22">
-        <v>363078</v>
+        <v>363081</v>
       </c>
       <c r="AK28" s="5">
         <f t="shared" si="13"/>
-        <v>0.95868506172024559</v>
+        <v>0.9586929830351838</v>
       </c>
       <c r="AL28" s="9">
         <v>382864</v>
@@ -5279,14 +5279,14 @@
       </c>
       <c r="AN28" s="4">
         <f t="shared" si="14"/>
-        <v>58061</v>
+        <v>58064</v>
       </c>
       <c r="AO28" s="22">
-        <v>368531</v>
+        <v>368534</v>
       </c>
       <c r="AP28" s="5">
         <f t="shared" si="15"/>
-        <v>0.96256373020184716</v>
+        <v>0.96257156588240211</v>
       </c>
       <c r="AQ28" s="15">
         <v>653033</v>
@@ -5296,14 +5296,14 @@
       </c>
       <c r="AS28" s="4">
         <f t="shared" si="16"/>
-        <v>88404</v>
+        <v>88407</v>
       </c>
       <c r="AT28" s="8">
-        <v>628965</v>
+        <v>628968</v>
       </c>
       <c r="AU28" s="5">
         <f t="shared" si="17"/>
-        <v>0.96314428214194381</v>
+        <v>0.96314887609048849</v>
       </c>
       <c r="AV28" s="9">
         <v>393378</v>
@@ -5313,14 +5313,14 @@
       </c>
       <c r="AX28" s="4">
         <f t="shared" si="18"/>
-        <v>54872</v>
+        <v>54875</v>
       </c>
       <c r="AY28" s="22">
-        <v>371536</v>
+        <v>371539</v>
       </c>
       <c r="AZ28" s="5">
         <f t="shared" si="19"/>
-        <v>0.94447579681629379</v>
+        <v>0.94448342306890576</v>
       </c>
       <c r="BA28" s="9">
         <v>381893</v>
@@ -5330,14 +5330,14 @@
       </c>
       <c r="BC28" s="4">
         <f t="shared" si="20"/>
-        <v>57998</v>
+        <v>58001</v>
       </c>
       <c r="BD28" s="8">
-        <v>376655</v>
+        <v>376658</v>
       </c>
       <c r="BE28" s="5">
         <f t="shared" si="21"/>
-        <v>0.98628411623150991</v>
+        <v>0.9862919718350428</v>
       </c>
       <c r="BF28" s="9">
         <v>643514</v>
@@ -5347,14 +5347,14 @@
       </c>
       <c r="BH28" s="4">
         <f t="shared" si="22"/>
-        <v>133755</v>
+        <v>133757</v>
       </c>
       <c r="BI28" s="8">
-        <v>639630</v>
+        <v>639632</v>
       </c>
       <c r="BJ28" s="5">
         <f t="shared" si="23"/>
-        <v>0.9939643892751362</v>
+        <v>0.99396749721062794</v>
       </c>
     </row>
     <row r="29" spans="1:62" x14ac:dyDescent="0.3">
@@ -5372,14 +5372,14 @@
       </c>
       <c r="E29" s="4">
         <f t="shared" si="0"/>
-        <v>22288</v>
+        <v>22289</v>
       </c>
       <c r="F29" s="22">
-        <v>115937</v>
+        <v>115938</v>
       </c>
       <c r="G29" s="5">
         <f t="shared" si="1"/>
-        <v>0.96166990162411459</v>
+        <v>0.96167819638680141</v>
       </c>
       <c r="H29" s="9">
         <v>121339</v>
@@ -5389,14 +5389,14 @@
       </c>
       <c r="J29" s="4">
         <f t="shared" si="2"/>
-        <v>25247</v>
+        <v>25248</v>
       </c>
       <c r="K29" s="22">
-        <v>116955</v>
+        <v>116956</v>
       </c>
       <c r="L29" s="5">
         <f t="shared" si="3"/>
-        <v>0.96386981926668258</v>
+        <v>0.96387806064002501</v>
       </c>
       <c r="M29" s="4">
         <v>168897</v>
@@ -5406,14 +5406,14 @@
       </c>
       <c r="O29" s="4">
         <f t="shared" si="4"/>
-        <v>30927</v>
+        <v>30928</v>
       </c>
       <c r="P29" s="8">
-        <v>162691</v>
+        <v>162692</v>
       </c>
       <c r="Q29" s="5">
         <f t="shared" si="5"/>
-        <v>0.96325571206119709</v>
+        <v>0.96326163282947597</v>
       </c>
       <c r="R29" s="9">
         <v>122532</v>
@@ -5423,14 +5423,14 @@
       </c>
       <c r="T29" s="4">
         <f t="shared" si="6"/>
-        <v>23588</v>
-      </c>
-      <c r="U29" s="22">
-        <v>118178</v>
+        <v>23589</v>
+      </c>
+      <c r="U29" s="8">
+        <v>118179</v>
       </c>
       <c r="V29" s="5">
         <f t="shared" si="7"/>
-        <v>0.96446642509711744</v>
+        <v>0.96447458623053572</v>
       </c>
       <c r="W29" s="9">
         <v>124179</v>
@@ -5440,14 +5440,14 @@
       </c>
       <c r="Y29" s="4">
         <f t="shared" si="8"/>
-        <v>24603</v>
+        <v>24604</v>
       </c>
       <c r="Z29" s="22">
-        <v>119482</v>
+        <v>119483</v>
       </c>
       <c r="AA29" s="5">
         <f t="shared" si="9"/>
-        <v>0.96217556913809899</v>
+        <v>0.9621836220294897</v>
       </c>
       <c r="AB29" s="9">
         <v>172673</v>
@@ -5457,14 +5457,14 @@
       </c>
       <c r="AD29" s="4">
         <f t="shared" si="10"/>
-        <v>37473</v>
+        <v>37474</v>
       </c>
       <c r="AE29" s="8">
-        <v>166137</v>
+        <v>166138</v>
       </c>
       <c r="AF29" s="5">
         <f t="shared" si="11"/>
-        <v>0.96214810653663285</v>
+        <v>0.96215389783000238</v>
       </c>
       <c r="AG29" s="9">
         <v>125793</v>
@@ -5474,14 +5474,14 @@
       </c>
       <c r="AI29" s="4">
         <f t="shared" si="12"/>
-        <v>24706</v>
+        <v>24707</v>
       </c>
       <c r="AJ29" s="22">
-        <v>120785</v>
+        <v>120786</v>
       </c>
       <c r="AK29" s="5">
         <f t="shared" si="13"/>
-        <v>0.96018856375156014</v>
+        <v>0.96019651331950107</v>
       </c>
       <c r="AL29" s="9">
         <v>126934</v>
@@ -5491,14 +5491,14 @@
       </c>
       <c r="AN29" s="4">
         <f t="shared" si="14"/>
-        <v>21696</v>
+        <v>21697</v>
       </c>
       <c r="AO29" s="22">
-        <v>122156</v>
+        <v>122157</v>
       </c>
       <c r="AP29" s="5">
         <f t="shared" si="15"/>
-        <v>0.96235839097483733</v>
+        <v>0.96236626908472123</v>
       </c>
       <c r="AQ29" s="15">
         <v>175834</v>
@@ -5508,14 +5508,14 @@
       </c>
       <c r="AS29" s="4">
         <f t="shared" si="16"/>
-        <v>28296</v>
+        <v>28297</v>
       </c>
       <c r="AT29" s="8">
-        <v>169052</v>
+        <v>169053</v>
       </c>
       <c r="AU29" s="5">
         <f t="shared" si="17"/>
-        <v>0.96142953012500432</v>
+        <v>0.96143521730723291</v>
       </c>
       <c r="AV29" s="9">
         <v>130198</v>
@@ -5525,14 +5525,14 @@
       </c>
       <c r="AX29" s="4">
         <f t="shared" si="18"/>
-        <v>22059</v>
+        <v>22060</v>
       </c>
       <c r="AY29" s="22">
-        <v>123786</v>
+        <v>123787</v>
       </c>
       <c r="AZ29" s="5">
         <f t="shared" si="19"/>
-        <v>0.95075193167329763</v>
+        <v>0.95075961228283079</v>
       </c>
       <c r="BA29" s="9">
         <v>127545</v>
@@ -5542,14 +5542,14 @@
       </c>
       <c r="BC29" s="4">
         <f t="shared" si="20"/>
-        <v>22790</v>
+        <v>22791</v>
       </c>
       <c r="BD29" s="8">
-        <v>125577</v>
+        <v>125578</v>
       </c>
       <c r="BE29" s="5">
         <f t="shared" si="21"/>
-        <v>0.9845701517111608</v>
+        <v>0.98457799208122621</v>
       </c>
       <c r="BF29" s="9">
         <v>174166</v>
@@ -5559,14 +5559,14 @@
       </c>
       <c r="BH29" s="4">
         <f t="shared" si="22"/>
-        <v>42587</v>
+        <v>42590</v>
       </c>
       <c r="BI29" s="8">
-        <v>172593</v>
+        <v>172596</v>
       </c>
       <c r="BJ29" s="5">
         <f t="shared" si="23"/>
-        <v>0.99096838648186214</v>
+        <v>0.99098561142817776</v>
       </c>
     </row>
     <row r="30" spans="1:62" x14ac:dyDescent="0.3">
@@ -5584,14 +5584,14 @@
       </c>
       <c r="E30" s="4">
         <f t="shared" si="0"/>
-        <v>33472</v>
+        <v>33474</v>
       </c>
       <c r="F30" s="22">
-        <v>151941</v>
+        <v>151943</v>
       </c>
       <c r="G30" s="5">
         <f t="shared" si="1"/>
-        <v>0.95785684566212348</v>
+        <v>0.95786945393567258</v>
       </c>
       <c r="H30" s="9">
         <v>160653</v>
@@ -5601,14 +5601,14 @@
       </c>
       <c r="J30" s="4">
         <f t="shared" si="2"/>
-        <v>39623</v>
+        <v>39625</v>
       </c>
       <c r="K30" s="22">
-        <v>155061</v>
+        <v>155063</v>
       </c>
       <c r="L30" s="5">
         <f t="shared" si="3"/>
-        <v>0.9651920599055106</v>
+        <v>0.96520450909724687</v>
       </c>
       <c r="M30" s="4">
         <v>275749</v>
@@ -5618,14 +5618,14 @@
       </c>
       <c r="O30" s="4">
         <f t="shared" si="4"/>
-        <v>59345</v>
+        <v>59348</v>
       </c>
       <c r="P30" s="8">
-        <v>264944</v>
+        <v>264947</v>
       </c>
       <c r="Q30" s="5">
         <f t="shared" si="5"/>
-        <v>0.96081581438191976</v>
+        <v>0.96082669384113817</v>
       </c>
       <c r="R30" s="9">
         <v>161454</v>
@@ -5635,14 +5635,14 @@
       </c>
       <c r="T30" s="4">
         <f t="shared" si="6"/>
-        <v>35706</v>
-      </c>
-      <c r="U30" s="22">
-        <v>154879</v>
+        <v>35708</v>
+      </c>
+      <c r="U30" s="8">
+        <v>154881</v>
       </c>
       <c r="V30" s="5">
         <f t="shared" si="7"/>
-        <v>0.95927632638398552</v>
+        <v>0.95928871381322234</v>
       </c>
       <c r="W30" s="9">
         <v>163696</v>
@@ -5652,14 +5652,14 @@
       </c>
       <c r="Y30" s="4">
         <f t="shared" si="8"/>
-        <v>38337</v>
+        <v>38339</v>
       </c>
       <c r="Z30" s="22">
-        <v>157863</v>
+        <v>157865</v>
       </c>
       <c r="AA30" s="5">
         <f t="shared" si="9"/>
-        <v>0.96436687518326658</v>
+        <v>0.96437909295279056</v>
       </c>
       <c r="AB30" s="9">
         <v>281667</v>
@@ -5669,14 +5669,14 @@
       </c>
       <c r="AD30" s="4">
         <f t="shared" si="10"/>
-        <v>68191</v>
+        <v>68195</v>
       </c>
       <c r="AE30" s="8">
-        <v>270990</v>
+        <v>270994</v>
       </c>
       <c r="AF30" s="5">
         <f t="shared" si="11"/>
-        <v>0.96209353598398106</v>
+        <v>0.96210773715060693</v>
       </c>
       <c r="AG30" s="9">
         <v>165324</v>
@@ -5686,14 +5686,14 @@
       </c>
       <c r="AI30" s="4">
         <f t="shared" si="12"/>
-        <v>38753</v>
+        <v>38755</v>
       </c>
       <c r="AJ30" s="22">
-        <v>158465</v>
+        <v>158467</v>
       </c>
       <c r="AK30" s="5">
         <f t="shared" si="13"/>
-        <v>0.95851177082577244</v>
+        <v>0.95852386828288694</v>
       </c>
       <c r="AL30" s="9">
         <v>168552</v>
@@ -5703,14 +5703,14 @@
       </c>
       <c r="AN30" s="4">
         <f t="shared" si="14"/>
-        <v>34438</v>
+        <v>34440</v>
       </c>
       <c r="AO30" s="22">
-        <v>161930</v>
+        <v>161932</v>
       </c>
       <c r="AP30" s="5">
         <f t="shared" si="15"/>
-        <v>0.96071242109260047</v>
+        <v>0.96072428686696099</v>
       </c>
       <c r="AQ30" s="15">
         <v>288456</v>
@@ -5720,14 +5720,14 @@
       </c>
       <c r="AS30" s="4">
         <f t="shared" si="16"/>
-        <v>55846</v>
+        <v>55849</v>
       </c>
       <c r="AT30" s="8">
-        <v>277219</v>
+        <v>277222</v>
       </c>
       <c r="AU30" s="5">
         <f t="shared" si="17"/>
-        <v>0.961044318717586</v>
+        <v>0.9610547189172699</v>
       </c>
       <c r="AV30" s="9">
         <v>173481</v>
@@ -5737,14 +5737,14 @@
       </c>
       <c r="AX30" s="4">
         <f t="shared" si="18"/>
-        <v>35290</v>
+        <v>35292</v>
       </c>
       <c r="AY30" s="22">
-        <v>162972</v>
+        <v>162974</v>
       </c>
       <c r="AZ30" s="5">
         <f t="shared" si="19"/>
-        <v>0.93942276099399935</v>
+        <v>0.93943428963402331</v>
       </c>
       <c r="BA30" s="9">
         <v>168414</v>
@@ -5754,14 +5754,14 @@
       </c>
       <c r="BC30" s="4">
         <f t="shared" si="20"/>
-        <v>35319</v>
+        <v>35321</v>
       </c>
       <c r="BD30" s="8">
-        <v>165839</v>
+        <v>165841</v>
       </c>
       <c r="BE30" s="5">
         <f t="shared" si="21"/>
-        <v>0.98471029724369707</v>
+        <v>0.9847221727409835</v>
       </c>
       <c r="BF30" s="9">
         <v>284492</v>
@@ -5771,14 +5771,14 @@
       </c>
       <c r="BH30" s="4">
         <f t="shared" si="22"/>
-        <v>78362</v>
+        <v>78365</v>
       </c>
       <c r="BI30" s="8">
-        <v>283042</v>
+        <v>283045</v>
       </c>
       <c r="BJ30" s="5">
         <f t="shared" si="23"/>
-        <v>0.9949031958719402</v>
+        <v>0.99491374098392926</v>
       </c>
     </row>
     <row r="31" spans="1:62" x14ac:dyDescent="0.3">
@@ -5830,14 +5830,14 @@
       </c>
       <c r="O31" s="4">
         <f t="shared" si="4"/>
-        <v>36849</v>
+        <v>36850</v>
       </c>
       <c r="P31" s="8">
-        <v>126933</v>
+        <v>126934</v>
       </c>
       <c r="Q31" s="5">
         <f t="shared" si="5"/>
-        <v>0.96050032916392358</v>
+        <v>0.96050789615067389</v>
       </c>
       <c r="R31" s="9">
         <v>74474</v>
@@ -5847,14 +5847,14 @@
       </c>
       <c r="T31" s="4">
         <f t="shared" si="6"/>
-        <v>20043</v>
-      </c>
-      <c r="U31" s="22">
-        <v>71229</v>
+        <v>20044</v>
+      </c>
+      <c r="U31" s="8">
+        <v>71230</v>
       </c>
       <c r="V31" s="5">
         <f t="shared" si="7"/>
-        <v>0.9564277465961275</v>
+        <v>0.95644117410102858</v>
       </c>
       <c r="W31" s="9">
         <v>75697</v>
@@ -5881,14 +5881,14 @@
       </c>
       <c r="AD31" s="4">
         <f t="shared" si="10"/>
-        <v>38788</v>
+        <v>38790</v>
       </c>
       <c r="AE31" s="8">
-        <v>129179</v>
+        <v>129181</v>
       </c>
       <c r="AF31" s="5">
         <f t="shared" si="11"/>
-        <v>0.96539844106151307</v>
+        <v>0.96541338773924024</v>
       </c>
       <c r="AG31" s="9">
         <v>75434</v>
@@ -5932,14 +5932,14 @@
       </c>
       <c r="AS31" s="4">
         <f t="shared" si="16"/>
-        <v>32617</v>
+        <v>32619</v>
       </c>
       <c r="AT31" s="8">
-        <v>131034</v>
+        <v>131036</v>
       </c>
       <c r="AU31" s="5">
         <f t="shared" si="17"/>
-        <v>0.96671240759594523</v>
+        <v>0.96672716273442227</v>
       </c>
       <c r="AV31" s="9">
         <v>78435</v>
@@ -5966,14 +5966,14 @@
       </c>
       <c r="BC31" s="4">
         <f t="shared" si="20"/>
-        <v>19443</v>
+        <v>19444</v>
       </c>
       <c r="BD31" s="8">
-        <v>74506</v>
+        <v>74507</v>
       </c>
       <c r="BE31" s="5">
         <f t="shared" si="21"/>
-        <v>0.97820549851639838</v>
+        <v>0.97821862773415957</v>
       </c>
       <c r="BF31" s="9">
         <v>132970</v>
@@ -5983,14 +5983,14 @@
       </c>
       <c r="BH31" s="4">
         <f t="shared" si="22"/>
-        <v>49530</v>
+        <v>49531</v>
       </c>
       <c r="BI31" s="8">
-        <v>132952</v>
+        <v>132953</v>
       </c>
       <c r="BJ31" s="5">
         <f t="shared" si="23"/>
-        <v>0.99986463111980151</v>
+        <v>0.9998721516131458</v>
       </c>
     </row>
     <row r="32" spans="1:62" x14ac:dyDescent="0.3">
@@ -6008,14 +6008,14 @@
       </c>
       <c r="E32" s="4">
         <f t="shared" si="0"/>
-        <v>38781</v>
+        <v>38782</v>
       </c>
       <c r="F32" s="22">
-        <v>188995</v>
+        <v>188996</v>
       </c>
       <c r="G32" s="5">
         <f t="shared" si="1"/>
-        <v>0.98435921207512578</v>
+        <v>0.98436442046271311</v>
       </c>
       <c r="H32" s="9">
         <v>196288</v>
@@ -6025,14 +6025,14 @@
       </c>
       <c r="J32" s="4">
         <f t="shared" si="2"/>
-        <v>46872</v>
+        <v>46873</v>
       </c>
       <c r="K32" s="22">
-        <v>192872</v>
+        <v>192873</v>
       </c>
       <c r="L32" s="5">
         <f t="shared" si="3"/>
-        <v>0.98259700032605146</v>
+        <v>0.98260209488099115</v>
       </c>
       <c r="M32" s="4">
         <v>418497</v>
@@ -6042,14 +6042,14 @@
       </c>
       <c r="O32" s="4">
         <f t="shared" si="4"/>
-        <v>94442</v>
+        <v>94443</v>
       </c>
       <c r="P32" s="8">
-        <v>409072</v>
+        <v>409073</v>
       </c>
       <c r="Q32" s="5">
         <f t="shared" si="5"/>
-        <v>0.97747893055386303</v>
+        <v>0.97748132005725252</v>
       </c>
       <c r="R32" s="9">
         <v>194320</v>
@@ -6059,14 +6059,14 @@
       </c>
       <c r="T32" s="4">
         <f t="shared" si="6"/>
-        <v>42839</v>
-      </c>
-      <c r="U32" s="22">
-        <v>190345</v>
+        <v>42841</v>
+      </c>
+      <c r="U32" s="8">
+        <v>190347</v>
       </c>
       <c r="V32" s="5">
         <f t="shared" si="7"/>
-        <v>0.97954405104981479</v>
+        <v>0.97955434335117331</v>
       </c>
       <c r="W32" s="9">
         <v>198209</v>
@@ -6076,14 +6076,14 @@
       </c>
       <c r="Y32" s="4">
         <f t="shared" si="8"/>
-        <v>47431</v>
+        <v>47433</v>
       </c>
       <c r="Z32" s="22">
-        <v>194354</v>
+        <v>194356</v>
       </c>
       <c r="AA32" s="5">
         <f t="shared" si="9"/>
-        <v>0.98055083270689025</v>
+        <v>0.98056092306605658</v>
       </c>
       <c r="AB32" s="9">
         <v>426405</v>
@@ -6093,14 +6093,14 @@
       </c>
       <c r="AD32" s="4">
         <f t="shared" si="10"/>
-        <v>98666</v>
+        <v>98667</v>
       </c>
       <c r="AE32" s="8">
-        <v>418380</v>
+        <v>418381</v>
       </c>
       <c r="AF32" s="5">
         <f t="shared" si="11"/>
-        <v>0.98117986421359971</v>
+        <v>0.98118220940185974</v>
       </c>
       <c r="AG32" s="9">
         <v>199136</v>
@@ -6110,14 +6110,14 @@
       </c>
       <c r="AI32" s="4">
         <f t="shared" si="12"/>
-        <v>44767</v>
+        <v>44768</v>
       </c>
       <c r="AJ32" s="22">
-        <v>195380</v>
+        <v>195381</v>
       </c>
       <c r="AK32" s="5">
         <f t="shared" si="13"/>
-        <v>0.98113851839948574</v>
+        <v>0.98114354009320259</v>
       </c>
       <c r="AL32" s="9">
         <v>204506</v>
@@ -6127,14 +6127,14 @@
       </c>
       <c r="AN32" s="4">
         <f t="shared" si="14"/>
-        <v>38342</v>
+        <v>38345</v>
       </c>
       <c r="AO32" s="22">
-        <v>199947</v>
+        <v>199950</v>
       </c>
       <c r="AP32" s="5">
         <f t="shared" si="15"/>
-        <v>0.97770725553284499</v>
+        <v>0.9777219250290945</v>
       </c>
       <c r="AQ32" s="15">
         <v>435626</v>
@@ -6144,14 +6144,14 @@
       </c>
       <c r="AS32" s="4">
         <f t="shared" si="16"/>
-        <v>82518</v>
+        <v>82521</v>
       </c>
       <c r="AT32" s="8">
-        <v>426564</v>
+        <v>426567</v>
       </c>
       <c r="AU32" s="5">
         <f t="shared" si="17"/>
-        <v>0.97919775220028193</v>
+        <v>0.97920463884157516</v>
       </c>
       <c r="AV32" s="9">
         <v>208760</v>
@@ -6161,14 +6161,14 @@
       </c>
       <c r="AX32" s="4">
         <f t="shared" si="18"/>
-        <v>38566</v>
+        <v>38569</v>
       </c>
       <c r="AY32" s="22">
-        <v>199580</v>
+        <v>199583</v>
       </c>
       <c r="AZ32" s="5">
         <f t="shared" si="19"/>
-        <v>0.9560260586319218</v>
+        <v>0.95604042920099641</v>
       </c>
       <c r="BA32" s="9">
         <v>206539</v>
@@ -6178,14 +6178,14 @@
       </c>
       <c r="BC32" s="4">
         <f t="shared" si="20"/>
-        <v>40476</v>
+        <v>40479</v>
       </c>
       <c r="BD32" s="8">
-        <v>203797</v>
+        <v>203800</v>
       </c>
       <c r="BE32" s="5">
         <f t="shared" si="21"/>
-        <v>0.98672405695776588</v>
+        <v>0.98673858205956255</v>
       </c>
       <c r="BF32" s="9">
         <v>435831</v>
@@ -6195,14 +6195,14 @@
       </c>
       <c r="BH32" s="4">
         <f t="shared" si="22"/>
-        <v>128639</v>
+        <v>128642</v>
       </c>
       <c r="BI32" s="8">
-        <v>435171</v>
+        <v>435174</v>
       </c>
       <c r="BJ32" s="5">
         <f t="shared" si="23"/>
-        <v>0.99848565154842128</v>
+        <v>0.99849253495047396</v>
       </c>
     </row>
     <row r="33" spans="1:62" x14ac:dyDescent="0.3">
@@ -6220,14 +6220,14 @@
       </c>
       <c r="E33" s="4">
         <f t="shared" si="0"/>
-        <v>71716</v>
+        <v>71718</v>
       </c>
       <c r="F33" s="22">
-        <v>581084</v>
+        <v>581086</v>
       </c>
       <c r="G33" s="5">
         <f t="shared" si="1"/>
-        <v>0.99075373354452723</v>
+        <v>0.99075714356350397</v>
       </c>
       <c r="H33" s="9">
         <v>594451</v>
@@ -6237,14 +6237,14 @@
       </c>
       <c r="J33" s="4">
         <f t="shared" si="2"/>
-        <v>83847</v>
+        <v>83849</v>
       </c>
       <c r="K33" s="22">
-        <v>590880</v>
+        <v>590882</v>
       </c>
       <c r="L33" s="5">
         <f t="shared" si="3"/>
-        <v>0.99399277652825879</v>
+        <v>0.99399614097713684</v>
       </c>
       <c r="M33" s="4">
         <v>1006436</v>
@@ -6254,14 +6254,14 @@
       </c>
       <c r="O33" s="4">
         <f t="shared" si="4"/>
-        <v>139356</v>
+        <v>139358</v>
       </c>
       <c r="P33" s="8">
-        <v>991605</v>
+        <v>991607</v>
       </c>
       <c r="Q33" s="5">
         <f t="shared" si="5"/>
-        <v>0.98526384191344507</v>
+        <v>0.98526582912375948</v>
       </c>
       <c r="R33" s="9">
         <v>599279</v>
@@ -6271,14 +6271,14 @@
       </c>
       <c r="T33" s="4">
         <f t="shared" si="6"/>
-        <v>86664</v>
-      </c>
-      <c r="U33" s="22">
-        <v>593528</v>
+        <v>86667</v>
+      </c>
+      <c r="U33" s="8">
+        <v>593531</v>
       </c>
       <c r="V33" s="5">
         <f t="shared" si="7"/>
-        <v>0.9904034681675814</v>
+        <v>0.99040847418314337</v>
       </c>
       <c r="W33" s="9">
         <v>608923</v>
@@ -6288,14 +6288,14 @@
       </c>
       <c r="Y33" s="4">
         <f t="shared" si="8"/>
-        <v>85230</v>
+        <v>85232</v>
       </c>
       <c r="Z33" s="22">
-        <v>601218</v>
+        <v>601220</v>
       </c>
       <c r="AA33" s="5">
         <f t="shared" si="9"/>
-        <v>0.9873465117921314</v>
+        <v>0.98734979627966102</v>
       </c>
       <c r="AB33" s="9">
         <v>1019860</v>
@@ -6305,14 +6305,14 @@
       </c>
       <c r="AD33" s="4">
         <f t="shared" si="10"/>
-        <v>135720</v>
+        <v>135722</v>
       </c>
       <c r="AE33" s="8">
-        <v>1006181</v>
+        <v>1006183</v>
       </c>
       <c r="AF33" s="5">
         <f t="shared" si="11"/>
-        <v>0.98658737473770908</v>
+        <v>0.98658933579118702</v>
       </c>
       <c r="AG33" s="9">
         <v>610453</v>
@@ -6322,14 +6322,14 @@
       </c>
       <c r="AI33" s="4">
         <f t="shared" si="12"/>
-        <v>86832</v>
+        <v>86834</v>
       </c>
       <c r="AJ33" s="22">
-        <v>602923</v>
+        <v>602925</v>
       </c>
       <c r="AK33" s="5">
         <f t="shared" si="13"/>
-        <v>0.98766489803473811</v>
+        <v>0.98766817429024023</v>
       </c>
       <c r="AL33" s="9">
         <v>617988</v>
@@ -6339,14 +6339,14 @@
       </c>
       <c r="AN33" s="4">
         <f t="shared" si="14"/>
-        <v>70940</v>
+        <v>70941</v>
       </c>
       <c r="AO33" s="22">
-        <v>608866</v>
+        <v>608867</v>
       </c>
       <c r="AP33" s="5">
         <f t="shared" si="15"/>
-        <v>0.9852391955830857</v>
+        <v>0.98524081373748362</v>
       </c>
       <c r="AQ33" s="15">
         <v>1027609</v>
@@ -6356,14 +6356,14 @@
       </c>
       <c r="AS33" s="4">
         <f t="shared" si="16"/>
-        <v>122617</v>
+        <v>122619</v>
       </c>
       <c r="AT33" s="8">
-        <v>1015122</v>
+        <v>1015124</v>
       </c>
       <c r="AU33" s="5">
         <f t="shared" si="17"/>
-        <v>0.98784849101165906</v>
+        <v>0.98785043727721344</v>
       </c>
       <c r="AV33" s="9">
         <v>625585</v>
@@ -6373,14 +6373,14 @@
       </c>
       <c r="AX33" s="4">
         <f t="shared" si="18"/>
-        <v>71278</v>
+        <v>71279</v>
       </c>
       <c r="AY33" s="22">
-        <v>611825</v>
+        <v>611826</v>
       </c>
       <c r="AZ33" s="5">
         <f t="shared" si="19"/>
-        <v>0.97800458770590726</v>
+        <v>0.9780061862097077</v>
       </c>
       <c r="BA33" s="9">
         <v>617039</v>
@@ -6390,14 +6390,14 @@
       </c>
       <c r="BC33" s="4">
         <f t="shared" si="20"/>
-        <v>71309</v>
+        <v>71310</v>
       </c>
       <c r="BD33" s="8">
-        <v>617613</v>
+        <v>617614</v>
       </c>
       <c r="BE33" s="5">
         <f t="shared" si="21"/>
-        <v>1.0009302491414642</v>
+        <v>1.0009318697845679</v>
       </c>
       <c r="BF33" s="9">
         <v>1025594</v>
@@ -6407,14 +6407,14 @@
       </c>
       <c r="BH33" s="4">
         <f t="shared" si="22"/>
-        <v>171345</v>
+        <v>171347</v>
       </c>
       <c r="BI33" s="8">
-        <v>1028385</v>
+        <v>1028387</v>
       </c>
       <c r="BJ33" s="5">
         <f t="shared" si="23"/>
-        <v>1.0027213497738872</v>
+        <v>1.0027232998632987</v>
       </c>
     </row>
     <row r="34" spans="1:62" x14ac:dyDescent="0.3">
@@ -6478,7 +6478,7 @@
       <c r="T34" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="U34" s="23">
+      <c r="U34" s="8">
         <v>0</v>
       </c>
       <c r="V34" s="23" t="s">
@@ -6673,7 +6673,7 @@
         <f t="shared" si="6"/>
         <v>2235</v>
       </c>
-      <c r="U35" s="22">
+      <c r="U35" s="8">
         <v>11154</v>
       </c>
       <c r="V35" s="5">
@@ -6832,14 +6832,14 @@
       </c>
       <c r="E36" s="4">
         <f t="shared" si="0"/>
-        <v>170295</v>
+        <v>170299</v>
       </c>
       <c r="F36" s="22">
-        <v>777386</v>
+        <v>777390</v>
       </c>
       <c r="G36" s="5">
         <f t="shared" si="24"/>
-        <v>0.96671645001995898</v>
+        <v>0.96672142421012974</v>
       </c>
       <c r="H36" s="9">
         <v>814447</v>
@@ -6849,14 +6849,14 @@
       </c>
       <c r="J36" s="4">
         <f t="shared" si="2"/>
-        <v>192035</v>
+        <v>192039</v>
       </c>
       <c r="K36" s="22">
-        <v>789165</v>
+        <v>789169</v>
       </c>
       <c r="L36" s="5">
         <f t="shared" si="3"/>
-        <v>0.96895807830343783</v>
+        <v>0.96896298961135596</v>
       </c>
       <c r="M36" s="4">
         <v>1485608</v>
@@ -6866,14 +6866,14 @@
       </c>
       <c r="O36" s="4">
         <f t="shared" si="4"/>
-        <v>325451</v>
+        <v>325457</v>
       </c>
       <c r="P36" s="8">
-        <v>1435393</v>
+        <v>1435399</v>
       </c>
       <c r="Q36" s="5">
         <f t="shared" si="5"/>
-        <v>0.96619902423788784</v>
+        <v>0.96620306298835223</v>
       </c>
       <c r="R36" s="9">
         <v>815623</v>
@@ -6883,14 +6883,14 @@
       </c>
       <c r="T36" s="4">
         <f t="shared" si="6"/>
-        <v>178507</v>
-      </c>
-      <c r="U36" s="22">
-        <v>787769</v>
+        <v>178513</v>
+      </c>
+      <c r="U36" s="8">
+        <v>787775</v>
       </c>
       <c r="V36" s="5">
         <f t="shared" si="7"/>
-        <v>0.96584941817481851</v>
+        <v>0.96585677451469609</v>
       </c>
       <c r="W36" s="9">
         <v>826349</v>
@@ -6900,14 +6900,14 @@
       </c>
       <c r="Y36" s="4">
         <f t="shared" si="8"/>
-        <v>192823</v>
+        <v>192829</v>
       </c>
       <c r="Z36" s="22">
-        <v>797811</v>
+        <v>797817</v>
       </c>
       <c r="AA36" s="5">
         <f t="shared" si="9"/>
-        <v>0.96546495487983885</v>
+        <v>0.96547221573451414</v>
       </c>
       <c r="AB36" s="9">
         <v>1500292</v>
@@ -6917,14 +6917,14 @@
       </c>
       <c r="AD36" s="4">
         <f t="shared" si="10"/>
-        <v>350445</v>
+        <v>350452</v>
       </c>
       <c r="AE36" s="8">
-        <v>1453917</v>
+        <v>1453924</v>
       </c>
       <c r="AF36" s="5">
         <f t="shared" si="11"/>
-        <v>0.96908935060641532</v>
+        <v>0.96909401636481429</v>
       </c>
       <c r="AG36" s="9">
         <v>833041</v>
@@ -6934,14 +6934,14 @@
       </c>
       <c r="AI36" s="4">
         <f t="shared" si="12"/>
-        <v>198245</v>
+        <v>198252</v>
       </c>
       <c r="AJ36" s="22">
-        <v>803841</v>
+        <v>803848</v>
       </c>
       <c r="AK36" s="5">
         <f t="shared" si="13"/>
-        <v>0.96494770365444194</v>
+        <v>0.964956106602196</v>
       </c>
       <c r="AL36" s="9">
         <v>845911</v>
@@ -6951,14 +6951,14 @@
       </c>
       <c r="AN36" s="4">
         <f t="shared" si="14"/>
-        <v>169654</v>
+        <v>169662</v>
       </c>
       <c r="AO36" s="22">
-        <v>816463</v>
+        <v>816471</v>
       </c>
       <c r="AP36" s="5">
         <f t="shared" si="15"/>
-        <v>0.96518782708819251</v>
+        <v>0.96519728434788055</v>
       </c>
       <c r="AQ36" s="15">
         <v>1519147</v>
@@ -6968,14 +6968,14 @@
       </c>
       <c r="AS36" s="4">
         <f t="shared" si="16"/>
-        <v>287931</v>
+        <v>287941</v>
       </c>
       <c r="AT36" s="8">
-        <v>1474557</v>
+        <v>1474567</v>
       </c>
       <c r="AU36" s="5">
         <f t="shared" si="17"/>
-        <v>0.97064800180627686</v>
+        <v>0.97065458444771968</v>
       </c>
       <c r="AV36" s="9">
         <v>864672</v>
@@ -6985,14 +6985,14 @@
       </c>
       <c r="AX36" s="4">
         <f t="shared" si="18"/>
-        <v>160498</v>
+        <v>160506</v>
       </c>
       <c r="AY36" s="22">
-        <v>819052</v>
+        <v>819060</v>
       </c>
       <c r="AZ36" s="5">
         <f t="shared" si="19"/>
-        <v>0.94724010954442839</v>
+        <v>0.94724936160763851</v>
       </c>
       <c r="BA36" s="9">
         <v>838532</v>
@@ -7002,14 +7002,14 @@
       </c>
       <c r="BC36" s="4">
         <f t="shared" si="20"/>
-        <v>161113</v>
+        <v>161121</v>
       </c>
       <c r="BD36" s="8">
-        <v>830655</v>
+        <v>830663</v>
       </c>
       <c r="BE36" s="5">
         <f t="shared" si="21"/>
-        <v>0.99060620226777274</v>
+        <v>0.99061574275042574</v>
       </c>
       <c r="BF36" s="9">
         <v>1502094</v>
@@ -7019,14 +7019,14 @@
       </c>
       <c r="BH36" s="4">
         <f t="shared" si="22"/>
-        <v>388495</v>
+        <v>388504</v>
       </c>
       <c r="BI36" s="8">
-        <v>1495214</v>
+        <v>1495223</v>
       </c>
       <c r="BJ36" s="5">
         <f t="shared" si="23"/>
-        <v>0.99541972739389151</v>
+        <v>0.995425719029568</v>
       </c>
     </row>
     <row r="37" spans="1:62" x14ac:dyDescent="0.3">
@@ -7044,14 +7044,14 @@
       </c>
       <c r="E37" s="4">
         <f t="shared" si="0"/>
-        <v>111288</v>
+        <v>111292</v>
       </c>
       <c r="F37" s="22">
-        <v>621136</v>
+        <v>621140</v>
       </c>
       <c r="G37" s="5">
         <f t="shared" si="24"/>
-        <v>0.95465828103842854</v>
+        <v>0.95466442885971747</v>
       </c>
       <c r="H37" s="9">
         <v>656039</v>
@@ -7061,14 +7061,14 @@
       </c>
       <c r="J37" s="4">
         <f t="shared" si="2"/>
-        <v>125865</v>
+        <v>125869</v>
       </c>
       <c r="K37" s="22">
-        <v>626359</v>
+        <v>626363</v>
       </c>
       <c r="L37" s="5">
         <f t="shared" si="3"/>
-        <v>0.9547587872062484</v>
+        <v>0.95476488440473817</v>
       </c>
       <c r="M37" s="4">
         <v>844882</v>
@@ -7078,14 +7078,14 @@
       </c>
       <c r="O37" s="4">
         <f t="shared" si="4"/>
-        <v>156051</v>
+        <v>156055</v>
       </c>
       <c r="P37" s="8">
-        <v>804129</v>
+        <v>804133</v>
       </c>
       <c r="Q37" s="5">
         <f t="shared" si="5"/>
-        <v>0.95176486183869469</v>
+        <v>0.9517695962276389</v>
       </c>
       <c r="R37" s="9">
         <v>664863</v>
@@ -7095,14 +7095,14 @@
       </c>
       <c r="T37" s="4">
         <f t="shared" si="6"/>
-        <v>120159</v>
-      </c>
-      <c r="U37" s="22">
-        <v>632157</v>
+        <v>120164</v>
+      </c>
+      <c r="U37" s="8">
+        <v>632162</v>
       </c>
       <c r="V37" s="5">
         <f t="shared" si="7"/>
-        <v>0.95080791080267668</v>
+        <v>0.9508154311489736</v>
       </c>
       <c r="W37" s="9">
         <v>670009</v>
@@ -7112,14 +7112,14 @@
       </c>
       <c r="Y37" s="4">
         <f t="shared" si="8"/>
-        <v>127254</v>
+        <v>127257</v>
       </c>
       <c r="Z37" s="22">
-        <v>638024</v>
+        <v>638027</v>
       </c>
       <c r="AA37" s="5">
         <f t="shared" si="9"/>
-        <v>0.95226183528877972</v>
+        <v>0.95226631284057384</v>
       </c>
       <c r="AB37" s="9">
         <v>858143</v>
@@ -7129,14 +7129,14 @@
       </c>
       <c r="AD37" s="4">
         <f t="shared" si="10"/>
-        <v>183055</v>
+        <v>183057</v>
       </c>
       <c r="AE37" s="8">
-        <v>818672</v>
+        <v>818674</v>
       </c>
       <c r="AF37" s="5">
         <f t="shared" si="11"/>
-        <v>0.95400416946825883</v>
+        <v>0.95400650008215415</v>
       </c>
       <c r="AG37" s="9">
         <v>675943</v>
@@ -7146,14 +7146,14 @@
       </c>
       <c r="AI37" s="4">
         <f t="shared" si="12"/>
-        <v>129771</v>
+        <v>129774</v>
       </c>
       <c r="AJ37" s="22">
-        <v>644478</v>
+        <v>644481</v>
       </c>
       <c r="AK37" s="5">
         <f t="shared" si="13"/>
-        <v>0.9534502169561635</v>
+        <v>0.95345465520021655</v>
       </c>
       <c r="AL37" s="9">
         <v>678429</v>
@@ -7163,14 +7163,14 @@
       </c>
       <c r="AN37" s="4">
         <f t="shared" si="14"/>
-        <v>111965</v>
+        <v>111968</v>
       </c>
       <c r="AO37" s="22">
-        <v>650679</v>
+        <v>650682</v>
       </c>
       <c r="AP37" s="5">
         <f t="shared" si="15"/>
-        <v>0.9590966777658384</v>
+        <v>0.9591010997466205</v>
       </c>
       <c r="AQ37" s="15">
         <v>865622</v>
@@ -7180,14 +7180,14 @@
       </c>
       <c r="AS37" s="4">
         <f t="shared" si="16"/>
-        <v>140847</v>
+        <v>140851</v>
       </c>
       <c r="AT37" s="8">
-        <v>832588</v>
+        <v>832592</v>
       </c>
       <c r="AU37" s="5">
         <f t="shared" si="17"/>
-        <v>0.96183784608062184</v>
+        <v>0.96184246703526477</v>
       </c>
       <c r="AV37" s="9">
         <v>690116</v>
@@ -7197,14 +7197,14 @@
       </c>
       <c r="AX37" s="4">
         <f t="shared" si="18"/>
-        <v>115283</v>
+        <v>115288</v>
       </c>
       <c r="AY37" s="22">
-        <v>658571</v>
+        <v>658576</v>
       </c>
       <c r="AZ37" s="5">
         <f t="shared" si="19"/>
-        <v>0.95429029322606629</v>
+        <v>0.95429753838485121</v>
       </c>
       <c r="BA37" s="9">
         <v>673244</v>
@@ -7214,14 +7214,14 @@
       </c>
       <c r="BC37" s="4">
         <f t="shared" si="20"/>
-        <v>114863</v>
+        <v>114868</v>
       </c>
       <c r="BD37" s="8">
-        <v>664882</v>
+        <v>664887</v>
       </c>
       <c r="BE37" s="5">
         <f t="shared" si="21"/>
-        <v>0.98757954025583594</v>
+        <v>0.98758696698373849</v>
       </c>
       <c r="BF37" s="9">
         <v>856336</v>
@@ -7231,14 +7231,14 @@
       </c>
       <c r="BH37" s="4">
         <f t="shared" si="22"/>
-        <v>202724</v>
+        <v>202730</v>
       </c>
       <c r="BI37" s="8">
-        <v>846539</v>
+        <v>846545</v>
       </c>
       <c r="BJ37" s="5">
         <f t="shared" si="23"/>
-        <v>0.98855939724594089</v>
+        <v>0.98856640384148275</v>
       </c>
     </row>
     <row r="38" spans="1:62" x14ac:dyDescent="0.3">
@@ -7309,7 +7309,7 @@
         <f t="shared" si="6"/>
         <v>5838</v>
       </c>
-      <c r="U38" s="22">
+      <c r="U38" s="8">
         <v>21460</v>
       </c>
       <c r="V38" s="5">
@@ -7521,7 +7521,7 @@
         <f t="shared" si="6"/>
         <v>55</v>
       </c>
-      <c r="U39" s="22">
+      <c r="U39" s="8">
         <v>175</v>
       </c>
       <c r="V39" s="5">
@@ -7680,14 +7680,14 @@
       </c>
       <c r="E40" s="4">
         <f t="shared" si="0"/>
-        <v>50304</v>
+        <v>50307</v>
       </c>
       <c r="F40" s="22">
-        <v>260472</v>
+        <v>260475</v>
       </c>
       <c r="G40" s="5">
         <f t="shared" si="24"/>
-        <v>0.95243876129428584</v>
+        <v>0.9524497310579606</v>
       </c>
       <c r="H40" s="9">
         <v>275367</v>
@@ -7697,14 +7697,14 @@
       </c>
       <c r="J40" s="4">
         <f t="shared" si="2"/>
-        <v>57014</v>
+        <v>57017</v>
       </c>
       <c r="K40" s="22">
-        <v>262126</v>
+        <v>262129</v>
       </c>
       <c r="L40" s="5">
         <f t="shared" si="3"/>
-        <v>0.95191508060152452</v>
+        <v>0.95192597515315924</v>
       </c>
       <c r="M40" s="4">
         <v>339208</v>
@@ -7714,14 +7714,14 @@
       </c>
       <c r="O40" s="4">
         <f t="shared" si="4"/>
-        <v>69723</v>
+        <v>69729</v>
       </c>
       <c r="P40" s="8">
-        <v>323323</v>
+        <v>323329</v>
       </c>
       <c r="Q40" s="5">
         <f t="shared" si="5"/>
-        <v>0.95317032617155251</v>
+        <v>0.95318801443362189</v>
       </c>
       <c r="R40" s="9">
         <v>277547</v>
@@ -7731,14 +7731,14 @@
       </c>
       <c r="T40" s="4">
         <f t="shared" si="6"/>
-        <v>54033</v>
-      </c>
-      <c r="U40" s="22">
-        <v>264295</v>
+        <v>54041</v>
+      </c>
+      <c r="U40" s="8">
+        <v>264303</v>
       </c>
       <c r="V40" s="5">
         <f t="shared" si="7"/>
-        <v>0.95225313190198413</v>
+        <v>0.95228195584891928</v>
       </c>
       <c r="W40" s="9">
         <v>278758</v>
@@ -7748,14 +7748,14 @@
       </c>
       <c r="Y40" s="4">
         <f t="shared" si="8"/>
-        <v>62696</v>
+        <v>62703</v>
       </c>
       <c r="Z40" s="22">
-        <v>266741</v>
+        <v>266748</v>
       </c>
       <c r="AA40" s="5">
         <f t="shared" si="9"/>
-        <v>0.95689092330982428</v>
+        <v>0.95691603469676212</v>
       </c>
       <c r="AB40" s="9">
         <v>343140</v>
@@ -7765,14 +7765,14 @@
       </c>
       <c r="AD40" s="4">
         <f t="shared" si="10"/>
-        <v>81800</v>
+        <v>81810</v>
       </c>
       <c r="AE40" s="8">
-        <v>328057</v>
+        <v>328067</v>
       </c>
       <c r="AF40" s="5">
         <f t="shared" si="11"/>
-        <v>0.95604418021798687</v>
+        <v>0.95607332284198865</v>
       </c>
       <c r="AG40" s="9">
         <v>282101</v>
@@ -7782,14 +7782,14 @@
       </c>
       <c r="AI40" s="4">
         <f t="shared" si="12"/>
-        <v>62419</v>
+        <v>62428</v>
       </c>
       <c r="AJ40" s="22">
-        <v>268617</v>
+        <v>268626</v>
       </c>
       <c r="AK40" s="5">
         <f t="shared" si="13"/>
-        <v>0.95220151647814077</v>
+        <v>0.95223341994533872</v>
       </c>
       <c r="AL40" s="9">
         <v>282756</v>
@@ -7799,14 +7799,14 @@
       </c>
       <c r="AN40" s="4">
         <f t="shared" si="14"/>
-        <v>55727</v>
+        <v>55738</v>
       </c>
       <c r="AO40" s="22">
-        <v>270842</v>
+        <v>270853</v>
       </c>
       <c r="AP40" s="5">
         <f t="shared" si="15"/>
-        <v>0.95786473142921813</v>
+        <v>0.95790363422880509</v>
       </c>
       <c r="AQ40" s="15">
         <v>343988</v>
@@ -7816,14 +7816,14 @@
       </c>
       <c r="AS40" s="4">
         <f t="shared" si="16"/>
-        <v>66685</v>
+        <v>66697</v>
       </c>
       <c r="AT40" s="8">
-        <v>332166</v>
+        <v>332178</v>
       </c>
       <c r="AU40" s="5">
         <f t="shared" si="17"/>
-        <v>0.96563252206472316</v>
+        <v>0.96566740700256981</v>
       </c>
       <c r="AV40" s="9">
         <v>285285</v>
@@ -7833,14 +7833,14 @@
       </c>
       <c r="AX40" s="4">
         <f t="shared" si="18"/>
-        <v>56513</v>
+        <v>56525</v>
       </c>
       <c r="AY40" s="22">
-        <v>273365</v>
+        <v>273377</v>
       </c>
       <c r="AZ40" s="5">
         <f t="shared" si="19"/>
-        <v>0.95821722137511611</v>
+        <v>0.95825928457507403</v>
       </c>
       <c r="BA40" s="9">
         <v>276279</v>
@@ -7850,14 +7850,14 @@
       </c>
       <c r="BC40" s="4">
         <f t="shared" si="20"/>
-        <v>55338</v>
+        <v>55347</v>
       </c>
       <c r="BD40" s="8">
-        <v>275291</v>
+        <v>275300</v>
       </c>
       <c r="BE40" s="5">
         <f t="shared" si="21"/>
-        <v>0.99642390482085141</v>
+        <v>0.99645648058665337</v>
       </c>
       <c r="BF40" s="9">
         <v>339189</v>
@@ -7867,14 +7867,14 @@
       </c>
       <c r="BH40" s="4">
         <f t="shared" si="22"/>
-        <v>95133</v>
+        <v>95141</v>
       </c>
       <c r="BI40" s="8">
-        <v>336907</v>
+        <v>336915</v>
       </c>
       <c r="BJ40" s="5">
         <f t="shared" si="23"/>
-        <v>0.99327218748249502</v>
+        <v>0.99329577315302087</v>
       </c>
     </row>
     <row r="41" spans="1:62" x14ac:dyDescent="0.3">
@@ -7892,14 +7892,14 @@
       </c>
       <c r="E41" s="4">
         <f t="shared" si="0"/>
-        <v>119516</v>
+        <v>119530</v>
       </c>
       <c r="F41" s="22">
-        <v>840964</v>
+        <v>840978</v>
       </c>
       <c r="G41" s="5">
         <f t="shared" si="24"/>
-        <v>0.96364573903677131</v>
+        <v>0.96366178138858016</v>
       </c>
       <c r="H41" s="9">
         <v>878008</v>
@@ -7909,14 +7909,14 @@
       </c>
       <c r="J41" s="4">
         <f t="shared" si="2"/>
-        <v>149505</v>
+        <v>149518</v>
       </c>
       <c r="K41" s="22">
-        <v>848029</v>
+        <v>848042</v>
       </c>
       <c r="L41" s="5">
         <f t="shared" si="3"/>
-        <v>0.96585566418529212</v>
+        <v>0.96587047042851548</v>
       </c>
       <c r="M41" s="4">
         <v>999035</v>
@@ -7926,14 +7926,14 @@
       </c>
       <c r="O41" s="4">
         <f t="shared" si="4"/>
-        <v>161294</v>
+        <v>161308</v>
       </c>
       <c r="P41" s="8">
-        <v>960781</v>
+        <v>960795</v>
       </c>
       <c r="Q41" s="5">
         <f t="shared" si="5"/>
-        <v>0.96170904923250933</v>
+        <v>0.96172306275555908</v>
       </c>
       <c r="R41" s="9">
         <v>889467</v>
@@ -7943,14 +7943,14 @@
       </c>
       <c r="T41" s="4">
         <f t="shared" si="6"/>
-        <v>146322</v>
-      </c>
-      <c r="U41" s="22">
-        <v>857016</v>
+        <v>146336</v>
+      </c>
+      <c r="U41" s="8">
+        <v>857030</v>
       </c>
       <c r="V41" s="5">
         <f t="shared" si="7"/>
-        <v>0.96351635305188388</v>
+        <v>0.96353209281513541</v>
       </c>
       <c r="W41" s="9">
         <v>894020</v>
@@ -7960,14 +7960,14 @@
       </c>
       <c r="Y41" s="4">
         <f t="shared" si="8"/>
-        <v>153046</v>
+        <v>153057</v>
       </c>
       <c r="Z41" s="22">
-        <v>862422</v>
+        <v>862433</v>
       </c>
       <c r="AA41" s="5">
         <f t="shared" si="9"/>
-        <v>0.9646562716717747</v>
+        <v>0.9646685756470772</v>
       </c>
       <c r="AB41" s="9">
         <v>1012178</v>
@@ -7977,14 +7977,14 @@
       </c>
       <c r="AD41" s="4">
         <f t="shared" si="10"/>
-        <v>189499</v>
+        <v>189517</v>
       </c>
       <c r="AE41" s="8">
-        <v>976703</v>
+        <v>976721</v>
       </c>
       <c r="AF41" s="5">
         <f t="shared" si="11"/>
-        <v>0.96495181677531028</v>
+        <v>0.96496960020865896</v>
       </c>
       <c r="AG41" s="9">
         <v>904846</v>
@@ -7994,14 +7994,14 @@
       </c>
       <c r="AI41" s="4">
         <f t="shared" si="12"/>
-        <v>152721</v>
+        <v>152734</v>
       </c>
       <c r="AJ41" s="22">
-        <v>872476</v>
+        <v>872489</v>
       </c>
       <c r="AK41" s="5">
         <f t="shared" si="13"/>
-        <v>0.96422595668213151</v>
+        <v>0.96424032376780133</v>
       </c>
       <c r="AL41" s="9">
         <v>910192</v>
@@ -8011,14 +8011,14 @@
       </c>
       <c r="AN41" s="4">
         <f t="shared" si="14"/>
-        <v>133982</v>
+        <v>133995</v>
       </c>
       <c r="AO41" s="22">
-        <v>878388</v>
+        <v>878401</v>
       </c>
       <c r="AP41" s="5">
         <f t="shared" si="15"/>
-        <v>0.96505792184506123</v>
+        <v>0.96507220454585407</v>
       </c>
       <c r="AQ41" s="15">
         <v>1025826</v>
@@ -8028,14 +8028,14 @@
       </c>
       <c r="AS41" s="4">
         <f t="shared" si="16"/>
-        <v>163951</v>
+        <v>163966</v>
       </c>
       <c r="AT41" s="8">
-        <v>991915</v>
+        <v>991930</v>
       </c>
       <c r="AU41" s="5">
         <f t="shared" si="17"/>
-        <v>0.96694273687740417</v>
+        <v>0.96695735924026105</v>
       </c>
       <c r="AV41" s="9">
         <v>923071</v>
@@ -8045,14 +8045,14 @@
       </c>
       <c r="AX41" s="4">
         <f t="shared" si="18"/>
-        <v>137843</v>
+        <v>137857</v>
       </c>
       <c r="AY41" s="22">
-        <v>890382</v>
+        <v>890396</v>
       </c>
       <c r="AZ41" s="5">
         <f t="shared" si="19"/>
-        <v>0.96458668943125714</v>
+        <v>0.96460185619524397</v>
       </c>
       <c r="BA41" s="9">
         <v>907892</v>
@@ -8062,14 +8062,14 @@
       </c>
       <c r="BC41" s="4">
         <f t="shared" si="20"/>
-        <v>135531</v>
+        <v>135544</v>
       </c>
       <c r="BD41" s="8">
-        <v>897218</v>
+        <v>897231</v>
       </c>
       <c r="BE41" s="5">
         <f t="shared" si="21"/>
-        <v>0.98824309499367768</v>
+        <v>0.9882574138774215</v>
       </c>
       <c r="BF41" s="9">
         <v>1023930</v>
@@ -8079,14 +8079,14 @@
       </c>
       <c r="BH41" s="4">
         <f t="shared" si="22"/>
-        <v>214791</v>
+        <v>214806</v>
       </c>
       <c r="BI41" s="8">
-        <v>1010506</v>
+        <v>1010521</v>
       </c>
       <c r="BJ41" s="5">
         <f t="shared" si="23"/>
-        <v>0.98688972879005399</v>
+        <v>0.98690437822898047</v>
       </c>
     </row>
     <row r="42" spans="1:62" x14ac:dyDescent="0.3">
@@ -8157,7 +8157,7 @@
         <f t="shared" si="6"/>
         <v>3776</v>
       </c>
-      <c r="U42" s="22">
+      <c r="U42" s="8">
         <v>17517</v>
       </c>
       <c r="V42" s="5">
@@ -8189,14 +8189,14 @@
       </c>
       <c r="AD42" s="4">
         <f t="shared" si="10"/>
-        <v>4970</v>
+        <v>4971</v>
       </c>
       <c r="AE42" s="8">
-        <v>19817</v>
+        <v>19818</v>
       </c>
       <c r="AF42" s="5">
         <f t="shared" si="11"/>
-        <v>0.95678833526458096</v>
+        <v>0.95683661645422946</v>
       </c>
       <c r="AG42" s="9">
         <v>18585</v>
@@ -8206,14 +8206,14 @@
       </c>
       <c r="AI42" s="4">
         <f t="shared" si="12"/>
-        <v>3798</v>
+        <v>3799</v>
       </c>
       <c r="AJ42" s="22">
-        <v>17750</v>
+        <v>17751</v>
       </c>
       <c r="AK42" s="5">
         <f t="shared" si="13"/>
-        <v>0.95507129405434488</v>
+        <v>0.95512510088781277</v>
       </c>
       <c r="AL42" s="9">
         <v>18498</v>
@@ -8223,14 +8223,14 @@
       </c>
       <c r="AN42" s="4">
         <f t="shared" si="14"/>
-        <v>3452</v>
+        <v>3453</v>
       </c>
       <c r="AO42" s="22">
-        <v>17808</v>
+        <v>17809</v>
       </c>
       <c r="AP42" s="5">
         <f t="shared" si="15"/>
-        <v>0.96269867012650012</v>
+        <v>0.9627527300248675</v>
       </c>
       <c r="AQ42" s="15">
         <v>20775</v>
@@ -8240,14 +8240,14 @@
       </c>
       <c r="AS42" s="4">
         <f t="shared" si="16"/>
-        <v>4079</v>
+        <v>4080</v>
       </c>
       <c r="AT42" s="8">
-        <v>20024</v>
+        <v>20025</v>
       </c>
       <c r="AU42" s="5">
         <f t="shared" si="17"/>
-        <v>0.96385078219013232</v>
+        <v>0.96389891696750907</v>
       </c>
       <c r="AV42" s="9">
         <v>18672</v>
@@ -8257,14 +8257,14 @@
       </c>
       <c r="AX42" s="4">
         <f t="shared" si="18"/>
-        <v>3584</v>
+        <v>3585</v>
       </c>
       <c r="AY42" s="22">
-        <v>17980</v>
+        <v>17981</v>
       </c>
       <c r="AZ42" s="5">
         <f t="shared" si="19"/>
-        <v>0.96293916023993142</v>
+        <v>0.96299271636675232</v>
       </c>
       <c r="BA42" s="9">
         <v>18422</v>
@@ -8274,14 +8274,14 @@
       </c>
       <c r="BC42" s="4">
         <f t="shared" si="20"/>
-        <v>3452</v>
+        <v>3453</v>
       </c>
       <c r="BD42" s="8">
-        <v>18094</v>
+        <v>18095</v>
       </c>
       <c r="BE42" s="5">
         <f t="shared" si="21"/>
-        <v>0.98219520138964278</v>
+        <v>0.98224948431223535</v>
       </c>
       <c r="BF42" s="9">
         <v>20562</v>
@@ -8291,14 +8291,14 @@
       </c>
       <c r="BH42" s="4">
         <f t="shared" si="22"/>
-        <v>5003</v>
+        <v>5004</v>
       </c>
       <c r="BI42" s="8">
-        <v>20391</v>
+        <v>20392</v>
       </c>
       <c r="BJ42" s="5">
         <f t="shared" si="23"/>
-        <v>0.9916836883571637</v>
+        <v>0.99173232175858383</v>
       </c>
     </row>
     <row r="43" spans="1:62" x14ac:dyDescent="0.3">
@@ -8369,7 +8369,7 @@
         <f t="shared" si="6"/>
         <v>1108</v>
       </c>
-      <c r="U43" s="22">
+      <c r="U43" s="8">
         <v>3283</v>
       </c>
       <c r="V43" s="5">
@@ -8528,14 +8528,14 @@
       </c>
       <c r="E44" s="4">
         <f t="shared" si="0"/>
-        <v>67403</v>
+        <v>67405</v>
       </c>
       <c r="F44" s="22">
-        <v>304561</v>
+        <v>304563</v>
       </c>
       <c r="G44" s="5">
         <f t="shared" si="24"/>
-        <v>0.89538052665465229</v>
+        <v>0.89538640646543999</v>
       </c>
       <c r="H44" s="9">
         <v>343940</v>
@@ -8545,14 +8545,14 @@
       </c>
       <c r="J44" s="4">
         <f t="shared" si="2"/>
-        <v>78207</v>
+        <v>78209</v>
       </c>
       <c r="K44" s="22">
-        <v>307773</v>
+        <v>307775</v>
       </c>
       <c r="L44" s="5">
         <f t="shared" si="3"/>
-        <v>0.89484503111007729</v>
+        <v>0.8948508460778043</v>
       </c>
       <c r="M44" s="4">
         <v>415294</v>
@@ -8562,14 +8562,14 @@
       </c>
       <c r="O44" s="4">
         <f t="shared" si="4"/>
-        <v>88837</v>
+        <v>88839</v>
       </c>
       <c r="P44" s="8">
-        <v>373544</v>
+        <v>373546</v>
       </c>
       <c r="Q44" s="5">
         <f t="shared" si="5"/>
-        <v>0.89946881004782153</v>
+        <v>0.89947362591320845</v>
       </c>
       <c r="R44" s="9">
         <v>349377</v>
@@ -8579,14 +8579,14 @@
       </c>
       <c r="T44" s="4">
         <f t="shared" si="6"/>
-        <v>76586</v>
-      </c>
-      <c r="U44" s="22">
-        <v>311987</v>
+        <v>76588</v>
+      </c>
+      <c r="U44" s="8">
+        <v>311989</v>
       </c>
       <c r="V44" s="5">
         <f t="shared" si="7"/>
-        <v>0.89298093463507899</v>
+        <v>0.89298665911035935</v>
       </c>
       <c r="W44" s="9">
         <v>352323</v>
@@ -8596,14 +8596,14 @@
       </c>
       <c r="Y44" s="4">
         <f t="shared" si="8"/>
-        <v>77411</v>
+        <v>77413</v>
       </c>
       <c r="Z44" s="22">
-        <v>315072</v>
+        <v>315074</v>
       </c>
       <c r="AA44" s="5">
         <f t="shared" si="9"/>
-        <v>0.89427031445576932</v>
+        <v>0.8942759910650171</v>
       </c>
       <c r="AB44" s="9">
         <v>424236</v>
@@ -8613,14 +8613,14 @@
       </c>
       <c r="AD44" s="4">
         <f t="shared" si="10"/>
-        <v>99655</v>
+        <v>99658</v>
       </c>
       <c r="AE44" s="8">
-        <v>382537</v>
+        <v>382540</v>
       </c>
       <c r="AF44" s="5">
         <f t="shared" si="11"/>
-        <v>0.90170801157846103</v>
+        <v>0.90171508311411575</v>
       </c>
       <c r="AG44" s="9">
         <v>358309</v>
@@ -8630,14 +8630,14 @@
       </c>
       <c r="AI44" s="4">
         <f t="shared" si="12"/>
-        <v>80226</v>
+        <v>80230</v>
       </c>
       <c r="AJ44" s="22">
-        <v>319566</v>
+        <v>319570</v>
       </c>
       <c r="AK44" s="5">
         <f t="shared" si="13"/>
-        <v>0.89187265739906063</v>
+        <v>0.89188382094784113</v>
       </c>
       <c r="AL44" s="9">
         <v>359722</v>
@@ -8647,14 +8647,14 @@
       </c>
       <c r="AN44" s="4">
         <f t="shared" si="14"/>
-        <v>71145</v>
+        <v>71149</v>
       </c>
       <c r="AO44" s="22">
-        <v>323327</v>
+        <v>323331</v>
       </c>
       <c r="AP44" s="5">
         <f t="shared" si="15"/>
-        <v>0.89882464792256245</v>
+        <v>0.8988357676205514</v>
       </c>
       <c r="AQ44" s="15">
         <v>432157</v>
@@ -8664,14 +8664,14 @@
       </c>
       <c r="AS44" s="4">
         <f t="shared" si="16"/>
-        <v>82578</v>
+        <v>82582</v>
       </c>
       <c r="AT44" s="8">
-        <v>390810</v>
+        <v>390814</v>
       </c>
       <c r="AU44" s="5">
         <f t="shared" si="17"/>
-        <v>0.90432412294605891</v>
+        <v>0.9043333788414859</v>
       </c>
       <c r="AV44" s="9">
         <v>367733</v>
@@ -8681,14 +8681,14 @@
       </c>
       <c r="AX44" s="4">
         <f t="shared" si="18"/>
-        <v>71249</v>
+        <v>71253</v>
       </c>
       <c r="AY44" s="22">
-        <v>327462</v>
+        <v>327466</v>
       </c>
       <c r="AZ44" s="5">
         <f t="shared" si="19"/>
-        <v>0.89048847941305243</v>
+        <v>0.89049935687033799</v>
       </c>
       <c r="BA44" s="9">
         <v>337773</v>
@@ -8698,14 +8698,14 @@
       </c>
       <c r="BC44" s="4">
         <f t="shared" si="20"/>
-        <v>71561</v>
+        <v>71566</v>
       </c>
       <c r="BD44" s="8">
-        <v>331163</v>
+        <v>331168</v>
       </c>
       <c r="BE44" s="5">
         <f t="shared" si="21"/>
-        <v>0.98043064424924431</v>
+        <v>0.98044544709020554</v>
       </c>
       <c r="BF44" s="9">
         <v>408499</v>
@@ -8715,14 +8715,14 @@
       </c>
       <c r="BH44" s="4">
         <f t="shared" si="22"/>
-        <v>111941</v>
+        <v>111946</v>
       </c>
       <c r="BI44" s="8">
-        <v>399291</v>
+        <v>399296</v>
       </c>
       <c r="BJ44" s="5">
         <f t="shared" si="23"/>
-        <v>0.97745894114795873</v>
+        <v>0.97747118108000264</v>
       </c>
     </row>
     <row r="45" spans="1:62" x14ac:dyDescent="0.3">
@@ -8740,14 +8740,14 @@
       </c>
       <c r="E45" s="4">
         <f t="shared" si="0"/>
-        <v>45806</v>
+        <v>45809</v>
       </c>
       <c r="F45" s="22">
-        <v>235576</v>
+        <v>235579</v>
       </c>
       <c r="G45" s="5">
         <f t="shared" si="24"/>
-        <v>0.94165614057528424</v>
+        <v>0.94166813232496038</v>
       </c>
       <c r="H45" s="9">
         <v>249985</v>
@@ -8757,14 +8757,14 @@
       </c>
       <c r="J45" s="4">
         <f t="shared" si="2"/>
-        <v>49311</v>
+        <v>49313</v>
       </c>
       <c r="K45" s="22">
-        <v>237257</v>
+        <v>237259</v>
       </c>
       <c r="L45" s="5">
         <f t="shared" si="3"/>
-        <v>0.94908494509670582</v>
+        <v>0.94909294557673463</v>
       </c>
       <c r="M45" s="4">
         <v>300587</v>
@@ -8774,14 +8774,14 @@
       </c>
       <c r="O45" s="4">
         <f t="shared" si="4"/>
-        <v>59178</v>
+        <v>59180</v>
       </c>
       <c r="P45" s="8">
-        <v>288724</v>
+        <v>288726</v>
       </c>
       <c r="Q45" s="5">
         <f t="shared" si="5"/>
-        <v>0.96053388869112766</v>
+        <v>0.96054054233882369</v>
       </c>
       <c r="R45" s="9">
         <v>247712</v>
@@ -8791,14 +8791,14 @@
       </c>
       <c r="T45" s="4">
         <f t="shared" si="6"/>
-        <v>49702</v>
-      </c>
-      <c r="U45" s="22">
-        <v>238336</v>
+        <v>49704</v>
+      </c>
+      <c r="U45" s="8">
+        <v>238338</v>
       </c>
       <c r="V45" s="5">
         <f t="shared" si="7"/>
-        <v>0.96214959307583003</v>
+        <v>0.96215766696809202</v>
       </c>
       <c r="W45" s="9">
         <v>250023</v>
@@ -8808,14 +8808,14 @@
       </c>
       <c r="Y45" s="4">
         <f t="shared" si="8"/>
-        <v>53056</v>
+        <v>53058</v>
       </c>
       <c r="Z45" s="22">
-        <v>240168</v>
+        <v>240170</v>
       </c>
       <c r="AA45" s="5">
         <f t="shared" si="9"/>
-        <v>0.96058362630637983</v>
+        <v>0.96059162557044753</v>
       </c>
       <c r="AB45" s="9">
         <v>306096</v>
@@ -8825,14 +8825,14 @@
       </c>
       <c r="AD45" s="4">
         <f t="shared" si="10"/>
-        <v>69241</v>
+        <v>69243</v>
       </c>
       <c r="AE45" s="8">
-        <v>293555</v>
+        <v>293557</v>
       </c>
       <c r="AF45" s="5">
         <f t="shared" si="11"/>
-        <v>0.95902919345564785</v>
+        <v>0.95903572735351006</v>
       </c>
       <c r="AG45" s="9">
         <v>252706</v>
@@ -8842,14 +8842,14 @@
       </c>
       <c r="AI45" s="4">
         <f t="shared" si="12"/>
-        <v>51719</v>
+        <v>51721</v>
       </c>
       <c r="AJ45" s="22">
-        <v>243557</v>
+        <v>243559</v>
       </c>
       <c r="AK45" s="5">
         <f t="shared" si="13"/>
-        <v>0.96379587346560824</v>
+        <v>0.96380378780084364</v>
       </c>
       <c r="AL45" s="9">
         <v>254538</v>
@@ -8859,14 +8859,14 @@
       </c>
       <c r="AN45" s="4">
         <f t="shared" si="14"/>
-        <v>44677</v>
+        <v>44679</v>
       </c>
       <c r="AO45" s="22">
-        <v>245890</v>
+        <v>245892</v>
       </c>
       <c r="AP45" s="5">
         <f t="shared" si="15"/>
-        <v>0.96602471929535083</v>
+        <v>0.96603257666831677</v>
       </c>
       <c r="AQ45" s="15">
         <v>310997</v>
@@ -8876,14 +8876,14 @@
       </c>
       <c r="AS45" s="4">
         <f t="shared" si="16"/>
-        <v>57336</v>
+        <v>57338</v>
       </c>
       <c r="AT45" s="8">
-        <v>299348</v>
+        <v>299350</v>
       </c>
       <c r="AU45" s="5">
         <f t="shared" si="17"/>
-        <v>0.96254304703903892</v>
+        <v>0.96254947796924084</v>
       </c>
       <c r="AV45" s="9">
         <v>259359</v>
@@ -8893,14 +8893,14 @@
       </c>
       <c r="AX45" s="4">
         <f t="shared" si="18"/>
-        <v>47791</v>
+        <v>47793</v>
       </c>
       <c r="AY45" s="22">
-        <v>248471</v>
+        <v>248473</v>
       </c>
       <c r="AZ45" s="5">
         <f t="shared" si="19"/>
-        <v>0.95801957903909252</v>
+        <v>0.95802729035815226</v>
       </c>
       <c r="BA45" s="9">
         <v>254394</v>
@@ -9005,7 +9005,7 @@
         <f t="shared" si="6"/>
         <v>803</v>
       </c>
-      <c r="U46" s="22">
+      <c r="U46" s="8">
         <v>2407</v>
       </c>
       <c r="V46" s="5">
@@ -9217,7 +9217,7 @@
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="U47" s="22">
+      <c r="U47" s="8">
         <v>64</v>
       </c>
       <c r="V47" s="5">
@@ -9362,10 +9362,10 @@
       </c>
     </row>
     <row r="48" spans="1:62" x14ac:dyDescent="0.3">
-      <c r="A48" s="30" t="s">
+      <c r="A48" s="36" t="s">
         <v>44</v>
       </c>
-      <c r="B48" s="30"/>
+      <c r="B48" s="36"/>
       <c r="C48" s="11">
         <f>SUM(C10:C47)</f>
         <v>7396603</v>
@@ -9376,15 +9376,15 @@
       </c>
       <c r="E48" s="13">
         <f t="shared" ref="E48" si="25">F48-D48</f>
-        <v>1278016</v>
+        <v>1278073</v>
       </c>
       <c r="F48" s="12">
         <f>SUM(F10:F47)</f>
-        <v>7088278</v>
+        <v>7088335</v>
       </c>
       <c r="G48" s="14">
         <f t="shared" ref="G48" si="26">F48/C48</f>
-        <v>0.95831532393992214</v>
+        <v>0.9583230301802057</v>
       </c>
       <c r="H48" s="11">
         <f>SUM(H10:H47)</f>
@@ -9396,15 +9396,15 @@
       </c>
       <c r="J48" s="13">
         <f t="shared" ref="J48" si="27">K48-I48</f>
-        <v>1509254</v>
+        <v>1509312</v>
       </c>
       <c r="K48" s="12">
         <f>SUM(K10:K47)</f>
-        <v>7194387</v>
+        <v>7194445</v>
       </c>
       <c r="L48" s="14">
         <f t="shared" ref="L48" si="28">K48/H48</f>
-        <v>0.95981725230068926</v>
+        <v>0.95982499019422107</v>
       </c>
       <c r="M48" s="11">
         <f>SUM(M10:M47)</f>
@@ -9416,15 +9416,15 @@
       </c>
       <c r="O48" s="13">
         <f t="shared" si="4"/>
-        <v>2205329</v>
+        <v>2205408</v>
       </c>
       <c r="P48" s="12">
         <f>SUM(P10:P47)</f>
-        <v>11346666</v>
+        <v>11346745</v>
       </c>
       <c r="Q48" s="14">
         <f t="shared" si="5"/>
-        <v>0.95823575387808924</v>
+        <v>0.9582424254963916</v>
       </c>
       <c r="R48" s="11">
         <f>SUM(R10:R47)</f>
@@ -9436,15 +9436,15 @@
       </c>
       <c r="T48" s="13">
         <f t="shared" si="6"/>
-        <v>1415938</v>
+        <v>1416009</v>
       </c>
       <c r="U48" s="12">
         <f>SUM(U10:U47)</f>
-        <v>7214323</v>
+        <v>7214394</v>
       </c>
       <c r="V48" s="14">
         <f t="shared" si="7"/>
-        <v>0.95637284462845173</v>
+        <v>0.95638225680364386</v>
       </c>
       <c r="W48" s="11">
         <f>SUM(W10:W47)</f>
@@ -9456,15 +9456,15 @@
       </c>
       <c r="Y48" s="13">
         <f t="shared" ref="Y48" si="29">Z48-X48</f>
-        <v>1498786</v>
+        <v>1498849</v>
       </c>
       <c r="Z48" s="12">
         <f>SUM(Z10:Z47)</f>
-        <v>7308803</v>
+        <v>7308866</v>
       </c>
       <c r="AA48" s="14">
         <f t="shared" ref="AA48" si="30">Z48/W48</f>
-        <v>0.95776834092597163</v>
+        <v>0.95777659664246562</v>
       </c>
       <c r="AB48" s="11">
         <f>SUM(AB10:AB47)</f>
@@ -9476,15 +9476,15 @@
       </c>
       <c r="AD48" s="13">
         <f t="shared" si="10"/>
-        <v>2513014</v>
+        <v>2513110</v>
       </c>
       <c r="AE48" s="12">
         <f>SUM(AE10:AE47)</f>
-        <v>11559650</v>
+        <v>11559746</v>
       </c>
       <c r="AF48" s="14">
         <f t="shared" si="11"/>
-        <v>0.96007017029801778</v>
+        <v>0.96007814344048736</v>
       </c>
       <c r="AG48" s="11">
         <f>SUM(AG10:AG47)</f>
@@ -9496,15 +9496,15 @@
       </c>
       <c r="AI48" s="13">
         <f t="shared" si="12"/>
-        <v>1514745</v>
+        <v>1514820</v>
       </c>
       <c r="AJ48" s="12">
         <f>SUM(AJ10:AJ47)</f>
-        <v>7365037</v>
+        <v>7365112</v>
       </c>
       <c r="AK48" s="14">
         <f t="shared" si="13"/>
-        <v>0.95568337441085949</v>
+        <v>0.9556931063718912</v>
       </c>
       <c r="AL48" s="11">
         <f>SUM(AL10:AL47)</f>
@@ -9516,15 +9516,15 @@
       </c>
       <c r="AN48" s="13">
         <f t="shared" si="14"/>
-        <v>1322578</v>
+        <v>1322656</v>
       </c>
       <c r="AO48" s="12">
         <f>SUM(AO10:AO47)</f>
-        <v>7467791</v>
+        <v>7467869</v>
       </c>
       <c r="AP48" s="14">
         <f t="shared" si="15"/>
-        <v>0.9575037481268982</v>
+        <v>0.95751374911545739</v>
       </c>
       <c r="AQ48" s="11">
         <f>SUM(AQ10:AQ47)</f>
@@ -9536,15 +9536,15 @@
       </c>
       <c r="AS48" s="13">
         <f t="shared" si="16"/>
-        <v>1994598</v>
+        <v>1994706</v>
       </c>
       <c r="AT48" s="12">
         <f>SUM(AT10:AT47)</f>
-        <v>11757267</v>
+        <v>11757375</v>
       </c>
       <c r="AU48" s="14">
         <f t="shared" si="17"/>
-        <v>0.96132671357276311</v>
+        <v>0.96133554413560274</v>
       </c>
       <c r="AV48" s="11">
         <f>SUM(AV10:AV47)</f>
@@ -9556,15 +9556,15 @@
       </c>
       <c r="AX48" s="13">
         <f t="shared" si="18"/>
-        <v>1323047</v>
+        <v>1323133</v>
       </c>
       <c r="AY48" s="12">
         <f>SUM(AY10:AY47)</f>
-        <v>7529731</v>
+        <v>7529817</v>
       </c>
       <c r="AZ48" s="14">
         <f t="shared" si="19"/>
-        <v>0.94282046617063109</v>
+        <v>0.94283123449158313</v>
       </c>
       <c r="BA48" s="11">
         <f>SUM(BA10:BA47)</f>
@@ -9576,15 +9576,15 @@
       </c>
       <c r="BC48" s="13">
         <f t="shared" si="20"/>
-        <v>1344704</v>
+        <v>1344785</v>
       </c>
       <c r="BD48" s="12">
         <f>SUM(BD10:BD47)</f>
-        <v>7633184</v>
+        <v>7633265</v>
       </c>
       <c r="BE48" s="14">
         <f t="shared" si="21"/>
-        <v>0.98856847131860692</v>
+        <v>0.98857896157354863</v>
       </c>
       <c r="BF48" s="11">
         <f>SUM(BF10:BF47)</f>
@@ -9596,18 +9596,18 @@
       </c>
       <c r="BH48" s="13">
         <f t="shared" si="22"/>
-        <v>2842003</v>
+        <v>2842114</v>
       </c>
       <c r="BI48" s="12">
         <f>SUM(BI10:BI47)</f>
-        <v>11979891</v>
+        <v>11980002</v>
       </c>
       <c r="BJ48" s="14">
         <f t="shared" si="23"/>
-        <v>0.99274724416906923</v>
+        <v>0.9927564424951727</v>
       </c>
     </row>
-    <row r="49" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
@@ -9670,9 +9670,8 @@
       <c r="BH49" s="1"/>
       <c r="BI49" s="1"/>
       <c r="BJ49" s="1"/>
-      <c r="BK49" s="1"/>
     </row>
-    <row r="50" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
@@ -9735,9 +9734,8 @@
       <c r="BH50" s="1"/>
       <c r="BI50" s="1"/>
       <c r="BJ50" s="1"/>
-      <c r="BK50" s="1"/>
     </row>
-    <row r="51" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
@@ -9801,7 +9799,7 @@
       <c r="BI51" s="1"/>
       <c r="BJ51" s="1"/>
     </row>
-    <row r="52" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
@@ -9865,7 +9863,7 @@
       <c r="BI52" s="1"/>
       <c r="BJ52" s="1"/>
     </row>
-    <row r="53" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
@@ -9929,71 +9927,7 @@
       <c r="BI53" s="1"/>
       <c r="BJ53" s="1"/>
     </row>
-    <row r="54" spans="1:63" x14ac:dyDescent="0.3">
-      <c r="A54" s="1"/>
-      <c r="B54" s="1"/>
-      <c r="C54" s="1"/>
-      <c r="D54" s="1"/>
-      <c r="E54" s="1"/>
-      <c r="F54" s="1"/>
-      <c r="G54" s="1"/>
-      <c r="H54" s="1"/>
-      <c r="I54" s="1"/>
-      <c r="J54" s="1"/>
-      <c r="K54" s="1"/>
-      <c r="L54" s="1"/>
-      <c r="M54" s="1"/>
-      <c r="N54" s="1"/>
-      <c r="O54" s="1"/>
-      <c r="P54" s="1"/>
-      <c r="Q54" s="1"/>
-      <c r="R54" s="1"/>
-      <c r="S54" s="1"/>
-      <c r="T54" s="1"/>
-      <c r="U54" s="1"/>
-      <c r="V54" s="1"/>
-      <c r="W54" s="1"/>
-      <c r="X54" s="1"/>
-      <c r="Y54" s="1"/>
-      <c r="Z54" s="1"/>
-      <c r="AA54" s="1"/>
-      <c r="AB54" s="1"/>
-      <c r="AC54" s="1"/>
-      <c r="AD54" s="1"/>
-      <c r="AE54" s="1"/>
-      <c r="AF54" s="1"/>
-      <c r="AG54" s="1"/>
-      <c r="AH54" s="1"/>
-      <c r="AI54" s="1"/>
-      <c r="AJ54" s="1"/>
-      <c r="AK54" s="1"/>
-      <c r="AL54" s="1"/>
-      <c r="AM54" s="1"/>
-      <c r="AN54" s="1"/>
-      <c r="AO54" s="1"/>
-      <c r="AP54" s="1"/>
-      <c r="AQ54" s="1"/>
-      <c r="AR54" s="1"/>
-      <c r="AS54" s="1"/>
-      <c r="AT54" s="1"/>
-      <c r="AU54" s="1"/>
-      <c r="AV54" s="1"/>
-      <c r="AW54" s="1"/>
-      <c r="AX54" s="1"/>
-      <c r="AY54" s="1"/>
-      <c r="AZ54" s="1"/>
-      <c r="BA54" s="1"/>
-      <c r="BB54" s="1"/>
-      <c r="BC54" s="1"/>
-      <c r="BD54" s="1"/>
-      <c r="BE54" s="1"/>
-      <c r="BF54" s="1"/>
-      <c r="BG54" s="1"/>
-      <c r="BH54" s="1"/>
-      <c r="BI54" s="1"/>
-      <c r="BJ54" s="1"/>
-    </row>
-    <row r="55" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
@@ -10057,113 +9991,57 @@
       <c r="BI55" s="1"/>
       <c r="BJ55" s="1"/>
     </row>
-    <row r="57" spans="1:63" x14ac:dyDescent="0.3">
-      <c r="A57" s="1"/>
-      <c r="B57" s="1"/>
-      <c r="C57" s="1"/>
-      <c r="D57" s="1"/>
-      <c r="E57" s="1"/>
-      <c r="F57" s="1"/>
-      <c r="G57" s="1"/>
-      <c r="H57" s="1"/>
-      <c r="I57" s="1"/>
-      <c r="J57" s="1"/>
-      <c r="K57" s="1"/>
-      <c r="L57" s="1"/>
-      <c r="M57" s="1"/>
-      <c r="N57" s="1"/>
-      <c r="O57" s="1"/>
-      <c r="P57" s="1"/>
-      <c r="Q57" s="1"/>
-      <c r="R57" s="1"/>
-      <c r="S57" s="1"/>
-      <c r="T57" s="1"/>
-      <c r="U57" s="1"/>
-      <c r="V57" s="1"/>
-      <c r="W57" s="1"/>
-      <c r="X57" s="1"/>
-      <c r="Y57" s="1"/>
-      <c r="Z57" s="1"/>
-      <c r="AA57" s="1"/>
-      <c r="AB57" s="1"/>
-      <c r="AC57" s="1"/>
-      <c r="AD57" s="1"/>
-      <c r="AE57" s="1"/>
-      <c r="AF57" s="1"/>
-      <c r="AG57" s="1"/>
-      <c r="AH57" s="1"/>
-      <c r="AI57" s="1"/>
-      <c r="AJ57" s="1"/>
-      <c r="AK57" s="1"/>
-      <c r="AL57" s="1"/>
-      <c r="AM57" s="1"/>
-      <c r="AN57" s="1"/>
-      <c r="AO57" s="1"/>
-      <c r="AP57" s="1"/>
-      <c r="AQ57" s="1"/>
-      <c r="AR57" s="1"/>
-      <c r="AS57" s="1"/>
-      <c r="AT57" s="1"/>
-      <c r="AU57" s="1"/>
-      <c r="AV57" s="1"/>
-      <c r="AW57" s="1"/>
-      <c r="AX57" s="1"/>
-      <c r="AY57" s="1"/>
-      <c r="AZ57" s="1"/>
-      <c r="BA57" s="1"/>
-      <c r="BB57" s="1"/>
-      <c r="BC57" s="1"/>
-      <c r="BD57" s="1"/>
-      <c r="BE57" s="1"/>
-      <c r="BF57" s="1"/>
-      <c r="BG57" s="1"/>
-      <c r="BH57" s="1"/>
-      <c r="BI57" s="1"/>
-      <c r="BJ57" s="1"/>
-    </row>
-    <row r="58" spans="1:63" x14ac:dyDescent="0.3">
-      <c r="A58" s="29" t="s">
+    <row r="56" spans="1:62" x14ac:dyDescent="0.3">
+      <c r="A56" s="35" t="s">
         <v>45</v>
       </c>
-      <c r="B58" s="29"/>
-      <c r="C58" s="29"/>
-      <c r="D58" s="29"/>
-      <c r="E58" s="29"/>
-      <c r="F58" s="6"/>
-      <c r="G58" s="1"/>
-      <c r="H58" s="1"/>
-      <c r="I58" s="1"/>
-      <c r="J58" s="1"/>
-      <c r="K58" s="1"/>
-      <c r="L58" s="1"/>
-      <c r="M58" s="1"/>
-      <c r="N58" s="1"/>
-      <c r="O58" s="1"/>
-      <c r="P58" s="1"/>
-      <c r="Q58" s="1"/>
-      <c r="R58" s="1"/>
-      <c r="S58" s="1"/>
-      <c r="T58" s="1"/>
-      <c r="U58" s="1"/>
-      <c r="V58" s="1"/>
-      <c r="W58" s="1"/>
-      <c r="X58" s="1"/>
-      <c r="Y58" s="1"/>
-      <c r="Z58" s="1"/>
-      <c r="AA58" s="1"/>
-      <c r="AB58" s="1"/>
-      <c r="AC58" s="1"/>
-      <c r="AD58" s="1"/>
-      <c r="AE58" s="1"/>
-      <c r="AF58" s="1"/>
-      <c r="AG58" s="1"/>
-      <c r="AH58" s="1"/>
-      <c r="AI58" s="1"/>
-      <c r="AJ58" s="1"/>
-      <c r="AK58" s="1"/>
+      <c r="B56" s="35"/>
+      <c r="C56" s="35"/>
+      <c r="D56" s="35"/>
+      <c r="E56" s="35"/>
+      <c r="F56" s="6"/>
+      <c r="G56" s="1"/>
+      <c r="H56" s="1"/>
+      <c r="I56" s="1"/>
+      <c r="J56" s="1"/>
+      <c r="K56" s="1"/>
+      <c r="L56" s="1"/>
+      <c r="M56" s="1"/>
+      <c r="N56" s="1"/>
+      <c r="O56" s="1"/>
+      <c r="P56" s="1"/>
+      <c r="Q56" s="1"/>
+      <c r="R56" s="1"/>
+      <c r="S56" s="1"/>
+      <c r="T56" s="1"/>
+      <c r="U56" s="1"/>
+      <c r="V56" s="1"/>
+      <c r="W56" s="1"/>
+      <c r="X56" s="1"/>
+      <c r="Y56" s="1"/>
+      <c r="Z56" s="1"/>
+      <c r="AA56" s="1"/>
+      <c r="AB56" s="1"/>
+      <c r="AC56" s="1"/>
+      <c r="AD56" s="1"/>
+      <c r="AE56" s="1"/>
+      <c r="AF56" s="1"/>
+      <c r="AG56" s="1"/>
+      <c r="AH56" s="1"/>
+      <c r="AI56" s="1"/>
+      <c r="AJ56" s="1"/>
+      <c r="AK56" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A56:E56"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="AB8:AF8"/>
+    <mergeCell ref="AG8:AK8"/>
+    <mergeCell ref="W8:AA8"/>
+    <mergeCell ref="R8:V8"/>
+    <mergeCell ref="M8:Q8"/>
     <mergeCell ref="BF8:BJ8"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A5:C5"/>
@@ -10175,14 +10053,6 @@
     <mergeCell ref="AV8:AZ8"/>
     <mergeCell ref="AQ8:AU8"/>
     <mergeCell ref="AL8:AP8"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A58:E58"/>
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="AB8:AF8"/>
-    <mergeCell ref="AG8:AK8"/>
-    <mergeCell ref="W8:AA8"/>
-    <mergeCell ref="R8:V8"/>
-    <mergeCell ref="M8:Q8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
